--- a/gstdatabase/GSTR-1-2025-2026.xlsx
+++ b/gstdatabase/GSTR-1-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008B7BA3-8C26-435A-898C-BAA6377315A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03282E4-E06E-44BC-BEB1-DB9644B0CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="50">
   <si>
     <t>STATE WISE RETURN PERIOD WISE GSTR-1 FILING SUMMARY</t>
   </si>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -360,8 +360,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -372,14 +378,8 @@
     <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -667,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:BJ48"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
@@ -691,10 +691,12 @@
     <col min="43" max="43" width="24.21875" customWidth="1"/>
     <col min="44" max="47" width="18.77734375" customWidth="1"/>
     <col min="48" max="48" width="24.21875" customWidth="1"/>
-    <col min="49" max="52" width="18.77734375" customWidth="1"/>
+    <col min="49" max="51" width="18.77734375" customWidth="1"/>
+    <col min="52" max="56" width="18.5546875" customWidth="1"/>
+    <col min="57" max="62" width="18.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -702,7 +704,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -756,11 +758,11 @@
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
     </row>
-    <row r="3" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="18"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -812,7 +814,7 @@
       <c r="AY3" s="1"/>
       <c r="AZ3" s="1"/>
     </row>
-    <row r="4" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -866,7 +868,7 @@
       <c r="AY4" s="1"/>
       <c r="AZ4" s="1"/>
     </row>
-    <row r="5" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -922,7 +924,7 @@
       <c r="AY5" s="1"/>
       <c r="AZ5" s="1"/>
     </row>
-    <row r="6" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -964,87 +966,101 @@
       <c r="AY6" s="1"/>
       <c r="AZ6" s="1"/>
     </row>
-    <row r="8" spans="1:52" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="17">
         <v>45748</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="15">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="17">
         <v>45778</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="15">
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="17">
         <v>45809</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="15">
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="17">
         <v>45839</v>
       </c>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="15">
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="17">
         <v>45870</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="15">
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="17">
         <v>45901</v>
       </c>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="15">
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="19"/>
+      <c r="AG8" s="17">
         <v>45931</v>
       </c>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="15">
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="17">
         <v>45962</v>
       </c>
-      <c r="AM8" s="16"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="16"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="15">
+      <c r="AM8" s="18"/>
+      <c r="AN8" s="18"/>
+      <c r="AO8" s="18"/>
+      <c r="AP8" s="19"/>
+      <c r="AQ8" s="17">
         <v>45992</v>
       </c>
-      <c r="AR8" s="16"/>
-      <c r="AS8" s="16"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="17"/>
-      <c r="AV8" s="15">
+      <c r="AR8" s="18"/>
+      <c r="AS8" s="18"/>
+      <c r="AT8" s="18"/>
+      <c r="AU8" s="19"/>
+      <c r="AV8" s="17">
         <v>46023</v>
       </c>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="16"/>
-      <c r="AZ8" s="17"/>
+      <c r="AW8" s="18"/>
+      <c r="AX8" s="18"/>
+      <c r="AY8" s="18"/>
+      <c r="AZ8" s="19"/>
+      <c r="BA8" s="17">
+        <v>46054</v>
+      </c>
+      <c r="BB8" s="18"/>
+      <c r="BC8" s="18"/>
+      <c r="BD8" s="18"/>
+      <c r="BE8" s="19"/>
+      <c r="BF8" s="17">
+        <v>46082</v>
+      </c>
+      <c r="BG8" s="18"/>
+      <c r="BH8" s="18"/>
+      <c r="BI8" s="18"/>
+      <c r="BJ8" s="19"/>
     </row>
-    <row r="9" spans="1:52" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
+    <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1195,8 +1211,38 @@
       <c r="AZ9" s="12" t="s">
         <v>49</v>
       </c>
+      <c r="BA9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BD9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="BF9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BH9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BI9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BJ9" s="12" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -1211,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>47128</v>
+        <v>47220</v>
       </c>
       <c r="F10" s="5">
-        <v>74018</v>
+        <v>74110</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.99769507608944719</v>
+        <v>0.99893515211149897</v>
       </c>
       <c r="H10" s="5">
         <v>75899</v>
@@ -1228,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>45267</v>
+        <v>45378</v>
       </c>
       <c r="K10" s="5">
-        <v>74734</v>
+        <v>74845</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.98465065415881636</v>
+        <v>0.98611312402007933</v>
       </c>
       <c r="M10" s="5">
         <v>134494</v>
@@ -1245,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>87842</v>
+        <v>88109</v>
       </c>
       <c r="P10" s="5">
-        <v>134061</v>
+        <v>134328</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99678052552530227</v>
+        <v>0.99876574419676711</v>
       </c>
       <c r="R10" s="5">
         <v>73914</v>
@@ -1262,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42057</v>
+        <v>42258</v>
       </c>
       <c r="U10" s="5">
-        <v>73384</v>
+        <v>73585</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>0.99282950455935282</v>
+        <v>0.99554888113212647</v>
       </c>
       <c r="W10" s="5">
         <v>75592</v>
@@ -1279,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42192</v>
+        <v>42475</v>
       </c>
       <c r="Z10" s="5">
-        <v>74317</v>
+        <v>74600</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98313313578156414</v>
+        <v>0.98687691819240131</v>
       </c>
       <c r="AB10" s="5">
         <v>136558</v>
@@ -1296,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>88237</v>
+        <v>88990</v>
       </c>
       <c r="AE10" s="5">
-        <v>135359</v>
+        <v>136112</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99121984797668394</v>
+        <v>0.99673398848840788</v>
       </c>
       <c r="AG10" s="5">
         <v>73704</v>
@@ -1313,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41734</v>
+        <v>42289</v>
       </c>
       <c r="AJ10" s="5">
-        <v>72721</v>
+        <v>73276</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.9866628676869641</v>
+        <v>0.99419298816889179</v>
       </c>
       <c r="AL10" s="5">
         <v>75897</v>
@@ -1330,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>41833</v>
+        <v>42684</v>
       </c>
       <c r="AO10" s="5">
-        <v>74999</v>
+        <v>75850</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.98816817529019596</v>
+        <v>0.99938073968668062</v>
       </c>
       <c r="AQ10" s="5">
         <v>140117</v>
@@ -1347,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>87891</v>
+        <v>90952</v>
       </c>
       <c r="AT10" s="5">
-        <v>136914</v>
+        <v>139975</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>0.97714053255493627</v>
+        <v>0.99898656123097129</v>
       </c>
       <c r="AV10" s="5">
         <v>75508</v>
@@ -1364,17 +1410,51 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>9304</v>
+        <v>13072</v>
       </c>
       <c r="AY10" s="5">
-        <v>71700</v>
+        <v>75468</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.94956825766806163</v>
+        <v>0.99947025480743767</v>
+      </c>
+      <c r="BA10" s="5">
+        <v>78056</v>
+      </c>
+      <c r="BB10" s="5">
+        <v>34439</v>
+      </c>
+      <c r="BC10" s="3">
+        <f>BD10-BB10</f>
+        <v>42350</v>
+      </c>
+      <c r="BD10" s="5">
+        <v>76789</v>
+      </c>
+      <c r="BE10" s="4">
+        <f>BD10/BA10</f>
+        <v>0.98376806395408423</v>
+      </c>
+      <c r="BF10" s="5">
+        <v>144885</v>
+      </c>
+      <c r="BG10" s="5">
+        <v>49500</v>
+      </c>
+      <c r="BH10" s="3">
+        <f>BI10-BG10</f>
+        <v>90212</v>
+      </c>
+      <c r="BI10" s="5">
+        <v>139712</v>
+      </c>
+      <c r="BJ10" s="4">
+        <f>BI10/BF10</f>
+        <v>0.9642958208234117</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -1389,14 +1469,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>16217</v>
+        <v>16296</v>
       </c>
       <c r="F11" s="5">
-        <v>47381</v>
+        <v>47460</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99050904149681196</v>
+        <v>0.99216055189714647</v>
       </c>
       <c r="H11" s="5">
         <v>49123</v>
@@ -1406,14 +1486,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>16658</v>
+        <v>16759</v>
       </c>
       <c r="K11" s="5">
-        <v>48083</v>
+        <v>48184</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.97882865460171409</v>
+        <v>0.98088471795289378</v>
       </c>
       <c r="M11" s="5">
         <v>111861</v>
@@ -1423,14 +1503,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>47887</v>
+        <v>48163</v>
       </c>
       <c r="P11" s="5">
-        <v>111145</v>
+        <v>111421</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.9935991990059091</v>
+        <v>0.99606654687513974</v>
       </c>
       <c r="R11" s="5">
         <v>47958</v>
@@ -1440,14 +1520,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15720</v>
+        <v>15871</v>
       </c>
       <c r="U11" s="5">
-        <v>47355</v>
+        <v>47506</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.98742649818591266</v>
+        <v>0.99057508653405058</v>
       </c>
       <c r="W11" s="5">
         <v>49731</v>
@@ -1457,14 +1537,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>14967</v>
+        <v>15170</v>
       </c>
       <c r="Z11" s="5">
-        <v>47981</v>
+        <v>48184</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.96481068146628868</v>
+        <v>0.9688926424161991</v>
       </c>
       <c r="AB11" s="5">
         <v>113134</v>
@@ -1474,14 +1554,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>49702</v>
+        <v>50340</v>
       </c>
       <c r="AE11" s="5">
-        <v>111466</v>
+        <v>112104</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.98525642158855875</v>
+        <v>0.99089575194017709</v>
       </c>
       <c r="AG11" s="5">
         <v>48119</v>
@@ -1491,14 +1571,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>14915</v>
+        <v>15350</v>
       </c>
       <c r="AJ11" s="5">
-        <v>47123</v>
+        <v>47558</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.97930131548868427</v>
+        <v>0.98834140360356615</v>
       </c>
       <c r="AL11" s="5">
         <v>49938</v>
@@ -1508,14 +1588,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14092</v>
+        <v>14716</v>
       </c>
       <c r="AO11" s="5">
-        <v>48273</v>
+        <v>48897</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.96665865673435059</v>
+        <v>0.97915415114742277</v>
       </c>
       <c r="AQ11" s="5">
         <v>114343</v>
@@ -1525,14 +1605,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>44678</v>
+        <v>46933</v>
       </c>
       <c r="AT11" s="5">
-        <v>111372</v>
+        <v>113627</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.97401677409198639</v>
+        <v>0.99373813875794759</v>
       </c>
       <c r="AV11" s="5">
         <v>49251</v>
@@ -1542,17 +1622,51 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>4595</v>
+        <v>6592</v>
       </c>
       <c r="AY11" s="5">
-        <v>46358</v>
+        <v>48355</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.94126007593754446</v>
+        <v>0.98180747599033524</v>
+      </c>
+      <c r="BA11" s="5">
+        <v>50523</v>
+      </c>
+      <c r="BB11" s="5">
+        <v>34967</v>
+      </c>
+      <c r="BC11" s="3">
+        <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
+        <v>14142</v>
+      </c>
+      <c r="BD11" s="5">
+        <v>49109</v>
+      </c>
+      <c r="BE11" s="4">
+        <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
+        <v>0.97201274666983351</v>
+      </c>
+      <c r="BF11" s="5">
+        <v>116408</v>
+      </c>
+      <c r="BG11" s="5">
+        <v>66429</v>
+      </c>
+      <c r="BH11" s="3">
+        <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
+        <v>46004</v>
+      </c>
+      <c r="BI11" s="5">
+        <v>112433</v>
+      </c>
+      <c r="BJ11" s="4">
+        <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
+        <v>0.96585286234623047</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>3</v>
       </c>
@@ -1567,14 +1681,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>43882</v>
+        <v>44037</v>
       </c>
       <c r="F12" s="5">
-        <v>181435</v>
+        <v>181590</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99281524284807499</v>
+        <v>0.99366340534506536</v>
       </c>
       <c r="H12" s="5">
         <v>186824</v>
@@ -1584,14 +1698,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>41003</v>
+        <v>41194</v>
       </c>
       <c r="K12" s="5">
-        <v>184153</v>
+        <v>184344</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98570312165460539</v>
+        <v>0.98672547424313795</v>
       </c>
       <c r="M12" s="5">
         <v>372375</v>
@@ -1601,14 +1715,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>106518</v>
+        <v>107038</v>
       </c>
       <c r="P12" s="5">
-        <v>370690</v>
+        <v>371210</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99547499160792208</v>
+        <v>0.99687143336690165</v>
       </c>
       <c r="R12" s="5">
         <v>184659</v>
@@ -1618,14 +1732,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40189</v>
+        <v>40527</v>
       </c>
       <c r="U12" s="5">
-        <v>182928</v>
+        <v>183266</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.9906259646158595</v>
+        <v>0.99245636551697991</v>
       </c>
       <c r="W12" s="5">
         <v>189081</v>
@@ -1635,14 +1749,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>40179</v>
+        <v>40687</v>
       </c>
       <c r="Z12" s="5">
-        <v>184984</v>
+        <v>185492</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.97833203759235465</v>
+        <v>0.98101871684621933</v>
       </c>
       <c r="AB12" s="5">
         <v>377441</v>
@@ -1652,14 +1766,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>111586</v>
+        <v>113427</v>
       </c>
       <c r="AE12" s="5">
-        <v>372678</v>
+        <v>374519</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.98738080918607152</v>
+        <v>0.99225839270243565</v>
       </c>
       <c r="AG12" s="5">
         <v>186148</v>
@@ -1669,14 +1783,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>40535</v>
+        <v>41786</v>
       </c>
       <c r="AJ12" s="5">
-        <v>183243</v>
+        <v>184494</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.98439413799772224</v>
+        <v>0.99111459698734339</v>
       </c>
       <c r="AL12" s="5">
         <v>192239</v>
@@ -1686,14 +1800,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>39154</v>
+        <v>41016</v>
       </c>
       <c r="AO12" s="5">
-        <v>188799</v>
+        <v>190661</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98210560812322156</v>
+        <v>0.9917914679123383</v>
       </c>
       <c r="AQ12" s="5">
         <v>384779</v>
@@ -1703,14 +1817,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>104109</v>
+        <v>111304</v>
       </c>
       <c r="AT12" s="5">
-        <v>375498</v>
+        <v>382693</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.97587966079229893</v>
+        <v>0.99457870621837474</v>
       </c>
       <c r="AV12" s="5">
         <v>191743</v>
@@ -1720,17 +1834,51 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>17935</v>
+        <v>24455</v>
       </c>
       <c r="AY12" s="5">
-        <v>183440</v>
+        <v>189960</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.95669724579254523</v>
+        <v>0.99070109469446077</v>
+      </c>
+      <c r="BA12" s="5">
+        <v>197493</v>
+      </c>
+      <c r="BB12" s="5">
+        <v>153659</v>
+      </c>
+      <c r="BC12" s="3">
+        <f t="shared" si="20"/>
+        <v>39349</v>
+      </c>
+      <c r="BD12" s="5">
+        <v>193008</v>
+      </c>
+      <c r="BE12" s="4">
+        <f t="shared" si="21"/>
+        <v>0.97729033434096402</v>
+      </c>
+      <c r="BF12" s="5">
+        <v>393305</v>
+      </c>
+      <c r="BG12" s="5">
+        <v>276589</v>
+      </c>
+      <c r="BH12" s="3">
+        <f t="shared" si="22"/>
+        <v>104708</v>
+      </c>
+      <c r="BI12" s="5">
+        <v>381297</v>
+      </c>
+      <c r="BJ12" s="4">
+        <f t="shared" si="23"/>
+        <v>0.96946898717280483</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -1745,14 +1893,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3897</v>
+        <v>3912</v>
       </c>
       <c r="F13" s="5">
-        <v>17971</v>
+        <v>17986</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>0.99645134460770723</v>
+        <v>0.99728306071527584</v>
       </c>
       <c r="H13" s="5">
         <v>18257</v>
@@ -1762,14 +1910,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3751</v>
+        <v>3768</v>
       </c>
       <c r="K13" s="5">
-        <v>18053</v>
+        <v>18070</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.98882620364791585</v>
+        <v>0.9897573533439229</v>
       </c>
       <c r="M13" s="5">
         <v>29011</v>
@@ -1779,14 +1927,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>7128</v>
+        <v>7180</v>
       </c>
       <c r="P13" s="5">
-        <v>28979</v>
+        <v>29031</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>0.99889697011478407</v>
+        <v>1.0006893936782599</v>
       </c>
       <c r="R13" s="5">
         <v>18140</v>
@@ -1796,14 +1944,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3692</v>
+        <v>3731</v>
       </c>
       <c r="U13" s="5">
-        <v>18082</v>
+        <v>18121</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99680264608599778</v>
+        <v>0.99895259095920619</v>
       </c>
       <c r="W13" s="5">
         <v>18401</v>
@@ -1813,14 +1961,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>3419</v>
+        <v>3480</v>
       </c>
       <c r="Z13" s="5">
-        <v>18167</v>
+        <v>18228</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.98728329982066187</v>
+        <v>0.99059833704689959</v>
       </c>
       <c r="AB13" s="5">
         <v>29242</v>
@@ -1830,14 +1978,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7347</v>
+        <v>7522</v>
       </c>
       <c r="AE13" s="5">
-        <v>29069</v>
+        <v>29244</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>0.99408385199370763</v>
+        <v>1.0000683947746392</v>
       </c>
       <c r="AG13" s="5">
         <v>18261</v>
@@ -1847,14 +1995,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3622</v>
+        <v>3770</v>
       </c>
       <c r="AJ13" s="5">
-        <v>18216</v>
+        <v>18364</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>0.99753573188762934</v>
+        <v>1.0056404359016484</v>
       </c>
       <c r="AL13" s="5">
         <v>18637</v>
@@ -1864,14 +2012,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3410</v>
+        <v>3620</v>
       </c>
       <c r="AO13" s="5">
-        <v>18473</v>
+        <v>18683</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>0.9912003004775447</v>
+        <v>1.0024682084026399</v>
       </c>
       <c r="AQ13" s="5">
         <v>29668</v>
@@ -1881,14 +2029,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>6742</v>
+        <v>7343</v>
       </c>
       <c r="AT13" s="5">
-        <v>29133</v>
+        <v>29734</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>0.98196710260213027</v>
+        <v>1.0022246191182418</v>
       </c>
       <c r="AV13" s="5">
         <v>18676</v>
@@ -1898,17 +2046,51 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>1660</v>
+        <v>2394</v>
       </c>
       <c r="AY13" s="5">
-        <v>18031</v>
+        <v>18765</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>0.96546369672306709</v>
+        <v>1.0047654744056542</v>
+      </c>
+      <c r="BA13" s="5">
+        <v>19025</v>
+      </c>
+      <c r="BB13" s="5">
+        <v>15515</v>
+      </c>
+      <c r="BC13" s="3">
+        <f t="shared" si="20"/>
+        <v>3464</v>
+      </c>
+      <c r="BD13" s="5">
+        <v>18979</v>
+      </c>
+      <c r="BE13" s="4">
+        <f t="shared" si="21"/>
+        <v>0.99758212877792374</v>
+      </c>
+      <c r="BF13" s="5">
+        <v>30254</v>
+      </c>
+      <c r="BG13" s="5">
+        <v>22876</v>
+      </c>
+      <c r="BH13" s="3">
+        <f t="shared" si="22"/>
+        <v>6699</v>
+      </c>
+      <c r="BI13" s="5">
+        <v>29575</v>
+      </c>
+      <c r="BJ13" s="4">
+        <f t="shared" si="23"/>
+        <v>0.97755668671911156</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>5</v>
       </c>
@@ -1923,14 +2105,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>42104</v>
+        <v>42227</v>
       </c>
       <c r="F14" s="5">
-        <v>95008</v>
+        <v>95131</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>1.004174901969074</v>
+        <v>1.0054749347341274</v>
       </c>
       <c r="H14" s="5">
         <v>97351</v>
@@ -1940,14 +2122,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>43338</v>
+        <v>43488</v>
       </c>
       <c r="K14" s="5">
-        <v>96958</v>
+        <v>97108</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.99596306149911151</v>
+        <v>0.99750387772082461</v>
       </c>
       <c r="M14" s="5">
         <v>172809</v>
@@ -1957,14 +2139,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>87668</v>
+        <v>88080</v>
       </c>
       <c r="P14" s="5">
-        <v>172453</v>
+        <v>172865</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99793992211053817</v>
+        <v>1.0003240571960952</v>
       </c>
       <c r="R14" s="5">
         <v>97326</v>
@@ -1974,14 +2156,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>41541</v>
+        <v>41819</v>
       </c>
       <c r="U14" s="5">
-        <v>96065</v>
+        <v>96343</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98704354437663111</v>
+        <v>0.98989992396687421</v>
       </c>
       <c r="W14" s="5">
         <v>98912</v>
@@ -1991,14 +2173,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>40846</v>
+        <v>41254</v>
       </c>
       <c r="Z14" s="5">
-        <v>97222</v>
+        <v>97630</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.98291410546748625</v>
+        <v>0.98703898414752511</v>
       </c>
       <c r="AB14" s="5">
         <v>175426</v>
@@ -2008,14 +2190,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>90084</v>
+        <v>91333</v>
       </c>
       <c r="AE14" s="5">
-        <v>174101</v>
+        <v>175350</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99244695769156221</v>
+        <v>0.99956676889400664</v>
       </c>
       <c r="AG14" s="5">
         <v>98057</v>
@@ -2025,14 +2207,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>41585</v>
+        <v>42473</v>
       </c>
       <c r="AJ14" s="5">
-        <v>96930</v>
+        <v>97818</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.98850668488736149</v>
+        <v>0.99756264213671642</v>
       </c>
       <c r="AL14" s="5">
         <v>101581</v>
@@ -2042,14 +2224,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>42116</v>
+        <v>43473</v>
       </c>
       <c r="AO14" s="5">
-        <v>100822</v>
+        <v>102179</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.99252813026058018</v>
+        <v>1.0058869276734823</v>
       </c>
       <c r="AQ14" s="5">
         <v>182247</v>
@@ -2059,14 +2241,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>87489</v>
+        <v>92092</v>
       </c>
       <c r="AT14" s="5">
-        <v>177258</v>
+        <v>181861</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.97262506378705826</v>
+        <v>0.99788199531405186</v>
       </c>
       <c r="AV14" s="5">
         <v>102257</v>
@@ -2076,17 +2258,51 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>11821</v>
+        <v>16843</v>
       </c>
       <c r="AY14" s="5">
-        <v>97329</v>
+        <v>102351</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.95180770020634287</v>
+        <v>1.0009192524717134</v>
+      </c>
+      <c r="BA14" s="5">
+        <v>106311</v>
+      </c>
+      <c r="BB14" s="5">
+        <v>60736</v>
+      </c>
+      <c r="BC14" s="3">
+        <f t="shared" si="20"/>
+        <v>43836</v>
+      </c>
+      <c r="BD14" s="5">
+        <v>104572</v>
+      </c>
+      <c r="BE14" s="4">
+        <f t="shared" si="21"/>
+        <v>0.9836423324021033</v>
+      </c>
+      <c r="BF14" s="5">
+        <v>189210</v>
+      </c>
+      <c r="BG14" s="5">
+        <v>92851</v>
+      </c>
+      <c r="BH14" s="3">
+        <f t="shared" si="22"/>
+        <v>89875</v>
+      </c>
+      <c r="BI14" s="5">
+        <v>182726</v>
+      </c>
+      <c r="BJ14" s="4">
+        <f t="shared" si="23"/>
+        <v>0.96573119813963326</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>6</v>
       </c>
@@ -2101,14 +2317,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>85649</v>
+        <v>85840</v>
       </c>
       <c r="F15" s="5">
-        <v>323431</v>
+        <v>323622</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.99579736203647828</v>
+        <v>0.99638542346580627</v>
       </c>
       <c r="H15" s="5">
         <v>331968</v>
@@ -2118,14 +2334,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>84939</v>
+        <v>85197</v>
       </c>
       <c r="K15" s="5">
-        <v>329001</v>
+        <v>329259</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.99106239155581266</v>
+        <v>0.99183957489878538</v>
       </c>
       <c r="M15" s="5">
         <v>549212</v>
@@ -2135,14 +2351,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>164836</v>
+        <v>165435</v>
       </c>
       <c r="P15" s="5">
-        <v>547756</v>
+        <v>548355</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99734892901101946</v>
+        <v>0.99843958252915088</v>
       </c>
       <c r="R15" s="5">
         <v>333160</v>
@@ -2152,14 +2368,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>83873</v>
+        <v>84415</v>
       </c>
       <c r="U15" s="5">
-        <v>331101</v>
+        <v>331643</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99381978628887024</v>
+        <v>0.99544663224876939</v>
       </c>
       <c r="W15" s="5">
         <v>340519</v>
@@ -2169,14 +2385,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>81321</v>
+        <v>82266</v>
       </c>
       <c r="Z15" s="5">
-        <v>335627</v>
+        <v>336572</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98563369444876792</v>
+        <v>0.98840886998963351</v>
       </c>
       <c r="AB15" s="5">
         <v>562036</v>
@@ -2186,14 +2402,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>173261</v>
+        <v>175948</v>
       </c>
       <c r="AE15" s="5">
-        <v>556507</v>
+        <v>559194</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99016255186500512</v>
+        <v>0.99494338440953956</v>
       </c>
       <c r="AG15" s="5">
         <v>340264</v>
@@ -2203,14 +2419,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>84825</v>
+        <v>87536</v>
       </c>
       <c r="AJ15" s="5">
-        <v>335719</v>
+        <v>338430</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.98664272447276236</v>
+        <v>0.99461006747701786</v>
       </c>
       <c r="AL15" s="5">
         <v>350627</v>
@@ -2220,14 +2436,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>84076</v>
+        <v>88146</v>
       </c>
       <c r="AO15" s="5">
-        <v>347460</v>
+        <v>351530</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.99096760945392115</v>
+        <v>1.0025753863792577</v>
       </c>
       <c r="AQ15" s="5">
         <v>580651</v>
@@ -2237,14 +2453,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>163537</v>
+        <v>175240</v>
       </c>
       <c r="AT15" s="5">
-        <v>568726</v>
+        <v>580429</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.97946270651389566</v>
+        <v>0.99961767051120209</v>
       </c>
       <c r="AV15" s="5">
         <v>355536</v>
@@ -2254,17 +2470,51 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>34565</v>
+        <v>49396</v>
       </c>
       <c r="AY15" s="5">
-        <v>339585</v>
+        <v>354416</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.9551353449439719</v>
+        <v>0.99684982674047073</v>
+      </c>
+      <c r="BA15" s="5">
+        <v>365201</v>
+      </c>
+      <c r="BB15" s="5">
+        <v>274336</v>
+      </c>
+      <c r="BC15" s="3">
+        <f t="shared" si="20"/>
+        <v>86314</v>
+      </c>
+      <c r="BD15" s="5">
+        <v>360650</v>
+      </c>
+      <c r="BE15" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98753836928157368</v>
+      </c>
+      <c r="BF15" s="5">
+        <v>600313</v>
+      </c>
+      <c r="BG15" s="5">
+        <v>417598</v>
+      </c>
+      <c r="BH15" s="3">
+        <f t="shared" si="22"/>
+        <v>167231</v>
+      </c>
+      <c r="BI15" s="5">
+        <v>584829</v>
+      </c>
+      <c r="BJ15" s="4">
+        <f t="shared" si="23"/>
+        <v>0.97420678879184697</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>7</v>
       </c>
@@ -2279,14 +2529,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>118942</v>
+        <v>119425</v>
       </c>
       <c r="F16" s="5">
-        <v>450248</v>
+        <v>450731</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99278970184204374</v>
+        <v>0.99385470918464092</v>
       </c>
       <c r="H16" s="5">
         <v>461360</v>
@@ -2296,14 +2546,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>119109</v>
+        <v>119733</v>
       </c>
       <c r="K16" s="5">
-        <v>457729</v>
+        <v>458353</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.99212979018553837</v>
+        <v>0.99348231316108893</v>
       </c>
       <c r="M16" s="5">
         <v>788355</v>
@@ -2313,14 +2563,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>215733</v>
+        <v>217060</v>
       </c>
       <c r="P16" s="5">
-        <v>787716</v>
+        <v>789043</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99918945145270843</v>
+        <v>1.0008727032872247</v>
       </c>
       <c r="R16" s="5">
         <v>462019</v>
@@ -2330,14 +2580,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>118798</v>
+        <v>119844</v>
       </c>
       <c r="U16" s="5">
-        <v>460329</v>
+        <v>461375</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99634214177339031</v>
+        <v>0.99860611793021503</v>
       </c>
       <c r="W16" s="5">
         <v>472236</v>
@@ -2347,14 +2597,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>114125</v>
+        <v>115677</v>
       </c>
       <c r="Z16" s="5">
-        <v>465206</v>
+        <v>466758</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98511337551563205</v>
+        <v>0.98839986786267886</v>
       </c>
       <c r="AB16" s="5">
         <v>804216</v>
@@ -2364,14 +2614,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>227758</v>
+        <v>231914</v>
       </c>
       <c r="AE16" s="5">
-        <v>796920</v>
+        <v>801076</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99092781043898659</v>
+        <v>0.99609557631283141</v>
       </c>
       <c r="AG16" s="5">
         <v>471201</v>
@@ -2381,14 +2631,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>117877</v>
+        <v>121630</v>
       </c>
       <c r="AJ16" s="5">
-        <v>464769</v>
+        <v>468522</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98634977430013948</v>
+        <v>0.99431452819497412</v>
       </c>
       <c r="AL16" s="5">
         <v>484445</v>
@@ -2398,14 +2648,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>120902</v>
+        <v>126713</v>
       </c>
       <c r="AO16" s="5">
-        <v>482417</v>
+        <v>488228</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.99581376626861662</v>
+        <v>1.0078089359989266</v>
       </c>
       <c r="AQ16" s="5">
         <v>831010</v>
@@ -2415,14 +2665,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>217550</v>
+        <v>234429</v>
       </c>
       <c r="AT16" s="5">
-        <v>814546</v>
+        <v>831425</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.98018796404375397</v>
+        <v>1.0004993923057484</v>
       </c>
       <c r="AV16" s="5">
         <v>496237</v>
@@ -2432,17 +2682,51 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>49988</v>
+        <v>70944</v>
       </c>
       <c r="AY16" s="5">
-        <v>472856</v>
+        <v>493812</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.95288340047195186</v>
+        <v>0.99511322210959685</v>
+      </c>
+      <c r="BA16" s="5">
+        <v>510690</v>
+      </c>
+      <c r="BB16" s="5">
+        <v>379588</v>
+      </c>
+      <c r="BC16" s="3">
+        <f t="shared" si="20"/>
+        <v>122088</v>
+      </c>
+      <c r="BD16" s="5">
+        <v>501676</v>
+      </c>
+      <c r="BE16" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98234937045957427</v>
+      </c>
+      <c r="BF16" s="5">
+        <v>859721</v>
+      </c>
+      <c r="BG16" s="5">
+        <v>616936</v>
+      </c>
+      <c r="BH16" s="3">
+        <f t="shared" si="22"/>
+        <v>219994</v>
+      </c>
+      <c r="BI16" s="5">
+        <v>836930</v>
+      </c>
+      <c r="BJ16" s="4">
+        <f t="shared" si="23"/>
+        <v>0.97349023694896364</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>8</v>
       </c>
@@ -2457,14 +2741,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>106020</v>
+        <v>106370</v>
       </c>
       <c r="F17" s="5">
-        <v>339105</v>
+        <v>339455</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99078475657323839</v>
+        <v>0.99180737394779972</v>
       </c>
       <c r="H17" s="5">
         <v>352243</v>
@@ -2474,14 +2758,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>104644</v>
+        <v>105083</v>
       </c>
       <c r="K17" s="5">
-        <v>347030</v>
+        <v>347469</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98520055756963232</v>
+        <v>0.98644685628955009</v>
       </c>
       <c r="M17" s="5">
         <v>765449</v>
@@ -2491,14 +2775,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>300944</v>
+        <v>302483</v>
       </c>
       <c r="P17" s="5">
-        <v>763894</v>
+        <v>765433</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99796851259848796</v>
+        <v>0.99997909723574008</v>
       </c>
       <c r="R17" s="5">
         <v>346814</v>
@@ -2508,14 +2792,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>102989</v>
+        <v>103735</v>
       </c>
       <c r="U17" s="5">
-        <v>346037</v>
+        <v>346783</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99775960601359803</v>
+        <v>0.99991061491173938</v>
       </c>
       <c r="W17" s="5">
         <v>360071</v>
@@ -2525,14 +2809,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>104104</v>
+        <v>105241</v>
       </c>
       <c r="Z17" s="5">
-        <v>354356</v>
+        <v>355493</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.9841281302854159</v>
+        <v>0.98728584084805493</v>
       </c>
       <c r="AB17" s="5">
         <v>784641</v>
@@ -2542,14 +2826,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>312150</v>
+        <v>316881</v>
       </c>
       <c r="AE17" s="5">
-        <v>778751</v>
+        <v>783482</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99249338232389084</v>
+        <v>0.99852289136050754</v>
       </c>
       <c r="AG17" s="5">
         <v>355351</v>
@@ -2559,14 +2843,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>107118</v>
+        <v>109756</v>
       </c>
       <c r="AJ17" s="5">
-        <v>352270</v>
+        <v>354908</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99132969936766746</v>
+        <v>0.99875334528395865</v>
       </c>
       <c r="AL17" s="5">
         <v>371770</v>
@@ -2576,14 +2860,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>107270</v>
+        <v>111184</v>
       </c>
       <c r="AO17" s="5">
-        <v>367059</v>
+        <v>370973</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.98732818678215029</v>
+        <v>0.99785620141485332</v>
       </c>
       <c r="AQ17" s="5">
         <v>810773</v>
@@ -2593,14 +2877,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>296014</v>
+        <v>313140</v>
       </c>
       <c r="AT17" s="5">
-        <v>792739</v>
+        <v>809865</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.97775702940280451</v>
+        <v>0.99888008110778237</v>
       </c>
       <c r="AV17" s="5">
         <v>369648</v>
@@ -2610,17 +2894,51 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>37280</v>
+        <v>51611</v>
       </c>
       <c r="AY17" s="5">
-        <v>354711</v>
+        <v>369042</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.95959128684586414</v>
+        <v>0.99836060251915337</v>
+      </c>
+      <c r="BA17" s="5">
+        <v>385393</v>
+      </c>
+      <c r="BB17" s="5">
+        <v>268511</v>
+      </c>
+      <c r="BC17" s="3">
+        <f t="shared" si="20"/>
+        <v>111301</v>
+      </c>
+      <c r="BD17" s="5">
+        <v>379812</v>
+      </c>
+      <c r="BE17" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98551867833614004</v>
+      </c>
+      <c r="BF17" s="5">
+        <v>839843</v>
+      </c>
+      <c r="BG17" s="5">
+        <v>503654</v>
+      </c>
+      <c r="BH17" s="3">
+        <f t="shared" si="22"/>
+        <v>310712</v>
+      </c>
+      <c r="BI17" s="5">
+        <v>814366</v>
+      </c>
+      <c r="BJ17" s="4">
+        <f t="shared" si="23"/>
+        <v>0.96966456825859115</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>9</v>
       </c>
@@ -2635,14 +2953,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>540957</v>
+        <v>542100</v>
       </c>
       <c r="F18" s="5">
-        <v>1061409</v>
+        <v>1062552</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99117808556892806</v>
+        <v>0.99224545597167124</v>
       </c>
       <c r="H18" s="5">
         <v>1089051</v>
@@ -2652,14 +2970,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>553725</v>
+        <v>555187</v>
       </c>
       <c r="K18" s="5">
-        <v>1077666</v>
+        <v>1079128</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98954594412933827</v>
+        <v>0.99088839732941802</v>
       </c>
       <c r="M18" s="5">
         <v>1637429</v>
@@ -2669,14 +2987,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>871778</v>
+        <v>874821</v>
       </c>
       <c r="P18" s="5">
-        <v>1624566</v>
+        <v>1627609</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.9921443922148685</v>
+        <v>0.99400279340356135</v>
       </c>
       <c r="R18" s="5">
         <v>1090030</v>
@@ -2686,14 +3004,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>542006</v>
+        <v>544687</v>
       </c>
       <c r="U18" s="5">
-        <v>1075067</v>
+        <v>1077748</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98627285487555394</v>
+        <v>0.98873242020861807</v>
       </c>
       <c r="W18" s="5">
         <v>1107435</v>
@@ -2703,14 +3021,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>533843</v>
+        <v>538004</v>
       </c>
       <c r="Z18" s="5">
-        <v>1084849</v>
+        <v>1089010</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.97960512355126939</v>
+        <v>0.98336245468131311</v>
       </c>
       <c r="AB18" s="5">
         <v>1665905</v>
@@ -2720,14 +3038,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>893003</v>
+        <v>903254</v>
       </c>
       <c r="AE18" s="5">
-        <v>1639801</v>
+        <v>1650052</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.98433043901062789</v>
+        <v>0.99048385111996184</v>
       </c>
       <c r="AG18" s="5">
         <v>1104366</v>
@@ -2737,14 +3055,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>543970</v>
+        <v>553683</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1082777</v>
+        <v>1092490</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.98045122721996147</v>
+        <v>0.98924631870231428</v>
       </c>
       <c r="AL18" s="5">
         <v>1131950</v>
@@ -2754,14 +3072,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>548383</v>
+        <v>562586</v>
       </c>
       <c r="AO18" s="5">
-        <v>1116388</v>
+        <v>1130591</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98625204293475865</v>
+        <v>0.99879941693537699</v>
       </c>
       <c r="AQ18" s="5">
         <v>1717059</v>
@@ -2771,14 +3089,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>879031</v>
+        <v>916093</v>
       </c>
       <c r="AT18" s="5">
-        <v>1670989</v>
+        <v>1708051</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.97316923879726902</v>
+        <v>0.99475382034047755</v>
       </c>
       <c r="AV18" s="5">
         <v>1151692</v>
@@ -2788,17 +3106,51 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>125091</v>
+        <v>177139</v>
       </c>
       <c r="AY18" s="5">
-        <v>1090608</v>
+        <v>1142656</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.94696151401590012</v>
+        <v>0.99215415232544812</v>
+      </c>
+      <c r="BA18" s="5">
+        <v>1182353</v>
+      </c>
+      <c r="BB18" s="5">
+        <v>588563</v>
+      </c>
+      <c r="BC18" s="3">
+        <f t="shared" si="20"/>
+        <v>571996</v>
+      </c>
+      <c r="BD18" s="5">
+        <v>1160559</v>
+      </c>
+      <c r="BE18" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98156726459864352</v>
+      </c>
+      <c r="BF18" s="5">
+        <v>1777125</v>
+      </c>
+      <c r="BG18" s="5">
+        <v>817005</v>
+      </c>
+      <c r="BH18" s="3">
+        <f t="shared" si="22"/>
+        <v>898508</v>
+      </c>
+      <c r="BI18" s="5">
+        <v>1715513</v>
+      </c>
+      <c r="BJ18" s="4">
+        <f t="shared" si="23"/>
+        <v>0.9653305198002391</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>10</v>
       </c>
@@ -2813,14 +3165,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>177604</v>
+        <v>178268</v>
       </c>
       <c r="F19" s="5">
-        <v>298598</v>
+        <v>299262</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97702695185835964</v>
+        <v>0.97919959164842496</v>
       </c>
       <c r="H19" s="5">
         <v>314567</v>
@@ -2830,14 +3182,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>182818</v>
+        <v>183678</v>
       </c>
       <c r="K19" s="5">
-        <v>305326</v>
+        <v>306186</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97062311049792249</v>
+        <v>0.97335702727876727</v>
       </c>
       <c r="M19" s="5">
         <v>534704</v>
@@ -2847,14 +3199,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>331241</v>
+        <v>333123</v>
       </c>
       <c r="P19" s="5">
-        <v>525406</v>
+        <v>527288</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98261093988449688</v>
+        <v>0.9861306442442922</v>
       </c>
       <c r="R19" s="5">
         <v>310887</v>
@@ -2864,14 +3216,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>177734</v>
+        <v>179210</v>
       </c>
       <c r="U19" s="5">
-        <v>303603</v>
+        <v>305079</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97657026508023814</v>
+        <v>0.98131797083827887</v>
       </c>
       <c r="W19" s="5">
         <v>321022</v>
@@ -2881,14 +3233,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>176913</v>
+        <v>179100</v>
       </c>
       <c r="Z19" s="5">
-        <v>307968</v>
+        <v>310155</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.95933612026590076</v>
+        <v>0.96614873746970609</v>
       </c>
       <c r="AB19" s="5">
         <v>548160</v>
@@ -2898,14 +3250,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>344464</v>
+        <v>350365</v>
       </c>
       <c r="AE19" s="5">
-        <v>530854</v>
+        <v>536755</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.96842892586106244</v>
+        <v>0.97919403093987156</v>
       </c>
       <c r="AG19" s="5">
         <v>315587</v>
@@ -2915,14 +3267,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>183830</v>
+        <v>188373</v>
       </c>
       <c r="AJ19" s="5">
-        <v>303905</v>
+        <v>308448</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.96298326610411711</v>
+        <v>0.97737866261918271</v>
       </c>
       <c r="AL19" s="5">
         <v>327315</v>
@@ -2932,14 +3284,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>181391</v>
+        <v>187772</v>
       </c>
       <c r="AO19" s="5">
-        <v>314485</v>
+        <v>320866</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.96080228526037614</v>
+        <v>0.98029726715854759</v>
       </c>
       <c r="AQ19" s="5">
         <v>564697</v>
@@ -2949,14 +3301,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>336146</v>
+        <v>354206</v>
       </c>
       <c r="AT19" s="5">
-        <v>538481</v>
+        <v>556541</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.95357510310839266</v>
+        <v>0.98555685615471655</v>
       </c>
       <c r="AV19" s="5">
         <v>330794</v>
@@ -2966,17 +3318,51 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>35897</v>
+        <v>56977</v>
       </c>
       <c r="AY19" s="5">
-        <v>304022</v>
+        <v>325102</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.91906745587888539</v>
+        <v>0.98279291643742028</v>
+      </c>
+      <c r="BA19" s="5">
+        <v>346688</v>
+      </c>
+      <c r="BB19" s="5">
+        <v>138959</v>
+      </c>
+      <c r="BC19" s="3">
+        <f t="shared" si="20"/>
+        <v>194070</v>
+      </c>
+      <c r="BD19" s="5">
+        <v>333029</v>
+      </c>
+      <c r="BE19" s="4">
+        <f t="shared" si="21"/>
+        <v>0.96060146298689308</v>
+      </c>
+      <c r="BF19" s="5">
+        <v>595475</v>
+      </c>
+      <c r="BG19" s="5">
+        <v>199570</v>
+      </c>
+      <c r="BH19" s="3">
+        <f t="shared" si="22"/>
+        <v>355384</v>
+      </c>
+      <c r="BI19" s="5">
+        <v>554954</v>
+      </c>
+      <c r="BJ19" s="4">
+        <f t="shared" si="23"/>
+        <v>0.93195180318233339</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>11</v>
       </c>
@@ -2991,14 +3377,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3844</v>
+        <v>3885</v>
       </c>
       <c r="F20" s="5">
-        <v>6431</v>
+        <v>6472</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.98378461067768086</v>
+        <v>0.99005660088725711</v>
       </c>
       <c r="H20" s="5">
         <v>6601</v>
@@ -3008,14 +3394,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3788</v>
+        <v>3834</v>
       </c>
       <c r="K20" s="5">
-        <v>6458</v>
+        <v>6504</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.97833661566429331</v>
+        <v>0.98530525677927583</v>
       </c>
       <c r="M20" s="5">
         <v>10050</v>
@@ -3025,14 +3411,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5483</v>
+        <v>5555</v>
       </c>
       <c r="P20" s="5">
-        <v>9951</v>
+        <v>10023</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99014925373134333</v>
+        <v>0.99731343283582086</v>
       </c>
       <c r="R20" s="5">
         <v>6485</v>
@@ -3042,14 +3428,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3551</v>
+        <v>3617</v>
       </c>
       <c r="U20" s="5">
-        <v>6355</v>
+        <v>6421</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.97995373939861219</v>
+        <v>0.99013107170393211</v>
       </c>
       <c r="W20" s="5">
         <v>6573</v>
@@ -3059,14 +3445,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3335</v>
+        <v>3425</v>
       </c>
       <c r="Z20" s="5">
-        <v>6343</v>
+        <v>6433</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.9650083675642781</v>
+        <v>0.9787007454739084</v>
       </c>
       <c r="AB20" s="5">
         <v>10123</v>
@@ -3076,14 +3462,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5941</v>
+        <v>6127</v>
       </c>
       <c r="AE20" s="5">
-        <v>9837</v>
+        <v>10023</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.97174750568013435</v>
+        <v>0.9901215054825645</v>
       </c>
       <c r="AG20" s="5">
         <v>6547</v>
@@ -3093,14 +3479,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3234</v>
+        <v>3418</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6252</v>
+        <v>6436</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.95494119444020165</v>
+        <v>0.98304566977241481</v>
       </c>
       <c r="AL20" s="5">
         <v>6649</v>
@@ -3110,14 +3496,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3157</v>
+        <v>3422</v>
       </c>
       <c r="AO20" s="5">
-        <v>6248</v>
+        <v>6513</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.93969017897428186</v>
+        <v>0.97954579636035499</v>
       </c>
       <c r="AQ20" s="5">
         <v>10228</v>
@@ -3127,14 +3513,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5289</v>
+        <v>6040</v>
       </c>
       <c r="AT20" s="5">
-        <v>9285</v>
+        <v>10036</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>0.90780211184982407</v>
+        <v>0.98122800156433321</v>
       </c>
       <c r="AV20" s="5">
         <v>6568</v>
@@ -3144,17 +3530,51 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>635</v>
+        <v>1314</v>
       </c>
       <c r="AY20" s="5">
-        <v>5719</v>
+        <v>6398</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.87073690621193667</v>
+        <v>0.97411693057247262</v>
+      </c>
+      <c r="BA20" s="5">
+        <v>6793</v>
+      </c>
+      <c r="BB20" s="5">
+        <v>3198</v>
+      </c>
+      <c r="BC20" s="3">
+        <f t="shared" si="20"/>
+        <v>3225</v>
+      </c>
+      <c r="BD20" s="5">
+        <v>6423</v>
+      </c>
+      <c r="BE20" s="4">
+        <f t="shared" si="21"/>
+        <v>0.94553216546444874</v>
+      </c>
+      <c r="BF20" s="5">
+        <v>10395</v>
+      </c>
+      <c r="BG20" s="5">
+        <v>4208</v>
+      </c>
+      <c r="BH20" s="3">
+        <f t="shared" si="22"/>
+        <v>5507</v>
+      </c>
+      <c r="BI20" s="5">
+        <v>9715</v>
+      </c>
+      <c r="BJ20" s="4">
+        <f t="shared" si="23"/>
+        <v>0.93458393458393463</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <v>12</v>
       </c>
@@ -3169,14 +3589,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>8952</v>
+        <v>9069</v>
       </c>
       <c r="F21" s="5">
-        <v>11922</v>
+        <v>12039</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.99267277268942544</v>
+        <v>1.0024146544546211</v>
       </c>
       <c r="H21" s="5">
         <v>12254</v>
@@ -3186,14 +3606,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>8895</v>
+        <v>9034</v>
       </c>
       <c r="K21" s="5">
-        <v>12119</v>
+        <v>12258</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.98898318916272243</v>
+        <v>1.0003264240248082</v>
       </c>
       <c r="M21" s="5">
         <v>16207</v>
@@ -3203,14 +3623,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>11878</v>
+        <v>12101</v>
       </c>
       <c r="P21" s="5">
-        <v>16145</v>
+        <v>16368</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>0.99617449250323931</v>
+        <v>1.0099339791448139</v>
       </c>
       <c r="R21" s="5">
         <v>12383</v>
@@ -3220,14 +3640,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>8904</v>
+        <v>9111</v>
       </c>
       <c r="U21" s="5">
-        <v>12323</v>
+        <v>12530</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>0.99515464750060567</v>
+        <v>1.0118711136235161</v>
       </c>
       <c r="W21" s="5">
         <v>12782</v>
@@ -3237,14 +3657,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>8847</v>
+        <v>9131</v>
       </c>
       <c r="Z21" s="5">
-        <v>12448</v>
+        <v>12732</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>0.97386950398998595</v>
+        <v>0.99608824910029725</v>
       </c>
       <c r="AB21" s="5">
         <v>16816</v>
@@ -3254,14 +3674,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>12077</v>
+        <v>12579</v>
       </c>
       <c r="AE21" s="5">
-        <v>16286</v>
+        <v>16788</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>0.9684823977164605</v>
+        <v>0.99833491912464323</v>
       </c>
       <c r="AG21" s="5">
         <v>12696</v>
@@ -3271,14 +3691,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>8715</v>
+        <v>9234</v>
       </c>
       <c r="AJ21" s="5">
-        <v>12157</v>
+        <v>12676</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>0.95754568367989923</v>
+        <v>0.99842470069313172</v>
       </c>
       <c r="AL21" s="5">
         <v>13072</v>
@@ -3288,14 +3708,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>8528</v>
+        <v>9236</v>
       </c>
       <c r="AO21" s="5">
-        <v>12179</v>
+        <v>12887</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>0.9316860465116279</v>
+        <v>0.9858476132190942</v>
       </c>
       <c r="AQ21" s="5">
         <v>17310</v>
@@ -3305,14 +3725,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>11214</v>
+        <v>12568</v>
       </c>
       <c r="AT21" s="5">
-        <v>15693</v>
+        <v>17047</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>0.90658578856152516</v>
+        <v>0.98480647024841128</v>
       </c>
       <c r="AV21" s="5">
         <v>13094</v>
@@ -3322,17 +3742,51 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>1455</v>
+        <v>3251</v>
       </c>
       <c r="AY21" s="5">
-        <v>10944</v>
+        <v>12740</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>0.83580265770581941</v>
+        <v>0.97296471666412099</v>
+      </c>
+      <c r="BA21" s="5">
+        <v>13518</v>
+      </c>
+      <c r="BB21" s="5">
+        <v>4148</v>
+      </c>
+      <c r="BC21" s="3">
+        <f t="shared" si="20"/>
+        <v>8612</v>
+      </c>
+      <c r="BD21" s="5">
+        <v>12760</v>
+      </c>
+      <c r="BE21" s="4">
+        <f t="shared" si="21"/>
+        <v>0.94392661636336739</v>
+      </c>
+      <c r="BF21" s="5">
+        <v>17905</v>
+      </c>
+      <c r="BG21" s="5">
+        <v>4608</v>
+      </c>
+      <c r="BH21" s="3">
+        <f t="shared" si="22"/>
+        <v>11084</v>
+      </c>
+      <c r="BI21" s="5">
+        <v>15692</v>
+      </c>
+      <c r="BJ21" s="4">
+        <f t="shared" si="23"/>
+        <v>0.87640323931862607</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>13</v>
       </c>
@@ -3347,14 +3801,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4816</v>
+        <v>4860</v>
       </c>
       <c r="F22" s="5">
-        <v>6929</v>
+        <v>6973</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99042309891366498</v>
+        <v>0.99671240708976561</v>
       </c>
       <c r="H22" s="5">
         <v>7077</v>
@@ -3364,14 +3818,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4760</v>
+        <v>4808</v>
       </c>
       <c r="K22" s="5">
-        <v>6980</v>
+        <v>7028</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.98629362724318215</v>
+        <v>0.99307616221562811</v>
       </c>
       <c r="M22" s="5">
         <v>8504</v>
@@ -3381,14 +3835,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5665</v>
+        <v>5740</v>
       </c>
       <c r="P22" s="5">
-        <v>8441</v>
+        <v>8516</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>0.9925917215428034</v>
+        <v>1.0014111006585136</v>
       </c>
       <c r="R22" s="5">
         <v>7111</v>
@@ -3398,14 +3852,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4555</v>
+        <v>4628</v>
       </c>
       <c r="U22" s="5">
-        <v>6995</v>
+        <v>7068</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>0.98368724511320493</v>
+        <v>0.99395303051610184</v>
       </c>
       <c r="W22" s="5">
         <v>7191</v>
@@ -3415,14 +3869,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4505</v>
+        <v>4618</v>
       </c>
       <c r="Z22" s="5">
-        <v>7014</v>
+        <v>7127</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.97538589904046724</v>
+        <v>0.99109998609372829</v>
       </c>
       <c r="AB22" s="5">
         <v>8707</v>
@@ -3432,14 +3886,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5668</v>
+        <v>5872</v>
       </c>
       <c r="AE22" s="5">
-        <v>8444</v>
+        <v>8648</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>0.96979441828413915</v>
+        <v>0.99322384288503507</v>
       </c>
       <c r="AG22" s="5">
         <v>7162</v>
@@ -3449,14 +3903,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4446</v>
+        <v>4658</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6899</v>
+        <v>7111</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>0.96327841385087964</v>
+        <v>0.99287908405473335</v>
       </c>
       <c r="AL22" s="5">
         <v>7226</v>
@@ -3466,14 +3920,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4333</v>
+        <v>4643</v>
       </c>
       <c r="AO22" s="5">
-        <v>6847</v>
+        <v>7157</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.94755051203985607</v>
+        <v>0.99045114862994743</v>
       </c>
       <c r="AQ22" s="5">
         <v>8754</v>
@@ -3483,14 +3937,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5472</v>
+        <v>6048</v>
       </c>
       <c r="AT22" s="5">
-        <v>8084</v>
+        <v>8660</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>0.92346355951564996</v>
+        <v>0.98926205163353897</v>
       </c>
       <c r="AV22" s="5">
         <v>7182</v>
@@ -3500,17 +3954,51 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>774</v>
+        <v>1650</v>
       </c>
       <c r="AY22" s="5">
-        <v>6160</v>
+        <v>7036</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.85769980506822607</v>
+        <v>0.97967140072403225</v>
+      </c>
+      <c r="BA22" s="5">
+        <v>7296</v>
+      </c>
+      <c r="BB22" s="5">
+        <v>2568</v>
+      </c>
+      <c r="BC22" s="3">
+        <f t="shared" si="20"/>
+        <v>4464</v>
+      </c>
+      <c r="BD22" s="5">
+        <v>7032</v>
+      </c>
+      <c r="BE22" s="4">
+        <f t="shared" si="21"/>
+        <v>0.96381578947368418</v>
+      </c>
+      <c r="BF22" s="5">
+        <v>8939</v>
+      </c>
+      <c r="BG22" s="5">
+        <v>2822</v>
+      </c>
+      <c r="BH22" s="3">
+        <f t="shared" si="22"/>
+        <v>5374</v>
+      </c>
+      <c r="BI22" s="5">
+        <v>8196</v>
+      </c>
+      <c r="BJ22" s="4">
+        <f t="shared" si="23"/>
+        <v>0.91688108289517845</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>14</v>
       </c>
@@ -3525,14 +4013,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6621</v>
+        <v>6663</v>
       </c>
       <c r="F23" s="5">
-        <v>9149</v>
+        <v>9191</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.97257361539279263</v>
+        <v>0.97703837567768681</v>
       </c>
       <c r="H23" s="5">
         <v>9786</v>
@@ -3542,14 +4030,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7276</v>
+        <v>7330</v>
       </c>
       <c r="K23" s="5">
-        <v>9273</v>
+        <v>9327</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.9475781729000613</v>
+        <v>0.95309625996321279</v>
       </c>
       <c r="M23" s="5">
         <v>12056</v>
@@ -3559,14 +4047,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8484</v>
+        <v>8581</v>
       </c>
       <c r="P23" s="5">
-        <v>11769</v>
+        <v>11866</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.97619442601194428</v>
+        <v>0.98424021234240211</v>
       </c>
       <c r="R23" s="5">
         <v>9480</v>
@@ -3576,14 +4064,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6512</v>
+        <v>6607</v>
       </c>
       <c r="U23" s="5">
-        <v>9286</v>
+        <v>9381</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.97953586497890299</v>
+        <v>0.98955696202531651</v>
       </c>
       <c r="W23" s="5">
         <v>9764</v>
@@ -3593,14 +4081,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6492</v>
+        <v>6621</v>
       </c>
       <c r="Z23" s="5">
-        <v>9320</v>
+        <v>9449</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.95452683326505527</v>
+        <v>0.96773863170831631</v>
       </c>
       <c r="AB23" s="5">
         <v>12327</v>
@@ -3610,14 +4098,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8598</v>
+        <v>8842</v>
       </c>
       <c r="AE23" s="5">
-        <v>11816</v>
+        <v>12060</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.95854628052243041</v>
+        <v>0.97834022876612314</v>
       </c>
       <c r="AG23" s="5">
         <v>9618</v>
@@ -3627,14 +4115,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6340</v>
+        <v>6616</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9069</v>
+        <v>9345</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.94291952588895822</v>
+        <v>0.97161572052401746</v>
       </c>
       <c r="AL23" s="5">
         <v>9741</v>
@@ -3644,14 +4132,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6425</v>
+        <v>6814</v>
       </c>
       <c r="AO23" s="5">
-        <v>9067</v>
+        <v>9456</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.93080792526434653</v>
+        <v>0.97074222359100704</v>
       </c>
       <c r="AQ23" s="5">
         <v>12556</v>
@@ -3661,14 +4149,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8047</v>
+        <v>8799</v>
       </c>
       <c r="AT23" s="5">
-        <v>11374</v>
+        <v>12126</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.90586173940745462</v>
+        <v>0.96575342465753422</v>
       </c>
       <c r="AV23" s="5">
         <v>9718</v>
@@ -3678,17 +4166,51 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>1333</v>
+        <v>2473</v>
       </c>
       <c r="AY23" s="5">
-        <v>8197</v>
+        <v>9337</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.84348631405639019</v>
+        <v>0.96079440214035805</v>
+      </c>
+      <c r="BA23" s="5">
+        <v>10107</v>
+      </c>
+      <c r="BB23" s="5">
+        <v>2932</v>
+      </c>
+      <c r="BC23" s="3">
+        <f t="shared" si="20"/>
+        <v>6474</v>
+      </c>
+      <c r="BD23" s="5">
+        <v>9406</v>
+      </c>
+      <c r="BE23" s="4">
+        <f t="shared" si="21"/>
+        <v>0.9306421292173741</v>
+      </c>
+      <c r="BF23" s="5">
+        <v>13018</v>
+      </c>
+      <c r="BG23" s="5">
+        <v>3320</v>
+      </c>
+      <c r="BH23" s="3">
+        <f t="shared" si="22"/>
+        <v>8184</v>
+      </c>
+      <c r="BI23" s="5">
+        <v>11504</v>
+      </c>
+      <c r="BJ23" s="4">
+        <f t="shared" si="23"/>
+        <v>0.88369949300967887</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>15</v>
       </c>
@@ -3703,14 +4225,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>5512</v>
+        <v>5531</v>
       </c>
       <c r="F24" s="5">
-        <v>6865</v>
+        <v>6884</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.98890809564966864</v>
+        <v>0.99164505906078937</v>
       </c>
       <c r="H24" s="5">
         <v>7059</v>
@@ -3720,14 +4242,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>5504</v>
+        <v>5530</v>
       </c>
       <c r="K24" s="5">
-        <v>6914</v>
+        <v>6940</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.97945884686216178</v>
+        <v>0.9831420881144638</v>
       </c>
       <c r="M24" s="5">
         <v>8056</v>
@@ -3737,14 +4259,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5473</v>
+        <v>5515</v>
       </c>
       <c r="P24" s="5">
-        <v>7888</v>
+        <v>7930</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.97914597815292947</v>
+        <v>0.98435948361469716</v>
       </c>
       <c r="R24" s="5">
         <v>7134</v>
@@ -3754,14 +4276,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4907</v>
+        <v>4954</v>
       </c>
       <c r="U24" s="5">
-        <v>6963</v>
+        <v>7010</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.97603027754415472</v>
+        <v>0.98261844687412392</v>
       </c>
       <c r="W24" s="5">
         <v>7208</v>
@@ -3771,14 +4293,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4784</v>
+        <v>4841</v>
       </c>
       <c r="Z24" s="5">
-        <v>6986</v>
+        <v>7043</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.96920088790233072</v>
+        <v>0.97710876803551605</v>
       </c>
       <c r="AB24" s="5">
         <v>8228</v>
@@ -3788,14 +4310,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5647</v>
+        <v>5749</v>
       </c>
       <c r="AE24" s="5">
-        <v>7954</v>
+        <v>8056</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.96669907632474472</v>
+        <v>0.97909577053962082</v>
       </c>
       <c r="AG24" s="5">
         <v>7344</v>
@@ -3805,14 +4327,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4824</v>
+        <v>4943</v>
       </c>
       <c r="AJ24" s="5">
-        <v>7029</v>
+        <v>7148</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.95710784313725494</v>
+        <v>0.97331154684095855</v>
       </c>
       <c r="AL24" s="5">
         <v>7506</v>
@@ -3822,14 +4344,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4717</v>
+        <v>4876</v>
       </c>
       <c r="AO24" s="5">
-        <v>7073</v>
+        <v>7232</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.94231281641353581</v>
+        <v>0.96349586997069014</v>
       </c>
       <c r="AQ24" s="5">
         <v>8509</v>
@@ -3839,14 +4361,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5611</v>
+        <v>5883</v>
       </c>
       <c r="AT24" s="5">
-        <v>7937</v>
+        <v>8209</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.93277705958396995</v>
+        <v>0.96474321306851574</v>
       </c>
       <c r="AV24" s="5">
         <v>7570</v>
@@ -3856,17 +4378,51 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>688</v>
+        <v>1191</v>
       </c>
       <c r="AY24" s="5">
-        <v>6731</v>
+        <v>7234</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.88916776750330251</v>
+        <v>0.95561426684280049</v>
+      </c>
+      <c r="BA24" s="5">
+        <v>7648</v>
+      </c>
+      <c r="BB24" s="5">
+        <v>2423</v>
+      </c>
+      <c r="BC24" s="3">
+        <f t="shared" si="20"/>
+        <v>4892</v>
+      </c>
+      <c r="BD24" s="5">
+        <v>7315</v>
+      </c>
+      <c r="BE24" s="4">
+        <f t="shared" si="21"/>
+        <v>0.95645920502092052</v>
+      </c>
+      <c r="BF24" s="5">
+        <v>8767</v>
+      </c>
+      <c r="BG24" s="5">
+        <v>2454</v>
+      </c>
+      <c r="BH24" s="3">
+        <f t="shared" si="22"/>
+        <v>5764</v>
+      </c>
+      <c r="BI24" s="5">
+        <v>8218</v>
+      </c>
+      <c r="BJ24" s="4">
+        <f t="shared" si="23"/>
+        <v>0.93737880688947184</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>16</v>
       </c>
@@ -3881,14 +4437,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>12752</v>
+        <v>12816</v>
       </c>
       <c r="F25" s="5">
-        <v>21270</v>
+        <v>21334</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.99054626740557905</v>
+        <v>0.99352675452894335</v>
       </c>
       <c r="H25" s="5">
         <v>21813</v>
@@ -3898,14 +4454,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>12712</v>
+        <v>12779</v>
       </c>
       <c r="K25" s="5">
-        <v>21456</v>
+        <v>21523</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.98363361298308349</v>
+        <v>0.98670517581258887</v>
       </c>
       <c r="M25" s="5">
         <v>29215</v>
@@ -3915,14 +4471,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>17467</v>
+        <v>17584</v>
       </c>
       <c r="P25" s="5">
-        <v>28915</v>
+        <v>29032</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.98973130241314389</v>
+        <v>0.99373609447201783</v>
       </c>
       <c r="R25" s="5">
         <v>21767</v>
@@ -3932,14 +4488,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>12285</v>
+        <v>12385</v>
       </c>
       <c r="U25" s="5">
-        <v>21499</v>
+        <v>21599</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>0.98768778426057791</v>
+        <v>0.99228189461110861</v>
       </c>
       <c r="W25" s="5">
         <v>22114</v>
@@ -3949,14 +4505,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>12066</v>
+        <v>12198</v>
       </c>
       <c r="Z25" s="5">
-        <v>21610</v>
+        <v>21742</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.97720900786831866</v>
+        <v>0.98317807723614004</v>
       </c>
       <c r="AB25" s="5">
         <v>29630</v>
@@ -3966,14 +4522,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18116</v>
+        <v>18388</v>
       </c>
       <c r="AE25" s="5">
-        <v>29099</v>
+        <v>29371</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>0.98207897401282485</v>
+        <v>0.99125885926425916</v>
       </c>
       <c r="AG25" s="5">
         <v>22174</v>
@@ -3983,14 +4539,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>12493</v>
+        <v>12745</v>
       </c>
       <c r="AJ25" s="5">
-        <v>21605</v>
+        <v>21857</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.97433931631640658</v>
+        <v>0.98570397763146023</v>
       </c>
       <c r="AL25" s="5">
         <v>22503</v>
@@ -4000,14 +4556,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>12398</v>
+        <v>12750</v>
       </c>
       <c r="AO25" s="5">
-        <v>21866</v>
+        <v>22218</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.97169266320046221</v>
+        <v>0.98733502199706702</v>
       </c>
       <c r="AQ25" s="5">
         <v>30294</v>
@@ -4017,14 +4573,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>17417</v>
+        <v>18259</v>
       </c>
       <c r="AT25" s="5">
-        <v>29083</v>
+        <v>29925</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>0.96002508747606785</v>
+        <v>0.98781937017231136</v>
       </c>
       <c r="AV25" s="5">
         <v>22740</v>
@@ -4034,17 +4590,51 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>2893</v>
+        <v>4201</v>
       </c>
       <c r="AY25" s="5">
-        <v>21156</v>
+        <v>22464</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.93034300791556723</v>
+        <v>0.98786279683377309</v>
+      </c>
+      <c r="BA25" s="5">
+        <v>23197</v>
+      </c>
+      <c r="BB25" s="5">
+        <v>9898</v>
+      </c>
+      <c r="BC25" s="3">
+        <f t="shared" si="20"/>
+        <v>12703</v>
+      </c>
+      <c r="BD25" s="5">
+        <v>22601</v>
+      </c>
+      <c r="BE25" s="4">
+        <f t="shared" si="21"/>
+        <v>0.97430702245980083</v>
+      </c>
+      <c r="BF25" s="5">
+        <v>31043</v>
+      </c>
+      <c r="BG25" s="5">
+        <v>12119</v>
+      </c>
+      <c r="BH25" s="3">
+        <f t="shared" si="22"/>
+        <v>17359</v>
+      </c>
+      <c r="BI25" s="5">
+        <v>29478</v>
+      </c>
+      <c r="BJ25" s="4">
+        <f t="shared" si="23"/>
+        <v>0.94958605804851337</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>17</v>
       </c>
@@ -4059,14 +4649,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>10170</v>
+        <v>10223</v>
       </c>
       <c r="F26" s="5">
-        <v>14357</v>
+        <v>14410</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.98659978009895544</v>
+        <v>0.99024189114898298</v>
       </c>
       <c r="H26" s="5">
         <v>14990</v>
@@ -4076,14 +4666,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>10056</v>
+        <v>10122</v>
       </c>
       <c r="K26" s="5">
-        <v>14680</v>
+        <v>14746</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.97931954636424279</v>
+        <v>0.98372248165443632</v>
       </c>
       <c r="M26" s="5">
         <v>28508</v>
@@ -4093,14 +4683,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>19958</v>
+        <v>20111</v>
       </c>
       <c r="P26" s="5">
-        <v>28252</v>
+        <v>28405</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99102006454328606</v>
+        <v>0.99638697909358775</v>
       </c>
       <c r="R26" s="5">
         <v>14719</v>
@@ -4110,14 +4700,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9693</v>
+        <v>9804</v>
       </c>
       <c r="U26" s="5">
-        <v>14448</v>
+        <v>14559</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.98158842312657113</v>
+        <v>0.98912969631089065</v>
       </c>
       <c r="W26" s="5">
         <v>15123</v>
@@ -4127,14 +4717,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9652</v>
+        <v>9804</v>
       </c>
       <c r="Z26" s="5">
-        <v>14620</v>
+        <v>14772</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.96673940355749521</v>
+        <v>0.97679031938107519</v>
       </c>
       <c r="AB26" s="5">
         <v>29054</v>
@@ -4144,14 +4734,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20238</v>
+        <v>20622</v>
       </c>
       <c r="AE26" s="5">
-        <v>28281</v>
+        <v>28665</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.97339436910580301</v>
+        <v>0.98661113788118671</v>
       </c>
       <c r="AG26" s="5">
         <v>14835</v>
@@ -4161,14 +4751,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9294</v>
+        <v>9597</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14255</v>
+        <v>14558</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.96090326929558478</v>
+        <v>0.98132794068082241</v>
       </c>
       <c r="AL26" s="5">
         <v>15316</v>
@@ -4178,14 +4768,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>8909</v>
+        <v>9336</v>
       </c>
       <c r="AO26" s="5">
-        <v>14385</v>
+        <v>14812</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.93921389396709321</v>
+        <v>0.96709323583180984</v>
       </c>
       <c r="AQ26" s="5">
         <v>29312</v>
@@ -4195,14 +4785,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>19413</v>
+        <v>20715</v>
       </c>
       <c r="AT26" s="5">
-        <v>27469</v>
+        <v>28771</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.93712472707423577</v>
+        <v>0.98154339519650657</v>
       </c>
       <c r="AV26" s="5">
         <v>15164</v>
@@ -4212,17 +4802,51 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>1354</v>
+        <v>2596</v>
       </c>
       <c r="AY26" s="5">
-        <v>13350</v>
+        <v>14592</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.88037457135320496</v>
+        <v>0.962279082036402</v>
+      </c>
+      <c r="BA26" s="5">
+        <v>15499</v>
+      </c>
+      <c r="BB26" s="5">
+        <v>4838</v>
+      </c>
+      <c r="BC26" s="3">
+        <f t="shared" si="20"/>
+        <v>9859</v>
+      </c>
+      <c r="BD26" s="5">
+        <v>14697</v>
+      </c>
+      <c r="BE26" s="4">
+        <f t="shared" si="21"/>
+        <v>0.94825472611136208</v>
+      </c>
+      <c r="BF26" s="5">
+        <v>29635</v>
+      </c>
+      <c r="BG26" s="5">
+        <v>8158</v>
+      </c>
+      <c r="BH26" s="3">
+        <f t="shared" si="22"/>
+        <v>19663</v>
+      </c>
+      <c r="BI26" s="5">
+        <v>27821</v>
+      </c>
+      <c r="BJ26" s="4">
+        <f t="shared" si="23"/>
+        <v>0.93878859456723474</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>18</v>
       </c>
@@ -4237,14 +4861,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>79656</v>
+        <v>80116</v>
       </c>
       <c r="F27" s="5">
-        <v>129013</v>
+        <v>129473</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.98387072173753887</v>
+        <v>0.98737874443292051</v>
       </c>
       <c r="H27" s="5">
         <v>134384</v>
@@ -4254,14 +4878,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>78791</v>
+        <v>79341</v>
       </c>
       <c r="K27" s="5">
-        <v>129738</v>
+        <v>130288</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.96542743183712343</v>
+        <v>0.96952018097392545</v>
       </c>
       <c r="M27" s="5">
         <v>190911</v>
@@ -4271,14 +4895,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>120354</v>
+        <v>121471</v>
       </c>
       <c r="P27" s="5">
-        <v>189775</v>
+        <v>190892</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99404958331369064</v>
+        <v>0.9999004771857043</v>
       </c>
       <c r="R27" s="5">
         <v>131264</v>
@@ -4288,14 +4912,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>75225</v>
+        <v>76142</v>
       </c>
       <c r="U27" s="5">
-        <v>129178</v>
+        <v>130095</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.98410836177474403</v>
+        <v>0.99109428327645055</v>
       </c>
       <c r="W27" s="5">
         <v>134144</v>
@@ -4305,14 +4929,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>74705</v>
+        <v>75962</v>
       </c>
       <c r="Z27" s="5">
-        <v>130175</v>
+        <v>131432</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97041239265267176</v>
+        <v>0.97978291984732824</v>
       </c>
       <c r="AB27" s="5">
         <v>194609</v>
@@ -4322,14 +4946,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>121860</v>
+        <v>124815</v>
       </c>
       <c r="AE27" s="5">
-        <v>189824</v>
+        <v>192779</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.97541223684413358</v>
+        <v>0.99059652945136145</v>
       </c>
       <c r="AG27" s="5">
         <v>134089</v>
@@ -4339,14 +4963,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>75940</v>
+        <v>78558</v>
       </c>
       <c r="AJ27" s="5">
-        <v>128955</v>
+        <v>131573</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.96171199725555412</v>
+        <v>0.98123634302590068</v>
       </c>
       <c r="AL27" s="5">
         <v>137688</v>
@@ -4356,14 +4980,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>75291</v>
+        <v>79136</v>
       </c>
       <c r="AO27" s="5">
-        <v>131680</v>
+        <v>135525</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.95636511533321711</v>
+        <v>0.98429056998431241</v>
       </c>
       <c r="AQ27" s="5">
         <v>200322</v>
@@ -4373,14 +4997,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>116087</v>
+        <v>125508</v>
       </c>
       <c r="AT27" s="5">
-        <v>188000</v>
+        <v>197421</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.93848903265742156</v>
+        <v>0.98551831551202562</v>
       </c>
       <c r="AV27" s="5">
         <v>139481</v>
@@ -4390,17 +5014,51 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>16870</v>
+        <v>28476</v>
       </c>
       <c r="AY27" s="5">
-        <v>124112</v>
+        <v>135718</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.88981294943397304</v>
+        <v>0.97302141510313234</v>
+      </c>
+      <c r="BA27" s="5">
+        <v>143305</v>
+      </c>
+      <c r="BB27" s="5">
+        <v>58981</v>
+      </c>
+      <c r="BC27" s="3">
+        <f t="shared" si="20"/>
+        <v>77680</v>
+      </c>
+      <c r="BD27" s="5">
+        <v>136661</v>
+      </c>
+      <c r="BE27" s="4">
+        <f t="shared" si="21"/>
+        <v>0.95363734691741386</v>
+      </c>
+      <c r="BF27" s="5">
+        <v>208143</v>
+      </c>
+      <c r="BG27" s="5">
+        <v>72024</v>
+      </c>
+      <c r="BH27" s="3">
+        <f t="shared" si="22"/>
+        <v>118754</v>
+      </c>
+      <c r="BI27" s="5">
+        <v>190778</v>
+      </c>
+      <c r="BJ27" s="4">
+        <f t="shared" si="23"/>
+        <v>0.91657177997818806</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>19</v>
       </c>
@@ -4415,14 +5073,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>188737</v>
+        <v>189178</v>
       </c>
       <c r="F28" s="5">
-        <v>434102</v>
+        <v>434543</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.9922036602340959</v>
+        <v>0.99321163028298587</v>
       </c>
       <c r="H28" s="5">
         <v>447363</v>
@@ -4432,14 +5090,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>190921</v>
+        <v>191493</v>
       </c>
       <c r="K28" s="5">
-        <v>441613</v>
+        <v>442185</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.98714690307423725</v>
+        <v>0.98842550680320007</v>
       </c>
       <c r="M28" s="5">
         <v>722935</v>
@@ -4449,14 +5107,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>332738</v>
+        <v>333964</v>
       </c>
       <c r="P28" s="5">
-        <v>717053</v>
+        <v>718279</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99186372218802521</v>
+        <v>0.99355958696148339</v>
       </c>
       <c r="R28" s="5">
         <v>448339</v>
@@ -4466,14 +5124,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>184592</v>
+        <v>185642</v>
       </c>
       <c r="U28" s="5">
-        <v>444110</v>
+        <v>445160</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99056740546773758</v>
+        <v>0.99290938330147505</v>
       </c>
       <c r="W28" s="5">
         <v>458076</v>
@@ -4483,14 +5141,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>185392</v>
+        <v>187166</v>
       </c>
       <c r="Z28" s="5">
-        <v>448621</v>
+        <v>450395</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.9793593202874632</v>
+        <v>0.98323204009814968</v>
       </c>
       <c r="AB28" s="5">
         <v>737235</v>
@@ -4500,14 +5158,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>348479</v>
+        <v>353032</v>
       </c>
       <c r="AE28" s="5">
-        <v>725391</v>
+        <v>729944</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.98393456631874499</v>
+        <v>0.99011034473404003</v>
       </c>
       <c r="AG28" s="5">
         <v>456666</v>
@@ -4517,14 +5175,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>187923</v>
+        <v>192302</v>
       </c>
       <c r="AJ28" s="5">
-        <v>446304</v>
+        <v>450683</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.97730945592621299</v>
+        <v>0.98689852101973874</v>
       </c>
       <c r="AL28" s="5">
         <v>468801</v>
@@ -4534,14 +5192,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>186188</v>
+        <v>192593</v>
       </c>
       <c r="AO28" s="5">
-        <v>456931</v>
+        <v>463336</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.97468008813974372</v>
+        <v>0.98834260165827292</v>
       </c>
       <c r="AQ28" s="5">
         <v>756132</v>
@@ -4551,14 +5209,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>332790</v>
+        <v>349959</v>
       </c>
       <c r="AT28" s="5">
-        <v>731803</v>
+        <v>748972</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.96782440103050793</v>
+        <v>0.99053075388953249</v>
       </c>
       <c r="AV28" s="5">
         <v>474991</v>
@@ -4568,17 +5226,51 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>41681</v>
+        <v>62241</v>
       </c>
       <c r="AY28" s="5">
-        <v>446716</v>
+        <v>467276</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.94047255632211979</v>
+        <v>0.98375758698585869</v>
+      </c>
+      <c r="BA28" s="5">
+        <v>487540</v>
+      </c>
+      <c r="BB28" s="5">
+        <v>280574</v>
+      </c>
+      <c r="BC28" s="3">
+        <f t="shared" si="20"/>
+        <v>192585</v>
+      </c>
+      <c r="BD28" s="5">
+        <v>473159</v>
+      </c>
+      <c r="BE28" s="4">
+        <f t="shared" si="21"/>
+        <v>0.97050293309266933</v>
+      </c>
+      <c r="BF28" s="5">
+        <v>779284</v>
+      </c>
+      <c r="BG28" s="5">
+        <v>407538</v>
+      </c>
+      <c r="BH28" s="3">
+        <f t="shared" si="22"/>
+        <v>336547</v>
+      </c>
+      <c r="BI28" s="5">
+        <v>744085</v>
+      </c>
+      <c r="BJ28" s="4">
+        <f t="shared" si="23"/>
+        <v>0.95483161466166377</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>20</v>
       </c>
@@ -4593,14 +5285,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>78128</v>
+        <v>78321</v>
       </c>
       <c r="F29" s="5">
-        <v>142461</v>
+        <v>142654</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99101925538427293</v>
+        <v>0.99236184540041183</v>
       </c>
       <c r="H29" s="5">
         <v>146310</v>
@@ -4610,14 +5302,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>77528</v>
+        <v>77774</v>
       </c>
       <c r="K29" s="5">
-        <v>143901</v>
+        <v>144147</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.9835349600164035</v>
+        <v>0.98521632150912442</v>
       </c>
       <c r="M29" s="5">
         <v>194093</v>
@@ -4627,14 +5319,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>105902</v>
+        <v>106332</v>
       </c>
       <c r="P29" s="5">
-        <v>191329</v>
+        <v>191759</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98575940399705297</v>
+        <v>0.98797483680503673</v>
       </c>
       <c r="R29" s="5">
         <v>146918</v>
@@ -4644,14 +5336,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>76892</v>
+        <v>77340</v>
       </c>
       <c r="U29" s="5">
-        <v>144636</v>
+        <v>145084</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98446752610299626</v>
+        <v>0.98751684613185586</v>
       </c>
       <c r="W29" s="5">
         <v>149105</v>
@@ -4661,14 +5353,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>74716</v>
+        <v>75435</v>
       </c>
       <c r="Z29" s="5">
-        <v>145690</v>
+        <v>146409</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.97709667683846957</v>
+        <v>0.9819187820663291</v>
       </c>
       <c r="AB29" s="5">
         <v>197403</v>
@@ -4678,14 +5370,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>108157</v>
+        <v>109716</v>
       </c>
       <c r="AE29" s="5">
-        <v>193023</v>
+        <v>194582</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.97781188735733504</v>
+        <v>0.98570943703996394</v>
       </c>
       <c r="AG29" s="5">
         <v>149309</v>
@@ -4695,14 +5387,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>76495</v>
+        <v>78251</v>
       </c>
       <c r="AJ29" s="5">
-        <v>145279</v>
+        <v>147035</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.97300899476923697</v>
+        <v>0.98476983972834864</v>
       </c>
       <c r="AL29" s="5">
         <v>152026</v>
@@ -4712,14 +5404,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>76571</v>
+        <v>79096</v>
       </c>
       <c r="AO29" s="5">
-        <v>149050</v>
+        <v>151575</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.98042440108928741</v>
+        <v>0.99703340218120584</v>
       </c>
       <c r="AQ29" s="5">
         <v>203571</v>
@@ -4729,14 +5421,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>106688</v>
+        <v>112321</v>
       </c>
       <c r="AT29" s="5">
-        <v>196325</v>
+        <v>201958</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.96440553909938054</v>
+        <v>0.9920764745469639</v>
       </c>
       <c r="AV29" s="5">
         <v>155780</v>
@@ -4746,17 +5438,51 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>15743</v>
+        <v>24604</v>
       </c>
       <c r="AY29" s="5">
-        <v>145092</v>
+        <v>153953</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.93139042239055081</v>
+        <v>0.98827192194119917</v>
+      </c>
+      <c r="BA29" s="5">
+        <v>159604</v>
+      </c>
+      <c r="BB29" s="5">
+        <v>75559</v>
+      </c>
+      <c r="BC29" s="3">
+        <f t="shared" si="20"/>
+        <v>80177</v>
+      </c>
+      <c r="BD29" s="5">
+        <v>155736</v>
+      </c>
+      <c r="BE29" s="4">
+        <f t="shared" si="21"/>
+        <v>0.97576501842059093</v>
+      </c>
+      <c r="BF29" s="5">
+        <v>211893</v>
+      </c>
+      <c r="BG29" s="5">
+        <v>94207</v>
+      </c>
+      <c r="BH29" s="3">
+        <f t="shared" si="22"/>
+        <v>107893</v>
+      </c>
+      <c r="BI29" s="5">
+        <v>202100</v>
+      </c>
+      <c r="BJ29" s="4">
+        <f t="shared" si="23"/>
+        <v>0.95378327740888091</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>21</v>
       </c>
@@ -4771,14 +5497,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>108985</v>
+        <v>109243</v>
       </c>
       <c r="F30" s="5">
-        <v>184992</v>
+        <v>185250</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99312832846589938</v>
+        <v>0.99451339975949149</v>
       </c>
       <c r="H30" s="5">
         <v>190966</v>
@@ -4788,14 +5514,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>109194</v>
+        <v>109502</v>
       </c>
       <c r="K30" s="5">
-        <v>187913</v>
+        <v>188221</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98401286092812335</v>
+        <v>0.98562571347779182</v>
       </c>
       <c r="M30" s="5">
         <v>320227</v>
@@ -4805,14 +5531,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>195774</v>
+        <v>196481</v>
       </c>
       <c r="P30" s="5">
-        <v>317508</v>
+        <v>318215</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99150914819799707</v>
+        <v>0.9937169570336043</v>
       </c>
       <c r="R30" s="5">
         <v>189502</v>
@@ -4822,14 +5548,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>105180</v>
+        <v>105775</v>
       </c>
       <c r="U30" s="5">
-        <v>187387</v>
+        <v>187982</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.98883916792434912</v>
+        <v>0.99197897647518229</v>
       </c>
       <c r="W30" s="5">
         <v>194334</v>
@@ -4839,14 +5565,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>103477</v>
+        <v>104396</v>
       </c>
       <c r="Z30" s="5">
-        <v>189433</v>
+        <v>190352</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97478053248530883</v>
+        <v>0.97950950425556005</v>
       </c>
       <c r="AB30" s="5">
         <v>325942</v>
@@ -4856,14 +5582,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>200067</v>
+        <v>202740</v>
       </c>
       <c r="AE30" s="5">
-        <v>320046</v>
+        <v>322719</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.98191089212191129</v>
+        <v>0.99011173767111937</v>
       </c>
       <c r="AG30" s="5">
         <v>192789</v>
@@ -4873,14 +5599,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>106382</v>
+        <v>108676</v>
       </c>
       <c r="AJ30" s="5">
-        <v>188416</v>
+        <v>190710</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.97731717058545875</v>
+        <v>0.98921618972036784</v>
       </c>
       <c r="AL30" s="5">
         <v>197994</v>
@@ -4890,14 +5616,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>104551</v>
+        <v>108049</v>
       </c>
       <c r="AO30" s="5">
-        <v>191842</v>
+        <v>195340</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.96892835136418276</v>
+        <v>0.98659555340060812</v>
       </c>
       <c r="AQ30" s="5">
         <v>333633</v>
@@ -4907,14 +5633,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>193093</v>
+        <v>203645</v>
       </c>
       <c r="AT30" s="5">
-        <v>319384</v>
+        <v>329936</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.9572913950358628</v>
+        <v>0.98891896185329387</v>
       </c>
       <c r="AV30" s="5">
         <v>198460</v>
@@ -4924,17 +5650,51 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>22459</v>
+        <v>35138</v>
       </c>
       <c r="AY30" s="5">
-        <v>182754</v>
+        <v>195433</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.92086062682656455</v>
+        <v>0.98474755618260612</v>
+      </c>
+      <c r="BA30" s="5">
+        <v>203942</v>
+      </c>
+      <c r="BB30" s="5">
+        <v>91009</v>
+      </c>
+      <c r="BC30" s="3">
+        <f t="shared" si="20"/>
+        <v>106529</v>
+      </c>
+      <c r="BD30" s="5">
+        <v>197538</v>
+      </c>
+      <c r="BE30" s="4">
+        <f t="shared" si="21"/>
+        <v>0.96859891537790155</v>
+      </c>
+      <c r="BF30" s="5">
+        <v>342999</v>
+      </c>
+      <c r="BG30" s="5">
+        <v>130806</v>
+      </c>
+      <c r="BH30" s="3">
+        <f t="shared" si="22"/>
+        <v>193107</v>
+      </c>
+      <c r="BI30" s="5">
+        <v>323913</v>
+      </c>
+      <c r="BJ30" s="4">
+        <f t="shared" si="23"/>
+        <v>0.9443555229023991</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>22</v>
       </c>
@@ -4949,14 +5709,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>36906</v>
+        <v>37001</v>
       </c>
       <c r="F31" s="5">
-        <v>83135</v>
+        <v>83230</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0030404304863483</v>
+        <v>1.0041866245189002</v>
       </c>
       <c r="H31" s="5">
         <v>85478</v>
@@ -4966,14 +5726,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35337</v>
+        <v>35461</v>
       </c>
       <c r="K31" s="5">
-        <v>84603</v>
+        <v>84727</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.98976344790472404</v>
+        <v>0.99121411357308309</v>
       </c>
       <c r="M31" s="5">
         <v>149930</v>
@@ -4983,14 +5743,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>74970</v>
+        <v>75315</v>
       </c>
       <c r="P31" s="5">
-        <v>150581</v>
+        <v>150926</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0043420262789302</v>
+        <v>1.0066431001133862</v>
       </c>
       <c r="R31" s="5">
         <v>83981</v>
@@ -5000,14 +5760,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34007</v>
+        <v>34219</v>
       </c>
       <c r="U31" s="5">
-        <v>83814</v>
+        <v>84026</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>0.99801145497195798</v>
+        <v>1.0005358354865981</v>
       </c>
       <c r="W31" s="5">
         <v>85994</v>
@@ -5017,14 +5777,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>33505</v>
+        <v>33814</v>
       </c>
       <c r="Z31" s="5">
-        <v>85080</v>
+        <v>85389</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.98937135148963884</v>
+        <v>0.99296462543898412</v>
       </c>
       <c r="AB31" s="5">
         <v>153633</v>
@@ -5034,14 +5794,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>76787</v>
+        <v>77761</v>
       </c>
       <c r="AE31" s="5">
-        <v>152515</v>
+        <v>153489</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>0.992722917602338</v>
+        <v>0.99906270137275199</v>
       </c>
       <c r="AG31" s="5">
         <v>85109</v>
@@ -5051,14 +5811,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>34839</v>
+        <v>35542</v>
       </c>
       <c r="AJ31" s="5">
-        <v>84656</v>
+        <v>85359</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>0.99467741366952966</v>
+        <v>1.0029374096746526</v>
       </c>
       <c r="AL31" s="5">
         <v>88549</v>
@@ -5068,14 +5828,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>33441</v>
+        <v>34533</v>
       </c>
       <c r="AO31" s="5">
-        <v>86738</v>
+        <v>87830</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.97954804684412022</v>
+        <v>0.99188020192209958</v>
       </c>
       <c r="AQ31" s="5">
         <v>156407</v>
@@ -5085,14 +5845,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>73256</v>
+        <v>77600</v>
       </c>
       <c r="AT31" s="5">
-        <v>152465</v>
+        <v>156809</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>0.97479652445223042</v>
+        <v>1.0025702174455107</v>
       </c>
       <c r="AV31" s="5">
         <v>87916</v>
@@ -5102,17 +5862,51 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>11179</v>
+        <v>16254</v>
       </c>
       <c r="AY31" s="5">
-        <v>82605</v>
+        <v>87680</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>0.93959006324218575</v>
+        <v>0.9973156194549343</v>
+      </c>
+      <c r="BA31" s="5">
+        <v>90084</v>
+      </c>
+      <c r="BB31" s="5">
+        <v>54478</v>
+      </c>
+      <c r="BC31" s="3">
+        <f t="shared" si="20"/>
+        <v>34571</v>
+      </c>
+      <c r="BD31" s="5">
+        <v>89049</v>
+      </c>
+      <c r="BE31" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98851072332489676</v>
+      </c>
+      <c r="BF31" s="5">
+        <v>159779</v>
+      </c>
+      <c r="BG31" s="5">
+        <v>79773</v>
+      </c>
+      <c r="BH31" s="3">
+        <f t="shared" si="22"/>
+        <v>73008</v>
+      </c>
+      <c r="BI31" s="5">
+        <v>152781</v>
+      </c>
+      <c r="BJ31" s="4">
+        <f t="shared" si="23"/>
+        <v>0.95620200401804989</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>23</v>
       </c>
@@ -5127,14 +5921,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>107291</v>
+        <v>107474</v>
       </c>
       <c r="F32" s="5">
-        <v>230585</v>
+        <v>230768</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99384088891187605</v>
+        <v>0.99462963441861263</v>
       </c>
       <c r="H32" s="5">
         <v>238678</v>
@@ -5144,14 +5938,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>107289</v>
+        <v>107529</v>
       </c>
       <c r="K32" s="5">
-        <v>235025</v>
+        <v>235265</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98469486085856262</v>
+        <v>0.9857003997016901</v>
       </c>
       <c r="M32" s="5">
         <v>498323</v>
@@ -5161,14 +5955,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>269437</v>
+        <v>270195</v>
       </c>
       <c r="P32" s="5">
-        <v>494802</v>
+        <v>495560</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99293430164772645</v>
+        <v>0.99445540342308103</v>
       </c>
       <c r="R32" s="5">
         <v>234167</v>
@@ -5178,14 +5972,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>102410</v>
+        <v>102877</v>
       </c>
       <c r="U32" s="5">
-        <v>232349</v>
+        <v>232816</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99223630998390033</v>
+        <v>0.99423061319485662</v>
       </c>
       <c r="W32" s="5">
         <v>242821</v>
@@ -5195,14 +5989,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>102660</v>
+        <v>103434</v>
       </c>
       <c r="Z32" s="5">
-        <v>236403</v>
+        <v>237177</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97356900762289922</v>
+        <v>0.97675654082637009</v>
       </c>
       <c r="AB32" s="5">
         <v>507064</v>
@@ -5212,14 +6006,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>276981</v>
+        <v>280059</v>
       </c>
       <c r="AE32" s="5">
-        <v>501202</v>
+        <v>504280</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.98843932915766053</v>
+        <v>0.99450956881182651</v>
       </c>
       <c r="AG32" s="5">
         <v>238186</v>
@@ -5229,14 +6023,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>103543</v>
+        <v>105538</v>
       </c>
       <c r="AJ32" s="5">
-        <v>234379</v>
+        <v>236374</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.98401669283669069</v>
+        <v>0.99239249997900802</v>
       </c>
       <c r="AL32" s="5">
         <v>247675</v>
@@ -5246,14 +6040,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>102432</v>
+        <v>105601</v>
       </c>
       <c r="AO32" s="5">
-        <v>242547</v>
+        <v>245716</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.97929544766326837</v>
+        <v>0.99209044110225098</v>
       </c>
       <c r="AQ32" s="5">
         <v>518099</v>
@@ -5263,14 +6057,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>263920</v>
+        <v>277058</v>
       </c>
       <c r="AT32" s="5">
-        <v>503626</v>
+        <v>516764</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.97206518445316437</v>
+        <v>0.99742327238616557</v>
       </c>
       <c r="AV32" s="5">
         <v>246693</v>
@@ -5280,17 +6074,51 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>27686</v>
+        <v>41005</v>
       </c>
       <c r="AY32" s="5">
-        <v>232522</v>
+        <v>245841</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.94255613252098758</v>
+        <v>0.99654631465019272</v>
+      </c>
+      <c r="BA32" s="5">
+        <v>255610</v>
+      </c>
+      <c r="BB32" s="5">
+        <v>144739</v>
+      </c>
+      <c r="BC32" s="3">
+        <f t="shared" si="20"/>
+        <v>107287</v>
+      </c>
+      <c r="BD32" s="5">
+        <v>252026</v>
+      </c>
+      <c r="BE32" s="4">
+        <f t="shared" si="21"/>
+        <v>0.98597863933335939</v>
+      </c>
+      <c r="BF32" s="5">
+        <v>535637</v>
+      </c>
+      <c r="BG32" s="5">
+        <v>253853</v>
+      </c>
+      <c r="BH32" s="3">
+        <f t="shared" si="22"/>
+        <v>260934</v>
+      </c>
+      <c r="BI32" s="5">
+        <v>514787</v>
+      </c>
+      <c r="BJ32" s="4">
+        <f t="shared" si="23"/>
+        <v>0.96107438433117953</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>24</v>
       </c>
@@ -5305,14 +6133,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112473</v>
+        <v>112636</v>
       </c>
       <c r="F33" s="5">
-        <v>716841</v>
+        <v>717004</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>1.0014641104341617</v>
+        <v>1.001691829900544</v>
       </c>
       <c r="H33" s="5">
         <v>726544</v>
@@ -5322,14 +6150,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>106021</v>
+        <v>106241</v>
       </c>
       <c r="K33" s="5">
-        <v>729140</v>
+        <v>729360</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>1.0035730802263869</v>
+        <v>1.0038758836354027</v>
       </c>
       <c r="M33" s="5">
         <v>1152516</v>
@@ -5339,14 +6167,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>203003</v>
+        <v>203513</v>
       </c>
       <c r="P33" s="5">
-        <v>1155331</v>
+        <v>1155841</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0024424823603317</v>
+        <v>1.0028849924860046</v>
       </c>
       <c r="R33" s="5">
         <v>733468</v>
@@ -5356,14 +6184,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>104479</v>
+        <v>104949</v>
       </c>
       <c r="U33" s="5">
-        <v>735766</v>
+        <v>736236</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0031330610197036</v>
+        <v>1.0037738524380069</v>
       </c>
       <c r="W33" s="5">
         <v>745690</v>
@@ -5373,14 +6201,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>104350</v>
+        <v>105060</v>
       </c>
       <c r="Z33" s="5">
-        <v>745307</v>
+        <v>746017</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.9994863817404015</v>
+        <v>1.00043852002843</v>
       </c>
       <c r="AB33" s="5">
         <v>1180887</v>
@@ -5390,14 +6218,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>207075</v>
+        <v>209106</v>
       </c>
       <c r="AE33" s="5">
-        <v>1180147</v>
+        <v>1182178</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>0.99937335240374392</v>
+        <v>1.001093246009144</v>
       </c>
       <c r="AG33" s="5">
         <v>749948</v>
@@ -5407,14 +6235,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>108584</v>
+        <v>110625</v>
       </c>
       <c r="AJ33" s="5">
-        <v>748439</v>
+        <v>750480</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>0.99798786049166077</v>
+        <v>1.0007093825171878</v>
       </c>
       <c r="AL33" s="5">
         <v>765123</v>
@@ -5424,14 +6252,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>106743</v>
+        <v>110293</v>
       </c>
       <c r="AO33" s="5">
-        <v>769606</v>
+        <v>773156</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>1.0058591886533277</v>
+        <v>1.0104989655258043</v>
       </c>
       <c r="AQ33" s="5">
         <v>1217820</v>
@@ -5441,14 +6269,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>202895</v>
+        <v>214754</v>
       </c>
       <c r="AT33" s="5">
-        <v>1211925</v>
+        <v>1223784</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>0.99515938316007291</v>
+        <v>1.0048972754594274</v>
       </c>
       <c r="AV33" s="5">
         <v>779865</v>
@@ -5458,17 +6286,51 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>54183</v>
+        <v>70467</v>
       </c>
       <c r="AY33" s="5">
-        <v>766712</v>
+        <v>782996</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>0.98313426041686702</v>
+        <v>1.004014797432889</v>
+      </c>
+      <c r="BA33" s="5">
+        <v>794982</v>
+      </c>
+      <c r="BB33" s="5">
+        <v>691836</v>
+      </c>
+      <c r="BC33" s="3">
+        <f t="shared" si="20"/>
+        <v>104952</v>
+      </c>
+      <c r="BD33" s="5">
+        <v>796788</v>
+      </c>
+      <c r="BE33" s="4">
+        <f t="shared" si="21"/>
+        <v>1.0022717495490463</v>
+      </c>
+      <c r="BF33" s="5">
+        <v>1258934</v>
+      </c>
+      <c r="BG33" s="5">
+        <v>1029526</v>
+      </c>
+      <c r="BH33" s="3">
+        <f t="shared" si="22"/>
+        <v>216663</v>
+      </c>
+      <c r="BI33" s="5">
+        <v>1246189</v>
+      </c>
+      <c r="BJ33" s="4">
+        <f t="shared" si="23"/>
+        <v>0.98987635571046617</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>25</v>
       </c>
@@ -5625,8 +6487,38 @@
       <c r="AZ34" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="BA34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BB34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BC34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="BD34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="BF34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BG34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BH34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="BI34" s="5">
+        <v>0</v>
+      </c>
+      <c r="BJ34" s="5" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>26</v>
       </c>
@@ -5640,15 +6532,15 @@
         <v>9903</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" ref="E35:E47" si="20">F35-D35</f>
-        <v>2329</v>
+        <f t="shared" ref="E35:E47" si="24">F35-D35</f>
+        <v>2335</v>
       </c>
       <c r="F35" s="5">
-        <v>12232</v>
+        <v>12238</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" ref="G35:G48" si="21">F35/C35</f>
-        <v>0.9978789362049274</v>
+        <f t="shared" ref="G35:G48" si="25">F35/C35</f>
+        <v>0.99836841246532881</v>
       </c>
       <c r="H35" s="5">
         <v>12343</v>
@@ -5657,15 +6549,15 @@
         <v>10077</v>
       </c>
       <c r="J35" s="3">
-        <f t="shared" ref="J35:J47" si="22">K35-I35</f>
-        <v>2241</v>
+        <f t="shared" ref="J35:J47" si="26">K35-I35</f>
+        <v>2248</v>
       </c>
       <c r="K35" s="5">
-        <v>12318</v>
+        <v>12325</v>
       </c>
       <c r="L35" s="4">
-        <f t="shared" ref="L35:L48" si="23">K35/H35</f>
-        <v>0.99797456047962407</v>
+        <f t="shared" ref="L35:L48" si="27">K35/H35</f>
+        <v>0.99854168354532935</v>
       </c>
       <c r="M35" s="5">
         <v>15097</v>
@@ -5674,15 +6566,15 @@
         <v>12241</v>
       </c>
       <c r="O35" s="3">
-        <f t="shared" ref="O35:O47" si="24">P35-N35</f>
-        <v>2821</v>
+        <f t="shared" ref="O35:O47" si="28">P35-N35</f>
+        <v>2836</v>
       </c>
       <c r="P35" s="5">
-        <v>15062</v>
+        <v>15077</v>
       </c>
       <c r="Q35" s="4">
-        <f t="shared" ref="Q35:Q48" si="25">P35/M35</f>
-        <v>0.99768165860767044</v>
+        <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
+        <v>0.99867523349009735</v>
       </c>
       <c r="R35" s="5">
         <v>12455</v>
@@ -5691,15 +6583,15 @@
         <v>10307</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" ref="T35:T47" si="26">U35-S35</f>
-        <v>2082</v>
+        <f t="shared" ref="T35:T47" si="30">U35-S35</f>
+        <v>2100</v>
       </c>
       <c r="U35" s="5">
-        <v>12389</v>
+        <v>12407</v>
       </c>
       <c r="V35" s="4">
-        <f t="shared" ref="V35:V48" si="27">U35/R35</f>
-        <v>0.99470092332396631</v>
+        <f t="shared" ref="V35:V48" si="31">U35/R35</f>
+        <v>0.99614612605379371</v>
       </c>
       <c r="W35" s="5">
         <v>12547</v>
@@ -5708,15 +6600,15 @@
         <v>10490</v>
       </c>
       <c r="Y35" s="3">
-        <f t="shared" ref="Y35:Y47" si="28">Z35-X35</f>
-        <v>1916</v>
+        <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
+        <v>1946</v>
       </c>
       <c r="Z35" s="5">
-        <v>12406</v>
+        <v>12436</v>
       </c>
       <c r="AA35" s="4">
-        <f t="shared" ref="AA35:AA48" si="29">Z35/W35</f>
-        <v>0.98876225392524109</v>
+        <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
+        <v>0.99115326372838131</v>
       </c>
       <c r="AB35" s="5">
         <v>15257</v>
@@ -5725,15 +6617,15 @@
         <v>12367</v>
       </c>
       <c r="AD35" s="3">
-        <f t="shared" ref="AD35:AD47" si="30">AE35-AC35</f>
-        <v>2756</v>
+        <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
+        <v>2822</v>
       </c>
       <c r="AE35" s="5">
-        <v>15123</v>
+        <v>15189</v>
       </c>
       <c r="AF35" s="4">
-        <f t="shared" ref="AF35:AF48" si="31">AE35/AB35</f>
-        <v>0.99121714622796098</v>
+        <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
+        <v>0.99554302942911455</v>
       </c>
       <c r="AG35" s="5">
         <v>12574</v>
@@ -5742,15 +6634,15 @@
         <v>10313</v>
       </c>
       <c r="AI35" s="3">
-        <f t="shared" ref="AI35:AI47" si="32">AJ35-AH35</f>
-        <v>2104</v>
+        <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
+        <v>2202</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12417</v>
+        <v>12515</v>
       </c>
       <c r="AK35" s="4">
-        <f t="shared" ref="AK35:AK48" si="33">AJ35/AG35</f>
-        <v>0.98751391760776208</v>
+        <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
+        <v>0.99530777795450931</v>
       </c>
       <c r="AL35" s="5">
         <v>12702</v>
@@ -5759,15 +6651,15 @@
         <v>10540</v>
       </c>
       <c r="AN35" s="3">
-        <f t="shared" ref="AN35:AN47" si="34">AO35-AM35</f>
-        <v>1906</v>
+        <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
+        <v>2056</v>
       </c>
       <c r="AO35" s="5">
-        <v>12446</v>
+        <v>12596</v>
       </c>
       <c r="AP35" s="4">
-        <f t="shared" ref="AP35:AP48" si="35">AO35/AL35</f>
-        <v>0.97984569359156037</v>
+        <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
+        <v>0.9916548575027555</v>
       </c>
       <c r="AQ35" s="5">
         <v>15458</v>
@@ -5776,15 +6668,15 @@
         <v>12572</v>
       </c>
       <c r="AS35" s="3">
-        <f t="shared" ref="AS35:AS47" si="36">AT35-AR35</f>
-        <v>2457</v>
+        <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
+        <v>2780</v>
       </c>
       <c r="AT35" s="5">
-        <v>15029</v>
+        <v>15352</v>
       </c>
       <c r="AU35" s="4">
-        <f t="shared" ref="AU35:AU48" si="37">AT35/AQ35</f>
-        <v>0.9722473799974124</v>
+        <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
+        <v>0.99314270927674986</v>
       </c>
       <c r="AV35" s="5">
         <v>12806</v>
@@ -5793,18 +6685,52 @@
         <v>10688</v>
       </c>
       <c r="AX35" s="3">
-        <f t="shared" ref="AX35:AX47" si="38">AY35-AW35</f>
-        <v>1455</v>
+        <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
+        <v>1930</v>
       </c>
       <c r="AY35" s="5">
-        <v>12143</v>
+        <v>12618</v>
       </c>
       <c r="AZ35" s="4">
-        <f t="shared" ref="AZ35:AZ48" si="39">AY35/AV35</f>
-        <v>0.94822739340933937</v>
+        <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
+        <v>0.98531938153990317</v>
+      </c>
+      <c r="BA35" s="5">
+        <v>12915</v>
+      </c>
+      <c r="BB35" s="5">
+        <v>10865</v>
+      </c>
+      <c r="BC35" s="3">
+        <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
+        <v>1745</v>
+      </c>
+      <c r="BD35" s="5">
+        <v>12610</v>
+      </c>
+      <c r="BE35" s="4">
+        <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
+        <v>0.97638404955478131</v>
+      </c>
+      <c r="BF35" s="5">
+        <v>15661</v>
+      </c>
+      <c r="BG35" s="5">
+        <v>12804</v>
+      </c>
+      <c r="BH35" s="3">
+        <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
+        <v>2348</v>
+      </c>
+      <c r="BI35" s="5">
+        <v>15152</v>
+      </c>
+      <c r="BJ35" s="4">
+        <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
+        <v>0.96749888257454819</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>27</v>
       </c>
@@ -5818,15 +6744,15 @@
         <v>675983</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="20"/>
-        <v>277640</v>
+        <f t="shared" si="24"/>
+        <v>278417</v>
       </c>
       <c r="F36" s="5">
-        <v>953623</v>
+        <v>954400</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" si="21"/>
-        <v>1.0008532656038456</v>
+        <f t="shared" si="25"/>
+        <v>1.0016687482289228</v>
       </c>
       <c r="H36" s="5">
         <v>975466</v>
@@ -5835,15 +6761,15 @@
         <v>699378</v>
       </c>
       <c r="J36" s="3">
-        <f t="shared" si="22"/>
-        <v>270329</v>
+        <f t="shared" si="26"/>
+        <v>271356</v>
       </c>
       <c r="K36" s="5">
-        <v>969707</v>
+        <v>970734</v>
       </c>
       <c r="L36" s="4">
-        <f t="shared" si="23"/>
-        <v>0.99409615506844928</v>
+        <f t="shared" si="27"/>
+        <v>0.99514898520296968</v>
       </c>
       <c r="M36" s="5">
         <v>1668278</v>
@@ -5852,15 +6778,15 @@
         <v>1135913</v>
       </c>
       <c r="O36" s="3">
-        <f t="shared" si="24"/>
-        <v>532091</v>
+        <f t="shared" si="28"/>
+        <v>534783</v>
       </c>
       <c r="P36" s="5">
-        <v>1668004</v>
+        <v>1670696</v>
       </c>
       <c r="Q36" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99983575878840336</v>
+        <f t="shared" si="29"/>
+        <v>1.0014493987213162</v>
       </c>
       <c r="R36" s="5">
         <v>976879</v>
@@ -5869,15 +6795,15 @@
         <v>714456</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" si="26"/>
-        <v>259385</v>
+        <f t="shared" si="30"/>
+        <v>261343</v>
       </c>
       <c r="U36" s="5">
-        <v>973841</v>
+        <v>975799</v>
       </c>
       <c r="V36" s="4">
-        <f t="shared" si="27"/>
-        <v>0.99689009590747679</v>
+        <f t="shared" si="31"/>
+        <v>0.99889443830812208</v>
       </c>
       <c r="W36" s="5">
         <v>1000117</v>
@@ -5886,15 +6812,15 @@
         <v>724393</v>
       </c>
       <c r="Y36" s="3">
-        <f t="shared" si="28"/>
-        <v>260723</v>
+        <f t="shared" si="32"/>
+        <v>263820</v>
       </c>
       <c r="Z36" s="5">
-        <v>985116</v>
+        <v>988213</v>
       </c>
       <c r="AA36" s="4">
-        <f t="shared" si="29"/>
-        <v>0.98500075491167538</v>
+        <f t="shared" si="33"/>
+        <v>0.98809739260506524</v>
       </c>
       <c r="AB36" s="5">
         <v>1701420</v>
@@ -5903,15 +6829,15 @@
         <v>1145984</v>
       </c>
       <c r="AD36" s="3">
-        <f t="shared" si="30"/>
-        <v>543050</v>
+        <f t="shared" si="34"/>
+        <v>553021</v>
       </c>
       <c r="AE36" s="5">
-        <v>1689034</v>
+        <v>1699005</v>
       </c>
       <c r="AF36" s="4">
-        <f t="shared" si="31"/>
-        <v>0.99272019842249415</v>
+        <f t="shared" si="35"/>
+        <v>0.99858059738336213</v>
       </c>
       <c r="AG36" s="5">
         <v>996655</v>
@@ -5920,15 +6846,15 @@
         <v>722237</v>
       </c>
       <c r="AI36" s="3">
-        <f t="shared" si="32"/>
-        <v>263765</v>
+        <f t="shared" si="36"/>
+        <v>272563</v>
       </c>
       <c r="AJ36" s="5">
-        <v>986002</v>
+        <v>994800</v>
       </c>
       <c r="AK36" s="4">
-        <f t="shared" si="33"/>
-        <v>0.9893112461182656</v>
+        <f t="shared" si="37"/>
+        <v>0.99813877419969799</v>
       </c>
       <c r="AL36" s="5">
         <v>1027093</v>
@@ -5937,15 +6863,15 @@
         <v>758486</v>
       </c>
       <c r="AN36" s="3">
-        <f t="shared" si="34"/>
-        <v>257462</v>
+        <f t="shared" si="38"/>
+        <v>271687</v>
       </c>
       <c r="AO36" s="5">
-        <v>1015948</v>
+        <v>1030173</v>
       </c>
       <c r="AP36" s="4">
-        <f t="shared" si="35"/>
-        <v>0.98914898650852456</v>
+        <f t="shared" si="39"/>
+        <v>1.0029987547378865</v>
       </c>
       <c r="AQ36" s="5">
         <v>1750886</v>
@@ -5954,15 +6880,15 @@
         <v>1205471</v>
       </c>
       <c r="AS36" s="3">
-        <f t="shared" si="36"/>
-        <v>509568</v>
+        <f t="shared" si="40"/>
+        <v>554554</v>
       </c>
       <c r="AT36" s="5">
-        <v>1715039</v>
+        <v>1760025</v>
       </c>
       <c r="AU36" s="4">
-        <f t="shared" si="37"/>
-        <v>0.97952636550866246</v>
+        <f t="shared" si="41"/>
+        <v>1.0052196430835589</v>
       </c>
       <c r="AV36" s="5">
         <v>1041088</v>
@@ -5971,18 +6897,52 @@
         <v>882000</v>
       </c>
       <c r="AX36" s="3">
-        <f t="shared" si="38"/>
-        <v>109400</v>
+        <f t="shared" si="42"/>
+        <v>161139</v>
       </c>
       <c r="AY36" s="5">
-        <v>991400</v>
+        <v>1043139</v>
       </c>
       <c r="AZ36" s="4">
-        <f t="shared" si="39"/>
-        <v>0.95227300670068238</v>
+        <f t="shared" si="43"/>
+        <v>1.0019700544046228</v>
+      </c>
+      <c r="BA36" s="5">
+        <v>1070068</v>
+      </c>
+      <c r="BB36" s="5">
+        <v>799970</v>
+      </c>
+      <c r="BC36" s="3">
+        <f t="shared" si="44"/>
+        <v>261183</v>
+      </c>
+      <c r="BD36" s="5">
+        <v>1061153</v>
+      </c>
+      <c r="BE36" s="4">
+        <f t="shared" si="45"/>
+        <v>0.99166875376144314</v>
+      </c>
+      <c r="BF36" s="5">
+        <v>1814069</v>
+      </c>
+      <c r="BG36" s="5">
+        <v>1251362</v>
+      </c>
+      <c r="BH36" s="3">
+        <f t="shared" si="46"/>
+        <v>502164</v>
+      </c>
+      <c r="BI36" s="5">
+        <v>1753526</v>
+      </c>
+      <c r="BJ36" s="4">
+        <f t="shared" si="47"/>
+        <v>0.96662585601760465</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>29</v>
       </c>
@@ -5996,15 +6956,15 @@
         <v>425480</v>
       </c>
       <c r="E37" s="3">
-        <f t="shared" si="20"/>
-        <v>308030</v>
+        <f t="shared" si="24"/>
+        <v>308901</v>
       </c>
       <c r="F37" s="5">
-        <v>733510</v>
+        <v>734381</v>
       </c>
       <c r="G37" s="4">
-        <f t="shared" si="21"/>
-        <v>0.98926723742629485</v>
+        <f t="shared" si="25"/>
+        <v>0.99044193410909165</v>
       </c>
       <c r="H37" s="5">
         <v>747767</v>
@@ -6013,15 +6973,15 @@
         <v>434995</v>
       </c>
       <c r="J37" s="3">
-        <f t="shared" si="22"/>
-        <v>303344</v>
+        <f t="shared" si="26"/>
+        <v>304444</v>
       </c>
       <c r="K37" s="5">
-        <v>738339</v>
+        <v>739439</v>
       </c>
       <c r="L37" s="4">
-        <f t="shared" si="23"/>
-        <v>0.9873917945028331</v>
+        <f t="shared" si="27"/>
+        <v>0.98886284096516697</v>
       </c>
       <c r="M37" s="5">
         <v>922163</v>
@@ -6030,15 +6990,15 @@
         <v>540960</v>
       </c>
       <c r="O37" s="3">
-        <f t="shared" si="24"/>
-        <v>372443</v>
+        <f t="shared" si="28"/>
+        <v>374273</v>
       </c>
       <c r="P37" s="5">
-        <v>913403</v>
+        <v>915233</v>
       </c>
       <c r="Q37" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99050059479723218</v>
+        <f t="shared" si="29"/>
+        <v>0.99248505958274191</v>
       </c>
       <c r="R37" s="5">
         <v>751356</v>
@@ -6047,15 +7007,15 @@
         <v>452020</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" si="26"/>
-        <v>290075</v>
+        <f t="shared" si="30"/>
+        <v>292145</v>
       </c>
       <c r="U37" s="5">
-        <v>742095</v>
+        <v>744165</v>
       </c>
       <c r="V37" s="4">
-        <f t="shared" si="27"/>
-        <v>0.98767428489291365</v>
+        <f t="shared" si="31"/>
+        <v>0.99042930381869576</v>
       </c>
       <c r="W37" s="5">
         <v>760191</v>
@@ -6064,15 +7024,15 @@
         <v>465684</v>
       </c>
       <c r="Y37" s="3">
-        <f t="shared" si="28"/>
-        <v>281039</v>
+        <f t="shared" si="32"/>
+        <v>284173</v>
       </c>
       <c r="Z37" s="5">
-        <v>746723</v>
+        <v>749857</v>
       </c>
       <c r="AA37" s="4">
-        <f t="shared" si="29"/>
-        <v>0.98228339982977964</v>
+        <f t="shared" si="33"/>
+        <v>0.98640604795373799</v>
       </c>
       <c r="AB37" s="5">
         <v>938023</v>
@@ -6081,15 +7041,15 @@
         <v>537499</v>
       </c>
       <c r="AD37" s="3">
-        <f t="shared" si="30"/>
-        <v>384906</v>
+        <f t="shared" si="34"/>
+        <v>391307</v>
       </c>
       <c r="AE37" s="5">
-        <v>922405</v>
+        <v>928806</v>
       </c>
       <c r="AF37" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98335008843066751</v>
+        <f t="shared" si="35"/>
+        <v>0.99017401492287505</v>
       </c>
       <c r="AG37" s="5">
         <v>763648</v>
@@ -6098,15 +7058,15 @@
         <v>456424</v>
       </c>
       <c r="AI37" s="3">
-        <f t="shared" si="32"/>
-        <v>290479</v>
+        <f t="shared" si="36"/>
+        <v>298242</v>
       </c>
       <c r="AJ37" s="5">
-        <v>746903</v>
+        <v>754666</v>
       </c>
       <c r="AK37" s="4">
-        <f t="shared" si="33"/>
-        <v>0.97807235794502179</v>
+        <f t="shared" si="37"/>
+        <v>0.98823803637277907</v>
       </c>
       <c r="AL37" s="5">
         <v>773685</v>
@@ -6115,15 +7075,15 @@
         <v>479460</v>
       </c>
       <c r="AN37" s="3">
-        <f t="shared" si="34"/>
-        <v>275884</v>
+        <f t="shared" si="38"/>
+        <v>287509</v>
       </c>
       <c r="AO37" s="5">
-        <v>755344</v>
+        <v>766969</v>
       </c>
       <c r="AP37" s="4">
-        <f t="shared" si="35"/>
-        <v>0.97629396976805805</v>
+        <f t="shared" si="39"/>
+        <v>0.99131946464000209</v>
       </c>
       <c r="AQ37" s="5">
         <v>957323</v>
@@ -6132,15 +7092,15 @@
         <v>562263</v>
       </c>
       <c r="AS37" s="3">
-        <f t="shared" si="36"/>
-        <v>361322</v>
+        <f t="shared" si="40"/>
+        <v>384986</v>
       </c>
       <c r="AT37" s="5">
-        <v>923585</v>
+        <v>947249</v>
       </c>
       <c r="AU37" s="4">
-        <f t="shared" si="37"/>
-        <v>0.96475797614807124</v>
+        <f t="shared" si="41"/>
+        <v>0.98947690591367798</v>
       </c>
       <c r="AV37" s="5">
         <v>783693</v>
@@ -6149,18 +7109,52 @@
         <v>650792</v>
       </c>
       <c r="AX37" s="3">
-        <f t="shared" si="38"/>
-        <v>81620</v>
+        <f t="shared" si="42"/>
+        <v>120406</v>
       </c>
       <c r="AY37" s="5">
-        <v>732412</v>
+        <v>771198</v>
       </c>
       <c r="AZ37" s="4">
-        <f t="shared" si="39"/>
-        <v>0.93456493805610108</v>
+        <f t="shared" si="43"/>
+        <v>0.98405625672297703</v>
+      </c>
+      <c r="BA37" s="5">
+        <v>794943</v>
+      </c>
+      <c r="BB37" s="5">
+        <v>501829</v>
+      </c>
+      <c r="BC37" s="3">
+        <f t="shared" si="44"/>
+        <v>271523</v>
+      </c>
+      <c r="BD37" s="5">
+        <v>773352</v>
+      </c>
+      <c r="BE37" s="4">
+        <f t="shared" si="45"/>
+        <v>0.97283956208180966</v>
+      </c>
+      <c r="BF37" s="5">
+        <v>980352</v>
+      </c>
+      <c r="BG37" s="5">
+        <v>575117</v>
+      </c>
+      <c r="BH37" s="3">
+        <f t="shared" si="46"/>
+        <v>357931</v>
+      </c>
+      <c r="BI37" s="5">
+        <v>933048</v>
+      </c>
+      <c r="BJ37" s="4">
+        <f t="shared" si="47"/>
+        <v>0.95174794359576964</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>30</v>
       </c>
@@ -6174,15 +7168,15 @@
         <v>16171</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="20"/>
-        <v>9952</v>
+        <f t="shared" si="24"/>
+        <v>10003</v>
       </c>
       <c r="F38" s="5">
-        <v>26123</v>
+        <v>26174</v>
       </c>
       <c r="G38" s="4">
-        <f t="shared" si="21"/>
-        <v>1.0023405724810068</v>
+        <f t="shared" si="25"/>
+        <v>1.0042974445552912</v>
       </c>
       <c r="H38" s="5">
         <v>26657</v>
@@ -6191,15 +7185,15 @@
         <v>16797</v>
       </c>
       <c r="J38" s="3">
-        <f t="shared" si="22"/>
-        <v>9598</v>
+        <f t="shared" si="26"/>
+        <v>9668</v>
       </c>
       <c r="K38" s="5">
-        <v>26395</v>
+        <v>26465</v>
       </c>
       <c r="L38" s="4">
-        <f t="shared" si="23"/>
-        <v>0.99017143714596545</v>
+        <f t="shared" si="27"/>
+        <v>0.99279738905353188</v>
       </c>
       <c r="M38" s="5">
         <v>40003</v>
@@ -6208,15 +7202,15 @@
         <v>25476</v>
       </c>
       <c r="O38" s="3">
-        <f t="shared" si="24"/>
-        <v>14445</v>
+        <f t="shared" si="28"/>
+        <v>14576</v>
       </c>
       <c r="P38" s="5">
-        <v>39921</v>
+        <v>40052</v>
       </c>
       <c r="Q38" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99795015373846963</v>
+        <f t="shared" si="29"/>
+        <v>1.00122490813189</v>
       </c>
       <c r="R38" s="5">
         <v>26603</v>
@@ -6225,15 +7219,15 @@
         <v>17468</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" si="26"/>
-        <v>8994</v>
+        <f t="shared" si="30"/>
+        <v>9116</v>
       </c>
       <c r="U38" s="5">
-        <v>26462</v>
+        <v>26584</v>
       </c>
       <c r="V38" s="4">
-        <f t="shared" si="27"/>
-        <v>0.99469984588204341</v>
+        <f t="shared" si="31"/>
+        <v>0.99928579483516899</v>
       </c>
       <c r="W38" s="5">
         <v>27177</v>
@@ -6242,15 +7236,15 @@
         <v>17793</v>
       </c>
       <c r="Y38" s="3">
-        <f t="shared" si="28"/>
-        <v>8838</v>
+        <f t="shared" si="32"/>
+        <v>9025</v>
       </c>
       <c r="Z38" s="5">
-        <v>26631</v>
+        <v>26818</v>
       </c>
       <c r="AA38" s="4">
-        <f t="shared" si="29"/>
-        <v>0.97990948228281272</v>
+        <f t="shared" si="33"/>
+        <v>0.98679030062184936</v>
       </c>
       <c r="AB38" s="5">
         <v>40627</v>
@@ -6259,15 +7253,15 @@
         <v>25513</v>
       </c>
       <c r="AD38" s="3">
-        <f t="shared" si="30"/>
-        <v>14616</v>
+        <f t="shared" si="34"/>
+        <v>15084</v>
       </c>
       <c r="AE38" s="5">
-        <v>40129</v>
+        <v>40597</v>
       </c>
       <c r="AF38" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98774214192532062</v>
+        <f t="shared" si="35"/>
+        <v>0.9992615748147784</v>
       </c>
       <c r="AG38" s="5">
         <v>26952</v>
@@ -6276,15 +7270,15 @@
         <v>17546</v>
       </c>
       <c r="AI38" s="3">
-        <f t="shared" si="32"/>
-        <v>8845</v>
+        <f t="shared" si="36"/>
+        <v>9368</v>
       </c>
       <c r="AJ38" s="5">
-        <v>26391</v>
+        <v>26914</v>
       </c>
       <c r="AK38" s="4">
-        <f t="shared" si="33"/>
-        <v>0.97918521816562776</v>
+        <f t="shared" si="37"/>
+        <v>0.99859008607895516</v>
       </c>
       <c r="AL38" s="5">
         <v>27600</v>
@@ -6293,15 +7287,15 @@
         <v>18488</v>
       </c>
       <c r="AN38" s="3">
-        <f t="shared" si="34"/>
-        <v>8138</v>
+        <f t="shared" si="38"/>
+        <v>8889</v>
       </c>
       <c r="AO38" s="5">
-        <v>26626</v>
+        <v>27377</v>
       </c>
       <c r="AP38" s="4">
-        <f t="shared" si="35"/>
-        <v>0.96471014492753626</v>
+        <f t="shared" si="39"/>
+        <v>0.99192028985507241</v>
       </c>
       <c r="AQ38" s="5">
         <v>41434</v>
@@ -6310,15 +7304,15 @@
         <v>26424</v>
       </c>
       <c r="AS38" s="3">
-        <f t="shared" si="36"/>
-        <v>13204</v>
+        <f t="shared" si="40"/>
+        <v>14866</v>
       </c>
       <c r="AT38" s="5">
-        <v>39628</v>
+        <v>41290</v>
       </c>
       <c r="AU38" s="4">
-        <f t="shared" si="37"/>
-        <v>0.95641260800308925</v>
+        <f t="shared" si="41"/>
+        <v>0.99652459332915</v>
       </c>
       <c r="AV38" s="5">
         <v>27593</v>
@@ -6327,18 +7321,52 @@
         <v>22356</v>
       </c>
       <c r="AX38" s="3">
-        <f t="shared" si="38"/>
-        <v>2899</v>
+        <f t="shared" si="42"/>
+        <v>4901</v>
       </c>
       <c r="AY38" s="5">
-        <v>25255</v>
+        <v>27257</v>
       </c>
       <c r="AZ38" s="4">
-        <f t="shared" si="39"/>
-        <v>0.91526836516507815</v>
+        <f t="shared" si="43"/>
+        <v>0.98782299858659806</v>
+      </c>
+      <c r="BA38" s="5">
+        <v>28279</v>
+      </c>
+      <c r="BB38" s="5">
+        <v>19302</v>
+      </c>
+      <c r="BC38" s="3">
+        <f t="shared" si="44"/>
+        <v>7955</v>
+      </c>
+      <c r="BD38" s="5">
+        <v>27257</v>
+      </c>
+      <c r="BE38" s="4">
+        <f t="shared" si="45"/>
+        <v>0.96386010820750379</v>
+      </c>
+      <c r="BF38" s="5">
+        <v>42642</v>
+      </c>
+      <c r="BG38" s="5">
+        <v>26999</v>
+      </c>
+      <c r="BH38" s="3">
+        <f t="shared" si="46"/>
+        <v>12842</v>
+      </c>
+      <c r="BI38" s="5">
+        <v>39841</v>
+      </c>
+      <c r="BJ38" s="4">
+        <f t="shared" si="47"/>
+        <v>0.93431358754279814</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>31</v>
       </c>
@@ -6352,15 +7380,15 @@
         <v>135</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="20"/>
-        <v>120</v>
+        <f t="shared" si="24"/>
+        <v>122</v>
       </c>
       <c r="F39" s="5">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G39" s="4">
-        <f t="shared" si="21"/>
-        <v>0.99609375</v>
+        <f t="shared" si="25"/>
+        <v>1.00390625</v>
       </c>
       <c r="H39" s="5">
         <v>262</v>
@@ -6369,15 +7397,15 @@
         <v>129</v>
       </c>
       <c r="J39" s="3">
-        <f t="shared" si="22"/>
-        <v>127</v>
+        <f t="shared" si="26"/>
+        <v>129</v>
       </c>
       <c r="K39" s="5">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L39" s="4">
-        <f t="shared" si="23"/>
-        <v>0.97709923664122134</v>
+        <f t="shared" si="27"/>
+        <v>0.98473282442748089</v>
       </c>
       <c r="M39" s="5">
         <v>313</v>
@@ -6386,15 +7414,15 @@
         <v>163</v>
       </c>
       <c r="O39" s="3">
-        <f t="shared" si="24"/>
-        <v>145</v>
+        <f t="shared" si="28"/>
+        <v>147</v>
       </c>
       <c r="P39" s="5">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q39" s="4">
-        <f t="shared" si="25"/>
-        <v>0.98402555910543132</v>
+        <f t="shared" si="29"/>
+        <v>0.99041533546325877</v>
       </c>
       <c r="R39" s="5">
         <v>264</v>
@@ -6403,15 +7431,15 @@
         <v>139</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" si="26"/>
-        <v>113</v>
+        <f t="shared" si="30"/>
+        <v>114</v>
       </c>
       <c r="U39" s="5">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="V39" s="4">
-        <f t="shared" si="27"/>
-        <v>0.95454545454545459</v>
+        <f t="shared" si="31"/>
+        <v>0.95833333333333337</v>
       </c>
       <c r="W39" s="5">
         <v>265</v>
@@ -6420,15 +7448,15 @@
         <v>135</v>
       </c>
       <c r="Y39" s="3">
-        <f t="shared" si="28"/>
-        <v>116</v>
+        <f t="shared" si="32"/>
+        <v>119</v>
       </c>
       <c r="Z39" s="5">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AA39" s="4">
-        <f t="shared" si="29"/>
-        <v>0.94716981132075473</v>
+        <f t="shared" si="33"/>
+        <v>0.95849056603773586</v>
       </c>
       <c r="AB39" s="5">
         <v>322</v>
@@ -6437,15 +7465,15 @@
         <v>174</v>
       </c>
       <c r="AD39" s="3">
-        <f t="shared" si="30"/>
-        <v>129</v>
+        <f t="shared" si="34"/>
+        <v>138</v>
       </c>
       <c r="AE39" s="5">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="AF39" s="4">
-        <f t="shared" si="31"/>
-        <v>0.94099378881987583</v>
+        <f t="shared" si="35"/>
+        <v>0.96894409937888204</v>
       </c>
       <c r="AG39" s="5">
         <v>267</v>
@@ -6454,15 +7482,15 @@
         <v>138</v>
       </c>
       <c r="AI39" s="3">
-        <f t="shared" si="32"/>
-        <v>105</v>
+        <f t="shared" si="36"/>
+        <v>114</v>
       </c>
       <c r="AJ39" s="5">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="AK39" s="4">
-        <f t="shared" si="33"/>
-        <v>0.9101123595505618</v>
+        <f t="shared" si="37"/>
+        <v>0.9438202247191011</v>
       </c>
       <c r="AL39" s="5">
         <v>276</v>
@@ -6471,15 +7499,15 @@
         <v>141</v>
       </c>
       <c r="AN39" s="3">
-        <f t="shared" si="34"/>
-        <v>108</v>
+        <f t="shared" si="38"/>
+        <v>119</v>
       </c>
       <c r="AO39" s="5">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="AP39" s="4">
-        <f t="shared" si="35"/>
-        <v>0.90217391304347827</v>
+        <f t="shared" si="39"/>
+        <v>0.94202898550724634</v>
       </c>
       <c r="AQ39" s="5">
         <v>338</v>
@@ -6488,15 +7516,15 @@
         <v>162</v>
       </c>
       <c r="AS39" s="3">
-        <f t="shared" si="36"/>
-        <v>142</v>
+        <f t="shared" si="40"/>
+        <v>157</v>
       </c>
       <c r="AT39" s="5">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="AU39" s="4">
-        <f t="shared" si="37"/>
-        <v>0.89940828402366868</v>
+        <f t="shared" si="41"/>
+        <v>0.94378698224852076</v>
       </c>
       <c r="AV39" s="5">
         <v>279</v>
@@ -6505,18 +7533,52 @@
         <v>216</v>
       </c>
       <c r="AX39" s="3">
-        <f t="shared" si="38"/>
-        <v>26</v>
+        <f t="shared" si="42"/>
+        <v>48</v>
       </c>
       <c r="AY39" s="5">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="AZ39" s="4">
-        <f t="shared" si="39"/>
-        <v>0.86738351254480284</v>
+        <f t="shared" si="43"/>
+        <v>0.94623655913978499</v>
+      </c>
+      <c r="BA39" s="5">
+        <v>291</v>
+      </c>
+      <c r="BB39" s="5">
+        <v>160</v>
+      </c>
+      <c r="BC39" s="3">
+        <f t="shared" si="44"/>
+        <v>106</v>
+      </c>
+      <c r="BD39" s="5">
+        <v>266</v>
+      </c>
+      <c r="BE39" s="4">
+        <f t="shared" si="45"/>
+        <v>0.91408934707903777</v>
+      </c>
+      <c r="BF39" s="5">
+        <v>344</v>
+      </c>
+      <c r="BG39" s="5">
+        <v>174</v>
+      </c>
+      <c r="BH39" s="3">
+        <f t="shared" si="46"/>
+        <v>146</v>
+      </c>
+      <c r="BI39" s="5">
+        <v>320</v>
+      </c>
+      <c r="BJ39" s="4">
+        <f t="shared" si="47"/>
+        <v>0.93023255813953487</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>32</v>
       </c>
@@ -6530,15 +7592,15 @@
         <v>176660</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="20"/>
-        <v>124425</v>
+        <f t="shared" si="24"/>
+        <v>124820</v>
       </c>
       <c r="F40" s="5">
-        <v>301085</v>
+        <v>301480</v>
       </c>
       <c r="G40" s="4">
-        <f t="shared" si="21"/>
-        <v>0.99075664540925457</v>
+        <f t="shared" si="25"/>
+        <v>0.99205644073262389</v>
       </c>
       <c r="H40" s="5">
         <v>306465</v>
@@ -6547,15 +7609,15 @@
         <v>175573</v>
       </c>
       <c r="J40" s="3">
-        <f t="shared" si="22"/>
-        <v>126737</v>
+        <f t="shared" si="26"/>
+        <v>127255</v>
       </c>
       <c r="K40" s="5">
-        <v>302310</v>
+        <v>302828</v>
       </c>
       <c r="L40" s="4">
-        <f t="shared" si="23"/>
-        <v>0.98644217121041555</v>
+        <f t="shared" si="27"/>
+        <v>0.98813241316300393</v>
       </c>
       <c r="M40" s="5">
         <v>361770</v>
@@ -6564,15 +7626,15 @@
         <v>209513</v>
       </c>
       <c r="O40" s="3">
-        <f t="shared" si="24"/>
-        <v>148700</v>
+        <f t="shared" si="28"/>
+        <v>149525</v>
       </c>
       <c r="P40" s="5">
-        <v>358213</v>
+        <v>359038</v>
       </c>
       <c r="Q40" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99016778616247891</v>
+        <f t="shared" si="29"/>
+        <v>0.99244824059485304</v>
       </c>
       <c r="R40" s="5">
         <v>306479</v>
@@ -6581,15 +7643,15 @@
         <v>186713</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" si="26"/>
-        <v>116746</v>
+        <f t="shared" si="30"/>
+        <v>117769</v>
       </c>
       <c r="U40" s="5">
-        <v>303459</v>
+        <v>304482</v>
       </c>
       <c r="V40" s="4">
-        <f t="shared" si="27"/>
-        <v>0.99014614378146626</v>
+        <f t="shared" si="31"/>
+        <v>0.99348405600383716</v>
       </c>
       <c r="W40" s="5">
         <v>309858</v>
@@ -6598,15 +7660,15 @@
         <v>181989</v>
       </c>
       <c r="Y40" s="3">
-        <f t="shared" si="28"/>
-        <v>122378</v>
+        <f t="shared" si="32"/>
+        <v>123984</v>
       </c>
       <c r="Z40" s="5">
-        <v>304367</v>
+        <v>305973</v>
       </c>
       <c r="AA40" s="4">
-        <f t="shared" si="29"/>
-        <v>0.98227897940346864</v>
+        <f t="shared" si="33"/>
+        <v>0.98746199872199525</v>
       </c>
       <c r="AB40" s="5">
         <v>365821</v>
@@ -6615,15 +7677,15 @@
         <v>212688</v>
       </c>
       <c r="AD40" s="3">
-        <f t="shared" si="30"/>
-        <v>146563</v>
+        <f t="shared" si="34"/>
+        <v>149968</v>
       </c>
       <c r="AE40" s="5">
-        <v>359251</v>
+        <v>362656</v>
       </c>
       <c r="AF40" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98204039680608823</v>
+        <f t="shared" si="35"/>
+        <v>0.99134822768512465</v>
       </c>
       <c r="AG40" s="5">
         <v>311342</v>
@@ -6632,15 +7694,15 @@
         <v>185358</v>
       </c>
       <c r="AI40" s="3">
-        <f t="shared" si="32"/>
-        <v>118084</v>
+        <f t="shared" si="36"/>
+        <v>122739</v>
       </c>
       <c r="AJ40" s="5">
-        <v>303442</v>
+        <v>308097</v>
       </c>
       <c r="AK40" s="4">
-        <f t="shared" si="33"/>
-        <v>0.97462597400928885</v>
+        <f t="shared" si="37"/>
+        <v>0.98957737793166356</v>
       </c>
       <c r="AL40" s="5">
         <v>314792</v>
@@ -6649,15 +7711,15 @@
         <v>187878</v>
       </c>
       <c r="AN40" s="3">
-        <f t="shared" si="34"/>
-        <v>116735</v>
+        <f t="shared" si="38"/>
+        <v>123452</v>
       </c>
       <c r="AO40" s="5">
-        <v>304613</v>
+        <v>311330</v>
       </c>
       <c r="AP40" s="4">
-        <f t="shared" si="35"/>
-        <v>0.96766436249968235</v>
+        <f t="shared" si="39"/>
+        <v>0.98900226181097362</v>
       </c>
       <c r="AQ40" s="5">
         <v>372144</v>
@@ -6666,15 +7728,15 @@
         <v>212701</v>
       </c>
       <c r="AS40" s="3">
-        <f t="shared" si="36"/>
-        <v>142999</v>
+        <f t="shared" si="40"/>
+        <v>154681</v>
       </c>
       <c r="AT40" s="5">
-        <v>355700</v>
+        <v>367382</v>
       </c>
       <c r="AU40" s="4">
-        <f t="shared" si="37"/>
-        <v>0.95581280364590049</v>
+        <f t="shared" si="41"/>
+        <v>0.98720387806870458</v>
       </c>
       <c r="AV40" s="5">
         <v>317868</v>
@@ -6683,18 +7745,52 @@
         <v>249816</v>
       </c>
       <c r="AX40" s="3">
-        <f t="shared" si="38"/>
-        <v>42973</v>
+        <f t="shared" si="42"/>
+        <v>61457</v>
       </c>
       <c r="AY40" s="5">
-        <v>292789</v>
+        <v>311273</v>
       </c>
       <c r="AZ40" s="4">
-        <f t="shared" si="39"/>
-        <v>0.92110247020775915</v>
+        <f t="shared" si="43"/>
+        <v>0.97925239407552822</v>
+      </c>
+      <c r="BA40" s="5">
+        <v>321637</v>
+      </c>
+      <c r="BB40" s="5">
+        <v>202767</v>
+      </c>
+      <c r="BC40" s="3">
+        <f t="shared" si="44"/>
+        <v>108435</v>
+      </c>
+      <c r="BD40" s="5">
+        <v>311202</v>
+      </c>
+      <c r="BE40" s="4">
+        <f t="shared" si="45"/>
+        <v>0.96755659330238752</v>
+      </c>
+      <c r="BF40" s="5">
+        <v>380248</v>
+      </c>
+      <c r="BG40" s="5">
+        <v>216941</v>
+      </c>
+      <c r="BH40" s="3">
+        <f t="shared" si="46"/>
+        <v>143358</v>
+      </c>
+      <c r="BI40" s="5">
+        <v>360299</v>
+      </c>
+      <c r="BJ40" s="4">
+        <f t="shared" si="47"/>
+        <v>0.94753687067387604</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>33</v>
       </c>
@@ -6708,15 +7804,15 @@
         <v>605202</v>
       </c>
       <c r="E41" s="3">
-        <f t="shared" si="20"/>
-        <v>370016</v>
+        <f t="shared" si="24"/>
+        <v>370714</v>
       </c>
       <c r="F41" s="5">
-        <v>975218</v>
+        <v>975916</v>
       </c>
       <c r="G41" s="4">
-        <f t="shared" si="21"/>
-        <v>0.99773386001904985</v>
+        <f t="shared" si="25"/>
+        <v>0.99844797546225672</v>
       </c>
       <c r="H41" s="5">
         <v>983280</v>
@@ -6725,15 +7821,15 @@
         <v>600780</v>
       </c>
       <c r="J41" s="3">
-        <f t="shared" si="22"/>
-        <v>378709</v>
+        <f t="shared" si="26"/>
+        <v>379631</v>
       </c>
       <c r="K41" s="5">
-        <v>979489</v>
+        <v>980411</v>
       </c>
       <c r="L41" s="4">
-        <f t="shared" si="23"/>
-        <v>0.99614453665283542</v>
+        <f t="shared" si="27"/>
+        <v>0.99708221462859004</v>
       </c>
       <c r="M41" s="5">
         <v>1084276</v>
@@ -6742,15 +7838,15 @@
         <v>692679</v>
       </c>
       <c r="O41" s="3">
-        <f t="shared" si="24"/>
-        <v>388856</v>
+        <f t="shared" si="28"/>
+        <v>390184</v>
       </c>
       <c r="P41" s="5">
-        <v>1081535</v>
+        <v>1082863</v>
       </c>
       <c r="Q41" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99747204586286153</v>
+        <f t="shared" si="29"/>
+        <v>0.99869682626932621</v>
       </c>
       <c r="R41" s="5">
         <v>988018</v>
@@ -6759,15 +7855,15 @@
         <v>639204</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" si="26"/>
-        <v>347262</v>
+        <f t="shared" si="30"/>
+        <v>348881</v>
       </c>
       <c r="U41" s="5">
-        <v>986466</v>
+        <v>988085</v>
       </c>
       <c r="V41" s="4">
-        <f t="shared" si="27"/>
-        <v>0.99842917841577783</v>
+        <f t="shared" si="31"/>
+        <v>1.0000678125297313</v>
       </c>
       <c r="W41" s="5">
         <v>994033</v>
@@ -6776,15 +7872,15 @@
         <v>649932</v>
       </c>
       <c r="Y41" s="3">
-        <f t="shared" si="28"/>
-        <v>340885</v>
+        <f t="shared" si="32"/>
+        <v>343218</v>
       </c>
       <c r="Z41" s="5">
-        <v>990817</v>
+        <v>993150</v>
       </c>
       <c r="AA41" s="4">
-        <f t="shared" si="29"/>
-        <v>0.99676469493467523</v>
+        <f t="shared" si="33"/>
+        <v>0.999111699510982</v>
       </c>
       <c r="AB41" s="5">
         <v>1097882</v>
@@ -6793,15 +7889,15 @@
         <v>702797</v>
       </c>
       <c r="AD41" s="3">
-        <f t="shared" si="30"/>
-        <v>390162</v>
+        <f t="shared" si="34"/>
+        <v>394248</v>
       </c>
       <c r="AE41" s="5">
-        <v>1092959</v>
+        <v>1097045</v>
       </c>
       <c r="AF41" s="4">
-        <f t="shared" si="31"/>
-        <v>0.99551591154604957</v>
+        <f t="shared" si="35"/>
+        <v>0.99923762298680552</v>
       </c>
       <c r="AG41" s="5">
         <v>1002140</v>
@@ -6810,15 +7906,15 @@
         <v>647375</v>
       </c>
       <c r="AI41" s="3">
-        <f t="shared" si="32"/>
-        <v>348117</v>
+        <f t="shared" si="36"/>
+        <v>353711</v>
       </c>
       <c r="AJ41" s="5">
-        <v>995492</v>
+        <v>1001086</v>
       </c>
       <c r="AK41" s="4">
-        <f t="shared" si="33"/>
-        <v>0.99336619633983281</v>
+        <f t="shared" si="37"/>
+        <v>0.99894825074340909</v>
       </c>
       <c r="AL41" s="5">
         <v>1011306</v>
@@ -6827,15 +7923,15 @@
         <v>671475</v>
       </c>
       <c r="AN41" s="3">
-        <f t="shared" si="34"/>
-        <v>333503</v>
+        <f t="shared" si="38"/>
+        <v>342166</v>
       </c>
       <c r="AO41" s="5">
-        <v>1004978</v>
+        <v>1013641</v>
       </c>
       <c r="AP41" s="4">
-        <f t="shared" si="35"/>
-        <v>0.99374274453033995</v>
+        <f t="shared" si="39"/>
+        <v>1.002308895626052</v>
       </c>
       <c r="AQ41" s="5">
         <v>1119532</v>
@@ -6844,15 +7940,15 @@
         <v>726843</v>
       </c>
       <c r="AS41" s="3">
-        <f t="shared" si="36"/>
-        <v>377562</v>
+        <f t="shared" si="40"/>
+        <v>394657</v>
       </c>
       <c r="AT41" s="5">
-        <v>1104405</v>
+        <v>1121500</v>
       </c>
       <c r="AU41" s="4">
-        <f t="shared" si="37"/>
-        <v>0.98648810395772524</v>
+        <f t="shared" si="41"/>
+        <v>1.0017578773987701</v>
       </c>
       <c r="AV41" s="5">
         <v>1028062</v>
@@ -6861,18 +7957,52 @@
         <v>879708</v>
       </c>
       <c r="AX41" s="3">
-        <f t="shared" si="38"/>
-        <v>108733</v>
+        <f t="shared" si="42"/>
+        <v>146266</v>
       </c>
       <c r="AY41" s="5">
-        <v>988441</v>
+        <v>1025974</v>
       </c>
       <c r="AZ41" s="4">
-        <f t="shared" si="39"/>
-        <v>0.96146049557322422</v>
+        <f t="shared" si="43"/>
+        <v>0.99796899408790518</v>
+      </c>
+      <c r="BA41" s="5">
+        <v>1037044</v>
+      </c>
+      <c r="BB41" s="5">
+        <v>704817</v>
+      </c>
+      <c r="BC41" s="3">
+        <f t="shared" si="44"/>
+        <v>325901</v>
+      </c>
+      <c r="BD41" s="5">
+        <v>1030718</v>
+      </c>
+      <c r="BE41" s="4">
+        <f t="shared" si="45"/>
+        <v>0.99389996952877602</v>
+      </c>
+      <c r="BF41" s="5">
+        <v>1143357</v>
+      </c>
+      <c r="BG41" s="5">
+        <v>743834</v>
+      </c>
+      <c r="BH41" s="3">
+        <f t="shared" si="46"/>
+        <v>378653</v>
+      </c>
+      <c r="BI41" s="5">
+        <v>1122487</v>
+      </c>
+      <c r="BJ41" s="4">
+        <f t="shared" si="47"/>
+        <v>0.98174673352242559</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>34</v>
       </c>
@@ -6886,15 +8016,15 @@
         <v>10333</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="20"/>
-        <v>9237</v>
+        <f t="shared" si="24"/>
+        <v>9249</v>
       </c>
       <c r="F42" s="5">
-        <v>19570</v>
+        <v>19582</v>
       </c>
       <c r="G42" s="4">
-        <f t="shared" si="21"/>
-        <v>0.99461272616385443</v>
+        <f t="shared" si="25"/>
+        <v>0.99522260622077663</v>
       </c>
       <c r="H42" s="5">
         <v>19882</v>
@@ -6903,15 +8033,15 @@
         <v>10157</v>
       </c>
       <c r="J42" s="3">
-        <f t="shared" si="22"/>
-        <v>9501</v>
+        <f t="shared" si="26"/>
+        <v>9520</v>
       </c>
       <c r="K42" s="5">
-        <v>19658</v>
+        <v>19677</v>
       </c>
       <c r="L42" s="4">
-        <f t="shared" si="23"/>
-        <v>0.98873352781410317</v>
+        <f t="shared" si="27"/>
+        <v>0.98968916607987123</v>
       </c>
       <c r="M42" s="5">
         <v>21930</v>
@@ -6920,15 +8050,15 @@
         <v>11791</v>
       </c>
       <c r="O42" s="3">
-        <f t="shared" si="24"/>
-        <v>9956</v>
+        <f t="shared" si="28"/>
+        <v>9984</v>
       </c>
       <c r="P42" s="5">
-        <v>21747</v>
+        <v>21775</v>
       </c>
       <c r="Q42" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99165526675786597</v>
+        <f t="shared" si="29"/>
+        <v>0.99293205654354766</v>
       </c>
       <c r="R42" s="5">
         <v>20021</v>
@@ -6937,15 +8067,15 @@
         <v>10884</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" si="26"/>
-        <v>8882</v>
+        <f t="shared" si="30"/>
+        <v>8922</v>
       </c>
       <c r="U42" s="5">
-        <v>19766</v>
+        <v>19806</v>
       </c>
       <c r="V42" s="4">
-        <f t="shared" si="27"/>
-        <v>0.98726337345786919</v>
+        <f t="shared" si="31"/>
+        <v>0.98926127566055644</v>
       </c>
       <c r="W42" s="5">
         <v>20153</v>
@@ -6954,15 +8084,15 @@
         <v>11207</v>
       </c>
       <c r="Y42" s="3">
-        <f t="shared" si="28"/>
-        <v>8612</v>
+        <f t="shared" si="32"/>
+        <v>8692</v>
       </c>
       <c r="Z42" s="5">
-        <v>19819</v>
+        <v>19899</v>
       </c>
       <c r="AA42" s="4">
-        <f t="shared" si="29"/>
-        <v>0.9834267850940307</v>
+        <f t="shared" si="33"/>
+        <v>0.9873964174068377</v>
       </c>
       <c r="AB42" s="5">
         <v>22238</v>
@@ -6971,15 +8101,15 @@
         <v>12055</v>
       </c>
       <c r="AD42" s="3">
-        <f t="shared" si="30"/>
-        <v>9843</v>
+        <f t="shared" si="34"/>
+        <v>9997</v>
       </c>
       <c r="AE42" s="5">
-        <v>21898</v>
+        <v>22052</v>
       </c>
       <c r="AF42" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98471085529274216</v>
+        <f t="shared" si="35"/>
+        <v>0.99163593848367659</v>
       </c>
       <c r="AG42" s="5">
         <v>20276</v>
@@ -6988,15 +8118,15 @@
         <v>11099</v>
       </c>
       <c r="AI42" s="3">
-        <f t="shared" si="32"/>
-        <v>8787</v>
+        <f t="shared" si="36"/>
+        <v>9022</v>
       </c>
       <c r="AJ42" s="5">
-        <v>19886</v>
+        <v>20121</v>
       </c>
       <c r="AK42" s="4">
-        <f t="shared" si="33"/>
-        <v>0.98076543696981655</v>
+        <f t="shared" si="37"/>
+        <v>0.99235549418031166</v>
       </c>
       <c r="AL42" s="5">
         <v>20453</v>
@@ -7005,15 +8135,15 @@
         <v>11588</v>
       </c>
       <c r="AN42" s="3">
-        <f t="shared" si="34"/>
-        <v>8318</v>
+        <f t="shared" si="38"/>
+        <v>8697</v>
       </c>
       <c r="AO42" s="5">
-        <v>19906</v>
+        <v>20285</v>
       </c>
       <c r="AP42" s="4">
-        <f t="shared" si="35"/>
-        <v>0.97325575710164769</v>
+        <f t="shared" si="39"/>
+        <v>0.9917860460568132</v>
       </c>
       <c r="AQ42" s="5">
         <v>22621</v>
@@ -7022,15 +8152,15 @@
         <v>12301</v>
       </c>
       <c r="AS42" s="3">
-        <f t="shared" si="36"/>
-        <v>9481</v>
+        <f t="shared" si="40"/>
+        <v>10143</v>
       </c>
       <c r="AT42" s="5">
-        <v>21782</v>
+        <v>22444</v>
       </c>
       <c r="AU42" s="4">
-        <f t="shared" si="37"/>
-        <v>0.96291056982449941</v>
+        <f t="shared" si="41"/>
+        <v>0.9921754122275761</v>
       </c>
       <c r="AV42" s="5">
         <v>20714</v>
@@ -7039,18 +8169,52 @@
         <v>16696</v>
       </c>
       <c r="AX42" s="3">
-        <f t="shared" si="38"/>
-        <v>2447</v>
+        <f t="shared" si="42"/>
+        <v>3702</v>
       </c>
       <c r="AY42" s="5">
-        <v>19143</v>
+        <v>20398</v>
       </c>
       <c r="AZ42" s="4">
-        <f t="shared" si="39"/>
-        <v>0.92415757458723569</v>
+        <f t="shared" si="43"/>
+        <v>0.98474461716713335</v>
+      </c>
+      <c r="BA42" s="5">
+        <v>20927</v>
+      </c>
+      <c r="BB42" s="5">
+        <v>12162</v>
+      </c>
+      <c r="BC42" s="3">
+        <f t="shared" si="44"/>
+        <v>8228</v>
+      </c>
+      <c r="BD42" s="5">
+        <v>20390</v>
+      </c>
+      <c r="BE42" s="4">
+        <f t="shared" si="45"/>
+        <v>0.97433937019161854</v>
+      </c>
+      <c r="BF42" s="5">
+        <v>23165</v>
+      </c>
+      <c r="BG42" s="5">
+        <v>12517</v>
+      </c>
+      <c r="BH42" s="3">
+        <f t="shared" si="46"/>
+        <v>9637</v>
+      </c>
+      <c r="BI42" s="5">
+        <v>22154</v>
+      </c>
+      <c r="BJ42" s="4">
+        <f t="shared" si="47"/>
+        <v>0.95635657241528171</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>35</v>
       </c>
@@ -7064,15 +8228,15 @@
         <v>1618</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="20"/>
-        <v>2254</v>
+        <f t="shared" si="24"/>
+        <v>2268</v>
       </c>
       <c r="F43" s="5">
-        <v>3872</v>
+        <v>3886</v>
       </c>
       <c r="G43" s="4">
-        <f t="shared" si="21"/>
-        <v>0.98926928972917727</v>
+        <f t="shared" si="25"/>
+        <v>0.99284619315278488</v>
       </c>
       <c r="H43" s="5">
         <v>3941</v>
@@ -7081,15 +8245,15 @@
         <v>1644</v>
       </c>
       <c r="J43" s="3">
-        <f t="shared" si="22"/>
-        <v>2262</v>
+        <f t="shared" si="26"/>
+        <v>2279</v>
       </c>
       <c r="K43" s="5">
-        <v>3906</v>
+        <v>3923</v>
       </c>
       <c r="L43" s="4">
-        <f t="shared" si="23"/>
-        <v>0.99111900532859676</v>
+        <f t="shared" si="27"/>
+        <v>0.99543263131184978</v>
       </c>
       <c r="M43" s="5">
         <v>4896</v>
@@ -7098,15 +8262,15 @@
         <v>2144</v>
       </c>
       <c r="O43" s="3">
-        <f t="shared" si="24"/>
-        <v>2685</v>
+        <f t="shared" si="28"/>
+        <v>2713</v>
       </c>
       <c r="P43" s="5">
-        <v>4829</v>
+        <v>4857</v>
       </c>
       <c r="Q43" s="4">
-        <f t="shared" si="25"/>
-        <v>0.98631535947712423</v>
+        <f t="shared" si="29"/>
+        <v>0.99203431372549022</v>
       </c>
       <c r="R43" s="5">
         <v>3969</v>
@@ -7115,15 +8279,15 @@
         <v>1773</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" si="26"/>
-        <v>2122</v>
+        <f t="shared" si="30"/>
+        <v>2152</v>
       </c>
       <c r="U43" s="5">
-        <v>3895</v>
+        <v>3925</v>
       </c>
       <c r="V43" s="4">
-        <f t="shared" si="27"/>
-        <v>0.98135550516502901</v>
+        <f t="shared" si="31"/>
+        <v>0.98891408415217941</v>
       </c>
       <c r="W43" s="5">
         <v>4009</v>
@@ -7132,15 +8296,15 @@
         <v>2012</v>
       </c>
       <c r="Y43" s="3">
-        <f t="shared" si="28"/>
-        <v>1906</v>
+        <f t="shared" si="32"/>
+        <v>1954</v>
       </c>
       <c r="Z43" s="5">
-        <v>3918</v>
+        <v>3966</v>
       </c>
       <c r="AA43" s="4">
-        <f t="shared" si="29"/>
-        <v>0.97730107258667998</v>
+        <f t="shared" si="33"/>
+        <v>0.98927413320029933</v>
       </c>
       <c r="AB43" s="5">
         <v>4962</v>
@@ -7149,15 +8313,15 @@
         <v>2254</v>
       </c>
       <c r="AD43" s="3">
-        <f t="shared" si="30"/>
-        <v>2573</v>
+        <f t="shared" si="34"/>
+        <v>2674</v>
       </c>
       <c r="AE43" s="5">
-        <v>4827</v>
+        <v>4928</v>
       </c>
       <c r="AF43" s="4">
-        <f t="shared" si="31"/>
-        <v>0.97279322853688033</v>
+        <f t="shared" si="35"/>
+        <v>0.99314792422410314</v>
       </c>
       <c r="AG43" s="5">
         <v>4018</v>
@@ -7166,15 +8330,15 @@
         <v>1763</v>
       </c>
       <c r="AI43" s="3">
-        <f t="shared" si="32"/>
-        <v>2093</v>
+        <f t="shared" si="36"/>
+        <v>2229</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3856</v>
+        <v>3992</v>
       </c>
       <c r="AK43" s="4">
-        <f t="shared" si="33"/>
-        <v>0.95968143354902935</v>
+        <f t="shared" si="37"/>
+        <v>0.99352911896465901</v>
       </c>
       <c r="AL43" s="5">
         <v>4086</v>
@@ -7183,15 +8347,15 @@
         <v>1915</v>
       </c>
       <c r="AN43" s="3">
-        <f t="shared" si="34"/>
-        <v>1947</v>
+        <f t="shared" si="38"/>
+        <v>2123</v>
       </c>
       <c r="AO43" s="5">
-        <v>3862</v>
+        <v>4038</v>
       </c>
       <c r="AP43" s="4">
-        <f t="shared" si="35"/>
-        <v>0.94517865883504648</v>
+        <f t="shared" si="39"/>
+        <v>0.98825256975036713</v>
       </c>
       <c r="AQ43" s="5">
         <v>5072</v>
@@ -7200,15 +8364,15 @@
         <v>2138</v>
       </c>
       <c r="AS43" s="3">
-        <f t="shared" si="36"/>
-        <v>2503</v>
+        <f t="shared" si="40"/>
+        <v>2868</v>
       </c>
       <c r="AT43" s="5">
-        <v>4641</v>
+        <v>5006</v>
       </c>
       <c r="AU43" s="4">
-        <f t="shared" si="37"/>
-        <v>0.91502365930599372</v>
+        <f t="shared" si="41"/>
+        <v>0.98698738170347</v>
       </c>
       <c r="AV43" s="5">
         <v>4151</v>
@@ -7217,18 +8381,52 @@
         <v>2841</v>
       </c>
       <c r="AX43" s="3">
-        <f t="shared" si="38"/>
-        <v>651</v>
+        <f t="shared" si="42"/>
+        <v>1176</v>
       </c>
       <c r="AY43" s="5">
-        <v>3492</v>
+        <v>4017</v>
       </c>
       <c r="AZ43" s="4">
-        <f t="shared" si="39"/>
-        <v>0.8412430739580824</v>
+        <f t="shared" si="43"/>
+        <v>0.96771862201879066</v>
+      </c>
+      <c r="BA43" s="5">
+        <v>4249</v>
+      </c>
+      <c r="BB43" s="5">
+        <v>1968</v>
+      </c>
+      <c r="BC43" s="3">
+        <f t="shared" si="44"/>
+        <v>2060</v>
+      </c>
+      <c r="BD43" s="5">
+        <v>4028</v>
+      </c>
+      <c r="BE43" s="4">
+        <f t="shared" si="45"/>
+        <v>0.94798776182631206</v>
+      </c>
+      <c r="BF43" s="5">
+        <v>5295</v>
+      </c>
+      <c r="BG43" s="5">
+        <v>2213</v>
+      </c>
+      <c r="BH43" s="3">
+        <f t="shared" si="46"/>
+        <v>2520</v>
+      </c>
+      <c r="BI43" s="5">
+        <v>4733</v>
+      </c>
+      <c r="BJ43" s="4">
+        <f t="shared" si="47"/>
+        <v>0.89386213408876303</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>36</v>
       </c>
@@ -7242,15 +8440,15 @@
         <v>194017</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="20"/>
-        <v>185434</v>
+        <f t="shared" si="24"/>
+        <v>185896</v>
       </c>
       <c r="F44" s="5">
-        <v>379451</v>
+        <v>379913</v>
       </c>
       <c r="G44" s="4">
-        <f t="shared" si="21"/>
-        <v>0.98934395027350619</v>
+        <f t="shared" si="25"/>
+        <v>0.99054852452690478</v>
       </c>
       <c r="H44" s="5">
         <v>388149</v>
@@ -7259,15 +8457,15 @@
         <v>198804</v>
       </c>
       <c r="J44" s="3">
-        <f t="shared" si="22"/>
-        <v>183773</v>
+        <f t="shared" si="26"/>
+        <v>184354</v>
       </c>
       <c r="K44" s="5">
-        <v>382577</v>
+        <v>383158</v>
       </c>
       <c r="L44" s="4">
-        <f t="shared" si="23"/>
-        <v>0.98564468799352822</v>
+        <f t="shared" si="27"/>
+        <v>0.98714153585349951</v>
       </c>
       <c r="M44" s="5">
         <v>456953</v>
@@ -7276,15 +8474,15 @@
         <v>241806</v>
       </c>
       <c r="O44" s="3">
-        <f t="shared" si="24"/>
-        <v>210994</v>
+        <f t="shared" si="28"/>
+        <v>211876</v>
       </c>
       <c r="P44" s="5">
-        <v>452800</v>
+        <v>453682</v>
       </c>
       <c r="Q44" s="4">
-        <f t="shared" si="25"/>
-        <v>0.99091153794810405</v>
+        <f t="shared" si="29"/>
+        <v>0.99284171457458426</v>
       </c>
       <c r="R44" s="5">
         <v>388846</v>
@@ -7293,15 +8491,15 @@
         <v>204094</v>
       </c>
       <c r="T44" s="3">
-        <f t="shared" si="26"/>
-        <v>180207</v>
+        <f t="shared" si="30"/>
+        <v>181157</v>
       </c>
       <c r="U44" s="5">
-        <v>384301</v>
+        <v>385251</v>
       </c>
       <c r="V44" s="4">
-        <f t="shared" si="27"/>
-        <v>0.98831156807579346</v>
+        <f t="shared" si="31"/>
+        <v>0.99075469466061117</v>
       </c>
       <c r="W44" s="5">
         <v>393146</v>
@@ -7310,15 +8508,15 @@
         <v>209588</v>
       </c>
       <c r="Y44" s="3">
-        <f t="shared" si="28"/>
-        <v>176902</v>
+        <f t="shared" si="32"/>
+        <v>178236</v>
       </c>
       <c r="Z44" s="5">
-        <v>386490</v>
+        <v>387824</v>
       </c>
       <c r="AA44" s="4">
-        <f t="shared" si="29"/>
-        <v>0.98306990278420736</v>
+        <f t="shared" si="33"/>
+        <v>0.98646304426345433</v>
       </c>
       <c r="AB44" s="5">
         <v>465292</v>
@@ -7327,15 +8525,15 @@
         <v>238024</v>
       </c>
       <c r="AD44" s="3">
-        <f t="shared" si="30"/>
-        <v>219956</v>
+        <f t="shared" si="34"/>
+        <v>222423</v>
       </c>
       <c r="AE44" s="5">
-        <v>457980</v>
+        <v>460447</v>
       </c>
       <c r="AF44" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98428513707521303</v>
+        <f t="shared" si="35"/>
+        <v>0.98958718396189915</v>
       </c>
       <c r="AG44" s="5">
         <v>393778</v>
@@ -7344,15 +8542,15 @@
         <v>210607</v>
       </c>
       <c r="AI44" s="3">
-        <f t="shared" si="32"/>
-        <v>177341</v>
+        <f t="shared" si="36"/>
+        <v>180614</v>
       </c>
       <c r="AJ44" s="5">
-        <v>387948</v>
+        <v>391221</v>
       </c>
       <c r="AK44" s="4">
-        <f t="shared" si="33"/>
-        <v>0.98519470361472705</v>
+        <f t="shared" si="37"/>
+        <v>0.99350649350649356</v>
       </c>
       <c r="AL44" s="5">
         <v>398873</v>
@@ -7361,15 +8559,15 @@
         <v>221504</v>
       </c>
       <c r="AN44" s="3">
-        <f t="shared" si="34"/>
-        <v>173669</v>
+        <f t="shared" si="38"/>
+        <v>178905</v>
       </c>
       <c r="AO44" s="5">
-        <v>395173</v>
+        <v>400409</v>
       </c>
       <c r="AP44" s="4">
-        <f t="shared" si="35"/>
-        <v>0.99072386448819549</v>
+        <f t="shared" si="39"/>
+        <v>1.0038508497692249</v>
       </c>
       <c r="AQ44" s="5">
         <v>476819</v>
@@ -7378,15 +8576,15 @@
         <v>255639</v>
       </c>
       <c r="AS44" s="3">
-        <f t="shared" si="36"/>
-        <v>209559</v>
+        <f t="shared" si="40"/>
+        <v>220923</v>
       </c>
       <c r="AT44" s="5">
-        <v>465198</v>
+        <v>476562</v>
       </c>
       <c r="AU44" s="4">
-        <f t="shared" si="37"/>
-        <v>0.97562806851237049</v>
+        <f t="shared" si="41"/>
+        <v>0.9994610114110386</v>
       </c>
       <c r="AV44" s="5">
         <v>408878</v>
@@ -7395,18 +8593,52 @@
         <v>335378</v>
       </c>
       <c r="AX44" s="3">
-        <f t="shared" si="38"/>
-        <v>50320</v>
+        <f t="shared" si="42"/>
+        <v>71479</v>
       </c>
       <c r="AY44" s="5">
-        <v>385698</v>
+        <v>406857</v>
       </c>
       <c r="AZ44" s="4">
-        <f t="shared" si="39"/>
-        <v>0.94330827288335395</v>
+        <f t="shared" si="43"/>
+        <v>0.99505720532775055</v>
+      </c>
+      <c r="BA44" s="5">
+        <v>416024</v>
+      </c>
+      <c r="BB44" s="5">
+        <v>235066</v>
+      </c>
+      <c r="BC44" s="3">
+        <f t="shared" si="44"/>
+        <v>174782</v>
+      </c>
+      <c r="BD44" s="5">
+        <v>409848</v>
+      </c>
+      <c r="BE44" s="4">
+        <f t="shared" si="45"/>
+        <v>0.98515470261331073</v>
+      </c>
+      <c r="BF44" s="5">
+        <v>493955</v>
+      </c>
+      <c r="BG44" s="5">
+        <v>259965</v>
+      </c>
+      <c r="BH44" s="3">
+        <f t="shared" si="46"/>
+        <v>214816</v>
+      </c>
+      <c r="BI44" s="5">
+        <v>474781</v>
+      </c>
+      <c r="BJ44" s="4">
+        <f t="shared" si="47"/>
+        <v>0.96118269882884066</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>37</v>
       </c>
@@ -7420,15 +8652,15 @@
         <v>138494</v>
       </c>
       <c r="E45" s="3">
-        <f t="shared" si="20"/>
-        <v>138164</v>
+        <f t="shared" si="24"/>
+        <v>138376</v>
       </c>
       <c r="F45" s="5">
-        <v>276658</v>
+        <v>276870</v>
       </c>
       <c r="G45" s="4">
-        <f t="shared" si="21"/>
-        <v>0.99698013665061835</v>
+        <f t="shared" si="25"/>
+        <v>0.9977441116268343</v>
       </c>
       <c r="H45" s="5">
         <v>280269</v>
@@ -7437,15 +8669,15 @@
         <v>140127</v>
       </c>
       <c r="J45" s="3">
-        <f t="shared" si="22"/>
-        <v>138407</v>
+        <f t="shared" si="26"/>
+        <v>138680</v>
       </c>
       <c r="K45" s="5">
-        <v>278534</v>
+        <v>278807</v>
       </c>
       <c r="L45" s="4">
-        <f t="shared" si="23"/>
-        <v>0.99380951871237988</v>
+        <f t="shared" si="27"/>
+        <v>0.99478358291498525</v>
       </c>
       <c r="M45" s="5">
         <v>334005</v>
@@ -7454,15 +8686,15 @@
         <v>169736</v>
       </c>
       <c r="O45" s="3">
-        <f t="shared" si="24"/>
-        <v>161865</v>
+        <f t="shared" si="28"/>
+        <v>162343</v>
       </c>
       <c r="P45" s="5">
-        <v>331601</v>
+        <v>332079</v>
       </c>
       <c r="Q45" s="4">
-        <f t="shared" si="25"/>
-        <v>0.9928025029565426</v>
+        <f t="shared" si="29"/>
+        <v>0.99423361925719678</v>
       </c>
       <c r="R45" s="5">
         <v>281510</v>
@@ -7471,15 +8703,15 @@
         <v>145581</v>
       </c>
       <c r="T45" s="3">
-        <f t="shared" si="26"/>
-        <v>133645</v>
+        <f t="shared" si="30"/>
+        <v>134197</v>
       </c>
       <c r="U45" s="5">
-        <v>279226</v>
+        <v>279778</v>
       </c>
       <c r="V45" s="4">
-        <f t="shared" si="27"/>
-        <v>0.99188661148804658</v>
+        <f t="shared" si="31"/>
+        <v>0.99384746545415792</v>
       </c>
       <c r="W45" s="5">
         <v>284325</v>
@@ -7488,15 +8720,15 @@
         <v>147899</v>
       </c>
       <c r="Y45" s="3">
-        <f t="shared" si="28"/>
-        <v>132108</v>
+        <f t="shared" si="32"/>
+        <v>132993</v>
       </c>
       <c r="Z45" s="5">
-        <v>280007</v>
+        <v>280892</v>
       </c>
       <c r="AA45" s="4">
-        <f t="shared" si="29"/>
-        <v>0.984813153961136</v>
+        <f t="shared" si="33"/>
+        <v>0.98792578914974061</v>
       </c>
       <c r="AB45" s="5">
         <v>338696</v>
@@ -7505,15 +8737,15 @@
         <v>163270</v>
       </c>
       <c r="AD45" s="3">
-        <f t="shared" si="30"/>
-        <v>169712</v>
+        <f t="shared" si="34"/>
+        <v>171576</v>
       </c>
       <c r="AE45" s="5">
-        <v>332982</v>
+        <v>334846</v>
       </c>
       <c r="AF45" s="4">
-        <f t="shared" si="31"/>
-        <v>0.98312941398776488</v>
+        <f t="shared" si="35"/>
+        <v>0.98863287431797242</v>
       </c>
       <c r="AG45" s="5">
         <v>285325</v>
@@ -7522,15 +8754,15 @@
         <v>143199</v>
       </c>
       <c r="AI45" s="3">
-        <f t="shared" si="32"/>
-        <v>137040</v>
+        <f t="shared" si="36"/>
+        <v>139214</v>
       </c>
       <c r="AJ45" s="5">
-        <v>280239</v>
+        <v>282413</v>
       </c>
       <c r="AK45" s="4">
-        <f t="shared" si="33"/>
-        <v>0.98217471304652593</v>
+        <f t="shared" si="37"/>
+        <v>0.98979409445369315</v>
       </c>
       <c r="AL45" s="5">
         <v>289428</v>
@@ -7539,15 +8771,15 @@
         <v>153834</v>
       </c>
       <c r="AN45" s="3">
-        <f t="shared" si="34"/>
-        <v>131547</v>
+        <f t="shared" si="38"/>
+        <v>135040</v>
       </c>
       <c r="AO45" s="5">
-        <v>285381</v>
+        <v>288874</v>
       </c>
       <c r="AP45" s="4">
-        <f t="shared" si="35"/>
-        <v>0.98601724781292754</v>
+        <f t="shared" si="39"/>
+        <v>0.9980858797352018</v>
       </c>
       <c r="AQ45" s="5">
         <v>348161</v>
@@ -7556,15 +8788,15 @@
         <v>175854</v>
       </c>
       <c r="AS45" s="3">
-        <f t="shared" si="36"/>
-        <v>161857</v>
+        <f t="shared" si="40"/>
+        <v>169876</v>
       </c>
       <c r="AT45" s="5">
-        <v>337711</v>
+        <v>345730</v>
       </c>
       <c r="AU45" s="4">
-        <f t="shared" si="37"/>
-        <v>0.96998515054816592</v>
+        <f t="shared" si="41"/>
+        <v>0.99301759818015234</v>
       </c>
       <c r="AV45" s="5">
         <v>296165</v>
@@ -7573,18 +8805,52 @@
         <v>242033</v>
       </c>
       <c r="AX45" s="3">
-        <f t="shared" si="38"/>
-        <v>35209</v>
+        <f t="shared" si="42"/>
+        <v>50804</v>
       </c>
       <c r="AY45" s="5">
-        <v>277242</v>
+        <v>292837</v>
       </c>
       <c r="AZ45" s="4">
-        <f t="shared" si="39"/>
-        <v>0.93610656222038391</v>
+        <f t="shared" si="43"/>
+        <v>0.9887630206135094</v>
+      </c>
+      <c r="BA45" s="5">
+        <v>300603</v>
+      </c>
+      <c r="BB45" s="5">
+        <v>162801</v>
+      </c>
+      <c r="BC45" s="3">
+        <f t="shared" si="44"/>
+        <v>132190</v>
+      </c>
+      <c r="BD45" s="5">
+        <v>294991</v>
+      </c>
+      <c r="BE45" s="4">
+        <f t="shared" si="45"/>
+        <v>0.98133085830813394</v>
+      </c>
+      <c r="BF45" s="5">
+        <v>359430</v>
+      </c>
+      <c r="BG45" s="5">
+        <v>176275</v>
+      </c>
+      <c r="BH45" s="3">
+        <f t="shared" si="46"/>
+        <v>168197</v>
+      </c>
+      <c r="BI45" s="5">
+        <v>344472</v>
+      </c>
+      <c r="BJ45" s="4">
+        <f t="shared" si="47"/>
+        <v>0.95838410817127118</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>38</v>
       </c>
@@ -7598,15 +8864,15 @@
         <v>852</v>
       </c>
       <c r="E46" s="3">
-        <f t="shared" si="20"/>
-        <v>1633</v>
+        <f t="shared" si="24"/>
+        <v>1642</v>
       </c>
       <c r="F46" s="5">
-        <v>2485</v>
+        <v>2494</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" si="21"/>
-        <v>1.022633744855967</v>
+        <f t="shared" si="25"/>
+        <v>1.0263374485596708</v>
       </c>
       <c r="H46" s="5">
         <v>2594</v>
@@ -7615,15 +8881,15 @@
         <v>1005</v>
       </c>
       <c r="J46" s="3">
-        <f t="shared" si="22"/>
-        <v>1625</v>
+        <f t="shared" si="26"/>
+        <v>1635</v>
       </c>
       <c r="K46" s="5">
-        <v>2630</v>
+        <v>2640</v>
       </c>
       <c r="L46" s="4">
-        <f t="shared" si="23"/>
-        <v>1.0138781804163455</v>
+        <f t="shared" si="27"/>
+        <v>1.0177332305319968</v>
       </c>
       <c r="M46" s="5">
         <v>8454</v>
@@ -7632,15 +8898,15 @@
         <v>2855</v>
       </c>
       <c r="O46" s="3">
-        <f t="shared" si="24"/>
-        <v>5711</v>
+        <f t="shared" si="28"/>
+        <v>5753</v>
       </c>
       <c r="P46" s="5">
-        <v>8566</v>
+        <v>8608</v>
       </c>
       <c r="Q46" s="4">
-        <f t="shared" si="25"/>
-        <v>1.0132481665483795</v>
+        <f t="shared" si="29"/>
+        <v>1.0182162290040218</v>
       </c>
       <c r="R46" s="5">
         <v>2484</v>
@@ -7649,15 +8915,15 @@
         <v>940</v>
       </c>
       <c r="T46" s="3">
-        <f t="shared" si="26"/>
-        <v>1624</v>
+        <f t="shared" si="30"/>
+        <v>1645</v>
       </c>
       <c r="U46" s="5">
-        <v>2564</v>
+        <v>2585</v>
       </c>
       <c r="V46" s="4">
-        <f t="shared" si="27"/>
-        <v>1.0322061191626408</v>
+        <f t="shared" si="31"/>
+        <v>1.0406602254428341</v>
       </c>
       <c r="W46" s="5">
         <v>2748</v>
@@ -7666,15 +8932,15 @@
         <v>1127</v>
       </c>
       <c r="Y46" s="3">
-        <f t="shared" si="28"/>
-        <v>1531</v>
+        <f t="shared" si="32"/>
+        <v>1563</v>
       </c>
       <c r="Z46" s="5">
-        <v>2658</v>
+        <v>2690</v>
       </c>
       <c r="AA46" s="4">
-        <f t="shared" si="29"/>
-        <v>0.96724890829694321</v>
+        <f t="shared" si="33"/>
+        <v>0.9788937409024745</v>
       </c>
       <c r="AB46" s="5">
         <v>8770</v>
@@ -7683,15 +8949,15 @@
         <v>2986</v>
       </c>
       <c r="AD46" s="3">
-        <f t="shared" si="30"/>
-        <v>5721</v>
+        <f t="shared" si="34"/>
+        <v>5847</v>
       </c>
       <c r="AE46" s="5">
-        <v>8707</v>
+        <v>8833</v>
       </c>
       <c r="AF46" s="4">
-        <f t="shared" si="31"/>
-        <v>0.9928164196123147</v>
+        <f t="shared" si="35"/>
+        <v>1.0071835803876852</v>
       </c>
       <c r="AG46" s="5">
         <v>2523</v>
@@ -7700,15 +8966,15 @@
         <v>1056</v>
       </c>
       <c r="AI46" s="3">
-        <f t="shared" si="32"/>
-        <v>1420</v>
+        <f t="shared" si="36"/>
+        <v>1487</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2476</v>
+        <v>2543</v>
       </c>
       <c r="AK46" s="4">
-        <f t="shared" si="33"/>
-        <v>0.98137138327388029</v>
+        <f t="shared" si="37"/>
+        <v>1.007927070947285</v>
       </c>
       <c r="AL46" s="5">
         <v>2722</v>
@@ -7717,15 +8983,15 @@
         <v>1164</v>
       </c>
       <c r="AN46" s="3">
-        <f t="shared" si="34"/>
-        <v>1398</v>
+        <f t="shared" si="38"/>
+        <v>1484</v>
       </c>
       <c r="AO46" s="5">
-        <v>2562</v>
+        <v>2648</v>
       </c>
       <c r="AP46" s="4">
-        <f t="shared" si="35"/>
-        <v>0.94121969140337991</v>
+        <f t="shared" si="39"/>
+        <v>0.97281410727406314</v>
       </c>
       <c r="AQ46" s="5">
         <v>8967</v>
@@ -7734,15 +9000,15 @@
         <v>3220</v>
       </c>
       <c r="AS46" s="3">
-        <f t="shared" si="36"/>
-        <v>5232</v>
+        <f t="shared" si="40"/>
+        <v>5680</v>
       </c>
       <c r="AT46" s="5">
-        <v>8452</v>
+        <v>8900</v>
       </c>
       <c r="AU46" s="4">
-        <f t="shared" si="37"/>
-        <v>0.94256719081075058</v>
+        <f t="shared" si="41"/>
+        <v>0.9925281588045054</v>
       </c>
       <c r="AV46" s="5">
         <v>2626</v>
@@ -7751,18 +9017,52 @@
         <v>2130</v>
       </c>
       <c r="AX46" s="3">
-        <f t="shared" si="38"/>
-        <v>224</v>
+        <f t="shared" si="42"/>
+        <v>459</v>
       </c>
       <c r="AY46" s="5">
-        <v>2354</v>
+        <v>2589</v>
       </c>
       <c r="AZ46" s="4">
-        <f t="shared" si="39"/>
-        <v>0.89642041127189642</v>
+        <f t="shared" si="43"/>
+        <v>0.98591012947448586</v>
+      </c>
+      <c r="BA46" s="5">
+        <v>2791</v>
+      </c>
+      <c r="BB46" s="5">
+        <v>1219</v>
+      </c>
+      <c r="BC46" s="3">
+        <f t="shared" si="44"/>
+        <v>1406</v>
+      </c>
+      <c r="BD46" s="5">
+        <v>2625</v>
+      </c>
+      <c r="BE46" s="4">
+        <f t="shared" si="45"/>
+        <v>0.94052310999641708</v>
+      </c>
+      <c r="BF46" s="5">
+        <v>9093</v>
+      </c>
+      <c r="BG46" s="5">
+        <v>3070</v>
+      </c>
+      <c r="BH46" s="3">
+        <f t="shared" si="46"/>
+        <v>5559</v>
+      </c>
+      <c r="BI46" s="5">
+        <v>8629</v>
+      </c>
+      <c r="BJ46" s="4">
+        <f t="shared" si="47"/>
+        <v>0.94897173650060485</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.3">
       <c r="A47" s="11">
         <v>97</v>
       </c>
@@ -7776,14 +9076,14 @@
         <v>95</v>
       </c>
       <c r="E47" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>28</v>
       </c>
       <c r="F47" s="5">
         <v>123</v>
       </c>
       <c r="G47" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>1.128440366972477</v>
       </c>
       <c r="H47" s="5">
@@ -7793,14 +9093,14 @@
         <v>85</v>
       </c>
       <c r="J47" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>29</v>
       </c>
       <c r="K47" s="5">
         <v>114</v>
       </c>
       <c r="L47" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>1.1632653061224489</v>
       </c>
       <c r="M47" s="5">
@@ -7810,14 +9110,14 @@
         <v>94</v>
       </c>
       <c r="O47" s="3">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>24</v>
       </c>
       <c r="P47" s="5">
         <v>118</v>
       </c>
       <c r="Q47" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>0.95934959349593496</v>
       </c>
       <c r="R47" s="5">
@@ -7827,14 +9127,14 @@
         <v>83</v>
       </c>
       <c r="T47" s="3">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>11</v>
       </c>
       <c r="U47" s="5">
         <v>94</v>
       </c>
       <c r="V47" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>0.70676691729323304</v>
       </c>
       <c r="W47" s="5">
@@ -7844,14 +9144,14 @@
         <v>69</v>
       </c>
       <c r="Y47" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v>4</v>
       </c>
       <c r="Z47" s="5">
         <v>73</v>
       </c>
       <c r="AA47" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>0.85882352941176465</v>
       </c>
       <c r="AB47" s="5">
@@ -7861,14 +9161,14 @@
         <v>74</v>
       </c>
       <c r="AD47" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v>2</v>
       </c>
       <c r="AE47" s="5">
         <v>76</v>
       </c>
       <c r="AF47" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>0.91566265060240959</v>
       </c>
       <c r="AG47" s="5">
@@ -7878,14 +9178,14 @@
         <v>68</v>
       </c>
       <c r="AI47" s="3">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v>4</v>
       </c>
       <c r="AJ47" s="5">
         <v>72</v>
       </c>
       <c r="AK47" s="4">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>0.94736842105263153</v>
       </c>
       <c r="AL47" s="5">
@@ -7895,14 +9195,14 @@
         <v>69</v>
       </c>
       <c r="AN47" s="3">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>4</v>
       </c>
       <c r="AO47" s="5">
         <v>73</v>
       </c>
       <c r="AP47" s="4">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>0.96052631578947367</v>
       </c>
       <c r="AQ47" s="5">
@@ -7912,14 +9212,14 @@
         <v>72</v>
       </c>
       <c r="AS47" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>3</v>
       </c>
       <c r="AT47" s="5">
         <v>75</v>
       </c>
       <c r="AU47" s="4">
-        <f t="shared" si="37"/>
+        <f t="shared" si="41"/>
         <v>0.94936708860759489</v>
       </c>
       <c r="AV47" s="5">
@@ -7929,22 +9229,56 @@
         <v>67</v>
       </c>
       <c r="AX47" s="3">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>4</v>
       </c>
       <c r="AY47" s="5">
         <v>71</v>
       </c>
       <c r="AZ47" s="4">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>0.94666666666666666</v>
       </c>
+      <c r="BA47" s="5">
+        <v>76</v>
+      </c>
+      <c r="BB47" s="5">
+        <v>64</v>
+      </c>
+      <c r="BC47" s="3">
+        <f t="shared" si="44"/>
+        <v>4</v>
+      </c>
+      <c r="BD47" s="5">
+        <v>68</v>
+      </c>
+      <c r="BE47" s="4">
+        <f t="shared" si="45"/>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="BF47" s="5">
+        <v>72</v>
+      </c>
+      <c r="BG47" s="5">
+        <v>67</v>
+      </c>
+      <c r="BH47" s="3">
+        <f t="shared" si="46"/>
+        <v>3</v>
+      </c>
+      <c r="BI47" s="5">
+        <v>70</v>
+      </c>
+      <c r="BJ47" s="4">
+        <f t="shared" si="47"/>
+        <v>0.97222222222222221</v>
+      </c>
     </row>
-    <row r="48" spans="1:52" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="14" t="s">
+    <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="14"/>
+      <c r="B48" s="20"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>8623084</v>
@@ -7955,15 +9289,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3376505</v>
+        <v>3385482</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8570861</v>
+        <v>8579838</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="21"/>
-        <v>0.9939438140693051</v>
+        <f t="shared" si="25"/>
+        <v>0.994984856925898</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -7975,15 +9309,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3380006</v>
+        <v>3391471</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8684779</v>
+        <v>8696244</v>
       </c>
       <c r="L48" s="6">
-        <f t="shared" si="23"/>
-        <v>0.98993060506759345</v>
+        <f t="shared" si="27"/>
+        <v>0.9912374379054929</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -7995,15 +9329,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5448897</v>
+        <v>5472967</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>13290513</v>
+        <v>13314583</v>
       </c>
       <c r="Q48" s="6">
-        <f t="shared" si="25"/>
-        <v>0.99513473521864526</v>
+        <f t="shared" si="29"/>
+        <v>0.99693699018628368</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -8015,15 +9349,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3252939</v>
+        <v>3273699</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8703870</v>
+        <v>8724630</v>
       </c>
       <c r="V48" s="6">
-        <f t="shared" si="27"/>
-        <v>0.99238687430178996</v>
+        <f t="shared" si="31"/>
+        <v>0.99475386180395919</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -8035,15 +9369,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3217353</v>
+        <v>3248986</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8789003</v>
+        <v>8820636</v>
       </c>
       <c r="AA48" s="6">
-        <f t="shared" si="29"/>
-        <v>0.98392736336999431</v>
+        <f t="shared" si="33"/>
+        <v>0.98746867224034995</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -8055,15 +9389,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5603272</v>
+        <v>5684489</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>13445045</v>
+        <v>13526262</v>
       </c>
       <c r="AF48" s="6">
-        <f t="shared" si="31"/>
-        <v>0.98803885415801662</v>
+        <f t="shared" si="35"/>
+        <v>0.99400726494564517</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -8075,15 +9409,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3281247</v>
+        <v>3358858</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8776734</v>
+        <v>8854345</v>
       </c>
       <c r="AK48" s="6">
-        <f t="shared" si="33"/>
-        <v>0.98425834217028307</v>
+        <f t="shared" si="37"/>
+        <v>0.99296195266983545</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -8095,15 +9429,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3226930</v>
+        <v>3344419</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>8992395</v>
+        <v>9109884</v>
       </c>
       <c r="AP48" s="6">
-        <f t="shared" si="35"/>
-        <v>0.98521313939627664</v>
+        <f t="shared" si="39"/>
+        <v>0.9980853171125057</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -8115,15 +9449,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>5380268</v>
+        <v>5697063</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>13619658</v>
+        <v>13936453</v>
       </c>
       <c r="AU48" s="6">
-        <f t="shared" si="37"/>
-        <v>0.97442485489684039</v>
+        <f t="shared" si="41"/>
+        <v>0.99709010257831998</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -8135,22 +9469,67 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>963030</v>
+        <v>1388055</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8762092</v>
+        <v>9187117</v>
       </c>
       <c r="AZ48" s="6">
-        <f t="shared" si="39"/>
-        <v>0.94719564065404893</v>
+        <f t="shared" si="43"/>
+        <v>0.99314149778143213</v>
+      </c>
+      <c r="BA48" s="7">
+        <f>SUM(BA10:BA47)</f>
+        <v>9470705</v>
+      </c>
+      <c r="BB48" s="7">
+        <f>SUM(BB10:BB47)</f>
+        <v>6029444</v>
+      </c>
+      <c r="BC48" s="8">
+        <f>BD48-BB48</f>
+        <v>3278438</v>
+      </c>
+      <c r="BD48" s="7">
+        <f>SUM(BD10:BD47)</f>
+        <v>9307882</v>
+      </c>
+      <c r="BE48" s="6">
+        <f t="shared" si="45"/>
+        <v>0.98280772128368477</v>
+      </c>
+      <c r="BF48" s="7">
+        <f>SUM(BF10:BF47)</f>
+        <v>14430593</v>
+      </c>
+      <c r="BG48" s="7">
+        <f>SUM(BG10:BG47)</f>
+        <v>8449762</v>
+      </c>
+      <c r="BH48" s="8">
+        <f>BI48-BG48</f>
+        <v>5467342</v>
+      </c>
+      <c r="BI48" s="7">
+        <f>SUM(BI10:BI47)</f>
+        <v>13917104</v>
+      </c>
+      <c r="BJ48" s="6">
+        <f t="shared" si="47"/>
+        <v>0.96441663901130048</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
+    <mergeCell ref="BF8:BJ8"/>
+    <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="AB8:AF8"/>
     <mergeCell ref="AV8:AZ8"/>
+    <mergeCell ref="AQ8:AU8"/>
+    <mergeCell ref="AL8:AP8"/>
+    <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -8159,9 +9538,6 @@
     <mergeCell ref="R8:V8"/>
     <mergeCell ref="H8:L8"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="AQ8:AU8"/>
-    <mergeCell ref="AL8:AP8"/>
-    <mergeCell ref="AG8:AK8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2025-2026.xlsx
+++ b/gstdatabase/GSTR-1-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03282E4-E06E-44BC-BEB1-DB9644B0CBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F326293-4FD7-409C-9911-7C9D07A601D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -360,15 +360,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -380,6 +371,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -759,10 +759,10 @@
       <c r="AZ2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="14"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -967,100 +967,100 @@
       <c r="AZ6" s="1"/>
     </row>
     <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="14">
         <v>45748</v>
       </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="17">
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="14">
         <v>45778</v>
       </c>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="17">
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="14">
         <v>45809</v>
       </c>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="17">
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="14">
         <v>45839</v>
       </c>
-      <c r="S8" s="18"/>
-      <c r="T8" s="18"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="17">
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="14">
         <v>45870</v>
       </c>
-      <c r="X8" s="18"/>
-      <c r="Y8" s="18"/>
-      <c r="Z8" s="18"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="17">
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="14">
         <v>45901</v>
       </c>
-      <c r="AC8" s="18"/>
-      <c r="AD8" s="18"/>
-      <c r="AE8" s="18"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="17">
+      <c r="AC8" s="15"/>
+      <c r="AD8" s="15"/>
+      <c r="AE8" s="15"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="14">
         <v>45931</v>
       </c>
-      <c r="AH8" s="18"/>
-      <c r="AI8" s="18"/>
-      <c r="AJ8" s="18"/>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="17">
+      <c r="AH8" s="15"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="15"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="14">
         <v>45962</v>
       </c>
-      <c r="AM8" s="18"/>
-      <c r="AN8" s="18"/>
-      <c r="AO8" s="18"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="17">
+      <c r="AM8" s="15"/>
+      <c r="AN8" s="15"/>
+      <c r="AO8" s="15"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="14">
         <v>45992</v>
       </c>
-      <c r="AR8" s="18"/>
-      <c r="AS8" s="18"/>
-      <c r="AT8" s="18"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="17">
+      <c r="AR8" s="15"/>
+      <c r="AS8" s="15"/>
+      <c r="AT8" s="15"/>
+      <c r="AU8" s="16"/>
+      <c r="AV8" s="14">
         <v>46023</v>
       </c>
-      <c r="AW8" s="18"/>
-      <c r="AX8" s="18"/>
-      <c r="AY8" s="18"/>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="17">
+      <c r="AW8" s="15"/>
+      <c r="AX8" s="15"/>
+      <c r="AY8" s="15"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="14">
         <v>46054</v>
       </c>
-      <c r="BB8" s="18"/>
-      <c r="BC8" s="18"/>
-      <c r="BD8" s="18"/>
-      <c r="BE8" s="19"/>
-      <c r="BF8" s="17">
+      <c r="BB8" s="15"/>
+      <c r="BC8" s="15"/>
+      <c r="BD8" s="15"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="14">
         <v>46082</v>
       </c>
-      <c r="BG8" s="18"/>
-      <c r="BH8" s="18"/>
-      <c r="BI8" s="18"/>
-      <c r="BJ8" s="19"/>
+      <c r="BG8" s="15"/>
+      <c r="BH8" s="15"/>
+      <c r="BI8" s="15"/>
+      <c r="BJ8" s="16"/>
     </row>
     <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>47220</v>
+        <v>47238</v>
       </c>
       <c r="F10" s="5">
-        <v>74110</v>
+        <v>74128</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.99893515211149897</v>
+        <v>0.99917777568103083</v>
       </c>
       <c r="H10" s="5">
         <v>75899</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>45378</v>
+        <v>45396</v>
       </c>
       <c r="K10" s="5">
-        <v>74845</v>
+        <v>74863</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.98611312402007933</v>
+        <v>0.98635028129487867</v>
       </c>
       <c r="M10" s="5">
         <v>134494</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>88109</v>
+        <v>88150</v>
       </c>
       <c r="P10" s="5">
-        <v>134328</v>
+        <v>134369</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99876574419676711</v>
+        <v>0.99907059050961378</v>
       </c>
       <c r="R10" s="5">
         <v>73914</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42258</v>
+        <v>42283</v>
       </c>
       <c r="U10" s="5">
-        <v>73585</v>
+        <v>73610</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>0.99554888113212647</v>
+        <v>0.99588711204913816</v>
       </c>
       <c r="W10" s="5">
         <v>75592</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42475</v>
+        <v>42507</v>
       </c>
       <c r="Z10" s="5">
-        <v>74600</v>
+        <v>74632</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98687691819240131</v>
+        <v>0.98730024341200129</v>
       </c>
       <c r="AB10" s="5">
         <v>136558</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>88990</v>
+        <v>89083</v>
       </c>
       <c r="AE10" s="5">
-        <v>136112</v>
+        <v>136205</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.99673398848840788</v>
+        <v>0.9974150177946367</v>
       </c>
       <c r="AG10" s="5">
         <v>73704</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>42289</v>
+        <v>42370</v>
       </c>
       <c r="AJ10" s="5">
-        <v>73276</v>
+        <v>73357</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99419298816889179</v>
+        <v>0.99529197872571362</v>
       </c>
       <c r="AL10" s="5">
         <v>75897</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>42684</v>
+        <v>42806</v>
       </c>
       <c r="AO10" s="5">
-        <v>75850</v>
+        <v>75972</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99938073968668062</v>
+        <v>1.0009881813510415</v>
       </c>
       <c r="AQ10" s="5">
         <v>140117</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>90952</v>
+        <v>91315</v>
       </c>
       <c r="AT10" s="5">
-        <v>139975</v>
+        <v>140338</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>0.99898656123097129</v>
+        <v>1.0015772532954603</v>
       </c>
       <c r="AV10" s="5">
         <v>75508</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>13072</v>
+        <v>13329</v>
       </c>
       <c r="AY10" s="5">
-        <v>75468</v>
+        <v>75725</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99947025480743767</v>
+        <v>1.0028738676696509</v>
       </c>
       <c r="BA10" s="5">
         <v>78056</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>42350</v>
+        <v>42785</v>
       </c>
       <c r="BD10" s="5">
-        <v>76789</v>
+        <v>77224</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98376806395408423</v>
+        <v>0.98934098595879882</v>
       </c>
       <c r="BF10" s="5">
         <v>144885</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>90212</v>
+        <v>91945</v>
       </c>
       <c r="BI10" s="5">
-        <v>139712</v>
+        <v>141445</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.9642958208234117</v>
+        <v>0.97625703143872722</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1469,14 +1469,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>16296</v>
+        <v>16308</v>
       </c>
       <c r="F11" s="5">
-        <v>47460</v>
+        <v>47472</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99216055189714647</v>
+        <v>0.99241141423643775</v>
       </c>
       <c r="H11" s="5">
         <v>49123</v>
@@ -1486,14 +1486,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>16759</v>
+        <v>16782</v>
       </c>
       <c r="K11" s="5">
-        <v>48184</v>
+        <v>48207</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98088471795289378</v>
+        <v>0.98135293039920202</v>
       </c>
       <c r="M11" s="5">
         <v>111861</v>
@@ -1503,14 +1503,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>48163</v>
+        <v>48211</v>
       </c>
       <c r="P11" s="5">
-        <v>111421</v>
+        <v>111469</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99606654687513974</v>
+        <v>0.99649565085239722</v>
       </c>
       <c r="R11" s="5">
         <v>47958</v>
@@ -1520,14 +1520,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15871</v>
+        <v>15907</v>
       </c>
       <c r="U11" s="5">
-        <v>47506</v>
+        <v>47542</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99057508653405058</v>
+        <v>0.99132574335877222</v>
       </c>
       <c r="W11" s="5">
         <v>49731</v>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>15170</v>
+        <v>15207</v>
       </c>
       <c r="Z11" s="5">
-        <v>48184</v>
+        <v>48221</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.9688926424161991</v>
+        <v>0.96963664515091186</v>
       </c>
       <c r="AB11" s="5">
         <v>113134</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>50340</v>
+        <v>50421</v>
       </c>
       <c r="AE11" s="5">
-        <v>112104</v>
+        <v>112185</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.99089575194017709</v>
+        <v>0.9916117170788622</v>
       </c>
       <c r="AG11" s="5">
         <v>48119</v>
@@ -1571,14 +1571,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15350</v>
+        <v>15406</v>
       </c>
       <c r="AJ11" s="5">
-        <v>47558</v>
+        <v>47614</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.98834140360356615</v>
+        <v>0.98950518506203367</v>
       </c>
       <c r="AL11" s="5">
         <v>49938</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14716</v>
+        <v>14796</v>
       </c>
       <c r="AO11" s="5">
-        <v>48897</v>
+        <v>48977</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.97915415114742277</v>
+        <v>0.98075613761063718</v>
       </c>
       <c r="AQ11" s="5">
         <v>114343</v>
@@ -1605,14 +1605,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>46933</v>
+        <v>47199</v>
       </c>
       <c r="AT11" s="5">
-        <v>113627</v>
+        <v>113893</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99373813875794759</v>
+        <v>0.99606447268306764</v>
       </c>
       <c r="AV11" s="5">
         <v>49251</v>
@@ -1622,14 +1622,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>6592</v>
+        <v>6759</v>
       </c>
       <c r="AY11" s="5">
-        <v>48355</v>
+        <v>48522</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.98180747599033524</v>
+        <v>0.98519827008588656</v>
       </c>
       <c r="BA11" s="5">
         <v>50523</v>
@@ -1639,14 +1639,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>14142</v>
+        <v>14396</v>
       </c>
       <c r="BD11" s="5">
-        <v>49109</v>
+        <v>49363</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97201274666983351</v>
+        <v>0.97704015992716187</v>
       </c>
       <c r="BF11" s="5">
         <v>116408</v>
@@ -1656,14 +1656,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>46004</v>
+        <v>47176</v>
       </c>
       <c r="BI11" s="5">
-        <v>112433</v>
+        <v>113605</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.96585286234623047</v>
+        <v>0.97592089890729161</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1681,14 +1681,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>44037</v>
+        <v>44065</v>
       </c>
       <c r="F12" s="5">
-        <v>181590</v>
+        <v>181618</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99366340534506536</v>
+        <v>0.99381662179613461</v>
       </c>
       <c r="H12" s="5">
         <v>186824</v>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>41194</v>
+        <v>41227</v>
       </c>
       <c r="K12" s="5">
-        <v>184344</v>
+        <v>184377</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98672547424313795</v>
+        <v>0.9869021110778059</v>
       </c>
       <c r="M12" s="5">
         <v>372375</v>
@@ -1715,14 +1715,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>107038</v>
+        <v>107158</v>
       </c>
       <c r="P12" s="5">
-        <v>371210</v>
+        <v>371330</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99687143336690165</v>
+        <v>0.99719368915743534</v>
       </c>
       <c r="R12" s="5">
         <v>184659</v>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40527</v>
+        <v>40573</v>
       </c>
       <c r="U12" s="5">
-        <v>183266</v>
+        <v>183312</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99245636551697991</v>
+        <v>0.99270547333192538</v>
       </c>
       <c r="W12" s="5">
         <v>189081</v>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>40687</v>
+        <v>40743</v>
       </c>
       <c r="Z12" s="5">
-        <v>185492</v>
+        <v>185548</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98101871684621933</v>
+        <v>0.98131488621278706</v>
       </c>
       <c r="AB12" s="5">
         <v>377441</v>
@@ -1766,14 +1766,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>113427</v>
+        <v>113667</v>
       </c>
       <c r="AE12" s="5">
-        <v>374519</v>
+        <v>374759</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99225839270243565</v>
+        <v>0.99289425367143469</v>
       </c>
       <c r="AG12" s="5">
         <v>186148</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>41786</v>
+        <v>41943</v>
       </c>
       <c r="AJ12" s="5">
-        <v>184494</v>
+        <v>184651</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99111459698734339</v>
+        <v>0.99195801190450605</v>
       </c>
       <c r="AL12" s="5">
         <v>192239</v>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>41016</v>
+        <v>41283</v>
       </c>
       <c r="AO12" s="5">
-        <v>190661</v>
+        <v>190928</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.9917914679123383</v>
+        <v>0.99318036402603005</v>
       </c>
       <c r="AQ12" s="5">
         <v>384779</v>
@@ -1817,14 +1817,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>111304</v>
+        <v>112338</v>
       </c>
       <c r="AT12" s="5">
-        <v>382693</v>
+        <v>383727</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99457870621837474</v>
+        <v>0.99726596305931459</v>
       </c>
       <c r="AV12" s="5">
         <v>191743</v>
@@ -1834,14 +1834,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>24455</v>
+        <v>25047</v>
       </c>
       <c r="AY12" s="5">
-        <v>189960</v>
+        <v>190552</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99070109469446077</v>
+        <v>0.99378856072972677</v>
       </c>
       <c r="BA12" s="5">
         <v>197493</v>
@@ -1851,14 +1851,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>39349</v>
+        <v>40244</v>
       </c>
       <c r="BD12" s="5">
-        <v>193008</v>
+        <v>193903</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.97729033434096402</v>
+        <v>0.98182214053156314</v>
       </c>
       <c r="BF12" s="5">
         <v>393305</v>
@@ -1868,14 +1868,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>104708</v>
+        <v>109137</v>
       </c>
       <c r="BI12" s="5">
-        <v>381297</v>
+        <v>385726</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.96946898717280483</v>
+        <v>0.98072996783666622</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3912</v>
+        <v>3914</v>
       </c>
       <c r="F13" s="5">
-        <v>17986</v>
+        <v>17988</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>0.99728306071527584</v>
+        <v>0.99739395619628501</v>
       </c>
       <c r="H13" s="5">
         <v>18257</v>
@@ -1910,14 +1910,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3768</v>
+        <v>3769</v>
       </c>
       <c r="K13" s="5">
-        <v>18070</v>
+        <v>18071</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.9897573533439229</v>
+        <v>0.98981212685545272</v>
       </c>
       <c r="M13" s="5">
         <v>29011</v>
@@ -1927,14 +1927,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>7180</v>
+        <v>7185</v>
       </c>
       <c r="P13" s="5">
-        <v>29031</v>
+        <v>29036</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.0006893936782599</v>
+        <v>1.000861742097825</v>
       </c>
       <c r="R13" s="5">
         <v>18140</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3731</v>
+        <v>3734</v>
       </c>
       <c r="U13" s="5">
-        <v>18121</v>
+        <v>18124</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99895259095920619</v>
+        <v>0.99911797133406832</v>
       </c>
       <c r="W13" s="5">
         <v>18401</v>
@@ -1961,14 +1961,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>3480</v>
+        <v>3486</v>
       </c>
       <c r="Z13" s="5">
-        <v>18228</v>
+        <v>18234</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.99059833704689959</v>
+        <v>0.9909244062822673</v>
       </c>
       <c r="AB13" s="5">
         <v>29242</v>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7522</v>
+        <v>7542</v>
       </c>
       <c r="AE13" s="5">
-        <v>29244</v>
+        <v>29264</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>1.0000683947746392</v>
+        <v>1.0007523425210314</v>
       </c>
       <c r="AG13" s="5">
         <v>18261</v>
@@ -1995,14 +1995,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3770</v>
+        <v>3791</v>
       </c>
       <c r="AJ13" s="5">
-        <v>18364</v>
+        <v>18385</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>1.0056404359016484</v>
+        <v>1.0067904276874213</v>
       </c>
       <c r="AL13" s="5">
         <v>18637</v>
@@ -2012,14 +2012,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3620</v>
+        <v>3655</v>
       </c>
       <c r="AO13" s="5">
-        <v>18683</v>
+        <v>18718</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>1.0024682084026399</v>
+        <v>1.0043461930568225</v>
       </c>
       <c r="AQ13" s="5">
         <v>29668</v>
@@ -2029,14 +2029,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>7343</v>
+        <v>7428</v>
       </c>
       <c r="AT13" s="5">
-        <v>29734</v>
+        <v>29819</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>1.0022246191182418</v>
+        <v>1.0050896588917353</v>
       </c>
       <c r="AV13" s="5">
         <v>18676</v>
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>2394</v>
+        <v>2460</v>
       </c>
       <c r="AY13" s="5">
-        <v>18765</v>
+        <v>18831</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>1.0047654744056542</v>
+        <v>1.0082994217177126</v>
       </c>
       <c r="BA13" s="5">
         <v>19025</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3464</v>
+        <v>3554</v>
       </c>
       <c r="BD13" s="5">
-        <v>18979</v>
+        <v>19069</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>0.99758212877792374</v>
+        <v>1.0023127463863337</v>
       </c>
       <c r="BF13" s="5">
         <v>30254</v>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>6699</v>
+        <v>7042</v>
       </c>
       <c r="BI13" s="5">
-        <v>29575</v>
+        <v>29918</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>0.97755668671911156</v>
+        <v>0.988894030541416</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>42227</v>
+        <v>42253</v>
       </c>
       <c r="F14" s="5">
-        <v>95131</v>
+        <v>95157</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>1.0054749347341274</v>
+        <v>1.0057497384080412</v>
       </c>
       <c r="H14" s="5">
         <v>97351</v>
@@ -2122,14 +2122,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>43488</v>
+        <v>43515</v>
       </c>
       <c r="K14" s="5">
-        <v>97108</v>
+        <v>97135</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.99750387772082461</v>
+        <v>0.99778122464073304</v>
       </c>
       <c r="M14" s="5">
         <v>172809</v>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>88080</v>
+        <v>88148</v>
       </c>
       <c r="P14" s="5">
-        <v>172865</v>
+        <v>172933</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>1.0003240571960952</v>
+        <v>1.0007175552199248</v>
       </c>
       <c r="R14" s="5">
         <v>97326</v>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>41819</v>
+        <v>41860</v>
       </c>
       <c r="U14" s="5">
-        <v>96343</v>
+        <v>96384</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98989992396687421</v>
+        <v>0.99032118858270146</v>
       </c>
       <c r="W14" s="5">
         <v>98912</v>
@@ -2173,14 +2173,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>41254</v>
+        <v>41310</v>
       </c>
       <c r="Z14" s="5">
-        <v>97630</v>
+        <v>97686</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.98703898414752511</v>
+        <v>0.9876051439663539</v>
       </c>
       <c r="AB14" s="5">
         <v>175426</v>
@@ -2190,14 +2190,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>91333</v>
+        <v>91491</v>
       </c>
       <c r="AE14" s="5">
-        <v>175350</v>
+        <v>175508</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99956676889400664</v>
+        <v>1.0004674335617296</v>
       </c>
       <c r="AG14" s="5">
         <v>98057</v>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>42473</v>
+        <v>42587</v>
       </c>
       <c r="AJ14" s="5">
-        <v>97818</v>
+        <v>97932</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99756264213671642</v>
+        <v>0.99872523124305246</v>
       </c>
       <c r="AL14" s="5">
         <v>101581</v>
@@ -2224,14 +2224,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>43473</v>
+        <v>43653</v>
       </c>
       <c r="AO14" s="5">
-        <v>102179</v>
+        <v>102359</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>1.0058869276734823</v>
+        <v>1.0076589125919218</v>
       </c>
       <c r="AQ14" s="5">
         <v>182247</v>
@@ -2241,14 +2241,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>92092</v>
+        <v>92692</v>
       </c>
       <c r="AT14" s="5">
-        <v>181861</v>
+        <v>182461</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>0.99788199531405186</v>
+        <v>1.0011742305771838</v>
       </c>
       <c r="AV14" s="5">
         <v>102257</v>
@@ -2258,14 +2258,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>16843</v>
+        <v>17196</v>
       </c>
       <c r="AY14" s="5">
-        <v>102351</v>
+        <v>102704</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>1.0009192524717134</v>
+        <v>1.0043713388814457</v>
       </c>
       <c r="BA14" s="5">
         <v>106311</v>
@@ -2275,14 +2275,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>43836</v>
+        <v>44362</v>
       </c>
       <c r="BD14" s="5">
-        <v>104572</v>
+        <v>105098</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.9836423324021033</v>
+        <v>0.98859008004816062</v>
       </c>
       <c r="BF14" s="5">
         <v>189210</v>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>89875</v>
+        <v>92323</v>
       </c>
       <c r="BI14" s="5">
-        <v>182726</v>
+        <v>185174</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.96573119813963326</v>
+        <v>0.97866920353046882</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2317,14 +2317,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>85840</v>
+        <v>85871</v>
       </c>
       <c r="F15" s="5">
-        <v>323622</v>
+        <v>323653</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.99638542346580627</v>
+        <v>0.99648086799098512</v>
       </c>
       <c r="H15" s="5">
         <v>331968</v>
@@ -2334,14 +2334,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>85197</v>
+        <v>85231</v>
       </c>
       <c r="K15" s="5">
-        <v>329259</v>
+        <v>329293</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.99183957489878538</v>
+        <v>0.99194199440909969</v>
       </c>
       <c r="M15" s="5">
         <v>549212</v>
@@ -2351,14 +2351,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>165435</v>
+        <v>165513</v>
       </c>
       <c r="P15" s="5">
-        <v>548355</v>
+        <v>548433</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99843958252915088</v>
+        <v>0.99858160418927477</v>
       </c>
       <c r="R15" s="5">
         <v>333160</v>
@@ -2368,14 +2368,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>84415</v>
+        <v>84474</v>
       </c>
       <c r="U15" s="5">
-        <v>331643</v>
+        <v>331702</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99544663224876939</v>
+        <v>0.99562372433665502</v>
       </c>
       <c r="W15" s="5">
         <v>340519</v>
@@ -2385,14 +2385,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>82266</v>
+        <v>82353</v>
       </c>
       <c r="Z15" s="5">
-        <v>336572</v>
+        <v>336659</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98840886998963351</v>
+        <v>0.98866436234101474</v>
       </c>
       <c r="AB15" s="5">
         <v>562036</v>
@@ -2402,14 +2402,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>175948</v>
+        <v>176176</v>
       </c>
       <c r="AE15" s="5">
-        <v>559194</v>
+        <v>559422</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99494338440953956</v>
+        <v>0.99534905237386928</v>
       </c>
       <c r="AG15" s="5">
         <v>340264</v>
@@ -2419,14 +2419,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>87536</v>
+        <v>87776</v>
       </c>
       <c r="AJ15" s="5">
-        <v>338430</v>
+        <v>338670</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99461006747701786</v>
+        <v>0.99531540215832415</v>
       </c>
       <c r="AL15" s="5">
         <v>350627</v>
@@ -2436,14 +2436,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>88146</v>
+        <v>88581</v>
       </c>
       <c r="AO15" s="5">
-        <v>351530</v>
+        <v>351965</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>1.0025753863792577</v>
+        <v>1.0038160210137839</v>
       </c>
       <c r="AQ15" s="5">
         <v>580651</v>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>175240</v>
+        <v>176561</v>
       </c>
       <c r="AT15" s="5">
-        <v>580429</v>
+        <v>581750</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99961767051120209</v>
+        <v>1.0018927031900402</v>
       </c>
       <c r="AV15" s="5">
         <v>355536</v>
@@ -2470,14 +2470,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>49396</v>
+        <v>50477</v>
       </c>
       <c r="AY15" s="5">
-        <v>354416</v>
+        <v>355497</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99684982674047073</v>
+        <v>0.99989030646685573</v>
       </c>
       <c r="BA15" s="5">
         <v>365201</v>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>86314</v>
+        <v>87956</v>
       </c>
       <c r="BD15" s="5">
-        <v>360650</v>
+        <v>362292</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98753836928157368</v>
+        <v>0.9920345234542074</v>
       </c>
       <c r="BF15" s="5">
         <v>600313</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>167231</v>
+        <v>173370</v>
       </c>
       <c r="BI15" s="5">
-        <v>584829</v>
+        <v>590968</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.97420678879184697</v>
+        <v>0.98443312072202338</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2529,14 +2529,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>119425</v>
+        <v>119518</v>
       </c>
       <c r="F16" s="5">
-        <v>450731</v>
+        <v>450824</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99385470918464092</v>
+        <v>0.99405977271023427</v>
       </c>
       <c r="H16" s="5">
         <v>461360</v>
@@ -2546,14 +2546,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>119733</v>
+        <v>119844</v>
       </c>
       <c r="K16" s="5">
-        <v>458353</v>
+        <v>458464</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.99348231316108893</v>
+        <v>0.99372290619039361</v>
       </c>
       <c r="M16" s="5">
         <v>788355</v>
@@ -2563,14 +2563,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>217060</v>
+        <v>217313</v>
       </c>
       <c r="P16" s="5">
-        <v>789043</v>
+        <v>789296</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>1.0008727032872247</v>
+        <v>1.0011936246995325</v>
       </c>
       <c r="R16" s="5">
         <v>462019</v>
@@ -2580,14 +2580,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>119844</v>
+        <v>120019</v>
       </c>
       <c r="U16" s="5">
-        <v>461375</v>
+        <v>461550</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99860611793021503</v>
+        <v>0.99898489023178705</v>
       </c>
       <c r="W16" s="5">
         <v>472236</v>
@@ -2597,14 +2597,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>115677</v>
+        <v>115888</v>
       </c>
       <c r="Z16" s="5">
-        <v>466758</v>
+        <v>466969</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98839986786267886</v>
+        <v>0.98884667835573736</v>
       </c>
       <c r="AB16" s="5">
         <v>804216</v>
@@ -2614,14 +2614,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>231914</v>
+        <v>232418</v>
       </c>
       <c r="AE16" s="5">
-        <v>801076</v>
+        <v>801580</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99609557631283141</v>
+        <v>0.99672227361803301</v>
       </c>
       <c r="AG16" s="5">
         <v>471201</v>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>121630</v>
+        <v>122076</v>
       </c>
       <c r="AJ16" s="5">
-        <v>468522</v>
+        <v>468968</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.99431452819497412</v>
+        <v>0.99526104571085372</v>
       </c>
       <c r="AL16" s="5">
         <v>484445</v>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>126713</v>
+        <v>127436</v>
       </c>
       <c r="AO16" s="5">
-        <v>488228</v>
+        <v>488951</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>1.0078089359989266</v>
+        <v>1.0093013654800855</v>
       </c>
       <c r="AQ16" s="5">
         <v>831010</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>234429</v>
+        <v>236406</v>
       </c>
       <c r="AT16" s="5">
-        <v>831425</v>
+        <v>833402</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>1.0004993923057484</v>
+        <v>1.0028784250490368</v>
       </c>
       <c r="AV16" s="5">
         <v>496237</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>70944</v>
+        <v>72631</v>
       </c>
       <c r="AY16" s="5">
-        <v>493812</v>
+        <v>495499</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99511322210959685</v>
+        <v>0.99851280738840509</v>
       </c>
       <c r="BA16" s="5">
         <v>510690</v>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>122088</v>
+        <v>124670</v>
       </c>
       <c r="BD16" s="5">
-        <v>501676</v>
+        <v>504258</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98234937045957427</v>
+        <v>0.98740527521588439</v>
       </c>
       <c r="BF16" s="5">
         <v>859721</v>
@@ -2716,14 +2716,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>219994</v>
+        <v>228619</v>
       </c>
       <c r="BI16" s="5">
-        <v>836930</v>
+        <v>845555</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.97349023694896364</v>
+        <v>0.98352256138910177</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>106370</v>
+        <v>106430</v>
       </c>
       <c r="F17" s="5">
-        <v>339455</v>
+        <v>339515</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99180737394779972</v>
+        <v>0.9919826797834389</v>
       </c>
       <c r="H17" s="5">
         <v>352243</v>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>105083</v>
+        <v>105160</v>
       </c>
       <c r="K17" s="5">
-        <v>347469</v>
+        <v>347546</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98644685628955009</v>
+        <v>0.98666545538165418</v>
       </c>
       <c r="M17" s="5">
         <v>765449</v>
@@ -2775,14 +2775,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>302483</v>
+        <v>302754</v>
       </c>
       <c r="P17" s="5">
-        <v>765433</v>
+        <v>765704</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99997909723574008</v>
+        <v>1.0003331378053926</v>
       </c>
       <c r="R17" s="5">
         <v>346814</v>
@@ -2792,14 +2792,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>103735</v>
+        <v>103856</v>
       </c>
       <c r="U17" s="5">
-        <v>346783</v>
+        <v>346904</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99991061491173938</v>
+        <v>1.0002595050949501</v>
       </c>
       <c r="W17" s="5">
         <v>360071</v>
@@ -2809,14 +2809,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>105241</v>
+        <v>105397</v>
       </c>
       <c r="Z17" s="5">
-        <v>355493</v>
+        <v>355649</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.98728584084805493</v>
+        <v>0.98771908873527725</v>
       </c>
       <c r="AB17" s="5">
         <v>784641</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>316881</v>
+        <v>317480</v>
       </c>
       <c r="AE17" s="5">
-        <v>783482</v>
+        <v>784081</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99852289136050754</v>
+        <v>0.99928629781008127</v>
       </c>
       <c r="AG17" s="5">
         <v>355351</v>
@@ -2843,14 +2843,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>109756</v>
+        <v>110107</v>
       </c>
       <c r="AJ17" s="5">
-        <v>354908</v>
+        <v>355259</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99875334528395865</v>
+        <v>0.99974110105219904</v>
       </c>
       <c r="AL17" s="5">
         <v>371770</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>111184</v>
+        <v>111701</v>
       </c>
       <c r="AO17" s="5">
-        <v>370973</v>
+        <v>371490</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.99785620141485332</v>
+        <v>0.99924684616832993</v>
       </c>
       <c r="AQ17" s="5">
         <v>810773</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>313140</v>
+        <v>315345</v>
       </c>
       <c r="AT17" s="5">
-        <v>809865</v>
+        <v>812070</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99888008110778237</v>
+        <v>1.0015997079330465</v>
       </c>
       <c r="AV17" s="5">
         <v>369648</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>51611</v>
+        <v>52665</v>
       </c>
       <c r="AY17" s="5">
-        <v>369042</v>
+        <v>370096</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99836060251915337</v>
+        <v>1.0012119638142232</v>
       </c>
       <c r="BA17" s="5">
         <v>385393</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>111301</v>
+        <v>112916</v>
       </c>
       <c r="BD17" s="5">
-        <v>379812</v>
+        <v>381427</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98551867833614004</v>
+        <v>0.98970920592745582</v>
       </c>
       <c r="BF17" s="5">
         <v>839843</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>310712</v>
+        <v>319856</v>
       </c>
       <c r="BI17" s="5">
-        <v>814366</v>
+        <v>823510</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.96966456825859115</v>
+        <v>0.98055231751648819</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>542100</v>
+        <v>542323</v>
       </c>
       <c r="F18" s="5">
-        <v>1062552</v>
+        <v>1062775</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99224545597167124</v>
+        <v>0.99245370059092908</v>
       </c>
       <c r="H18" s="5">
         <v>1089051</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>555187</v>
+        <v>555463</v>
       </c>
       <c r="K18" s="5">
-        <v>1079128</v>
+        <v>1079404</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.99088839732941802</v>
+        <v>0.99114182898688863</v>
       </c>
       <c r="M18" s="5">
         <v>1637429</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>874821</v>
+        <v>875374</v>
       </c>
       <c r="P18" s="5">
-        <v>1627609</v>
+        <v>1628162</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99400279340356135</v>
+        <v>0.99434051797055012</v>
       </c>
       <c r="R18" s="5">
         <v>1090030</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>544687</v>
+        <v>545114</v>
       </c>
       <c r="U18" s="5">
-        <v>1077748</v>
+        <v>1078175</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98873242020861807</v>
+        <v>0.98912415254626018</v>
       </c>
       <c r="W18" s="5">
         <v>1107435</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>538004</v>
+        <v>538555</v>
       </c>
       <c r="Z18" s="5">
-        <v>1089010</v>
+        <v>1089561</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98336245468131311</v>
+        <v>0.98386000081268876</v>
       </c>
       <c r="AB18" s="5">
         <v>1665905</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>903254</v>
+        <v>904474</v>
       </c>
       <c r="AE18" s="5">
-        <v>1650052</v>
+        <v>1651272</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.99048385111996184</v>
+        <v>0.99121618579690918</v>
       </c>
       <c r="AG18" s="5">
         <v>1104366</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>553683</v>
+        <v>554901</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1092490</v>
+        <v>1093708</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.98924631870231428</v>
+        <v>0.9903492139381328</v>
       </c>
       <c r="AL18" s="5">
         <v>1131950</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>562586</v>
+        <v>564470</v>
       </c>
       <c r="AO18" s="5">
-        <v>1130591</v>
+        <v>1132475</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.99879941693537699</v>
+        <v>1.0004638014046556</v>
       </c>
       <c r="AQ18" s="5">
         <v>1717059</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>916093</v>
+        <v>920710</v>
       </c>
       <c r="AT18" s="5">
-        <v>1708051</v>
+        <v>1712668</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99475382034047755</v>
+        <v>0.99744272037245085</v>
       </c>
       <c r="AV18" s="5">
         <v>1151692</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>177139</v>
+        <v>181135</v>
       </c>
       <c r="AY18" s="5">
-        <v>1142656</v>
+        <v>1146652</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99215415232544812</v>
+        <v>0.99562382998232168</v>
       </c>
       <c r="BA18" s="5">
         <v>1182353</v>
@@ -3123,14 +3123,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>571996</v>
+        <v>578030</v>
       </c>
       <c r="BD18" s="5">
-        <v>1160559</v>
+        <v>1166593</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98156726459864352</v>
+        <v>0.98667064742932098</v>
       </c>
       <c r="BF18" s="5">
         <v>1777125</v>
@@ -3140,14 +3140,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>898508</v>
+        <v>918551</v>
       </c>
       <c r="BI18" s="5">
-        <v>1715513</v>
+        <v>1735556</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.9653305198002391</v>
+        <v>0.97660884856158126</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3165,14 +3165,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>178268</v>
+        <v>178415</v>
       </c>
       <c r="F19" s="5">
-        <v>299262</v>
+        <v>299409</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97919959164842496</v>
+        <v>0.97968058268628588</v>
       </c>
       <c r="H19" s="5">
         <v>314567</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>183678</v>
+        <v>183869</v>
       </c>
       <c r="K19" s="5">
-        <v>306186</v>
+        <v>306377</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97335702727876727</v>
+        <v>0.97396421112195497</v>
       </c>
       <c r="M19" s="5">
         <v>534704</v>
@@ -3199,14 +3199,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>333123</v>
+        <v>333505</v>
       </c>
       <c r="P19" s="5">
-        <v>527288</v>
+        <v>527670</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.9861306442442922</v>
+        <v>0.9868450582004249</v>
       </c>
       <c r="R19" s="5">
         <v>310887</v>
@@ -3216,14 +3216,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>179210</v>
+        <v>179482</v>
       </c>
       <c r="U19" s="5">
-        <v>305079</v>
+        <v>305351</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.98131797083827887</v>
+        <v>0.98219288680453032</v>
       </c>
       <c r="W19" s="5">
         <v>321022</v>
@@ -3233,14 +3233,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>179100</v>
+        <v>179448</v>
       </c>
       <c r="Z19" s="5">
-        <v>310155</v>
+        <v>310503</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96614873746970609</v>
+        <v>0.96723277532380958</v>
       </c>
       <c r="AB19" s="5">
         <v>548160</v>
@@ -3250,14 +3250,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>350365</v>
+        <v>351167</v>
       </c>
       <c r="AE19" s="5">
-        <v>536755</v>
+        <v>537557</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.97919403093987156</v>
+        <v>0.98065710741389378</v>
       </c>
       <c r="AG19" s="5">
         <v>315587</v>
@@ -3267,14 +3267,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>188373</v>
+        <v>188980</v>
       </c>
       <c r="AJ19" s="5">
-        <v>308448</v>
+        <v>309055</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97737866261918271</v>
+        <v>0.97930206250574325</v>
       </c>
       <c r="AL19" s="5">
         <v>327315</v>
@@ -3284,14 +3284,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>187772</v>
+        <v>188646</v>
       </c>
       <c r="AO19" s="5">
-        <v>320866</v>
+        <v>321740</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.98029726715854759</v>
+        <v>0.98296747781189375</v>
       </c>
       <c r="AQ19" s="5">
         <v>564697</v>
@@ -3301,14 +3301,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>354206</v>
+        <v>356720</v>
       </c>
       <c r="AT19" s="5">
-        <v>556541</v>
+        <v>559055</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.98555685615471655</v>
+        <v>0.99000880118010193</v>
       </c>
       <c r="AV19" s="5">
         <v>330794</v>
@@ -3318,14 +3318,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>56977</v>
+        <v>58915</v>
       </c>
       <c r="AY19" s="5">
-        <v>325102</v>
+        <v>327040</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98279291643742028</v>
+        <v>0.98865154748876949</v>
       </c>
       <c r="BA19" s="5">
         <v>346688</v>
@@ -3335,14 +3335,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>194070</v>
+        <v>196931</v>
       </c>
       <c r="BD19" s="5">
-        <v>333029</v>
+        <v>335890</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96060146298689308</v>
+        <v>0.96885383976370687</v>
       </c>
       <c r="BF19" s="5">
         <v>595475</v>
@@ -3352,14 +3352,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>355384</v>
+        <v>366499</v>
       </c>
       <c r="BI19" s="5">
-        <v>554954</v>
+        <v>566069</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.93195180318233339</v>
+        <v>0.95061757420546622</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3885</v>
+        <v>3891</v>
       </c>
       <c r="F20" s="5">
-        <v>6472</v>
+        <v>6478</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.99005660088725711</v>
+        <v>0.99097445311304877</v>
       </c>
       <c r="H20" s="5">
         <v>6601</v>
@@ -3394,14 +3394,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3834</v>
+        <v>3840</v>
       </c>
       <c r="K20" s="5">
-        <v>6504</v>
+        <v>6510</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.98530525677927583</v>
+        <v>0.98621420996818665</v>
       </c>
       <c r="M20" s="5">
         <v>10050</v>
@@ -3411,14 +3411,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5555</v>
+        <v>5564</v>
       </c>
       <c r="P20" s="5">
-        <v>10023</v>
+        <v>10032</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99731343283582086</v>
+        <v>0.99820895522388065</v>
       </c>
       <c r="R20" s="5">
         <v>6485</v>
@@ -3428,14 +3428,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3617</v>
+        <v>3624</v>
       </c>
       <c r="U20" s="5">
-        <v>6421</v>
+        <v>6428</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.99013107170393211</v>
+        <v>0.99121048573631454</v>
       </c>
       <c r="W20" s="5">
         <v>6573</v>
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3425</v>
+        <v>3433</v>
       </c>
       <c r="Z20" s="5">
-        <v>6433</v>
+        <v>6441</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.9787007454739084</v>
+        <v>0.97991784573254226</v>
       </c>
       <c r="AB20" s="5">
         <v>10123</v>
@@ -3462,14 +3462,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>6127</v>
+        <v>6145</v>
       </c>
       <c r="AE20" s="5">
-        <v>10023</v>
+        <v>10041</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.9901215054825645</v>
+        <v>0.99189963449570284</v>
       </c>
       <c r="AG20" s="5">
         <v>6547</v>
@@ -3479,14 +3479,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3418</v>
+        <v>3434</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6436</v>
+        <v>6452</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.98304566977241481</v>
+        <v>0.98548953719260735</v>
       </c>
       <c r="AL20" s="5">
         <v>6649</v>
@@ -3496,14 +3496,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3422</v>
+        <v>3441</v>
       </c>
       <c r="AO20" s="5">
-        <v>6513</v>
+        <v>6532</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.97954579636035499</v>
+        <v>0.98240336892765834</v>
       </c>
       <c r="AQ20" s="5">
         <v>10228</v>
@@ -3513,14 +3513,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>6040</v>
+        <v>6094</v>
       </c>
       <c r="AT20" s="5">
-        <v>10036</v>
+        <v>10090</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>0.98122800156433321</v>
+        <v>0.98650762612436449</v>
       </c>
       <c r="AV20" s="5">
         <v>6568</v>
@@ -3530,14 +3530,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>1314</v>
+        <v>1356</v>
       </c>
       <c r="AY20" s="5">
-        <v>6398</v>
+        <v>6440</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.97411693057247262</v>
+        <v>0.98051157125456756</v>
       </c>
       <c r="BA20" s="5">
         <v>6793</v>
@@ -3547,14 +3547,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3225</v>
+        <v>3281</v>
       </c>
       <c r="BD20" s="5">
-        <v>6423</v>
+        <v>6479</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.94553216546444874</v>
+        <v>0.9537759458265862</v>
       </c>
       <c r="BF20" s="5">
         <v>10395</v>
@@ -3564,14 +3564,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>5507</v>
+        <v>5739</v>
       </c>
       <c r="BI20" s="5">
-        <v>9715</v>
+        <v>9947</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.93458393458393463</v>
+        <v>0.95690235690235692</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>9069</v>
+        <v>9086</v>
       </c>
       <c r="F21" s="5">
-        <v>12039</v>
+        <v>12056</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0024146544546211</v>
+        <v>1.0038301415487094</v>
       </c>
       <c r="H21" s="5">
         <v>12254</v>
@@ -3606,14 +3606,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>9034</v>
+        <v>9054</v>
       </c>
       <c r="K21" s="5">
-        <v>12258</v>
+        <v>12278</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>1.0003264240248082</v>
+        <v>1.0019585441488494</v>
       </c>
       <c r="M21" s="5">
         <v>16207</v>
@@ -3623,14 +3623,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>12101</v>
+        <v>12134</v>
       </c>
       <c r="P21" s="5">
-        <v>16368</v>
+        <v>16401</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0099339791448139</v>
+        <v>1.0119701363608318</v>
       </c>
       <c r="R21" s="5">
         <v>12383</v>
@@ -3640,14 +3640,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>9111</v>
+        <v>9143</v>
       </c>
       <c r="U21" s="5">
-        <v>12530</v>
+        <v>12562</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0118711136235161</v>
+        <v>1.0144553016231932</v>
       </c>
       <c r="W21" s="5">
         <v>12782</v>
@@ -3657,14 +3657,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>9131</v>
+        <v>9165</v>
       </c>
       <c r="Z21" s="5">
-        <v>12732</v>
+        <v>12766</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>0.99608824910029725</v>
+        <v>0.99874823971209514</v>
       </c>
       <c r="AB21" s="5">
         <v>16816</v>
@@ -3674,14 +3674,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>12579</v>
+        <v>12640</v>
       </c>
       <c r="AE21" s="5">
-        <v>16788</v>
+        <v>16849</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>0.99833491912464323</v>
+        <v>1.0019624167459562</v>
       </c>
       <c r="AG21" s="5">
         <v>12696</v>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>9234</v>
+        <v>9293</v>
       </c>
       <c r="AJ21" s="5">
-        <v>12676</v>
+        <v>12735</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>0.99842470069313172</v>
+        <v>1.0030718336483933</v>
       </c>
       <c r="AL21" s="5">
         <v>13072</v>
@@ -3708,14 +3708,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>9236</v>
+        <v>9313</v>
       </c>
       <c r="AO21" s="5">
-        <v>12887</v>
+        <v>12964</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>0.9858476132190942</v>
+        <v>0.99173806609547122</v>
       </c>
       <c r="AQ21" s="5">
         <v>17310</v>
@@ -3725,14 +3725,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>12568</v>
+        <v>12711</v>
       </c>
       <c r="AT21" s="5">
-        <v>17047</v>
+        <v>17190</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>0.98480647024841128</v>
+        <v>0.99306759098786823</v>
       </c>
       <c r="AV21" s="5">
         <v>13094</v>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>3251</v>
+        <v>3392</v>
       </c>
       <c r="AY21" s="5">
-        <v>12740</v>
+        <v>12881</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>0.97296471666412099</v>
+        <v>0.983733007484344</v>
       </c>
       <c r="BA21" s="5">
         <v>13518</v>
@@ -3759,14 +3759,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8612</v>
+        <v>8835</v>
       </c>
       <c r="BD21" s="5">
-        <v>12760</v>
+        <v>12983</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>0.94392661636336739</v>
+        <v>0.9604231395176801</v>
       </c>
       <c r="BF21" s="5">
         <v>17905</v>
@@ -3776,14 +3776,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11084</v>
+        <v>11758</v>
       </c>
       <c r="BI21" s="5">
-        <v>15692</v>
+        <v>16366</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>0.87640323931862607</v>
+        <v>0.91404635576654569</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4860</v>
+        <v>4868</v>
       </c>
       <c r="F22" s="5">
-        <v>6973</v>
+        <v>6981</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99671240708976561</v>
+        <v>0.99785591766723847</v>
       </c>
       <c r="H22" s="5">
         <v>7077</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4808</v>
+        <v>4818</v>
       </c>
       <c r="K22" s="5">
-        <v>7028</v>
+        <v>7038</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.99307616221562811</v>
+        <v>0.9944891903348877</v>
       </c>
       <c r="M22" s="5">
         <v>8504</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5740</v>
+        <v>5751</v>
       </c>
       <c r="P22" s="5">
-        <v>8516</v>
+        <v>8527</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0014111006585136</v>
+        <v>1.0027046095954846</v>
       </c>
       <c r="R22" s="5">
         <v>7111</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4628</v>
+        <v>4635</v>
       </c>
       <c r="U22" s="5">
-        <v>7068</v>
+        <v>7075</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>0.99395303051610184</v>
+        <v>0.9949374208972015</v>
       </c>
       <c r="W22" s="5">
         <v>7191</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4618</v>
+        <v>4631</v>
       </c>
       <c r="Z22" s="5">
-        <v>7127</v>
+        <v>7140</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99109998609372829</v>
+        <v>0.99290780141843971</v>
       </c>
       <c r="AB22" s="5">
         <v>8707</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5872</v>
+        <v>5889</v>
       </c>
       <c r="AE22" s="5">
-        <v>8648</v>
+        <v>8665</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>0.99322384288503507</v>
+        <v>0.99517629493510973</v>
       </c>
       <c r="AG22" s="5">
         <v>7162</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4658</v>
+        <v>4682</v>
       </c>
       <c r="AJ22" s="5">
-        <v>7111</v>
+        <v>7135</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>0.99287908405473335</v>
+        <v>0.99623010332309414</v>
       </c>
       <c r="AL22" s="5">
         <v>7226</v>
@@ -3920,14 +3920,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4643</v>
+        <v>4673</v>
       </c>
       <c r="AO22" s="5">
-        <v>7157</v>
+        <v>7187</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.99045114862994743</v>
+        <v>0.99460282313866588</v>
       </c>
       <c r="AQ22" s="5">
         <v>8754</v>
@@ -3937,14 +3937,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>6048</v>
+        <v>6102</v>
       </c>
       <c r="AT22" s="5">
-        <v>8660</v>
+        <v>8714</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>0.98926205163353897</v>
+        <v>0.99543066026959104</v>
       </c>
       <c r="AV22" s="5">
         <v>7182</v>
@@ -3954,14 +3954,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>1650</v>
+        <v>1715</v>
       </c>
       <c r="AY22" s="5">
-        <v>7036</v>
+        <v>7101</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.97967140072403225</v>
+        <v>0.98872180451127822</v>
       </c>
       <c r="BA22" s="5">
         <v>7296</v>
@@ -3971,14 +3971,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4464</v>
+        <v>4550</v>
       </c>
       <c r="BD22" s="5">
-        <v>7032</v>
+        <v>7118</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.96381578947368418</v>
+        <v>0.97560307017543857</v>
       </c>
       <c r="BF22" s="5">
         <v>8939</v>
@@ -3988,14 +3988,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5374</v>
+        <v>5620</v>
       </c>
       <c r="BI22" s="5">
-        <v>8196</v>
+        <v>8442</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.91688108289517845</v>
+        <v>0.94440093970242756</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4013,14 +4013,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6663</v>
+        <v>6671</v>
       </c>
       <c r="F23" s="5">
-        <v>9191</v>
+        <v>9199</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.97703837567768681</v>
+        <v>0.97788880620814289</v>
       </c>
       <c r="H23" s="5">
         <v>9786</v>
@@ -4030,14 +4030,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7330</v>
+        <v>7342</v>
       </c>
       <c r="K23" s="5">
-        <v>9327</v>
+        <v>9339</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.95309625996321279</v>
+        <v>0.95432250153280196</v>
       </c>
       <c r="M23" s="5">
         <v>12056</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8581</v>
+        <v>8598</v>
       </c>
       <c r="P23" s="5">
-        <v>11866</v>
+        <v>11883</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98424021234240211</v>
+        <v>0.98565029860650299</v>
       </c>
       <c r="R23" s="5">
         <v>9480</v>
@@ -4064,14 +4064,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6607</v>
+        <v>6620</v>
       </c>
       <c r="U23" s="5">
-        <v>9381</v>
+        <v>9394</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.98955696202531651</v>
+        <v>0.99092827004219408</v>
       </c>
       <c r="W23" s="5">
         <v>9764</v>
@@ -4081,14 +4081,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6621</v>
+        <v>6638</v>
       </c>
       <c r="Z23" s="5">
-        <v>9449</v>
+        <v>9466</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.96773863170831631</v>
+        <v>0.9694797214256452</v>
       </c>
       <c r="AB23" s="5">
         <v>12327</v>
@@ -4098,14 +4098,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8842</v>
+        <v>8878</v>
       </c>
       <c r="AE23" s="5">
-        <v>12060</v>
+        <v>12096</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.97834022876612314</v>
+        <v>0.98126064735945484</v>
       </c>
       <c r="AG23" s="5">
         <v>9618</v>
@@ -4115,14 +4115,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6616</v>
+        <v>6654</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9345</v>
+        <v>9383</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.97161572052401746</v>
+        <v>0.97556664587232278</v>
       </c>
       <c r="AL23" s="5">
         <v>9741</v>
@@ -4132,14 +4132,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6814</v>
+        <v>6872</v>
       </c>
       <c r="AO23" s="5">
-        <v>9456</v>
+        <v>9514</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.97074222359100704</v>
+        <v>0.97669643773739867</v>
       </c>
       <c r="AQ23" s="5">
         <v>12556</v>
@@ -4149,14 +4149,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8799</v>
+        <v>8906</v>
       </c>
       <c r="AT23" s="5">
-        <v>12126</v>
+        <v>12233</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.96575342465753422</v>
+        <v>0.97427524689391531</v>
       </c>
       <c r="AV23" s="5">
         <v>9718</v>
@@ -4166,14 +4166,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>2473</v>
+        <v>2577</v>
       </c>
       <c r="AY23" s="5">
-        <v>9337</v>
+        <v>9441</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.96079440214035805</v>
+        <v>0.97149619263222886</v>
       </c>
       <c r="BA23" s="5">
         <v>10107</v>
@@ -4183,14 +4183,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6474</v>
+        <v>6644</v>
       </c>
       <c r="BD23" s="5">
-        <v>9406</v>
+        <v>9576</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.9306421292173741</v>
+        <v>0.94746215494211927</v>
       </c>
       <c r="BF23" s="5">
         <v>13018</v>
@@ -4200,14 +4200,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8184</v>
+        <v>8640</v>
       </c>
       <c r="BI23" s="5">
-        <v>11504</v>
+        <v>11960</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.88369949300967887</v>
+        <v>0.91872791519434627</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>5531</v>
+        <v>5536</v>
       </c>
       <c r="F24" s="5">
-        <v>6884</v>
+        <v>6889</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.99164505906078937</v>
+        <v>0.99236531259003169</v>
       </c>
       <c r="H24" s="5">
         <v>7059</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>5530</v>
+        <v>5540</v>
       </c>
       <c r="K24" s="5">
-        <v>6940</v>
+        <v>6950</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.9831420881144638</v>
+        <v>0.98455871936534922</v>
       </c>
       <c r="M24" s="5">
         <v>8056</v>
@@ -4259,14 +4259,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5515</v>
+        <v>5527</v>
       </c>
       <c r="P24" s="5">
-        <v>7930</v>
+        <v>7942</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98435948361469716</v>
+        <v>0.98584905660377353</v>
       </c>
       <c r="R24" s="5">
         <v>7134</v>
@@ -4276,14 +4276,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4954</v>
+        <v>4967</v>
       </c>
       <c r="U24" s="5">
-        <v>7010</v>
+        <v>7023</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98261844687412392</v>
+        <v>0.98444070647603032</v>
       </c>
       <c r="W24" s="5">
         <v>7208</v>
@@ -4293,14 +4293,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4841</v>
+        <v>4859</v>
       </c>
       <c r="Z24" s="5">
-        <v>7043</v>
+        <v>7061</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97710876803551605</v>
+        <v>0.97960599334073251</v>
       </c>
       <c r="AB24" s="5">
         <v>8228</v>
@@ -4310,14 +4310,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5749</v>
+        <v>5774</v>
       </c>
       <c r="AE24" s="5">
-        <v>8056</v>
+        <v>8081</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.97909577053962082</v>
+        <v>0.98213417598444341</v>
       </c>
       <c r="AG24" s="5">
         <v>7344</v>
@@ -4327,14 +4327,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4943</v>
+        <v>4970</v>
       </c>
       <c r="AJ24" s="5">
-        <v>7148</v>
+        <v>7175</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97331154684095855</v>
+        <v>0.97698801742919394</v>
       </c>
       <c r="AL24" s="5">
         <v>7506</v>
@@ -4344,14 +4344,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4876</v>
+        <v>4915</v>
       </c>
       <c r="AO24" s="5">
-        <v>7232</v>
+        <v>7271</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.96349586997069014</v>
+        <v>0.96869171329602988</v>
       </c>
       <c r="AQ24" s="5">
         <v>8509</v>
@@ -4361,14 +4361,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5883</v>
+        <v>5933</v>
       </c>
       <c r="AT24" s="5">
-        <v>8209</v>
+        <v>8259</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.96474321306851574</v>
+        <v>0.97061934422376306</v>
       </c>
       <c r="AV24" s="5">
         <v>7570</v>
@@ -4378,14 +4378,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>1191</v>
+        <v>1249</v>
       </c>
       <c r="AY24" s="5">
-        <v>7234</v>
+        <v>7292</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.95561426684280049</v>
+        <v>0.96327608982826951</v>
       </c>
       <c r="BA24" s="5">
         <v>7648</v>
@@ -4395,14 +4395,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>4892</v>
+        <v>4981</v>
       </c>
       <c r="BD24" s="5">
-        <v>7315</v>
+        <v>7404</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.95645920502092052</v>
+        <v>0.96809623430962344</v>
       </c>
       <c r="BF24" s="5">
         <v>8767</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>5764</v>
+        <v>5917</v>
       </c>
       <c r="BI24" s="5">
-        <v>8218</v>
+        <v>8371</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.93737880688947184</v>
+        <v>0.95483061480552067</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>12816</v>
+        <v>12823</v>
       </c>
       <c r="F25" s="5">
-        <v>21334</v>
+        <v>21341</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.99352675452894335</v>
+        <v>0.99385274530806134</v>
       </c>
       <c r="H25" s="5">
         <v>21813</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>12779</v>
+        <v>12788</v>
       </c>
       <c r="K25" s="5">
-        <v>21523</v>
+        <v>21532</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.98670517581258887</v>
+        <v>0.98711777380461196</v>
       </c>
       <c r="M25" s="5">
         <v>29215</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>17584</v>
+        <v>17597</v>
       </c>
       <c r="P25" s="5">
-        <v>29032</v>
+        <v>29045</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.99373609447201783</v>
+        <v>0.99418107136744827</v>
       </c>
       <c r="R25" s="5">
         <v>21767</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>12385</v>
+        <v>12399</v>
       </c>
       <c r="U25" s="5">
-        <v>21599</v>
+        <v>21613</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>0.99228189461110861</v>
+        <v>0.99292507006018282</v>
       </c>
       <c r="W25" s="5">
         <v>22114</v>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>12198</v>
+        <v>12213</v>
       </c>
       <c r="Z25" s="5">
-        <v>21742</v>
+        <v>21757</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98317807723614004</v>
+        <v>0.98385638057339242</v>
       </c>
       <c r="AB25" s="5">
         <v>29630</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18388</v>
+        <v>18416</v>
       </c>
       <c r="AE25" s="5">
-        <v>29371</v>
+        <v>29399</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>0.99125885926425916</v>
+        <v>0.99220384745190682</v>
       </c>
       <c r="AG25" s="5">
         <v>22174</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>12745</v>
+        <v>12774</v>
       </c>
       <c r="AJ25" s="5">
-        <v>21857</v>
+        <v>21886</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.98570397763146023</v>
+        <v>0.98701181563993867</v>
       </c>
       <c r="AL25" s="5">
         <v>22503</v>
@@ -4556,14 +4556,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>12750</v>
+        <v>12792</v>
       </c>
       <c r="AO25" s="5">
-        <v>22218</v>
+        <v>22260</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.98733502199706702</v>
+        <v>0.98920143980802555</v>
       </c>
       <c r="AQ25" s="5">
         <v>30294</v>
@@ -4573,14 +4573,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>18259</v>
+        <v>18342</v>
       </c>
       <c r="AT25" s="5">
-        <v>29925</v>
+        <v>30008</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>0.98781937017231136</v>
+        <v>0.99055918663761799</v>
       </c>
       <c r="AV25" s="5">
         <v>22740</v>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>4201</v>
+        <v>4288</v>
       </c>
       <c r="AY25" s="5">
-        <v>22464</v>
+        <v>22551</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.98786279683377309</v>
+        <v>0.99168865435356202</v>
       </c>
       <c r="BA25" s="5">
         <v>23197</v>
@@ -4607,14 +4607,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12703</v>
+        <v>12856</v>
       </c>
       <c r="BD25" s="5">
-        <v>22601</v>
+        <v>22754</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.97430702245980083</v>
+        <v>0.98090270293572446</v>
       </c>
       <c r="BF25" s="5">
         <v>31043</v>
@@ -4624,14 +4624,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17359</v>
+        <v>17908</v>
       </c>
       <c r="BI25" s="5">
-        <v>29478</v>
+        <v>30027</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.94958605804851337</v>
+        <v>0.96727120445833203</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>10223</v>
+        <v>10238</v>
       </c>
       <c r="F26" s="5">
-        <v>14410</v>
+        <v>14425</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99024189114898298</v>
+        <v>0.99127267729521717</v>
       </c>
       <c r="H26" s="5">
         <v>14990</v>
@@ -4666,14 +4666,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>10122</v>
+        <v>10142</v>
       </c>
       <c r="K26" s="5">
-        <v>14746</v>
+        <v>14766</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98372248165443632</v>
+        <v>0.98505670446964644</v>
       </c>
       <c r="M26" s="5">
         <v>28508</v>
@@ -4683,14 +4683,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>20111</v>
+        <v>20151</v>
       </c>
       <c r="P26" s="5">
-        <v>28405</v>
+        <v>28445</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99638697909358775</v>
+        <v>0.99779009400869934</v>
       </c>
       <c r="R26" s="5">
         <v>14719</v>
@@ -4700,14 +4700,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9804</v>
+        <v>9828</v>
       </c>
       <c r="U26" s="5">
-        <v>14559</v>
+        <v>14583</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.98912969631089065</v>
+        <v>0.99076024186425704</v>
       </c>
       <c r="W26" s="5">
         <v>15123</v>
@@ -4717,14 +4717,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9804</v>
+        <v>9834</v>
       </c>
       <c r="Z26" s="5">
-        <v>14772</v>
+        <v>14802</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.97679031938107519</v>
+        <v>0.97877405276730811</v>
       </c>
       <c r="AB26" s="5">
         <v>29054</v>
@@ -4734,14 +4734,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20622</v>
+        <v>20699</v>
       </c>
       <c r="AE26" s="5">
-        <v>28665</v>
+        <v>28742</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.98661113788118671</v>
+        <v>0.9892613753700007</v>
       </c>
       <c r="AG26" s="5">
         <v>14835</v>
@@ -4751,14 +4751,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9597</v>
+        <v>9651</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14558</v>
+        <v>14612</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.98132794068082241</v>
+        <v>0.98496798112571626</v>
       </c>
       <c r="AL26" s="5">
         <v>15316</v>
@@ -4768,14 +4768,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9336</v>
+        <v>9408</v>
       </c>
       <c r="AO26" s="5">
-        <v>14812</v>
+        <v>14884</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.96709323583180984</v>
+        <v>0.97179420214155132</v>
       </c>
       <c r="AQ26" s="5">
         <v>29312</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>20715</v>
+        <v>20908</v>
       </c>
       <c r="AT26" s="5">
-        <v>28771</v>
+        <v>28964</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.98154339519650657</v>
+        <v>0.98812772925764192</v>
       </c>
       <c r="AV26" s="5">
         <v>15164</v>
@@ -4802,14 +4802,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>2596</v>
+        <v>2744</v>
       </c>
       <c r="AY26" s="5">
-        <v>14592</v>
+        <v>14740</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.962279082036402</v>
+        <v>0.97203903983117912</v>
       </c>
       <c r="BA26" s="5">
         <v>15499</v>
@@ -4819,14 +4819,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>9859</v>
+        <v>10052</v>
       </c>
       <c r="BD26" s="5">
-        <v>14697</v>
+        <v>14890</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.94825472611136208</v>
+        <v>0.96070714239628363</v>
       </c>
       <c r="BF26" s="5">
         <v>29635</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>19663</v>
+        <v>20247</v>
       </c>
       <c r="BI26" s="5">
-        <v>27821</v>
+        <v>28405</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.93878859456723474</v>
+        <v>0.95849502277712162</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>80116</v>
+        <v>80258</v>
       </c>
       <c r="F27" s="5">
-        <v>129473</v>
+        <v>129615</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.98737874443292051</v>
+        <v>0.98846165578671219</v>
       </c>
       <c r="H27" s="5">
         <v>134384</v>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>79341</v>
+        <v>79493</v>
       </c>
       <c r="K27" s="5">
-        <v>130288</v>
+        <v>130440</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.96952018097392545</v>
+        <v>0.9706512680080962</v>
       </c>
       <c r="M27" s="5">
         <v>190911</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>121471</v>
+        <v>121747</v>
       </c>
       <c r="P27" s="5">
-        <v>190892</v>
+        <v>191168</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.9999004771857043</v>
+        <v>1.0013461770144203</v>
       </c>
       <c r="R27" s="5">
         <v>131264</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>76142</v>
+        <v>76336</v>
       </c>
       <c r="U27" s="5">
-        <v>130095</v>
+        <v>130289</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99109428327645055</v>
+        <v>0.99257222086786934</v>
       </c>
       <c r="W27" s="5">
         <v>134144</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>75962</v>
+        <v>76205</v>
       </c>
       <c r="Z27" s="5">
-        <v>131432</v>
+        <v>131675</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.97978291984732824</v>
+        <v>0.98159440601145043</v>
       </c>
       <c r="AB27" s="5">
         <v>194609</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>124815</v>
+        <v>125292</v>
       </c>
       <c r="AE27" s="5">
-        <v>192779</v>
+        <v>193256</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99059652945136145</v>
+        <v>0.99304759800420328</v>
       </c>
       <c r="AG27" s="5">
         <v>134089</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>78558</v>
+        <v>78964</v>
       </c>
       <c r="AJ27" s="5">
-        <v>131573</v>
+        <v>131979</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.98123634302590068</v>
+        <v>0.98426418274429672</v>
       </c>
       <c r="AL27" s="5">
         <v>137688</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>79136</v>
+        <v>79740</v>
       </c>
       <c r="AO27" s="5">
-        <v>135525</v>
+        <v>136129</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.98429056998431241</v>
+        <v>0.98867729940154547</v>
       </c>
       <c r="AQ27" s="5">
         <v>200322</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>125508</v>
+        <v>127030</v>
       </c>
       <c r="AT27" s="5">
-        <v>197421</v>
+        <v>198943</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.98551831551202562</v>
+        <v>0.99311608310619903</v>
       </c>
       <c r="AV27" s="5">
         <v>139481</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>28476</v>
+        <v>29730</v>
       </c>
       <c r="AY27" s="5">
-        <v>135718</v>
+        <v>136972</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.97302141510313234</v>
+        <v>0.98201188692366703</v>
       </c>
       <c r="BA27" s="5">
         <v>143305</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>77680</v>
+        <v>79563</v>
       </c>
       <c r="BD27" s="5">
-        <v>136661</v>
+        <v>138544</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.95363734691741386</v>
+        <v>0.96677715362339067</v>
       </c>
       <c r="BF27" s="5">
         <v>208143</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>118754</v>
+        <v>124845</v>
       </c>
       <c r="BI27" s="5">
-        <v>190778</v>
+        <v>196869</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.91657177997818806</v>
+        <v>0.9458353151439155</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>189178</v>
+        <v>189312</v>
       </c>
       <c r="F28" s="5">
-        <v>434543</v>
+        <v>434677</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99321163028298587</v>
+        <v>0.99351790689648078</v>
       </c>
       <c r="H28" s="5">
         <v>447363</v>
@@ -5090,14 +5090,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>191493</v>
+        <v>191646</v>
       </c>
       <c r="K28" s="5">
-        <v>442185</v>
+        <v>442338</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.98842550680320007</v>
+        <v>0.98876751094748561</v>
       </c>
       <c r="M28" s="5">
         <v>722935</v>
@@ -5107,14 +5107,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>333964</v>
+        <v>334256</v>
       </c>
       <c r="P28" s="5">
-        <v>718279</v>
+        <v>718571</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99355958696148339</v>
+        <v>0.99396349602661371</v>
       </c>
       <c r="R28" s="5">
         <v>448339</v>
@@ -5124,14 +5124,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>185642</v>
+        <v>185857</v>
       </c>
       <c r="U28" s="5">
-        <v>445160</v>
+        <v>445375</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99290938330147505</v>
+        <v>0.99338893114362126</v>
       </c>
       <c r="W28" s="5">
         <v>458076</v>
@@ -5141,14 +5141,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>187166</v>
+        <v>187443</v>
       </c>
       <c r="Z28" s="5">
-        <v>450395</v>
+        <v>450672</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.98323204009814968</v>
+        <v>0.98383674324784531</v>
       </c>
       <c r="AB28" s="5">
         <v>737235</v>
@@ -5158,14 +5158,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>353032</v>
+        <v>353633</v>
       </c>
       <c r="AE28" s="5">
-        <v>729944</v>
+        <v>730545</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99011034473404003</v>
+        <v>0.9909255529105373</v>
       </c>
       <c r="AG28" s="5">
         <v>456666</v>
@@ -5175,14 +5175,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>192302</v>
+        <v>192885</v>
       </c>
       <c r="AJ28" s="5">
-        <v>450683</v>
+        <v>451266</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98689852101973874</v>
+        <v>0.98817516521921933</v>
       </c>
       <c r="AL28" s="5">
         <v>468801</v>
@@ -5192,14 +5192,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>192593</v>
+        <v>193497</v>
       </c>
       <c r="AO28" s="5">
-        <v>463336</v>
+        <v>464240</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.98834260165827292</v>
+        <v>0.99027092519000603</v>
       </c>
       <c r="AQ28" s="5">
         <v>756132</v>
@@ -5209,14 +5209,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>349959</v>
+        <v>352464</v>
       </c>
       <c r="AT28" s="5">
-        <v>748972</v>
+        <v>751477</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.99053075388953249</v>
+        <v>0.99384366750778963</v>
       </c>
       <c r="AV28" s="5">
         <v>474991</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>62241</v>
+        <v>64336</v>
       </c>
       <c r="AY28" s="5">
-        <v>467276</v>
+        <v>469371</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.98375758698585869</v>
+        <v>0.98816819687109858</v>
       </c>
       <c r="BA28" s="5">
         <v>487540</v>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>192585</v>
+        <v>195702</v>
       </c>
       <c r="BD28" s="5">
-        <v>473159</v>
+        <v>476276</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.97050293309266933</v>
+        <v>0.97689625466628383</v>
       </c>
       <c r="BF28" s="5">
         <v>779284</v>
@@ -5260,14 +5260,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>336547</v>
+        <v>347227</v>
       </c>
       <c r="BI28" s="5">
-        <v>744085</v>
+        <v>754765</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.95483161466166377</v>
+        <v>0.96853650273841119</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5285,14 +5285,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>78321</v>
+        <v>78351</v>
       </c>
       <c r="F29" s="5">
-        <v>142654</v>
+        <v>142684</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99236184540041183</v>
+        <v>0.9925705381490344</v>
       </c>
       <c r="H29" s="5">
         <v>146310</v>
@@ -5302,14 +5302,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>77774</v>
+        <v>77811</v>
       </c>
       <c r="K29" s="5">
-        <v>144147</v>
+        <v>144184</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98521632150912442</v>
+        <v>0.98546920921331416</v>
       </c>
       <c r="M29" s="5">
         <v>194093</v>
@@ -5319,14 +5319,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>106332</v>
+        <v>106402</v>
       </c>
       <c r="P29" s="5">
-        <v>191759</v>
+        <v>191829</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98797483680503673</v>
+        <v>0.98833548865749921</v>
       </c>
       <c r="R29" s="5">
         <v>146918</v>
@@ -5336,14 +5336,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>77340</v>
+        <v>77399</v>
       </c>
       <c r="U29" s="5">
-        <v>145084</v>
+        <v>145143</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98751684613185586</v>
+        <v>0.98791843068922802</v>
       </c>
       <c r="W29" s="5">
         <v>149105</v>
@@ -5353,14 +5353,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>75435</v>
+        <v>75521</v>
       </c>
       <c r="Z29" s="5">
-        <v>146409</v>
+        <v>146495</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.9819187820663291</v>
+        <v>0.98249555682237355</v>
       </c>
       <c r="AB29" s="5">
         <v>197403</v>
@@ -5370,14 +5370,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>109716</v>
+        <v>109869</v>
       </c>
       <c r="AE29" s="5">
-        <v>194582</v>
+        <v>194735</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98570943703996394</v>
+        <v>0.98648450124871456</v>
       </c>
       <c r="AG29" s="5">
         <v>149309</v>
@@ -5387,14 +5387,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>78251</v>
+        <v>78449</v>
       </c>
       <c r="AJ29" s="5">
-        <v>147035</v>
+        <v>147233</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98476983972834864</v>
+        <v>0.98609594867020745</v>
       </c>
       <c r="AL29" s="5">
         <v>152026</v>
@@ -5404,14 +5404,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>79096</v>
+        <v>79415</v>
       </c>
       <c r="AO29" s="5">
-        <v>151575</v>
+        <v>151894</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.99703340218120584</v>
+        <v>0.99913172746766998</v>
       </c>
       <c r="AQ29" s="5">
         <v>203571</v>
@@ -5421,14 +5421,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>112321</v>
+        <v>113026</v>
       </c>
       <c r="AT29" s="5">
-        <v>201958</v>
+        <v>202663</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.9920764745469639</v>
+        <v>0.99553963973257487</v>
       </c>
       <c r="AV29" s="5">
         <v>155780</v>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>24604</v>
+        <v>25325</v>
       </c>
       <c r="AY29" s="5">
-        <v>153953</v>
+        <v>154674</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.98827192194119917</v>
+        <v>0.99290024393375276</v>
       </c>
       <c r="BA29" s="5">
         <v>159604</v>
@@ -5455,14 +5455,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>80177</v>
+        <v>81300</v>
       </c>
       <c r="BD29" s="5">
-        <v>155736</v>
+        <v>156859</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.97576501842059093</v>
+        <v>0.98280118292774621</v>
       </c>
       <c r="BF29" s="5">
         <v>211893</v>
@@ -5472,14 +5472,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>107893</v>
+        <v>110974</v>
       </c>
       <c r="BI29" s="5">
-        <v>202100</v>
+        <v>205181</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.95378327740888091</v>
+        <v>0.96832363504221475</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>109243</v>
+        <v>109307</v>
       </c>
       <c r="F30" s="5">
-        <v>185250</v>
+        <v>185314</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99451339975949149</v>
+        <v>0.99485698333619654</v>
       </c>
       <c r="H30" s="5">
         <v>190966</v>
@@ -5514,14 +5514,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>109502</v>
+        <v>109576</v>
       </c>
       <c r="K30" s="5">
-        <v>188221</v>
+        <v>188295</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98562571347779182</v>
+        <v>0.98601321701245248</v>
       </c>
       <c r="M30" s="5">
         <v>320227</v>
@@ -5531,14 +5531,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>196481</v>
+        <v>196622</v>
       </c>
       <c r="P30" s="5">
-        <v>318215</v>
+        <v>318356</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.9937169570336043</v>
+        <v>0.99415726968681595</v>
       </c>
       <c r="R30" s="5">
         <v>189502</v>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>105775</v>
+        <v>105876</v>
       </c>
       <c r="U30" s="5">
-        <v>187982</v>
+        <v>188083</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99197897647518229</v>
+        <v>0.99251195238044976</v>
       </c>
       <c r="W30" s="5">
         <v>194334</v>
@@ -5565,14 +5565,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>104396</v>
+        <v>104513</v>
       </c>
       <c r="Z30" s="5">
-        <v>190352</v>
+        <v>190469</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.97950950425556005</v>
+        <v>0.98011156050922643</v>
       </c>
       <c r="AB30" s="5">
         <v>325942</v>
@@ -5582,14 +5582,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>202740</v>
+        <v>203033</v>
       </c>
       <c r="AE30" s="5">
-        <v>322719</v>
+        <v>323012</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99011173767111937</v>
+        <v>0.9910106706101085</v>
       </c>
       <c r="AG30" s="5">
         <v>192789</v>
@@ -5599,14 +5599,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>108676</v>
+        <v>108950</v>
       </c>
       <c r="AJ30" s="5">
-        <v>190710</v>
+        <v>190984</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.98921618972036784</v>
+        <v>0.9906374326336046</v>
       </c>
       <c r="AL30" s="5">
         <v>197994</v>
@@ -5616,14 +5616,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>108049</v>
+        <v>108466</v>
       </c>
       <c r="AO30" s="5">
-        <v>195340</v>
+        <v>195757</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98659555340060812</v>
+        <v>0.98870167782862106</v>
       </c>
       <c r="AQ30" s="5">
         <v>333633</v>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>203645</v>
+        <v>204921</v>
       </c>
       <c r="AT30" s="5">
-        <v>329936</v>
+        <v>331212</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.98891896185329387</v>
+        <v>0.99274352357230844</v>
       </c>
       <c r="AV30" s="5">
         <v>198460</v>
@@ -5650,14 +5650,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>35138</v>
+        <v>36154</v>
       </c>
       <c r="AY30" s="5">
-        <v>195433</v>
+        <v>196449</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.98474755618260612</v>
+        <v>0.98986697571298998</v>
       </c>
       <c r="BA30" s="5">
         <v>203942</v>
@@ -5667,14 +5667,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>106529</v>
+        <v>108084</v>
       </c>
       <c r="BD30" s="5">
-        <v>197538</v>
+        <v>199093</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.96859891537790155</v>
+        <v>0.97622363220915753</v>
       </c>
       <c r="BF30" s="5">
         <v>342999</v>
@@ -5684,14 +5684,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>193107</v>
+        <v>199178</v>
       </c>
       <c r="BI30" s="5">
-        <v>323913</v>
+        <v>329984</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.9443555229023991</v>
+        <v>0.96205528296000864</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37001</v>
+        <v>37015</v>
       </c>
       <c r="F31" s="5">
-        <v>83230</v>
+        <v>83244</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0041866245189002</v>
+        <v>1.0043555373236972</v>
       </c>
       <c r="H31" s="5">
         <v>85478</v>
@@ -5726,14 +5726,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35461</v>
+        <v>35481</v>
       </c>
       <c r="K31" s="5">
-        <v>84727</v>
+        <v>84747</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99121411357308309</v>
+        <v>0.99144809190668948</v>
       </c>
       <c r="M31" s="5">
         <v>149930</v>
@@ -5743,14 +5743,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>75315</v>
+        <v>75381</v>
       </c>
       <c r="P31" s="5">
-        <v>150926</v>
+        <v>150992</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0066431001133862</v>
+        <v>1.0070833055425865</v>
       </c>
       <c r="R31" s="5">
         <v>83981</v>
@@ -5760,14 +5760,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34219</v>
+        <v>34250</v>
       </c>
       <c r="U31" s="5">
-        <v>84026</v>
+        <v>84057</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0005358354865981</v>
+        <v>1.0009049665995879</v>
       </c>
       <c r="W31" s="5">
         <v>85994</v>
@@ -5777,14 +5777,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>33814</v>
+        <v>33851</v>
       </c>
       <c r="Z31" s="5">
-        <v>85389</v>
+        <v>85426</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.99296462543898412</v>
+        <v>0.99339488801544296</v>
       </c>
       <c r="AB31" s="5">
         <v>153633</v>
@@ -5794,14 +5794,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77761</v>
+        <v>77893</v>
       </c>
       <c r="AE31" s="5">
-        <v>153489</v>
+        <v>153621</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>0.99906270137275199</v>
+        <v>0.99992189178106261</v>
       </c>
       <c r="AG31" s="5">
         <v>85109</v>
@@ -5811,14 +5811,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35542</v>
+        <v>35610</v>
       </c>
       <c r="AJ31" s="5">
-        <v>85359</v>
+        <v>85427</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.0029374096746526</v>
+        <v>1.003736385106158</v>
       </c>
       <c r="AL31" s="5">
         <v>88549</v>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>34533</v>
+        <v>34650</v>
       </c>
       <c r="AO31" s="5">
-        <v>87830</v>
+        <v>87947</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.99188020192209958</v>
+        <v>0.99320150425188314</v>
       </c>
       <c r="AQ31" s="5">
         <v>156407</v>
@@ -5845,14 +5845,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>77600</v>
+        <v>78069</v>
       </c>
       <c r="AT31" s="5">
-        <v>156809</v>
+        <v>157278</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0025702174455107</v>
+        <v>1.0055688044652733</v>
       </c>
       <c r="AV31" s="5">
         <v>87916</v>
@@ -5862,14 +5862,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>16254</v>
+        <v>16532</v>
       </c>
       <c r="AY31" s="5">
-        <v>87680</v>
+        <v>87958</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>0.9973156194549343</v>
+        <v>1.0004777287410711</v>
       </c>
       <c r="BA31" s="5">
         <v>90084</v>
@@ -5879,14 +5879,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>34571</v>
+        <v>35073</v>
       </c>
       <c r="BD31" s="5">
-        <v>89049</v>
+        <v>89551</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.98851072332489676</v>
+        <v>0.99408330003108214</v>
       </c>
       <c r="BF31" s="5">
         <v>159779</v>
@@ -5896,14 +5896,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>73008</v>
+        <v>76366</v>
       </c>
       <c r="BI31" s="5">
-        <v>152781</v>
+        <v>156139</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>0.95620200401804989</v>
+        <v>0.97721853309884277</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>107474</v>
+        <v>107508</v>
       </c>
       <c r="F32" s="5">
-        <v>230768</v>
+        <v>230802</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99462963441861263</v>
+        <v>0.99477617729964574</v>
       </c>
       <c r="H32" s="5">
         <v>238678</v>
@@ -5938,14 +5938,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>107529</v>
+        <v>107571</v>
       </c>
       <c r="K32" s="5">
-        <v>235265</v>
+        <v>235307</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.9857003997016901</v>
+        <v>0.98587636899923747</v>
       </c>
       <c r="M32" s="5">
         <v>498323</v>
@@ -5955,14 +5955,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>270195</v>
+        <v>270321</v>
       </c>
       <c r="P32" s="5">
-        <v>495560</v>
+        <v>495686</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99445540342308103</v>
+        <v>0.99470825147544861</v>
       </c>
       <c r="R32" s="5">
         <v>234167</v>
@@ -5972,14 +5972,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>102877</v>
+        <v>102936</v>
       </c>
       <c r="U32" s="5">
-        <v>232816</v>
+        <v>232875</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99423061319485662</v>
+        <v>0.99448257013157282</v>
       </c>
       <c r="W32" s="5">
         <v>242821</v>
@@ -5989,14 +5989,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>103434</v>
+        <v>103517</v>
       </c>
       <c r="Z32" s="5">
-        <v>237177</v>
+        <v>237260</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97675654082637009</v>
+        <v>0.97709835640245279</v>
       </c>
       <c r="AB32" s="5">
         <v>507064</v>
@@ -6006,14 +6006,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>280059</v>
+        <v>280400</v>
       </c>
       <c r="AE32" s="5">
-        <v>504280</v>
+        <v>504621</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99450956881182651</v>
+        <v>0.99518206774687223</v>
       </c>
       <c r="AG32" s="5">
         <v>238186</v>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>105538</v>
+        <v>105736</v>
       </c>
       <c r="AJ32" s="5">
-        <v>236374</v>
+        <v>236572</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99239249997900802</v>
+        <v>0.99322378309388459</v>
       </c>
       <c r="AL32" s="5">
         <v>247675</v>
@@ -6040,14 +6040,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>105601</v>
+        <v>105922</v>
       </c>
       <c r="AO32" s="5">
-        <v>245716</v>
+        <v>246037</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.99209044110225098</v>
+        <v>0.9933864943979005</v>
       </c>
       <c r="AQ32" s="5">
         <v>518099</v>
@@ -6057,14 +6057,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>277058</v>
+        <v>278471</v>
       </c>
       <c r="AT32" s="5">
-        <v>516764</v>
+        <v>518177</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>0.99742327238616557</v>
+        <v>1.0001505503774375</v>
       </c>
       <c r="AV32" s="5">
         <v>246693</v>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>41005</v>
+        <v>41769</v>
       </c>
       <c r="AY32" s="5">
-        <v>245841</v>
+        <v>246605</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99654631465019272</v>
+        <v>0.99964328132537206</v>
       </c>
       <c r="BA32" s="5">
         <v>255610</v>
@@ -6091,14 +6091,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>107287</v>
+        <v>108485</v>
       </c>
       <c r="BD32" s="5">
-        <v>252026</v>
+        <v>253224</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.98597863933335939</v>
+        <v>0.99066546692226443</v>
       </c>
       <c r="BF32" s="5">
         <v>535637</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>260934</v>
+        <v>268346</v>
       </c>
       <c r="BI32" s="5">
-        <v>514787</v>
+        <v>522199</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.96107438433117953</v>
+        <v>0.97491211398764466</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6133,14 +6133,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112636</v>
+        <v>112669</v>
       </c>
       <c r="F33" s="5">
-        <v>717004</v>
+        <v>717037</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>1.001691829900544</v>
+        <v>1.0017379326145968</v>
       </c>
       <c r="H33" s="5">
         <v>726544</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>106241</v>
+        <v>106278</v>
       </c>
       <c r="K33" s="5">
-        <v>729360</v>
+        <v>729397</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>1.0038758836354027</v>
+        <v>1.0039268096632825</v>
       </c>
       <c r="M33" s="5">
         <v>1152516</v>
@@ -6167,14 +6167,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>203513</v>
+        <v>203597</v>
       </c>
       <c r="P33" s="5">
-        <v>1155841</v>
+        <v>1155925</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0028849924860046</v>
+        <v>1.0029578765067035</v>
       </c>
       <c r="R33" s="5">
         <v>733468</v>
@@ -6184,14 +6184,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>104949</v>
+        <v>105014</v>
       </c>
       <c r="U33" s="5">
-        <v>736236</v>
+        <v>736301</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0037738524380069</v>
+        <v>1.0038624725277723</v>
       </c>
       <c r="W33" s="5">
         <v>745690</v>
@@ -6201,14 +6201,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>105060</v>
+        <v>105140</v>
       </c>
       <c r="Z33" s="5">
-        <v>746017</v>
+        <v>746097</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>1.00043852002843</v>
+        <v>1.0005458032158134</v>
       </c>
       <c r="AB33" s="5">
         <v>1180887</v>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>209106</v>
+        <v>209295</v>
       </c>
       <c r="AE33" s="5">
-        <v>1182178</v>
+        <v>1182367</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.001093246009144</v>
+        <v>1.0012532951925122</v>
       </c>
       <c r="AG33" s="5">
         <v>749948</v>
@@ -6235,14 +6235,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>110625</v>
+        <v>110808</v>
       </c>
       <c r="AJ33" s="5">
-        <v>750480</v>
+        <v>750663</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0007093825171878</v>
+        <v>1.0009533994356943</v>
       </c>
       <c r="AL33" s="5">
         <v>765123</v>
@@ -6252,14 +6252,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>110293</v>
+        <v>110619</v>
       </c>
       <c r="AO33" s="5">
-        <v>773156</v>
+        <v>773482</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>1.0104989655258043</v>
+        <v>1.0109250408104318</v>
       </c>
       <c r="AQ33" s="5">
         <v>1217820</v>
@@ -6269,14 +6269,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>214754</v>
+        <v>215825</v>
       </c>
       <c r="AT33" s="5">
-        <v>1223784</v>
+        <v>1224855</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0048972754594274</v>
+        <v>1.0057767157708035</v>
       </c>
       <c r="AV33" s="5">
         <v>779865</v>
@@ -6286,14 +6286,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>70467</v>
+        <v>71420</v>
       </c>
       <c r="AY33" s="5">
-        <v>782996</v>
+        <v>783949</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.004014797432889</v>
+        <v>1.0052368038057868</v>
       </c>
       <c r="BA33" s="5">
         <v>794982</v>
@@ -6303,14 +6303,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>104952</v>
+        <v>106634</v>
       </c>
       <c r="BD33" s="5">
-        <v>796788</v>
+        <v>798470</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0022717495490463</v>
+        <v>1.0043875207237396</v>
       </c>
       <c r="BF33" s="5">
         <v>1258934</v>
@@ -6320,14 +6320,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>216663</v>
+        <v>224156</v>
       </c>
       <c r="BI33" s="5">
-        <v>1246189</v>
+        <v>1253682</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>0.98987635571046617</v>
+        <v>0.99582821657052711</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="E35" s="3">
         <f t="shared" ref="E35:E47" si="24">F35-D35</f>
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="F35" s="5">
-        <v>12238</v>
+        <v>12239</v>
       </c>
       <c r="G35" s="4">
         <f t="shared" ref="G35:G48" si="25">F35/C35</f>
-        <v>0.99836841246532881</v>
+        <v>0.99844999184206229</v>
       </c>
       <c r="H35" s="5">
         <v>12343</v>
@@ -6550,14 +6550,14 @@
       </c>
       <c r="J35" s="3">
         <f t="shared" ref="J35:J47" si="26">K35-I35</f>
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="K35" s="5">
-        <v>12325</v>
+        <v>12327</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" ref="L35:L48" si="27">K35/H35</f>
-        <v>0.99854168354532935</v>
+        <v>0.9987037187069594</v>
       </c>
       <c r="M35" s="5">
         <v>15097</v>
@@ -6567,14 +6567,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2836</v>
+        <v>2840</v>
       </c>
       <c r="P35" s="5">
-        <v>15077</v>
+        <v>15081</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99867523349009735</v>
+        <v>0.99894018679207786</v>
       </c>
       <c r="R35" s="5">
         <v>12455</v>
@@ -6584,14 +6584,14 @@
       </c>
       <c r="T35" s="3">
         <f t="shared" ref="T35:T47" si="30">U35-S35</f>
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="U35" s="5">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99614612605379371</v>
+        <v>0.99646728221597747</v>
       </c>
       <c r="W35" s="5">
         <v>12547</v>
@@ -6601,14 +6601,14 @@
       </c>
       <c r="Y35" s="3">
         <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="Z35" s="5">
-        <v>12436</v>
+        <v>12441</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.99115326372838131</v>
+        <v>0.99155176536223799</v>
       </c>
       <c r="AB35" s="5">
         <v>15257</v>
@@ -6618,14 +6618,14 @@
       </c>
       <c r="AD35" s="3">
         <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
-        <v>2822</v>
+        <v>2832</v>
       </c>
       <c r="AE35" s="5">
-        <v>15189</v>
+        <v>15199</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99554302942911455</v>
+        <v>0.99619846627777409</v>
       </c>
       <c r="AG35" s="5">
         <v>12574</v>
@@ -6635,14 +6635,14 @@
       </c>
       <c r="AI35" s="3">
         <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
-        <v>2202</v>
+        <v>2212</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12515</v>
+        <v>12525</v>
       </c>
       <c r="AK35" s="4">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99530777795450931</v>
+        <v>0.99610306982662633</v>
       </c>
       <c r="AL35" s="5">
         <v>12702</v>
@@ -6652,14 +6652,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2056</v>
+        <v>2074</v>
       </c>
       <c r="AO35" s="5">
-        <v>12596</v>
+        <v>12614</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.9916548575027555</v>
+        <v>0.99307195717209884</v>
       </c>
       <c r="AQ35" s="5">
         <v>15458</v>
@@ -6669,14 +6669,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2780</v>
+        <v>2821</v>
       </c>
       <c r="AT35" s="5">
-        <v>15352</v>
+        <v>15393</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.99314270927674986</v>
+        <v>0.99579505757536546</v>
       </c>
       <c r="AV35" s="5">
         <v>12806</v>
@@ -6686,14 +6686,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>1930</v>
+        <v>1979</v>
       </c>
       <c r="AY35" s="5">
-        <v>12618</v>
+        <v>12667</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.98531938153990317</v>
+        <v>0.98914571294705611</v>
       </c>
       <c r="BA35" s="5">
         <v>12915</v>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>1745</v>
+        <v>1819</v>
       </c>
       <c r="BD35" s="5">
-        <v>12610</v>
+        <v>12684</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.97638404955478131</v>
+        <v>0.98211382113821133</v>
       </c>
       <c r="BF35" s="5">
         <v>15661</v>
@@ -6720,14 +6720,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2348</v>
+        <v>2552</v>
       </c>
       <c r="BI35" s="5">
-        <v>15152</v>
+        <v>15356</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.96749888257454819</v>
+        <v>0.98052487069791205</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>278417</v>
+        <v>278556</v>
       </c>
       <c r="F36" s="5">
-        <v>954400</v>
+        <v>954539</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>1.0016687482289228</v>
+        <v>1.001814632508055</v>
       </c>
       <c r="H36" s="5">
         <v>975466</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>271356</v>
+        <v>271532</v>
       </c>
       <c r="K36" s="5">
-        <v>970734</v>
+        <v>970910</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.99514898520296968</v>
+        <v>0.99532941178882706</v>
       </c>
       <c r="M36" s="5">
         <v>1668278</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>534783</v>
+        <v>535178</v>
       </c>
       <c r="P36" s="5">
-        <v>1670696</v>
+        <v>1671091</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>1.0014493987213162</v>
+        <v>1.0016861698110266</v>
       </c>
       <c r="R36" s="5">
         <v>976879</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>261343</v>
+        <v>261606</v>
       </c>
       <c r="U36" s="5">
-        <v>975799</v>
+        <v>976062</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99889443830812208</v>
+        <v>0.99916366305345905</v>
       </c>
       <c r="W36" s="5">
         <v>1000117</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>263820</v>
+        <v>264149</v>
       </c>
       <c r="Z36" s="5">
-        <v>988213</v>
+        <v>988542</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98809739260506524</v>
+        <v>0.98842635411656832</v>
       </c>
       <c r="AB36" s="5">
         <v>1701420</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>553021</v>
+        <v>553855</v>
       </c>
       <c r="AE36" s="5">
-        <v>1699005</v>
+        <v>1699839</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99858059738336213</v>
+        <v>0.9990707761751948</v>
       </c>
       <c r="AG36" s="5">
         <v>996655</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>272563</v>
+        <v>273315</v>
       </c>
       <c r="AJ36" s="5">
-        <v>994800</v>
+        <v>995552</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99813877419969799</v>
+        <v>0.9988932980820846</v>
       </c>
       <c r="AL36" s="5">
         <v>1027093</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>271687</v>
+        <v>272947</v>
       </c>
       <c r="AO36" s="5">
-        <v>1030173</v>
+        <v>1031433</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>1.0029987547378865</v>
+        <v>1.004225518039749</v>
       </c>
       <c r="AQ36" s="5">
         <v>1750886</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>554554</v>
+        <v>558236</v>
       </c>
       <c r="AT36" s="5">
-        <v>1760025</v>
+        <v>1763707</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0052196430835589</v>
+        <v>1.0073225783974513</v>
       </c>
       <c r="AV36" s="5">
         <v>1041088</v>
@@ -6898,14 +6898,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>161139</v>
+        <v>164112</v>
       </c>
       <c r="AY36" s="5">
-        <v>1043139</v>
+        <v>1046112</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>1.0019700544046228</v>
+        <v>1.0048257207844102</v>
       </c>
       <c r="BA36" s="5">
         <v>1070068</v>
@@ -6915,14 +6915,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>261183</v>
+        <v>265917</v>
       </c>
       <c r="BD36" s="5">
-        <v>1061153</v>
+        <v>1065887</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99166875376144314</v>
+        <v>0.99609277167432353</v>
       </c>
       <c r="BF36" s="5">
         <v>1814069</v>
@@ -6932,14 +6932,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>502164</v>
+        <v>528042</v>
       </c>
       <c r="BI36" s="5">
-        <v>1753526</v>
+        <v>1779404</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>0.96662585601760465</v>
+        <v>0.98089102454206534</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6957,14 +6957,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>308901</v>
+        <v>309064</v>
       </c>
       <c r="F37" s="5">
-        <v>734381</v>
+        <v>734544</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.99044193410909165</v>
+        <v>0.99066176827590668</v>
       </c>
       <c r="H37" s="5">
         <v>747767</v>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>304444</v>
+        <v>304659</v>
       </c>
       <c r="K37" s="5">
-        <v>739439</v>
+        <v>739654</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98886284096516697</v>
+        <v>0.98915036368280496</v>
       </c>
       <c r="M37" s="5">
         <v>922163</v>
@@ -6991,14 +6991,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>374273</v>
+        <v>374596</v>
       </c>
       <c r="P37" s="5">
-        <v>915233</v>
+        <v>915556</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99248505958274191</v>
+        <v>0.99283532303941924</v>
       </c>
       <c r="R37" s="5">
         <v>751356</v>
@@ -7008,14 +7008,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>292145</v>
+        <v>292487</v>
       </c>
       <c r="U37" s="5">
-        <v>744165</v>
+        <v>744507</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.99042930381869576</v>
+        <v>0.99088448085860759</v>
       </c>
       <c r="W37" s="5">
         <v>760191</v>
@@ -7025,14 +7025,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>284173</v>
+        <v>284638</v>
       </c>
       <c r="Z37" s="5">
-        <v>749857</v>
+        <v>750322</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98640604795373799</v>
+        <v>0.98701773633205336</v>
       </c>
       <c r="AB37" s="5">
         <v>938023</v>
@@ -7042,14 +7042,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>391307</v>
+        <v>392102</v>
       </c>
       <c r="AE37" s="5">
-        <v>928806</v>
+        <v>929601</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.99017401492287505</v>
+        <v>0.99102154211570503</v>
       </c>
       <c r="AG37" s="5">
         <v>763648</v>
@@ -7059,14 +7059,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>298242</v>
+        <v>299282</v>
       </c>
       <c r="AJ37" s="5">
-        <v>754666</v>
+        <v>755706</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98823803637277907</v>
+        <v>0.9895999203821656</v>
       </c>
       <c r="AL37" s="5">
         <v>773685</v>
@@ -7076,14 +7076,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>287509</v>
+        <v>289120</v>
       </c>
       <c r="AO37" s="5">
-        <v>766969</v>
+        <v>768580</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.99131946464000209</v>
+        <v>0.99340170741322376</v>
       </c>
       <c r="AQ37" s="5">
         <v>957323</v>
@@ -7093,14 +7093,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>384986</v>
+        <v>388229</v>
       </c>
       <c r="AT37" s="5">
-        <v>947249</v>
+        <v>950492</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.98947690591367798</v>
+        <v>0.99286447729763094</v>
       </c>
       <c r="AV37" s="5">
         <v>783693</v>
@@ -7110,14 +7110,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>120406</v>
+        <v>124177</v>
       </c>
       <c r="AY37" s="5">
-        <v>771198</v>
+        <v>774969</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.98405625672297703</v>
+        <v>0.98886808992807129</v>
       </c>
       <c r="BA37" s="5">
         <v>794943</v>
@@ -7127,14 +7127,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>271523</v>
+        <v>277405</v>
       </c>
       <c r="BD37" s="5">
-        <v>773352</v>
+        <v>779234</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.97283956208180966</v>
+        <v>0.9802388347340627</v>
       </c>
       <c r="BF37" s="5">
         <v>980352</v>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>357931</v>
+        <v>373146</v>
       </c>
       <c r="BI37" s="5">
-        <v>933048</v>
+        <v>948263</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.95174794359576964</v>
+        <v>0.96726787929233582</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7169,14 +7169,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>10003</v>
+        <v>10011</v>
       </c>
       <c r="F38" s="5">
-        <v>26174</v>
+        <v>26182</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0042974445552912</v>
+        <v>1.0046044048806693</v>
       </c>
       <c r="H38" s="5">
         <v>26657</v>
@@ -7186,14 +7186,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>9668</v>
+        <v>9680</v>
       </c>
       <c r="K38" s="5">
-        <v>26465</v>
+        <v>26477</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99279738905353188</v>
+        <v>0.99324755223768613</v>
       </c>
       <c r="M38" s="5">
         <v>40003</v>
@@ -7203,14 +7203,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>14576</v>
+        <v>14600</v>
       </c>
       <c r="P38" s="5">
-        <v>40052</v>
+        <v>40076</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.00122490813189</v>
+        <v>1.0018248631352649</v>
       </c>
       <c r="R38" s="5">
         <v>26603</v>
@@ -7220,14 +7220,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9116</v>
+        <v>9141</v>
       </c>
       <c r="U38" s="5">
-        <v>26584</v>
+        <v>26609</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>0.99928579483516899</v>
+        <v>1.0002255384731045</v>
       </c>
       <c r="W38" s="5">
         <v>27177</v>
@@ -7237,14 +7237,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>9025</v>
+        <v>9050</v>
       </c>
       <c r="Z38" s="5">
-        <v>26818</v>
+        <v>26843</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.98679030062184936</v>
+        <v>0.98771019612172062</v>
       </c>
       <c r="AB38" s="5">
         <v>40627</v>
@@ -7254,14 +7254,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>15084</v>
+        <v>15141</v>
       </c>
       <c r="AE38" s="5">
-        <v>40597</v>
+        <v>40654</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>0.9992615748147784</v>
+        <v>1.0006645826666996</v>
       </c>
       <c r="AG38" s="5">
         <v>26952</v>
@@ -7271,14 +7271,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9368</v>
+        <v>9434</v>
       </c>
       <c r="AJ38" s="5">
-        <v>26914</v>
+        <v>26980</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>0.99859008607895516</v>
+        <v>1.0010388839418225</v>
       </c>
       <c r="AL38" s="5">
         <v>27600</v>
@@ -7288,14 +7288,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>8889</v>
+        <v>9001</v>
       </c>
       <c r="AO38" s="5">
-        <v>27377</v>
+        <v>27489</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>0.99192028985507241</v>
+        <v>0.9959782608695652</v>
       </c>
       <c r="AQ38" s="5">
         <v>41434</v>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>14866</v>
+        <v>15108</v>
       </c>
       <c r="AT38" s="5">
-        <v>41290</v>
+        <v>41532</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>0.99652459332915</v>
+        <v>1.0023652073176619</v>
       </c>
       <c r="AV38" s="5">
         <v>27593</v>
@@ -7322,14 +7322,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>4901</v>
+        <v>5150</v>
       </c>
       <c r="AY38" s="5">
-        <v>27257</v>
+        <v>27506</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>0.98782299858659806</v>
+        <v>0.9968470264197441</v>
       </c>
       <c r="BA38" s="5">
         <v>28279</v>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>7955</v>
+        <v>8317</v>
       </c>
       <c r="BD38" s="5">
-        <v>27257</v>
+        <v>27619</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>0.96386010820750379</v>
+        <v>0.97666112663106897</v>
       </c>
       <c r="BF38" s="5">
         <v>42642</v>
@@ -7356,14 +7356,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>12842</v>
+        <v>13852</v>
       </c>
       <c r="BI38" s="5">
-        <v>39841</v>
+        <v>40851</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>0.93431358754279814</v>
+        <v>0.95799915576192485</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7432,14 +7432,14 @@
       </c>
       <c r="T39" s="3">
         <f t="shared" si="30"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U39" s="5">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="V39" s="4">
         <f t="shared" si="31"/>
-        <v>0.95833333333333337</v>
+        <v>0.96212121212121215</v>
       </c>
       <c r="W39" s="5">
         <v>265</v>
@@ -7449,14 +7449,14 @@
       </c>
       <c r="Y39" s="3">
         <f t="shared" si="32"/>
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z39" s="5">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA39" s="4">
         <f t="shared" si="33"/>
-        <v>0.95849056603773586</v>
+        <v>0.96226415094339623</v>
       </c>
       <c r="AB39" s="5">
         <v>322</v>
@@ -7466,14 +7466,14 @@
       </c>
       <c r="AD39" s="3">
         <f t="shared" si="34"/>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AE39" s="5">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AF39" s="4">
         <f t="shared" si="35"/>
-        <v>0.96894409937888204</v>
+        <v>0.97204968944099379</v>
       </c>
       <c r="AG39" s="5">
         <v>267</v>
@@ -7483,14 +7483,14 @@
       </c>
       <c r="AI39" s="3">
         <f t="shared" si="36"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AJ39" s="5">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AK39" s="4">
         <f t="shared" si="37"/>
-        <v>0.9438202247191011</v>
+        <v>0.94756554307116103</v>
       </c>
       <c r="AL39" s="5">
         <v>276</v>
@@ -7500,14 +7500,14 @@
       </c>
       <c r="AN39" s="3">
         <f t="shared" si="38"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AO39" s="5">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AP39" s="4">
         <f t="shared" si="39"/>
-        <v>0.94202898550724634</v>
+        <v>0.94927536231884058</v>
       </c>
       <c r="AQ39" s="5">
         <v>338</v>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="AS39" s="3">
         <f t="shared" si="40"/>
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AT39" s="5">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AU39" s="4">
         <f t="shared" si="41"/>
-        <v>0.94378698224852076</v>
+        <v>0.94970414201183428</v>
       </c>
       <c r="AV39" s="5">
         <v>279</v>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="AX39" s="3">
         <f t="shared" si="42"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AY39" s="5">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AZ39" s="4">
         <f t="shared" si="43"/>
-        <v>0.94623655913978499</v>
+        <v>0.95340501792114696</v>
       </c>
       <c r="BA39" s="5">
         <v>291</v>
@@ -7551,14 +7551,14 @@
       </c>
       <c r="BC39" s="3">
         <f t="shared" si="44"/>
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BD39" s="5">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BE39" s="4">
         <f t="shared" si="45"/>
-        <v>0.91408934707903777</v>
+        <v>0.92096219931271472</v>
       </c>
       <c r="BF39" s="5">
         <v>344</v>
@@ -7568,14 +7568,14 @@
       </c>
       <c r="BH39" s="3">
         <f t="shared" si="46"/>
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="BI39" s="5">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="BJ39" s="4">
         <f t="shared" si="47"/>
-        <v>0.93023255813953487</v>
+        <v>0.96220930232558144</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>124820</v>
+        <v>124893</v>
       </c>
       <c r="F40" s="5">
-        <v>301480</v>
+        <v>301553</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.99205644073262389</v>
+        <v>0.99229665607086681</v>
       </c>
       <c r="H40" s="5">
         <v>306465</v>
@@ -7610,14 +7610,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>127255</v>
+        <v>127345</v>
       </c>
       <c r="K40" s="5">
-        <v>302828</v>
+        <v>302918</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.98813241316300393</v>
+        <v>0.9884260845447278</v>
       </c>
       <c r="M40" s="5">
         <v>361770</v>
@@ -7627,14 +7627,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>149525</v>
+        <v>149660</v>
       </c>
       <c r="P40" s="5">
-        <v>359038</v>
+        <v>359173</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99244824059485304</v>
+        <v>0.99282140586560519</v>
       </c>
       <c r="R40" s="5">
         <v>306479</v>
@@ -7644,14 +7644,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>117769</v>
+        <v>117912</v>
       </c>
       <c r="U40" s="5">
-        <v>304482</v>
+        <v>304625</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99348405600383716</v>
+        <v>0.99395064588438364</v>
       </c>
       <c r="W40" s="5">
         <v>309858</v>
@@ -7661,14 +7661,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>123984</v>
+        <v>124181</v>
       </c>
       <c r="Z40" s="5">
-        <v>305973</v>
+        <v>306170</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.98746199872199525</v>
+        <v>0.98809777381897512</v>
       </c>
       <c r="AB40" s="5">
         <v>365821</v>
@@ -7678,14 +7678,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>149968</v>
+        <v>150344</v>
       </c>
       <c r="AE40" s="5">
-        <v>362656</v>
+        <v>363032</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99134822768512465</v>
+        <v>0.99237605276897722</v>
       </c>
       <c r="AG40" s="5">
         <v>311342</v>
@@ -7695,14 +7695,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>122739</v>
+        <v>123278</v>
       </c>
       <c r="AJ40" s="5">
-        <v>308097</v>
+        <v>308636</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.98957737793166356</v>
+        <v>0.99130859312267539</v>
       </c>
       <c r="AL40" s="5">
         <v>314792</v>
@@ -7712,14 +7712,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>123452</v>
+        <v>124363</v>
       </c>
       <c r="AO40" s="5">
-        <v>311330</v>
+        <v>312241</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.98900226181097362</v>
+        <v>0.99189623624488554</v>
       </c>
       <c r="AQ40" s="5">
         <v>372144</v>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>154681</v>
+        <v>156557</v>
       </c>
       <c r="AT40" s="5">
-        <v>367382</v>
+        <v>369258</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.98720387806870458</v>
+        <v>0.99224493744357023</v>
       </c>
       <c r="AV40" s="5">
         <v>317868</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>61457</v>
+        <v>63727</v>
       </c>
       <c r="AY40" s="5">
-        <v>311273</v>
+        <v>313543</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.97925239407552822</v>
+        <v>0.98639372318069141</v>
       </c>
       <c r="BA40" s="5">
         <v>321637</v>
@@ -7763,14 +7763,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>108435</v>
+        <v>111637</v>
       </c>
       <c r="BD40" s="5">
-        <v>311202</v>
+        <v>314404</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.96755659330238752</v>
+        <v>0.97751191560672435</v>
       </c>
       <c r="BF40" s="5">
         <v>380248</v>
@@ -7780,14 +7780,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>143358</v>
+        <v>150060</v>
       </c>
       <c r="BI40" s="5">
-        <v>360299</v>
+        <v>367001</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.94753687067387604</v>
+        <v>0.96516220992615342</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>370714</v>
+        <v>370841</v>
       </c>
       <c r="F41" s="5">
-        <v>975916</v>
+        <v>976043</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99844797546225672</v>
+        <v>0.99857790764175136</v>
       </c>
       <c r="H41" s="5">
         <v>983280</v>
@@ -7822,14 +7822,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>379631</v>
+        <v>379780</v>
       </c>
       <c r="K41" s="5">
-        <v>980411</v>
+        <v>980560</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.99708221462859004</v>
+        <v>0.99723374827109268</v>
       </c>
       <c r="M41" s="5">
         <v>1084276</v>
@@ -7839,14 +7839,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>390184</v>
+        <v>390389</v>
       </c>
       <c r="P41" s="5">
-        <v>1082863</v>
+        <v>1083068</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.99869682626932621</v>
+        <v>0.99888589252183024</v>
       </c>
       <c r="R41" s="5">
         <v>988018</v>
@@ -7856,14 +7856,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>348881</v>
+        <v>349114</v>
       </c>
       <c r="U41" s="5">
-        <v>988085</v>
+        <v>988318</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>1.0000678125297313</v>
+        <v>1.0003036381928265</v>
       </c>
       <c r="W41" s="5">
         <v>994033</v>
@@ -7873,14 +7873,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>343218</v>
+        <v>343520</v>
       </c>
       <c r="Z41" s="5">
-        <v>993150</v>
+        <v>993452</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.999111699510982</v>
+        <v>0.99941551236226567</v>
       </c>
       <c r="AB41" s="5">
         <v>1097882</v>
@@ -7890,14 +7890,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>394248</v>
+        <v>394702</v>
       </c>
       <c r="AE41" s="5">
-        <v>1097045</v>
+        <v>1097499</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.99923762298680552</v>
+        <v>0.9996511464802228</v>
       </c>
       <c r="AG41" s="5">
         <v>1002140</v>
@@ -7907,14 +7907,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>353711</v>
+        <v>354282</v>
       </c>
       <c r="AJ41" s="5">
-        <v>1001086</v>
+        <v>1001657</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99894825074340909</v>
+        <v>0.99951803141277662</v>
       </c>
       <c r="AL41" s="5">
         <v>1011306</v>
@@ -7924,14 +7924,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>342166</v>
+        <v>343062</v>
       </c>
       <c r="AO41" s="5">
-        <v>1013641</v>
+        <v>1014537</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>1.002308895626052</v>
+        <v>1.003194878701402</v>
       </c>
       <c r="AQ41" s="5">
         <v>1119532</v>
@@ -7941,14 +7941,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>394657</v>
+        <v>396389</v>
       </c>
       <c r="AT41" s="5">
-        <v>1121500</v>
+        <v>1123232</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>1.0017578773987701</v>
+        <v>1.0033049524265496</v>
       </c>
       <c r="AV41" s="5">
         <v>1028062</v>
@@ -7958,14 +7958,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>146266</v>
+        <v>148542</v>
       </c>
       <c r="AY41" s="5">
-        <v>1025974</v>
+        <v>1028250</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>0.99796899408790518</v>
+        <v>1.0001828683484071</v>
       </c>
       <c r="BA41" s="5">
         <v>1037044</v>
@@ -7975,14 +7975,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>325901</v>
+        <v>329795</v>
       </c>
       <c r="BD41" s="5">
-        <v>1030718</v>
+        <v>1034612</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.99389996952877602</v>
+        <v>0.99765487288871058</v>
       </c>
       <c r="BF41" s="5">
         <v>1143357</v>
@@ -7992,14 +7992,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>378653</v>
+        <v>390345</v>
       </c>
       <c r="BI41" s="5">
-        <v>1122487</v>
+        <v>1134179</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.98174673352242559</v>
+        <v>0.99197276091369535</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>9249</v>
+        <v>9254</v>
       </c>
       <c r="F42" s="5">
-        <v>19582</v>
+        <v>19587</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.99522260622077663</v>
+        <v>0.99547672291116085</v>
       </c>
       <c r="H42" s="5">
         <v>19882</v>
@@ -8034,14 +8034,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>9520</v>
+        <v>9524</v>
       </c>
       <c r="K42" s="5">
-        <v>19677</v>
+        <v>19681</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.98968916607987123</v>
+        <v>0.98989035308319084</v>
       </c>
       <c r="M42" s="5">
         <v>21930</v>
@@ -8051,14 +8051,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9984</v>
+        <v>9987</v>
       </c>
       <c r="P42" s="5">
-        <v>21775</v>
+        <v>21778</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99293205654354766</v>
+        <v>0.99306885544915635</v>
       </c>
       <c r="R42" s="5">
         <v>20021</v>
@@ -8068,14 +8068,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8922</v>
+        <v>8928</v>
       </c>
       <c r="U42" s="5">
-        <v>19806</v>
+        <v>19812</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.98926127566055644</v>
+        <v>0.98956096099095947</v>
       </c>
       <c r="W42" s="5">
         <v>20153</v>
@@ -8085,14 +8085,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>8692</v>
+        <v>8700</v>
       </c>
       <c r="Z42" s="5">
-        <v>19899</v>
+        <v>19907</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.9873964174068377</v>
+        <v>0.98779338063811839</v>
       </c>
       <c r="AB42" s="5">
         <v>22238</v>
@@ -8102,14 +8102,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>9997</v>
+        <v>10012</v>
       </c>
       <c r="AE42" s="5">
-        <v>22052</v>
+        <v>22067</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.99163593848367659</v>
+        <v>0.99231045957370267</v>
       </c>
       <c r="AG42" s="5">
         <v>20276</v>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>9022</v>
+        <v>9048</v>
       </c>
       <c r="AJ42" s="5">
-        <v>20121</v>
+        <v>20147</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.99235549418031166</v>
+        <v>0.99363779838232391</v>
       </c>
       <c r="AL42" s="5">
         <v>20453</v>
@@ -8136,14 +8136,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8697</v>
+        <v>8745</v>
       </c>
       <c r="AO42" s="5">
-        <v>20285</v>
+        <v>20333</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.9917860460568132</v>
+        <v>0.99413289004058081</v>
       </c>
       <c r="AQ42" s="5">
         <v>22621</v>
@@ -8153,14 +8153,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>10143</v>
+        <v>10247</v>
       </c>
       <c r="AT42" s="5">
-        <v>22444</v>
+        <v>22548</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.9921754122275761</v>
+        <v>0.99677291012775737</v>
       </c>
       <c r="AV42" s="5">
         <v>20714</v>
@@ -8170,14 +8170,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>3702</v>
+        <v>3857</v>
       </c>
       <c r="AY42" s="5">
-        <v>20398</v>
+        <v>20553</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.98474461716713335</v>
+        <v>0.99222747899971031</v>
       </c>
       <c r="BA42" s="5">
         <v>20927</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8228</v>
+        <v>8449</v>
       </c>
       <c r="BD42" s="5">
-        <v>20390</v>
+        <v>20611</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.97433937019161854</v>
+        <v>0.98489989009413681</v>
       </c>
       <c r="BF42" s="5">
         <v>23165</v>
@@ -8204,14 +8204,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>9637</v>
+        <v>10041</v>
       </c>
       <c r="BI42" s="5">
-        <v>22154</v>
+        <v>22558</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.95635657241528171</v>
+        <v>0.97379667601985753</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8246,14 +8246,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="K43" s="5">
-        <v>3923</v>
+        <v>3926</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.99543263131184978</v>
+        <v>0.99619385942654148</v>
       </c>
       <c r="M43" s="5">
         <v>4896</v>
@@ -8263,14 +8263,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2713</v>
+        <v>2717</v>
       </c>
       <c r="P43" s="5">
-        <v>4857</v>
+        <v>4861</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.99203431372549022</v>
+        <v>0.99285130718954251</v>
       </c>
       <c r="R43" s="5">
         <v>3969</v>
@@ -8280,14 +8280,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="30"/>
-        <v>2152</v>
+        <v>2157</v>
       </c>
       <c r="U43" s="5">
-        <v>3925</v>
+        <v>3930</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="31"/>
-        <v>0.98891408415217941</v>
+        <v>0.99017384731670444</v>
       </c>
       <c r="W43" s="5">
         <v>4009</v>
@@ -8297,14 +8297,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="Z43" s="5">
-        <v>3966</v>
+        <v>3971</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.98927413320029933</v>
+        <v>0.99052132701421802</v>
       </c>
       <c r="AB43" s="5">
         <v>4962</v>
@@ -8314,14 +8314,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="34"/>
-        <v>2674</v>
+        <v>2683</v>
       </c>
       <c r="AE43" s="5">
-        <v>4928</v>
+        <v>4937</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99314792422410314</v>
+        <v>0.99496170898831116</v>
       </c>
       <c r="AG43" s="5">
         <v>4018</v>
@@ -8331,14 +8331,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2229</v>
+        <v>2243</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3992</v>
+        <v>4006</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>0.99352911896465901</v>
+        <v>0.99701343952215027</v>
       </c>
       <c r="AL43" s="5">
         <v>4086</v>
@@ -8348,14 +8348,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="38"/>
-        <v>2123</v>
+        <v>2143</v>
       </c>
       <c r="AO43" s="5">
-        <v>4038</v>
+        <v>4058</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="39"/>
-        <v>0.98825256975036713</v>
+        <v>0.9931473323543808</v>
       </c>
       <c r="AQ43" s="5">
         <v>5072</v>
@@ -8365,14 +8365,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2868</v>
+        <v>2908</v>
       </c>
       <c r="AT43" s="5">
-        <v>5006</v>
+        <v>5046</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>0.98698738170347</v>
+        <v>0.99487381703470035</v>
       </c>
       <c r="AV43" s="5">
         <v>4151</v>
@@ -8382,14 +8382,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="42"/>
-        <v>1176</v>
+        <v>1221</v>
       </c>
       <c r="AY43" s="5">
-        <v>4017</v>
+        <v>4062</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="43"/>
-        <v>0.96771862201879066</v>
+        <v>0.97855938328113712</v>
       </c>
       <c r="BA43" s="5">
         <v>4249</v>
@@ -8399,14 +8399,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>2060</v>
+        <v>2127</v>
       </c>
       <c r="BD43" s="5">
-        <v>4028</v>
+        <v>4095</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.94798776182631206</v>
+        <v>0.96375617792421742</v>
       </c>
       <c r="BF43" s="5">
         <v>5295</v>
@@ -8416,14 +8416,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2520</v>
+        <v>2686</v>
       </c>
       <c r="BI43" s="5">
-        <v>4733</v>
+        <v>4899</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.89386213408876303</v>
+        <v>0.92521246458923512</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>185896</v>
+        <v>185961</v>
       </c>
       <c r="F44" s="5">
-        <v>379913</v>
+        <v>379978</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.99054852452690478</v>
+        <v>0.99071799925952575</v>
       </c>
       <c r="H44" s="5">
         <v>388149</v>
@@ -8458,14 +8458,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>184354</v>
+        <v>184437</v>
       </c>
       <c r="K44" s="5">
-        <v>383158</v>
+        <v>383241</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98714153585349951</v>
+        <v>0.98735537126206685</v>
       </c>
       <c r="M44" s="5">
         <v>456953</v>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>211876</v>
+        <v>212005</v>
       </c>
       <c r="P44" s="5">
-        <v>453682</v>
+        <v>453811</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.99284171457458426</v>
+        <v>0.99312401931927352</v>
       </c>
       <c r="R44" s="5">
         <v>388846</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>181157</v>
+        <v>181286</v>
       </c>
       <c r="U44" s="5">
-        <v>385251</v>
+        <v>385380</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.99075469466061117</v>
+        <v>0.99108644553370739</v>
       </c>
       <c r="W44" s="5">
         <v>393146</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>178236</v>
+        <v>178405</v>
       </c>
       <c r="Z44" s="5">
-        <v>387824</v>
+        <v>387993</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.98646304426345433</v>
+        <v>0.986892910013074</v>
       </c>
       <c r="AB44" s="5">
         <v>465292</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>222423</v>
+        <v>222698</v>
       </c>
       <c r="AE44" s="5">
-        <v>460447</v>
+        <v>460722</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.98958718396189915</v>
+        <v>0.99017821067200806</v>
       </c>
       <c r="AG44" s="5">
         <v>393778</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>180614</v>
+        <v>180954</v>
       </c>
       <c r="AJ44" s="5">
-        <v>391221</v>
+        <v>391561</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.99350649350649356</v>
+        <v>0.99436992417047165</v>
       </c>
       <c r="AL44" s="5">
         <v>398873</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>178905</v>
+        <v>179471</v>
       </c>
       <c r="AO44" s="5">
-        <v>400409</v>
+        <v>400975</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>1.0038508497692249</v>
+        <v>1.0052698477961657</v>
       </c>
       <c r="AQ44" s="5">
         <v>476819</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>220923</v>
+        <v>222200</v>
       </c>
       <c r="AT44" s="5">
-        <v>476562</v>
+        <v>477839</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>0.9994610114110386</v>
+        <v>1.0021391765009364</v>
       </c>
       <c r="AV44" s="5">
         <v>408878</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>71479</v>
+        <v>73046</v>
       </c>
       <c r="AY44" s="5">
-        <v>406857</v>
+        <v>408424</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.99505720532775055</v>
+        <v>0.99888964434378957</v>
       </c>
       <c r="BA44" s="5">
         <v>416024</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>174782</v>
+        <v>177571</v>
       </c>
       <c r="BD44" s="5">
-        <v>409848</v>
+        <v>412637</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.98515470261331073</v>
+        <v>0.99185864277060942</v>
       </c>
       <c r="BF44" s="5">
         <v>493955</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>214816</v>
+        <v>222811</v>
       </c>
       <c r="BI44" s="5">
-        <v>474781</v>
+        <v>482776</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.96118269882884066</v>
+        <v>0.97736838375965418</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8653,14 +8653,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>138376</v>
+        <v>138416</v>
       </c>
       <c r="F45" s="5">
-        <v>276870</v>
+        <v>276910</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.9977441116268343</v>
+        <v>0.99788825784876178</v>
       </c>
       <c r="H45" s="5">
         <v>280269</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>138680</v>
+        <v>138726</v>
       </c>
       <c r="K45" s="5">
-        <v>278807</v>
+        <v>278853</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.99478358291498525</v>
+        <v>0.99494771094912393</v>
       </c>
       <c r="M45" s="5">
         <v>334005</v>
@@ -8687,14 +8687,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>162343</v>
+        <v>162422</v>
       </c>
       <c r="P45" s="5">
-        <v>332079</v>
+        <v>332158</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.99423361925719678</v>
+        <v>0.99447014266253497</v>
       </c>
       <c r="R45" s="5">
         <v>281510</v>
@@ -8704,14 +8704,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>134197</v>
+        <v>134264</v>
       </c>
       <c r="U45" s="5">
-        <v>279778</v>
+        <v>279845</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.99384746545415792</v>
+        <v>0.99408546765656636</v>
       </c>
       <c r="W45" s="5">
         <v>284325</v>
@@ -8721,14 +8721,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>132993</v>
+        <v>133068</v>
       </c>
       <c r="Z45" s="5">
-        <v>280892</v>
+        <v>280967</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.98792578914974061</v>
+        <v>0.98818957179284272</v>
       </c>
       <c r="AB45" s="5">
         <v>338696</v>
@@ -8738,14 +8738,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>171576</v>
+        <v>171745</v>
       </c>
       <c r="AE45" s="5">
-        <v>334846</v>
+        <v>335015</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98863287431797242</v>
+        <v>0.98913184684791078</v>
       </c>
       <c r="AG45" s="5">
         <v>285325</v>
@@ -8755,14 +8755,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>139214</v>
+        <v>139441</v>
       </c>
       <c r="AJ45" s="5">
-        <v>282413</v>
+        <v>282640</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98979409445369315</v>
+        <v>0.99058967843687018</v>
       </c>
       <c r="AL45" s="5">
         <v>289428</v>
@@ -8772,14 +8772,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>135040</v>
+        <v>135444</v>
       </c>
       <c r="AO45" s="5">
-        <v>288874</v>
+        <v>289278</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.9980858797352018</v>
+        <v>0.99948173639039761</v>
       </c>
       <c r="AQ45" s="5">
         <v>348161</v>
@@ -8789,14 +8789,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>169876</v>
+        <v>170831</v>
       </c>
       <c r="AT45" s="5">
-        <v>345730</v>
+        <v>346685</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99301759818015234</v>
+        <v>0.99576058202957829</v>
       </c>
       <c r="AV45" s="5">
         <v>296165</v>
@@ -8806,14 +8806,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>50804</v>
+        <v>51815</v>
       </c>
       <c r="AY45" s="5">
-        <v>292837</v>
+        <v>293848</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.9887630206135094</v>
+        <v>0.9921766582817011</v>
       </c>
       <c r="BA45" s="5">
         <v>300603</v>
@@ -8823,14 +8823,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>132190</v>
+        <v>133855</v>
       </c>
       <c r="BD45" s="5">
-        <v>294991</v>
+        <v>296656</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98133085830813394</v>
+        <v>0.98686972518571003</v>
       </c>
       <c r="BF45" s="5">
         <v>359430</v>
@@ -8840,14 +8840,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>168197</v>
+        <v>173496</v>
       </c>
       <c r="BI45" s="5">
-        <v>344472</v>
+        <v>349771</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.95838410817127118</v>
+        <v>0.97312689536210106</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8865,14 +8865,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="F46" s="5">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0263374485596708</v>
+        <v>1.0279835390946501</v>
       </c>
       <c r="H46" s="5">
         <v>2594</v>
@@ -8882,14 +8882,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1635</v>
+        <v>1640</v>
       </c>
       <c r="K46" s="5">
-        <v>2640</v>
+        <v>2645</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>1.0177332305319968</v>
+        <v>1.0196607555898227</v>
       </c>
       <c r="M46" s="5">
         <v>8454</v>
@@ -8899,14 +8899,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>5753</v>
+        <v>5764</v>
       </c>
       <c r="P46" s="5">
-        <v>8608</v>
+        <v>8619</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0182162290040218</v>
+        <v>1.0195173882185948</v>
       </c>
       <c r="R46" s="5">
         <v>2484</v>
@@ -8916,14 +8916,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="U46" s="5">
-        <v>2585</v>
+        <v>2590</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0406602254428341</v>
+        <v>1.0426731078904992</v>
       </c>
       <c r="W46" s="5">
         <v>2748</v>
@@ -8933,14 +8933,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="Z46" s="5">
-        <v>2690</v>
+        <v>2696</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.9788937409024745</v>
+        <v>0.98107714701601167</v>
       </c>
       <c r="AB46" s="5">
         <v>8770</v>
@@ -8950,14 +8950,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5847</v>
+        <v>5862</v>
       </c>
       <c r="AE46" s="5">
-        <v>8833</v>
+        <v>8848</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0071835803876852</v>
+        <v>1.0088939566704676</v>
       </c>
       <c r="AG46" s="5">
         <v>2523</v>
@@ -8967,14 +8967,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1487</v>
+        <v>1496</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2543</v>
+        <v>2552</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.007927070947285</v>
+        <v>1.0114942528735633</v>
       </c>
       <c r="AL46" s="5">
         <v>2722</v>
@@ -8984,14 +8984,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1484</v>
+        <v>1496</v>
       </c>
       <c r="AO46" s="5">
-        <v>2648</v>
+        <v>2660</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>0.97281410727406314</v>
+        <v>0.97722263041880975</v>
       </c>
       <c r="AQ46" s="5">
         <v>8967</v>
@@ -9001,14 +9001,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5680</v>
+        <v>5735</v>
       </c>
       <c r="AT46" s="5">
-        <v>8900</v>
+        <v>8955</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>0.9925281588045054</v>
+        <v>0.99866175978588156</v>
       </c>
       <c r="AV46" s="5">
         <v>2626</v>
@@ -9018,14 +9018,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="AY46" s="5">
-        <v>2589</v>
+        <v>2618</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>0.98591012947448586</v>
+        <v>0.99695354150799698</v>
       </c>
       <c r="BA46" s="5">
         <v>2791</v>
@@ -9035,14 +9035,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1406</v>
+        <v>1444</v>
       </c>
       <c r="BD46" s="5">
-        <v>2625</v>
+        <v>2663</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.94052310999641708</v>
+        <v>0.95413830168398428</v>
       </c>
       <c r="BF46" s="5">
         <v>9093</v>
@@ -9052,14 +9052,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5559</v>
+        <v>5716</v>
       </c>
       <c r="BI46" s="5">
-        <v>8629</v>
+        <v>8786</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>0.94897173650060485</v>
+        <v>0.96623776531397776</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9230,14 +9230,14 @@
       </c>
       <c r="AX47" s="3">
         <f t="shared" si="42"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY47" s="5">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AZ47" s="4">
         <f t="shared" si="43"/>
-        <v>0.94666666666666666</v>
+        <v>0.96</v>
       </c>
       <c r="BA47" s="5">
         <v>76</v>
@@ -9275,10 +9275,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="20"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>8623084</v>
@@ -9289,15 +9289,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3385482</v>
+        <v>3387264</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8579838</v>
+        <v>8581620</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.994984856925898</v>
+        <v>0.9951915115288219</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3391471</v>
+        <v>3393649</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8696244</v>
+        <v>8698422</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.9912374379054929</v>
+        <v>0.99148569625010219</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5472967</v>
+        <v>5477288</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>13314583</v>
+        <v>13318904</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99693699018628368</v>
+        <v>0.99726052752384764</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3273699</v>
+        <v>3276961</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8724630</v>
+        <v>8727892</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99475386180395919</v>
+        <v>0.99512578440666033</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3248986</v>
+        <v>3253171</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8820636</v>
+        <v>8824821</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98746867224034995</v>
+        <v>0.98793718226540106</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9389,15 +9389,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5684489</v>
+        <v>5693892</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>13526262</v>
+        <v>13535665</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99400726494564517</v>
+        <v>0.99469826518741811</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9409,15 +9409,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3358858</v>
+        <v>3367901</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8854345</v>
+        <v>8863388</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99296195266983545</v>
+        <v>0.99397607115494002</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9429,15 +9429,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3344419</v>
+        <v>3358741</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>9109884</v>
+        <v>9124206</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.9980853171125057</v>
+        <v>0.99965444553518212</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9449,15 +9449,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>5697063</v>
+        <v>5734939</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>13936453</v>
+        <v>13974329</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99709010257831998</v>
+        <v>0.99979995886135387</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9469,15 +9469,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>1388055</v>
+        <v>1421370</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>9187117</v>
+        <v>9220432</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99314149778143213</v>
+        <v>0.99674290059349913</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9489,15 +9489,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3278438</v>
+        <v>3330332</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>9307882</v>
+        <v>9359776</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98280772128368477</v>
+        <v>0.98828714441005183</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9509,19 +9509,27 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5467342</v>
+        <v>5654346</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>13917104</v>
+        <v>14104108</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.96441663901130048</v>
+        <v>0.97737549662720025</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="M8:Q8"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="R8:V8"/>
+    <mergeCell ref="H8:L8"/>
+    <mergeCell ref="C8:G8"/>
     <mergeCell ref="BF8:BJ8"/>
     <mergeCell ref="BA8:BE8"/>
     <mergeCell ref="A48:B48"/>
@@ -9530,14 +9538,6 @@
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="AG8:AK8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="M8:Q8"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="R8:V8"/>
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/gstdatabase/GSTR-1-2025-2026.xlsx
+++ b/gstdatabase/GSTR-1-2025-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F326293-4FD7-409C-9911-7C9D07A601D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7F230-AF9F-4EC7-A00B-A9B72350E7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
     <t>FINANCIAL YEAR 2025-2026</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1257,14 +1257,14 @@
       </c>
       <c r="E10" s="3">
         <f>F10-D10</f>
-        <v>47238</v>
+        <v>47255</v>
       </c>
       <c r="F10" s="5">
-        <v>74128</v>
+        <v>74145</v>
       </c>
       <c r="G10" s="4">
         <f>F10/C10</f>
-        <v>0.99917777568103083</v>
+        <v>0.99940692016336652</v>
       </c>
       <c r="H10" s="5">
         <v>75899</v>
@@ -1274,14 +1274,14 @@
       </c>
       <c r="J10" s="3">
         <f>K10-I10</f>
-        <v>45396</v>
+        <v>45414</v>
       </c>
       <c r="K10" s="5">
-        <v>74863</v>
+        <v>74881</v>
       </c>
       <c r="L10" s="4">
         <f>K10/H10</f>
-        <v>0.98635028129487867</v>
+        <v>0.98658743856967812</v>
       </c>
       <c r="M10" s="5">
         <v>134494</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>88150</v>
+        <v>88208</v>
       </c>
       <c r="P10" s="5">
-        <v>134369</v>
+        <v>134427</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>0.99907059050961378</v>
+        <v>0.99950183651315305</v>
       </c>
       <c r="R10" s="5">
         <v>73914</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="T10" s="3">
         <f>U10-S10</f>
-        <v>42283</v>
+        <v>42320</v>
       </c>
       <c r="U10" s="5">
-        <v>73610</v>
+        <v>73647</v>
       </c>
       <c r="V10" s="4">
         <f>U10/R10</f>
-        <v>0.99588711204913816</v>
+        <v>0.99638769380631542</v>
       </c>
       <c r="W10" s="5">
         <v>75592</v>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42507</v>
+        <v>42546</v>
       </c>
       <c r="Z10" s="5">
-        <v>74632</v>
+        <v>74671</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.98730024341200129</v>
+        <v>0.9878161710233887</v>
       </c>
       <c r="AB10" s="5">
         <v>136558</v>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>89083</v>
+        <v>89183</v>
       </c>
       <c r="AE10" s="5">
-        <v>136205</v>
+        <v>136305</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>0.9974150177946367</v>
+        <v>0.99814730737122692</v>
       </c>
       <c r="AG10" s="5">
         <v>73704</v>
@@ -1359,14 +1359,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>42370</v>
+        <v>42437</v>
       </c>
       <c r="AJ10" s="5">
-        <v>73357</v>
+        <v>73424</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99529197872571362</v>
+        <v>0.99620102029740587</v>
       </c>
       <c r="AL10" s="5">
         <v>75897</v>
@@ -1376,14 +1376,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>42806</v>
+        <v>42902</v>
       </c>
       <c r="AO10" s="5">
-        <v>75972</v>
+        <v>76068</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>1.0009881813510415</v>
+        <v>1.0022530534803746</v>
       </c>
       <c r="AQ10" s="5">
         <v>140117</v>
@@ -1393,14 +1393,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>91315</v>
+        <v>91618</v>
       </c>
       <c r="AT10" s="5">
-        <v>140338</v>
+        <v>140641</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0015772532954603</v>
+        <v>1.0037397317955707</v>
       </c>
       <c r="AV10" s="5">
         <v>75508</v>
@@ -1410,14 +1410,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>13329</v>
+        <v>13568</v>
       </c>
       <c r="AY10" s="5">
-        <v>75725</v>
+        <v>75964</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>1.0028738676696509</v>
+        <v>1.0060390951952112</v>
       </c>
       <c r="BA10" s="5">
         <v>78056</v>
@@ -1427,14 +1427,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>42785</v>
+        <v>43131</v>
       </c>
       <c r="BD10" s="5">
-        <v>77224</v>
+        <v>77570</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.98934098595879882</v>
+        <v>0.99377370093266371</v>
       </c>
       <c r="BF10" s="5">
         <v>144885</v>
@@ -1444,14 +1444,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>91945</v>
+        <v>93699</v>
       </c>
       <c r="BI10" s="5">
-        <v>141445</v>
+        <v>143199</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>0.97625703143872722</v>
+        <v>0.98836318459467853</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1469,14 +1469,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E33" si="0">F11-D11</f>
-        <v>16308</v>
+        <v>16321</v>
       </c>
       <c r="F11" s="5">
-        <v>47472</v>
+        <v>47485</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G33" si="1">F11/C11</f>
-        <v>0.99241141423643775</v>
+        <v>0.99268318177067005</v>
       </c>
       <c r="H11" s="5">
         <v>49123</v>
@@ -1486,14 +1486,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>16782</v>
+        <v>16795</v>
       </c>
       <c r="K11" s="5">
-        <v>48207</v>
+        <v>48220</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.98135293039920202</v>
+        <v>0.98161757221668056</v>
       </c>
       <c r="M11" s="5">
         <v>111861</v>
@@ -1503,14 +1503,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>48211</v>
+        <v>48251</v>
       </c>
       <c r="P11" s="5">
-        <v>111469</v>
+        <v>111509</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>0.99649565085239722</v>
+        <v>0.99685323750011179</v>
       </c>
       <c r="R11" s="5">
         <v>47958</v>
@@ -1520,14 +1520,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>15907</v>
+        <v>15923</v>
       </c>
       <c r="U11" s="5">
-        <v>47542</v>
+        <v>47558</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99132574335877222</v>
+        <v>0.99165936861420412</v>
       </c>
       <c r="W11" s="5">
         <v>49731</v>
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>15207</v>
+        <v>15229</v>
       </c>
       <c r="Z11" s="5">
-        <v>48221</v>
+        <v>48243</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.96963664515091186</v>
+        <v>0.97007902515533573</v>
       </c>
       <c r="AB11" s="5">
         <v>113134</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>50421</v>
+        <v>50485</v>
       </c>
       <c r="AE11" s="5">
-        <v>112185</v>
+        <v>112249</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>0.9916117170788622</v>
+        <v>0.99217741792918135</v>
       </c>
       <c r="AG11" s="5">
         <v>48119</v>
@@ -1571,14 +1571,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15406</v>
+        <v>15441</v>
       </c>
       <c r="AJ11" s="5">
-        <v>47614</v>
+        <v>47649</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.98950518506203367</v>
+        <v>0.99023254847357589</v>
       </c>
       <c r="AL11" s="5">
         <v>49938</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN33" si="14">AO11-AM11</f>
-        <v>14796</v>
+        <v>14847</v>
       </c>
       <c r="AO11" s="5">
-        <v>48977</v>
+        <v>49028</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP33" si="15">AO11/AL11</f>
-        <v>0.98075613761063718</v>
+        <v>0.98177740398093638</v>
       </c>
       <c r="AQ11" s="5">
         <v>114343</v>
@@ -1605,14 +1605,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS33" si="16">AT11-AR11</f>
-        <v>47199</v>
+        <v>47387</v>
       </c>
       <c r="AT11" s="5">
-        <v>113893</v>
+        <v>114081</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU33" si="17">AT11/AQ11</f>
-        <v>0.99606447268306764</v>
+        <v>0.99770864853991936</v>
       </c>
       <c r="AV11" s="5">
         <v>49251</v>
@@ -1622,14 +1622,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX33" si="18">AY11-AW11</f>
-        <v>6759</v>
+        <v>6893</v>
       </c>
       <c r="AY11" s="5">
-        <v>48522</v>
+        <v>48656</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ33" si="19">AY11/AV11</f>
-        <v>0.98519827008588656</v>
+        <v>0.98791902702483203</v>
       </c>
       <c r="BA11" s="5">
         <v>50523</v>
@@ -1639,14 +1639,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC33" si="20">BD11-BB11</f>
-        <v>14396</v>
+        <v>14579</v>
       </c>
       <c r="BD11" s="5">
-        <v>49363</v>
+        <v>49546</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE33" si="21">BD11/BA11</f>
-        <v>0.97704015992716187</v>
+        <v>0.98066227262830785</v>
       </c>
       <c r="BF11" s="5">
         <v>116408</v>
@@ -1656,14 +1656,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>47176</v>
+        <v>48287</v>
       </c>
       <c r="BI11" s="5">
-        <v>113605</v>
+        <v>114716</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.97592089890729161</v>
+        <v>0.9854649165005841</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1681,14 +1681,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>44065</v>
+        <v>44087</v>
       </c>
       <c r="F12" s="5">
-        <v>181618</v>
+        <v>181640</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99381662179613461</v>
+        <v>0.99393700615054614</v>
       </c>
       <c r="H12" s="5">
         <v>186824</v>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>41227</v>
+        <v>41252</v>
       </c>
       <c r="K12" s="5">
-        <v>184377</v>
+        <v>184402</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.9869021110778059</v>
+        <v>0.98703592686164521</v>
       </c>
       <c r="M12" s="5">
         <v>372375</v>
@@ -1715,14 +1715,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>107158</v>
+        <v>107245</v>
       </c>
       <c r="P12" s="5">
-        <v>371330</v>
+        <v>371417</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.99719368915743534</v>
+        <v>0.99742732460557237</v>
       </c>
       <c r="R12" s="5">
         <v>184659</v>
@@ -1732,14 +1732,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>40573</v>
+        <v>40620</v>
       </c>
       <c r="U12" s="5">
-        <v>183312</v>
+        <v>183359</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99270547333192538</v>
+        <v>0.99295999653415212</v>
       </c>
       <c r="W12" s="5">
         <v>189081</v>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>40743</v>
+        <v>40798</v>
       </c>
       <c r="Z12" s="5">
-        <v>185548</v>
+        <v>185603</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98131488621278706</v>
+        <v>0.98160576684066614</v>
       </c>
       <c r="AB12" s="5">
         <v>377441</v>
@@ -1766,14 +1766,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>113667</v>
+        <v>113830</v>
       </c>
       <c r="AE12" s="5">
-        <v>374759</v>
+        <v>374922</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99289425367143469</v>
+        <v>0.99332610924621334</v>
       </c>
       <c r="AG12" s="5">
         <v>186148</v>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>41943</v>
+        <v>42034</v>
       </c>
       <c r="AJ12" s="5">
-        <v>184651</v>
+        <v>184742</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99195801190450605</v>
+        <v>0.99244687023228828</v>
       </c>
       <c r="AL12" s="5">
         <v>192239</v>
@@ -1800,14 +1800,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>41283</v>
+        <v>41451</v>
       </c>
       <c r="AO12" s="5">
-        <v>190928</v>
+        <v>191096</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.99318036402603005</v>
+        <v>0.99405427618745412</v>
       </c>
       <c r="AQ12" s="5">
         <v>384779</v>
@@ -1817,14 +1817,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>112338</v>
+        <v>112939</v>
       </c>
       <c r="AT12" s="5">
-        <v>383727</v>
+        <v>384328</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99726596305931459</v>
+        <v>0.99882789861193044</v>
       </c>
       <c r="AV12" s="5">
         <v>191743</v>
@@ -1834,14 +1834,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>25047</v>
+        <v>25540</v>
       </c>
       <c r="AY12" s="5">
-        <v>190552</v>
+        <v>191045</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99378856072972677</v>
+        <v>0.99635971065436546</v>
       </c>
       <c r="BA12" s="5">
         <v>197493</v>
@@ -1851,14 +1851,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>40244</v>
+        <v>40968</v>
       </c>
       <c r="BD12" s="5">
-        <v>193903</v>
+        <v>194627</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98182214053156314</v>
+        <v>0.98548809324887465</v>
       </c>
       <c r="BF12" s="5">
         <v>393305</v>
@@ -1868,14 +1868,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>109137</v>
+        <v>112573</v>
       </c>
       <c r="BI12" s="5">
-        <v>385726</v>
+        <v>389162</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.98072996783666622</v>
+        <v>0.98946619036117012</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1893,14 +1893,14 @@
       </c>
       <c r="E13" s="3">
         <f t="shared" si="0"/>
-        <v>3914</v>
+        <v>3916</v>
       </c>
       <c r="F13" s="5">
-        <v>17988</v>
+        <v>17990</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="1"/>
-        <v>0.99739395619628501</v>
+        <v>0.99750485167729419</v>
       </c>
       <c r="H13" s="5">
         <v>18257</v>
@@ -1910,14 +1910,14 @@
       </c>
       <c r="J13" s="3">
         <f t="shared" si="2"/>
-        <v>3769</v>
+        <v>3773</v>
       </c>
       <c r="K13" s="5">
-        <v>18071</v>
+        <v>18075</v>
       </c>
       <c r="L13" s="4">
         <f t="shared" si="3"/>
-        <v>0.98981212685545272</v>
+        <v>0.99003122090157203</v>
       </c>
       <c r="M13" s="5">
         <v>29011</v>
@@ -1927,14 +1927,14 @@
       </c>
       <c r="O13" s="3">
         <f t="shared" si="4"/>
-        <v>7185</v>
+        <v>7195</v>
       </c>
       <c r="P13" s="5">
-        <v>29036</v>
+        <v>29046</v>
       </c>
       <c r="Q13" s="4">
         <f t="shared" si="5"/>
-        <v>1.000861742097825</v>
+        <v>1.001206438936955</v>
       </c>
       <c r="R13" s="5">
         <v>18140</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="T13" s="3">
         <f t="shared" si="6"/>
-        <v>3734</v>
+        <v>3741</v>
       </c>
       <c r="U13" s="5">
-        <v>18124</v>
+        <v>18131</v>
       </c>
       <c r="V13" s="4">
         <f t="shared" si="7"/>
-        <v>0.99911797133406832</v>
+        <v>0.99950385887541349</v>
       </c>
       <c r="W13" s="5">
         <v>18401</v>
@@ -1961,14 +1961,14 @@
       </c>
       <c r="Y13" s="3">
         <f t="shared" si="8"/>
-        <v>3486</v>
+        <v>3491</v>
       </c>
       <c r="Z13" s="5">
-        <v>18234</v>
+        <v>18239</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="9"/>
-        <v>0.9909244062822673</v>
+        <v>0.99119613064507361</v>
       </c>
       <c r="AB13" s="5">
         <v>29242</v>
@@ -1978,14 +1978,14 @@
       </c>
       <c r="AD13" s="3">
         <f t="shared" si="10"/>
-        <v>7542</v>
+        <v>7561</v>
       </c>
       <c r="AE13" s="5">
-        <v>29264</v>
+        <v>29283</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="11"/>
-        <v>1.0007523425210314</v>
+        <v>1.001402092880104</v>
       </c>
       <c r="AG13" s="5">
         <v>18261</v>
@@ -1995,14 +1995,14 @@
       </c>
       <c r="AI13" s="3">
         <f t="shared" si="12"/>
-        <v>3791</v>
+        <v>3798</v>
       </c>
       <c r="AJ13" s="5">
-        <v>18385</v>
+        <v>18392</v>
       </c>
       <c r="AK13" s="4">
         <f t="shared" si="13"/>
-        <v>1.0067904276874213</v>
+        <v>1.007173758282679</v>
       </c>
       <c r="AL13" s="5">
         <v>18637</v>
@@ -2012,14 +2012,14 @@
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="14"/>
-        <v>3655</v>
+        <v>3673</v>
       </c>
       <c r="AO13" s="5">
-        <v>18718</v>
+        <v>18736</v>
       </c>
       <c r="AP13" s="4">
         <f t="shared" si="15"/>
-        <v>1.0043461930568225</v>
+        <v>1.0053120137361162</v>
       </c>
       <c r="AQ13" s="5">
         <v>29668</v>
@@ -2029,14 +2029,14 @@
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="16"/>
-        <v>7428</v>
+        <v>7475</v>
       </c>
       <c r="AT13" s="5">
-        <v>29819</v>
+        <v>29866</v>
       </c>
       <c r="AU13" s="4">
         <f t="shared" si="17"/>
-        <v>1.0050896588917353</v>
+        <v>1.0066738573547256</v>
       </c>
       <c r="AV13" s="5">
         <v>18676</v>
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AX13" s="3">
         <f t="shared" si="18"/>
-        <v>2460</v>
+        <v>2495</v>
       </c>
       <c r="AY13" s="5">
-        <v>18831</v>
+        <v>18866</v>
       </c>
       <c r="AZ13" s="4">
         <f t="shared" si="19"/>
-        <v>1.0082994217177126</v>
+        <v>1.0101734846862283</v>
       </c>
       <c r="BA13" s="5">
         <v>19025</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="BC13" s="3">
         <f t="shared" si="20"/>
-        <v>3554</v>
+        <v>3616</v>
       </c>
       <c r="BD13" s="5">
-        <v>19069</v>
+        <v>19131</v>
       </c>
       <c r="BE13" s="4">
         <f t="shared" si="21"/>
-        <v>1.0023127463863337</v>
+        <v>1.0055716162943495</v>
       </c>
       <c r="BF13" s="5">
         <v>30254</v>
@@ -2080,14 +2080,14 @@
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="22"/>
-        <v>7042</v>
+        <v>7294</v>
       </c>
       <c r="BI13" s="5">
-        <v>29918</v>
+        <v>30170</v>
       </c>
       <c r="BJ13" s="4">
         <f t="shared" si="23"/>
-        <v>0.988894030541416</v>
+        <v>0.99722350763535406</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.3">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>42253</v>
+        <v>42279</v>
       </c>
       <c r="F14" s="5">
-        <v>95157</v>
+        <v>95183</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>1.0057497384080412</v>
+        <v>1.0060245420819549</v>
       </c>
       <c r="H14" s="5">
         <v>97351</v>
@@ -2122,14 +2122,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>43515</v>
+        <v>43547</v>
       </c>
       <c r="K14" s="5">
-        <v>97135</v>
+        <v>97167</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.99778122464073304</v>
+        <v>0.99810993210136512</v>
       </c>
       <c r="M14" s="5">
         <v>172809</v>
@@ -2139,14 +2139,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>88148</v>
+        <v>88216</v>
       </c>
       <c r="P14" s="5">
-        <v>172933</v>
+        <v>173001</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>1.0007175552199248</v>
+        <v>1.0011110532437546</v>
       </c>
       <c r="R14" s="5">
         <v>97326</v>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>41860</v>
+        <v>41905</v>
       </c>
       <c r="U14" s="5">
-        <v>96384</v>
+        <v>96429</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.99032118858270146</v>
+        <v>0.99078355218543868</v>
       </c>
       <c r="W14" s="5">
         <v>98912</v>
@@ -2173,14 +2173,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>41310</v>
+        <v>41365</v>
       </c>
       <c r="Z14" s="5">
-        <v>97686</v>
+        <v>97741</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.9876051439663539</v>
+        <v>0.98816119378841794</v>
       </c>
       <c r="AB14" s="5">
         <v>175426</v>
@@ -2190,14 +2190,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>91491</v>
+        <v>91629</v>
       </c>
       <c r="AE14" s="5">
-        <v>175508</v>
+        <v>175646</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>1.0004674335617296</v>
+        <v>1.0012540900436651</v>
       </c>
       <c r="AG14" s="5">
         <v>98057</v>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>42587</v>
+        <v>42681</v>
       </c>
       <c r="AJ14" s="5">
-        <v>97932</v>
+        <v>98026</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99872523124305246</v>
+        <v>0.99968385734827703</v>
       </c>
       <c r="AL14" s="5">
         <v>101581</v>
@@ -2224,14 +2224,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>43653</v>
+        <v>43789</v>
       </c>
       <c r="AO14" s="5">
-        <v>102359</v>
+        <v>102495</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>1.0076589125919218</v>
+        <v>1.0089977456414094</v>
       </c>
       <c r="AQ14" s="5">
         <v>182247</v>
@@ -2241,14 +2241,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>92692</v>
+        <v>93084</v>
       </c>
       <c r="AT14" s="5">
-        <v>182461</v>
+        <v>182853</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.0011742305771838</v>
+        <v>1.0033251576157631</v>
       </c>
       <c r="AV14" s="5">
         <v>102257</v>
@@ -2258,14 +2258,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>17196</v>
+        <v>17515</v>
       </c>
       <c r="AY14" s="5">
-        <v>102704</v>
+        <v>103023</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>1.0043713388814457</v>
+        <v>1.0074909297163031</v>
       </c>
       <c r="BA14" s="5">
         <v>106311</v>
@@ -2275,14 +2275,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>44362</v>
+        <v>44767</v>
       </c>
       <c r="BD14" s="5">
-        <v>105098</v>
+        <v>105503</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98859008004816062</v>
+        <v>0.99239965760833782</v>
       </c>
       <c r="BF14" s="5">
         <v>189210</v>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>92323</v>
+        <v>94336</v>
       </c>
       <c r="BI14" s="5">
-        <v>185174</v>
+        <v>187187</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.97866920353046882</v>
+        <v>0.98930817610062893</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2317,14 +2317,14 @@
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>85871</v>
+        <v>85899</v>
       </c>
       <c r="F15" s="5">
-        <v>323653</v>
+        <v>323681</v>
       </c>
       <c r="G15" s="4">
         <f t="shared" si="1"/>
-        <v>0.99648086799098512</v>
+        <v>0.99656707594921123</v>
       </c>
       <c r="H15" s="5">
         <v>331968</v>
@@ -2334,14 +2334,14 @@
       </c>
       <c r="J15" s="3">
         <f t="shared" si="2"/>
-        <v>85231</v>
+        <v>85272</v>
       </c>
       <c r="K15" s="5">
-        <v>329293</v>
+        <v>329334</v>
       </c>
       <c r="L15" s="4">
         <f t="shared" si="3"/>
-        <v>0.99194199440909969</v>
+        <v>0.9920655002891845</v>
       </c>
       <c r="M15" s="5">
         <v>549212</v>
@@ -2351,14 +2351,14 @@
       </c>
       <c r="O15" s="3">
         <f t="shared" si="4"/>
-        <v>165513</v>
+        <v>165589</v>
       </c>
       <c r="P15" s="5">
-        <v>548433</v>
+        <v>548509</v>
       </c>
       <c r="Q15" s="4">
         <f t="shared" si="5"/>
-        <v>0.99858160418927477</v>
+        <v>0.99871998426836994</v>
       </c>
       <c r="R15" s="5">
         <v>333160</v>
@@ -2368,14 +2368,14 @@
       </c>
       <c r="T15" s="3">
         <f t="shared" si="6"/>
-        <v>84474</v>
+        <v>84527</v>
       </c>
       <c r="U15" s="5">
-        <v>331702</v>
+        <v>331755</v>
       </c>
       <c r="V15" s="4">
         <f t="shared" si="7"/>
-        <v>0.99562372433665502</v>
+        <v>0.99578280705967104</v>
       </c>
       <c r="W15" s="5">
         <v>340519</v>
@@ -2385,14 +2385,14 @@
       </c>
       <c r="Y15" s="3">
         <f t="shared" si="8"/>
-        <v>82353</v>
+        <v>82422</v>
       </c>
       <c r="Z15" s="5">
-        <v>336659</v>
+        <v>336728</v>
       </c>
       <c r="AA15" s="4">
         <f t="shared" si="9"/>
-        <v>0.98866436234101474</v>
+        <v>0.98886699420590329</v>
       </c>
       <c r="AB15" s="5">
         <v>562036</v>
@@ -2402,14 +2402,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>176176</v>
+        <v>176360</v>
       </c>
       <c r="AE15" s="5">
-        <v>559422</v>
+        <v>559606</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99534905237386928</v>
+        <v>0.99567643353806523</v>
       </c>
       <c r="AG15" s="5">
         <v>340264</v>
@@ -2419,14 +2419,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>87776</v>
+        <v>87933</v>
       </c>
       <c r="AJ15" s="5">
-        <v>338670</v>
+        <v>338827</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99531540215832415</v>
+        <v>0.99577680859567863</v>
       </c>
       <c r="AL15" s="5">
         <v>350627</v>
@@ -2436,14 +2436,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>88581</v>
+        <v>88876</v>
       </c>
       <c r="AO15" s="5">
-        <v>351965</v>
+        <v>352260</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>1.0038160210137839</v>
+        <v>1.0046573709383475</v>
       </c>
       <c r="AQ15" s="5">
         <v>580651</v>
@@ -2453,14 +2453,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>176561</v>
+        <v>177366</v>
       </c>
       <c r="AT15" s="5">
-        <v>581750</v>
+        <v>582555</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>1.0018927031900402</v>
+        <v>1.0032790781381586</v>
       </c>
       <c r="AV15" s="5">
         <v>355536</v>
@@ -2470,14 +2470,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>50477</v>
+        <v>51270</v>
       </c>
       <c r="AY15" s="5">
-        <v>355497</v>
+        <v>356290</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.99989030646685573</v>
+        <v>1.0021207416407902</v>
       </c>
       <c r="BA15" s="5">
         <v>365201</v>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>87956</v>
+        <v>89167</v>
       </c>
       <c r="BD15" s="5">
-        <v>362292</v>
+        <v>363503</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.9920345234542074</v>
+        <v>0.99535050561197802</v>
       </c>
       <c r="BF15" s="5">
         <v>600313</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>173370</v>
+        <v>178185</v>
       </c>
       <c r="BI15" s="5">
-        <v>590968</v>
+        <v>595783</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.98443312072202338</v>
+        <v>0.99245393652977698</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2529,14 +2529,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>119518</v>
+        <v>119624</v>
       </c>
       <c r="F16" s="5">
-        <v>450824</v>
+        <v>450930</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99405977271023427</v>
+        <v>0.99429350102972758</v>
       </c>
       <c r="H16" s="5">
         <v>461360</v>
@@ -2546,14 +2546,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>119844</v>
+        <v>119968</v>
       </c>
       <c r="K16" s="5">
-        <v>458464</v>
+        <v>458588</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.99372290619039361</v>
+        <v>0.99399167678168887</v>
       </c>
       <c r="M16" s="5">
         <v>788355</v>
@@ -2563,14 +2563,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>217313</v>
+        <v>217565</v>
       </c>
       <c r="P16" s="5">
-        <v>789296</v>
+        <v>789548</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>1.0011936246995325</v>
+        <v>1.0015132776477602</v>
       </c>
       <c r="R16" s="5">
         <v>462019</v>
@@ -2580,14 +2580,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>120019</v>
+        <v>120187</v>
       </c>
       <c r="U16" s="5">
-        <v>461550</v>
+        <v>461718</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.99898489023178705</v>
+        <v>0.99934851164129612</v>
       </c>
       <c r="W16" s="5">
         <v>472236</v>
@@ -2597,14 +2597,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>115888</v>
+        <v>116086</v>
       </c>
       <c r="Z16" s="5">
-        <v>466969</v>
+        <v>467167</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98884667835573736</v>
+        <v>0.98926596024021884</v>
       </c>
       <c r="AB16" s="5">
         <v>804216</v>
@@ -2614,14 +2614,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>232418</v>
+        <v>232863</v>
       </c>
       <c r="AE16" s="5">
-        <v>801580</v>
+        <v>802025</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99672227361803301</v>
+        <v>0.99727560754822087</v>
       </c>
       <c r="AG16" s="5">
         <v>471201</v>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>122076</v>
+        <v>122395</v>
       </c>
       <c r="AJ16" s="5">
-        <v>468968</v>
+        <v>469287</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.99526104571085372</v>
+        <v>0.99593803918073176</v>
       </c>
       <c r="AL16" s="5">
         <v>484445</v>
@@ -2648,14 +2648,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>127436</v>
+        <v>127941</v>
       </c>
       <c r="AO16" s="5">
-        <v>488951</v>
+        <v>489456</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>1.0093013654800855</v>
+        <v>1.0103437954772987</v>
       </c>
       <c r="AQ16" s="5">
         <v>831010</v>
@@ -2665,14 +2665,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>236406</v>
+        <v>237679</v>
       </c>
       <c r="AT16" s="5">
-        <v>833402</v>
+        <v>834675</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>1.0028784250490368</v>
+        <v>1.004410295904983</v>
       </c>
       <c r="AV16" s="5">
         <v>496237</v>
@@ -2682,14 +2682,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>72631</v>
+        <v>73869</v>
       </c>
       <c r="AY16" s="5">
-        <v>495499</v>
+        <v>496737</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.99851280738840509</v>
+        <v>1.0010075830701861</v>
       </c>
       <c r="BA16" s="5">
         <v>510690</v>
@@ -2699,14 +2699,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>124670</v>
+        <v>126463</v>
       </c>
       <c r="BD16" s="5">
-        <v>504258</v>
+        <v>506051</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98740527521588439</v>
+        <v>0.99091621140026243</v>
       </c>
       <c r="BF16" s="5">
         <v>859721</v>
@@ -2716,14 +2716,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>228619</v>
+        <v>234764</v>
       </c>
       <c r="BI16" s="5">
-        <v>845555</v>
+        <v>851700</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.98352256138910177</v>
+        <v>0.99067022906268432</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2741,14 +2741,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>106430</v>
+        <v>106475</v>
       </c>
       <c r="F17" s="5">
-        <v>339515</v>
+        <v>339560</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.9919826797834389</v>
+        <v>0.99211415916016821</v>
       </c>
       <c r="H17" s="5">
         <v>352243</v>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>105160</v>
+        <v>105212</v>
       </c>
       <c r="K17" s="5">
-        <v>347546</v>
+        <v>347598</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.98666545538165418</v>
+        <v>0.98681308074255558</v>
       </c>
       <c r="M17" s="5">
         <v>765449</v>
@@ -2775,14 +2775,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>302754</v>
+        <v>302953</v>
       </c>
       <c r="P17" s="5">
-        <v>765704</v>
+        <v>765903</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>1.0003331378053926</v>
+        <v>1.0005931159358756</v>
       </c>
       <c r="R17" s="5">
         <v>346814</v>
@@ -2792,14 +2792,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>103856</v>
+        <v>103934</v>
       </c>
       <c r="U17" s="5">
-        <v>346904</v>
+        <v>346982</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>1.0002595050949501</v>
+        <v>1.0004844095105734</v>
       </c>
       <c r="W17" s="5">
         <v>360071</v>
@@ -2809,14 +2809,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>105397</v>
+        <v>105503</v>
       </c>
       <c r="Z17" s="5">
-        <v>355649</v>
+        <v>355755</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.98771908873527725</v>
+        <v>0.98801347512018467</v>
       </c>
       <c r="AB17" s="5">
         <v>784641</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>317480</v>
+        <v>317878</v>
       </c>
       <c r="AE17" s="5">
-        <v>784081</v>
+        <v>784479</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99928629781008127</v>
+        <v>0.99979353615220212</v>
       </c>
       <c r="AG17" s="5">
         <v>355351</v>
@@ -2843,14 +2843,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>110107</v>
+        <v>110331</v>
       </c>
       <c r="AJ17" s="5">
-        <v>355259</v>
+        <v>355483</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99974110105219904</v>
+        <v>1.0003714637077143</v>
       </c>
       <c r="AL17" s="5">
         <v>371770</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>111701</v>
+        <v>112062</v>
       </c>
       <c r="AO17" s="5">
-        <v>371490</v>
+        <v>371851</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.99924684616832993</v>
+        <v>1.0002178766441616</v>
       </c>
       <c r="AQ17" s="5">
         <v>810773</v>
@@ -2877,14 +2877,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>315345</v>
+        <v>316626</v>
       </c>
       <c r="AT17" s="5">
-        <v>812070</v>
+        <v>813351</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>1.0015997079330465</v>
+        <v>1.0031796816124858</v>
       </c>
       <c r="AV17" s="5">
         <v>369648</v>
@@ -2894,14 +2894,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>52665</v>
+        <v>53473</v>
       </c>
       <c r="AY17" s="5">
-        <v>370096</v>
+        <v>370904</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>1.0012119638142232</v>
+        <v>1.0033978271220187</v>
       </c>
       <c r="BA17" s="5">
         <v>385393</v>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>112916</v>
+        <v>114190</v>
       </c>
       <c r="BD17" s="5">
-        <v>381427</v>
+        <v>382701</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98970920592745582</v>
+        <v>0.99301492242983136</v>
       </c>
       <c r="BF17" s="5">
         <v>839843</v>
@@ -2928,14 +2928,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>319856</v>
+        <v>327664</v>
       </c>
       <c r="BI17" s="5">
-        <v>823510</v>
+        <v>831318</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.98055231751648819</v>
+        <v>0.98984929326076421</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>542323</v>
+        <v>542506</v>
       </c>
       <c r="F18" s="5">
-        <v>1062775</v>
+        <v>1062958</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.99245370059092908</v>
+        <v>0.99262459191525287</v>
       </c>
       <c r="H18" s="5">
         <v>1089051</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>555463</v>
+        <v>555686</v>
       </c>
       <c r="K18" s="5">
-        <v>1079404</v>
+        <v>1079627</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.99114182898688863</v>
+        <v>0.99134659442027973</v>
       </c>
       <c r="M18" s="5">
         <v>1637429</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>875374</v>
+        <v>875848</v>
       </c>
       <c r="P18" s="5">
-        <v>1628162</v>
+        <v>1628636</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.99434051797055012</v>
+        <v>0.99462999617082637</v>
       </c>
       <c r="R18" s="5">
         <v>1090030</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>545114</v>
+        <v>545459</v>
       </c>
       <c r="U18" s="5">
-        <v>1078175</v>
+        <v>1078520</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98912415254626018</v>
+        <v>0.98944065759657995</v>
       </c>
       <c r="W18" s="5">
         <v>1107435</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>538555</v>
+        <v>539007</v>
       </c>
       <c r="Z18" s="5">
-        <v>1089561</v>
+        <v>1090013</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98386000081268876</v>
+        <v>0.98426815117817301</v>
       </c>
       <c r="AB18" s="5">
         <v>1665905</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>904474</v>
+        <v>905486</v>
       </c>
       <c r="AE18" s="5">
-        <v>1651272</v>
+        <v>1652284</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.99121618579690918</v>
+        <v>0.99182366341418027</v>
       </c>
       <c r="AG18" s="5">
         <v>1104366</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>554901</v>
+        <v>555707</v>
       </c>
       <c r="AJ18" s="5">
-        <v>1093708</v>
+        <v>1094514</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.9903492139381328</v>
+        <v>0.99107904444722128</v>
       </c>
       <c r="AL18" s="5">
         <v>1131950</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>564470</v>
+        <v>565756</v>
       </c>
       <c r="AO18" s="5">
-        <v>1132475</v>
+        <v>1133761</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>1.0004638014046556</v>
+        <v>1.0015998939882504</v>
       </c>
       <c r="AQ18" s="5">
         <v>1717059</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>920710</v>
+        <v>923928</v>
       </c>
       <c r="AT18" s="5">
-        <v>1712668</v>
+        <v>1715886</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99744272037245085</v>
+        <v>0.99931685515756885</v>
       </c>
       <c r="AV18" s="5">
         <v>1151692</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>181135</v>
+        <v>184247</v>
       </c>
       <c r="AY18" s="5">
-        <v>1146652</v>
+        <v>1149764</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99562382998232168</v>
+        <v>0.99832594131069763</v>
       </c>
       <c r="BA18" s="5">
         <v>1182353</v>
@@ -3123,14 +3123,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>578030</v>
+        <v>582547</v>
       </c>
       <c r="BD18" s="5">
-        <v>1166593</v>
+        <v>1171110</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98667064742932098</v>
+        <v>0.99049099549796038</v>
       </c>
       <c r="BF18" s="5">
         <v>1777125</v>
@@ -3140,14 +3140,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>918551</v>
+        <v>934936</v>
       </c>
       <c r="BI18" s="5">
-        <v>1735556</v>
+        <v>1751941</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.97660884856158126</v>
+        <v>0.98582879651121891</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -3165,14 +3165,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>178415</v>
+        <v>178511</v>
       </c>
       <c r="F19" s="5">
-        <v>299409</v>
+        <v>299505</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.97968058268628588</v>
+        <v>0.97999469928243987</v>
       </c>
       <c r="H19" s="5">
         <v>314567</v>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>183869</v>
+        <v>183982</v>
       </c>
       <c r="K19" s="5">
-        <v>306377</v>
+        <v>306490</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97396421112195497</v>
+        <v>0.97432343507106589</v>
       </c>
       <c r="M19" s="5">
         <v>534704</v>
@@ -3199,14 +3199,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>333505</v>
+        <v>333776</v>
       </c>
       <c r="P19" s="5">
-        <v>527670</v>
+        <v>527941</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.9868450582004249</v>
+        <v>0.98735188066668667</v>
       </c>
       <c r="R19" s="5">
         <v>310887</v>
@@ -3216,14 +3216,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>179482</v>
+        <v>179669</v>
       </c>
       <c r="U19" s="5">
-        <v>305351</v>
+        <v>305538</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.98219288680453032</v>
+        <v>0.98279439153132808</v>
       </c>
       <c r="W19" s="5">
         <v>321022</v>
@@ -3233,14 +3233,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>179448</v>
+        <v>179687</v>
       </c>
       <c r="Z19" s="5">
-        <v>310503</v>
+        <v>310742</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96723277532380958</v>
+        <v>0.96797727258567945</v>
       </c>
       <c r="AB19" s="5">
         <v>548160</v>
@@ -3250,14 +3250,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>351167</v>
+        <v>351787</v>
       </c>
       <c r="AE19" s="5">
-        <v>537557</v>
+        <v>538177</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.98065710741389378</v>
+        <v>0.98178816403969649</v>
       </c>
       <c r="AG19" s="5">
         <v>315587</v>
@@ -3267,14 +3267,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>188980</v>
+        <v>189394</v>
       </c>
       <c r="AJ19" s="5">
-        <v>309055</v>
+        <v>309469</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97930206250574325</v>
+        <v>0.98061390361453415</v>
       </c>
       <c r="AL19" s="5">
         <v>327315</v>
@@ -3284,14 +3284,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>188646</v>
+        <v>189319</v>
       </c>
       <c r="AO19" s="5">
-        <v>321740</v>
+        <v>322413</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.98296747781189375</v>
+        <v>0.98502360111818887</v>
       </c>
       <c r="AQ19" s="5">
         <v>564697</v>
@@ -3301,14 +3301,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>356720</v>
+        <v>358554</v>
       </c>
       <c r="AT19" s="5">
-        <v>559055</v>
+        <v>560889</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.99000880118010193</v>
+        <v>0.99325656059798439</v>
       </c>
       <c r="AV19" s="5">
         <v>330794</v>
@@ -3318,14 +3318,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>58915</v>
+        <v>60463</v>
       </c>
       <c r="AY19" s="5">
-        <v>327040</v>
+        <v>328588</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98865154748876949</v>
+        <v>0.99333119705919692</v>
       </c>
       <c r="BA19" s="5">
         <v>346688</v>
@@ -3335,14 +3335,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>196931</v>
+        <v>199290</v>
       </c>
       <c r="BD19" s="5">
-        <v>335890</v>
+        <v>338249</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96885383976370687</v>
+        <v>0.97565822872438623</v>
       </c>
       <c r="BF19" s="5">
         <v>595475</v>
@@ -3352,14 +3352,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>366499</v>
+        <v>376194</v>
       </c>
       <c r="BI19" s="5">
-        <v>566069</v>
+        <v>575764</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.95061757420546622</v>
+        <v>0.9668986943196608</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3377,14 +3377,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3891</v>
+        <v>3892</v>
       </c>
       <c r="F20" s="5">
-        <v>6478</v>
+        <v>6479</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>0.99097445311304877</v>
+        <v>0.99112742848401403</v>
       </c>
       <c r="H20" s="5">
         <v>6601</v>
@@ -3394,14 +3394,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3840</v>
+        <v>3842</v>
       </c>
       <c r="K20" s="5">
-        <v>6510</v>
+        <v>6512</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>0.98621420996818665</v>
+        <v>0.98651719436449026</v>
       </c>
       <c r="M20" s="5">
         <v>10050</v>
@@ -3411,14 +3411,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5564</v>
+        <v>5572</v>
       </c>
       <c r="P20" s="5">
-        <v>10032</v>
+        <v>10040</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>0.99820895522388065</v>
+        <v>0.99900497512437814</v>
       </c>
       <c r="R20" s="5">
         <v>6485</v>
@@ -3428,14 +3428,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3624</v>
+        <v>3630</v>
       </c>
       <c r="U20" s="5">
-        <v>6428</v>
+        <v>6434</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>0.99121048573631454</v>
+        <v>0.99213569776407096</v>
       </c>
       <c r="W20" s="5">
         <v>6573</v>
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3433</v>
+        <v>3441</v>
       </c>
       <c r="Z20" s="5">
-        <v>6441</v>
+        <v>6449</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>0.97991784573254226</v>
+        <v>0.98113494599117601</v>
       </c>
       <c r="AB20" s="5">
         <v>10123</v>
@@ -3462,14 +3462,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>6145</v>
+        <v>6159</v>
       </c>
       <c r="AE20" s="5">
-        <v>10041</v>
+        <v>10055</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>0.99189963449570284</v>
+        <v>0.9932826237281438</v>
       </c>
       <c r="AG20" s="5">
         <v>6547</v>
@@ -3479,14 +3479,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3434</v>
+        <v>3448</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6452</v>
+        <v>6466</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>0.98548953719260735</v>
+        <v>0.98762792118527565</v>
       </c>
       <c r="AL20" s="5">
         <v>6649</v>
@@ -3496,14 +3496,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3441</v>
+        <v>3461</v>
       </c>
       <c r="AO20" s="5">
-        <v>6532</v>
+        <v>6552</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.98240336892765834</v>
+        <v>0.98541134005113551</v>
       </c>
       <c r="AQ20" s="5">
         <v>10228</v>
@@ -3513,14 +3513,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>6094</v>
+        <v>6141</v>
       </c>
       <c r="AT20" s="5">
-        <v>10090</v>
+        <v>10137</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>0.98650762612436449</v>
+        <v>0.99110285490809547</v>
       </c>
       <c r="AV20" s="5">
         <v>6568</v>
@@ -3530,14 +3530,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>1356</v>
+        <v>1394</v>
       </c>
       <c r="AY20" s="5">
-        <v>6440</v>
+        <v>6478</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.98051157125456756</v>
+        <v>0.98629719853836784</v>
       </c>
       <c r="BA20" s="5">
         <v>6793</v>
@@ -3547,14 +3547,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3281</v>
+        <v>3330</v>
       </c>
       <c r="BD20" s="5">
-        <v>6479</v>
+        <v>6528</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.9537759458265862</v>
+        <v>0.96098925364345655</v>
       </c>
       <c r="BF20" s="5">
         <v>10395</v>
@@ -3564,14 +3564,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>5739</v>
+        <v>5894</v>
       </c>
       <c r="BI20" s="5">
-        <v>9947</v>
+        <v>10102</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>0.95690235690235692</v>
+        <v>0.9718133718133718</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>9086</v>
+        <v>9108</v>
       </c>
       <c r="F21" s="5">
-        <v>12056</v>
+        <v>12078</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0038301415487094</v>
+        <v>1.0056619483763531</v>
       </c>
       <c r="H21" s="5">
         <v>12254</v>
@@ -3606,14 +3606,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>9054</v>
+        <v>9076</v>
       </c>
       <c r="K21" s="5">
-        <v>12278</v>
+        <v>12300</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>1.0019585441488494</v>
+        <v>1.0037538762852947</v>
       </c>
       <c r="M21" s="5">
         <v>16207</v>
@@ -3623,14 +3623,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>12134</v>
+        <v>12169</v>
       </c>
       <c r="P21" s="5">
-        <v>16401</v>
+        <v>16436</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0119701363608318</v>
+        <v>1.0141296970444869</v>
       </c>
       <c r="R21" s="5">
         <v>12383</v>
@@ -3640,14 +3640,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>9143</v>
+        <v>9170</v>
       </c>
       <c r="U21" s="5">
-        <v>12562</v>
+        <v>12589</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0144553016231932</v>
+        <v>1.0166357102479204</v>
       </c>
       <c r="W21" s="5">
         <v>12782</v>
@@ -3657,14 +3657,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>9165</v>
+        <v>9199</v>
       </c>
       <c r="Z21" s="5">
-        <v>12766</v>
+        <v>12800</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>0.99874823971209514</v>
+        <v>1.0014082303238929</v>
       </c>
       <c r="AB21" s="5">
         <v>16816</v>
@@ -3674,14 +3674,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>12640</v>
+        <v>12692</v>
       </c>
       <c r="AE21" s="5">
-        <v>16849</v>
+        <v>16901</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0019624167459562</v>
+        <v>1.0050547098001903</v>
       </c>
       <c r="AG21" s="5">
         <v>12696</v>
@@ -3691,14 +3691,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>9293</v>
+        <v>9340</v>
       </c>
       <c r="AJ21" s="5">
-        <v>12735</v>
+        <v>12782</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0030718336483933</v>
+        <v>1.0067737870195337</v>
       </c>
       <c r="AL21" s="5">
         <v>13072</v>
@@ -3708,14 +3708,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>9313</v>
+        <v>9378</v>
       </c>
       <c r="AO21" s="5">
-        <v>12964</v>
+        <v>13029</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>0.99173806609547122</v>
+        <v>0.99671052631578949</v>
       </c>
       <c r="AQ21" s="5">
         <v>17310</v>
@@ -3725,14 +3725,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>12711</v>
+        <v>12832</v>
       </c>
       <c r="AT21" s="5">
-        <v>17190</v>
+        <v>17311</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>0.99306759098786823</v>
+        <v>1.000057770075101</v>
       </c>
       <c r="AV21" s="5">
         <v>13094</v>
@@ -3742,14 +3742,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>3392</v>
+        <v>3526</v>
       </c>
       <c r="AY21" s="5">
-        <v>12881</v>
+        <v>13015</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>0.983733007484344</v>
+        <v>0.99396670230639983</v>
       </c>
       <c r="BA21" s="5">
         <v>13518</v>
@@ -3759,14 +3759,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>8835</v>
+        <v>9017</v>
       </c>
       <c r="BD21" s="5">
-        <v>12983</v>
+        <v>13165</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>0.9604231395176801</v>
+        <v>0.97388666962568426</v>
       </c>
       <c r="BF21" s="5">
         <v>17905</v>
@@ -3776,14 +3776,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>11758</v>
+        <v>12274</v>
       </c>
       <c r="BI21" s="5">
-        <v>16366</v>
+        <v>16882</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>0.91404635576654569</v>
+        <v>0.94286512147444845</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3801,14 +3801,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4868</v>
+        <v>4878</v>
       </c>
       <c r="F22" s="5">
-        <v>6981</v>
+        <v>6991</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.99785591766723847</v>
+        <v>0.99928530588907949</v>
       </c>
       <c r="H22" s="5">
         <v>7077</v>
@@ -3818,14 +3818,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4818</v>
+        <v>4832</v>
       </c>
       <c r="K22" s="5">
-        <v>7038</v>
+        <v>7052</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>0.9944891903348877</v>
+        <v>0.99646742970185109</v>
       </c>
       <c r="M22" s="5">
         <v>8504</v>
@@ -3835,14 +3835,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5751</v>
+        <v>5771</v>
       </c>
       <c r="P22" s="5">
-        <v>8527</v>
+        <v>8547</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0027046095954846</v>
+        <v>1.0050564440263405</v>
       </c>
       <c r="R22" s="5">
         <v>7111</v>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4635</v>
+        <v>4654</v>
       </c>
       <c r="U22" s="5">
-        <v>7075</v>
+        <v>7094</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>0.9949374208972015</v>
+        <v>0.99760933764590076</v>
       </c>
       <c r="W22" s="5">
         <v>7191</v>
@@ -3869,14 +3869,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4631</v>
+        <v>4651</v>
       </c>
       <c r="Z22" s="5">
-        <v>7140</v>
+        <v>7160</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>0.99290780141843971</v>
+        <v>0.99568905576414968</v>
       </c>
       <c r="AB22" s="5">
         <v>8707</v>
@@ -3886,14 +3886,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5889</v>
+        <v>5916</v>
       </c>
       <c r="AE22" s="5">
-        <v>8665</v>
+        <v>8692</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>0.99517629493510973</v>
+        <v>0.99827724819111063</v>
       </c>
       <c r="AG22" s="5">
         <v>7162</v>
@@ -3903,14 +3903,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4682</v>
+        <v>4706</v>
       </c>
       <c r="AJ22" s="5">
-        <v>7135</v>
+        <v>7159</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>0.99623010332309414</v>
+        <v>0.99958112259145493</v>
       </c>
       <c r="AL22" s="5">
         <v>7226</v>
@@ -3920,14 +3920,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4673</v>
+        <v>4699</v>
       </c>
       <c r="AO22" s="5">
-        <v>7187</v>
+        <v>7213</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>0.99460282313866588</v>
+        <v>0.99820094104622192</v>
       </c>
       <c r="AQ22" s="5">
         <v>8754</v>
@@ -3937,14 +3937,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>6102</v>
+        <v>6143</v>
       </c>
       <c r="AT22" s="5">
-        <v>8714</v>
+        <v>8755</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>0.99543066026959104</v>
+        <v>1.0001142334932602</v>
       </c>
       <c r="AV22" s="5">
         <v>7182</v>
@@ -3954,14 +3954,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>1715</v>
+        <v>1768</v>
       </c>
       <c r="AY22" s="5">
-        <v>7101</v>
+        <v>7154</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.98872180451127822</v>
+        <v>0.99610136452241715</v>
       </c>
       <c r="BA22" s="5">
         <v>7296</v>
@@ -3971,14 +3971,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4550</v>
+        <v>4627</v>
       </c>
       <c r="BD22" s="5">
-        <v>7118</v>
+        <v>7195</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.97560307017543857</v>
+        <v>0.98615679824561409</v>
       </c>
       <c r="BF22" s="5">
         <v>8939</v>
@@ -3988,14 +3988,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5620</v>
+        <v>5803</v>
       </c>
       <c r="BI22" s="5">
-        <v>8442</v>
+        <v>8625</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>0.94440093970242756</v>
+        <v>0.96487302830294219</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4013,14 +4013,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>6671</v>
+        <v>6682</v>
       </c>
       <c r="F23" s="5">
-        <v>9199</v>
+        <v>9210</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.97788880620814289</v>
+        <v>0.97905814818751991</v>
       </c>
       <c r="H23" s="5">
         <v>9786</v>
@@ -4030,14 +4030,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7342</v>
+        <v>7355</v>
       </c>
       <c r="K23" s="5">
-        <v>9339</v>
+        <v>9352</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.95432250153280196</v>
+        <v>0.95565092989985689</v>
       </c>
       <c r="M23" s="5">
         <v>12056</v>
@@ -4047,14 +4047,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8598</v>
+        <v>8619</v>
       </c>
       <c r="P23" s="5">
-        <v>11883</v>
+        <v>11904</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98565029860650299</v>
+        <v>0.98739216987392164</v>
       </c>
       <c r="R23" s="5">
         <v>9480</v>
@@ -4064,14 +4064,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6620</v>
+        <v>6642</v>
       </c>
       <c r="U23" s="5">
-        <v>9394</v>
+        <v>9416</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.99092827004219408</v>
+        <v>0.99324894514767936</v>
       </c>
       <c r="W23" s="5">
         <v>9764</v>
@@ -4081,14 +4081,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6638</v>
+        <v>6664</v>
       </c>
       <c r="Z23" s="5">
-        <v>9466</v>
+        <v>9492</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.9694797214256452</v>
+        <v>0.97214256452273662</v>
       </c>
       <c r="AB23" s="5">
         <v>12327</v>
@@ -4098,14 +4098,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>8878</v>
+        <v>8914</v>
       </c>
       <c r="AE23" s="5">
-        <v>12096</v>
+        <v>12132</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98126064735945484</v>
+        <v>0.98418106595278654</v>
       </c>
       <c r="AG23" s="5">
         <v>9618</v>
@@ -4115,14 +4115,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6654</v>
+        <v>6690</v>
       </c>
       <c r="AJ23" s="5">
-        <v>9383</v>
+        <v>9419</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.97556664587232278</v>
+        <v>0.97930962778124353</v>
       </c>
       <c r="AL23" s="5">
         <v>9741</v>
@@ -4132,14 +4132,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>6872</v>
+        <v>6920</v>
       </c>
       <c r="AO23" s="5">
-        <v>9514</v>
+        <v>9562</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.97669643773739867</v>
+        <v>0.98162406323786056</v>
       </c>
       <c r="AQ23" s="5">
         <v>12556</v>
@@ -4149,14 +4149,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>8906</v>
+        <v>8992</v>
       </c>
       <c r="AT23" s="5">
-        <v>12233</v>
+        <v>12319</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>0.97427524689391531</v>
+        <v>0.98112456196240838</v>
       </c>
       <c r="AV23" s="5">
         <v>9718</v>
@@ -4166,14 +4166,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>2577</v>
+        <v>2687</v>
       </c>
       <c r="AY23" s="5">
-        <v>9441</v>
+        <v>9551</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>0.97149619263222886</v>
+        <v>0.9828153941140152</v>
       </c>
       <c r="BA23" s="5">
         <v>10107</v>
@@ -4183,14 +4183,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6644</v>
+        <v>6788</v>
       </c>
       <c r="BD23" s="5">
-        <v>9576</v>
+        <v>9720</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.94746215494211927</v>
+        <v>0.96170970614425644</v>
       </c>
       <c r="BF23" s="5">
         <v>13018</v>
@@ -4200,14 +4200,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>8640</v>
+        <v>8978</v>
       </c>
       <c r="BI23" s="5">
-        <v>11960</v>
+        <v>12298</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.91872791519434627</v>
+        <v>0.94469196497157781</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4225,14 +4225,14 @@
       </c>
       <c r="E24" s="3">
         <f t="shared" si="0"/>
-        <v>5536</v>
+        <v>5542</v>
       </c>
       <c r="F24" s="5">
-        <v>6889</v>
+        <v>6895</v>
       </c>
       <c r="G24" s="4">
         <f t="shared" si="1"/>
-        <v>0.99236531259003169</v>
+        <v>0.99322961682512245</v>
       </c>
       <c r="H24" s="5">
         <v>7059</v>
@@ -4242,14 +4242,14 @@
       </c>
       <c r="J24" s="3">
         <f t="shared" si="2"/>
-        <v>5540</v>
+        <v>5547</v>
       </c>
       <c r="K24" s="5">
-        <v>6950</v>
+        <v>6957</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="3"/>
-        <v>0.98455871936534922</v>
+        <v>0.98555036124096895</v>
       </c>
       <c r="M24" s="5">
         <v>8056</v>
@@ -4259,14 +4259,14 @@
       </c>
       <c r="O24" s="3">
         <f t="shared" si="4"/>
-        <v>5527</v>
+        <v>5538</v>
       </c>
       <c r="P24" s="5">
-        <v>7942</v>
+        <v>7953</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="5"/>
-        <v>0.98584905660377353</v>
+        <v>0.98721449851042697</v>
       </c>
       <c r="R24" s="5">
         <v>7134</v>
@@ -4276,14 +4276,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="6"/>
-        <v>4967</v>
+        <v>4976</v>
       </c>
       <c r="U24" s="5">
-        <v>7023</v>
+        <v>7032</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="7"/>
-        <v>0.98444070647603032</v>
+        <v>0.98570227081581163</v>
       </c>
       <c r="W24" s="5">
         <v>7208</v>
@@ -4293,14 +4293,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="8"/>
-        <v>4859</v>
+        <v>4870</v>
       </c>
       <c r="Z24" s="5">
-        <v>7061</v>
+        <v>7072</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="9"/>
-        <v>0.97960599334073251</v>
+        <v>0.98113207547169812</v>
       </c>
       <c r="AB24" s="5">
         <v>8228</v>
@@ -4310,14 +4310,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="10"/>
-        <v>5774</v>
+        <v>5788</v>
       </c>
       <c r="AE24" s="5">
-        <v>8081</v>
+        <v>8095</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="11"/>
-        <v>0.98213417598444341</v>
+        <v>0.98383568303354396</v>
       </c>
       <c r="AG24" s="5">
         <v>7344</v>
@@ -4327,14 +4327,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4970</v>
+        <v>4981</v>
       </c>
       <c r="AJ24" s="5">
-        <v>7175</v>
+        <v>7186</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.97698801742919394</v>
+        <v>0.97848583877995643</v>
       </c>
       <c r="AL24" s="5">
         <v>7506</v>
@@ -4344,14 +4344,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4915</v>
+        <v>4934</v>
       </c>
       <c r="AO24" s="5">
-        <v>7271</v>
+        <v>7290</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.96869171329602988</v>
+        <v>0.97122302158273377</v>
       </c>
       <c r="AQ24" s="5">
         <v>8509</v>
@@ -4361,14 +4361,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5933</v>
+        <v>5965</v>
       </c>
       <c r="AT24" s="5">
-        <v>8259</v>
+        <v>8291</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.97061934422376306</v>
+        <v>0.97438006816312139</v>
       </c>
       <c r="AV24" s="5">
         <v>7570</v>
@@ -4378,14 +4378,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>1249</v>
+        <v>1287</v>
       </c>
       <c r="AY24" s="5">
-        <v>7292</v>
+        <v>7330</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.96327608982826951</v>
+        <v>0.96829590488771466</v>
       </c>
       <c r="BA24" s="5">
         <v>7648</v>
@@ -4395,14 +4395,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>4981</v>
+        <v>5044</v>
       </c>
       <c r="BD24" s="5">
-        <v>7404</v>
+        <v>7467</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.96809623430962344</v>
+        <v>0.97633368200836823</v>
       </c>
       <c r="BF24" s="5">
         <v>8767</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>5917</v>
+        <v>6034</v>
       </c>
       <c r="BI24" s="5">
-        <v>8371</v>
+        <v>8488</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.95483061480552067</v>
+        <v>0.96817611497661682</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4437,14 +4437,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>12823</v>
+        <v>12834</v>
       </c>
       <c r="F25" s="5">
-        <v>21341</v>
+        <v>21352</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.99385274530806134</v>
+        <v>0.99436501653238951</v>
       </c>
       <c r="H25" s="5">
         <v>21813</v>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>12788</v>
+        <v>12800</v>
       </c>
       <c r="K25" s="5">
-        <v>21532</v>
+        <v>21544</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.98711777380461196</v>
+        <v>0.98766790446064279</v>
       </c>
       <c r="M25" s="5">
         <v>29215</v>
@@ -4471,14 +4471,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>17597</v>
+        <v>17622</v>
       </c>
       <c r="P25" s="5">
-        <v>29045</v>
+        <v>29070</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>0.99418107136744827</v>
+        <v>0.99503679616635288</v>
       </c>
       <c r="R25" s="5">
         <v>21767</v>
@@ -4488,14 +4488,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>12399</v>
+        <v>12416</v>
       </c>
       <c r="U25" s="5">
-        <v>21613</v>
+        <v>21630</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>0.99292507006018282</v>
+        <v>0.99370606881977308</v>
       </c>
       <c r="W25" s="5">
         <v>22114</v>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>12213</v>
+        <v>12231</v>
       </c>
       <c r="Z25" s="5">
-        <v>21757</v>
+        <v>21775</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.98385638057339242</v>
+        <v>0.98467034457809532</v>
       </c>
       <c r="AB25" s="5">
         <v>29630</v>
@@ -4522,14 +4522,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>18416</v>
+        <v>18448</v>
       </c>
       <c r="AE25" s="5">
-        <v>29399</v>
+        <v>29431</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>0.99220384745190682</v>
+        <v>0.99328383395207565</v>
       </c>
       <c r="AG25" s="5">
         <v>22174</v>
@@ -4539,14 +4539,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>12774</v>
+        <v>12800</v>
       </c>
       <c r="AJ25" s="5">
-        <v>21886</v>
+        <v>21912</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>0.98701181563993867</v>
+        <v>0.98818436006133314</v>
       </c>
       <c r="AL25" s="5">
         <v>22503</v>
@@ -4556,14 +4556,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>12792</v>
+        <v>12824</v>
       </c>
       <c r="AO25" s="5">
-        <v>22260</v>
+        <v>22292</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.98920143980802555</v>
+        <v>0.99062347242589877</v>
       </c>
       <c r="AQ25" s="5">
         <v>30294</v>
@@ -4573,14 +4573,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>18342</v>
+        <v>18412</v>
       </c>
       <c r="AT25" s="5">
-        <v>30008</v>
+        <v>30078</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>0.99055918663761799</v>
+        <v>0.99286987522281644</v>
       </c>
       <c r="AV25" s="5">
         <v>22740</v>
@@ -4590,14 +4590,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>4288</v>
+        <v>4356</v>
       </c>
       <c r="AY25" s="5">
-        <v>22551</v>
+        <v>22619</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>0.99168865435356202</v>
+        <v>0.99467897977132802</v>
       </c>
       <c r="BA25" s="5">
         <v>23197</v>
@@ -4607,14 +4607,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>12856</v>
+        <v>12953</v>
       </c>
       <c r="BD25" s="5">
-        <v>22754</v>
+        <v>22851</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>0.98090270293572446</v>
+        <v>0.98508427813941457</v>
       </c>
       <c r="BF25" s="5">
         <v>31043</v>
@@ -4624,14 +4624,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>17908</v>
+        <v>18251</v>
       </c>
       <c r="BI25" s="5">
-        <v>30027</v>
+        <v>30370</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>0.96727120445833203</v>
+        <v>0.97832039429178885</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4649,14 +4649,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>10238</v>
+        <v>10250</v>
       </c>
       <c r="F26" s="5">
-        <v>14425</v>
+        <v>14437</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.99127267729521717</v>
+        <v>0.99209730621220449</v>
       </c>
       <c r="H26" s="5">
         <v>14990</v>
@@ -4666,14 +4666,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>10142</v>
+        <v>10156</v>
       </c>
       <c r="K26" s="5">
-        <v>14766</v>
+        <v>14780</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.98505670446964644</v>
+        <v>0.98599066044029349</v>
       </c>
       <c r="M26" s="5">
         <v>28508</v>
@@ -4683,14 +4683,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>20151</v>
+        <v>20185</v>
       </c>
       <c r="P26" s="5">
-        <v>28445</v>
+        <v>28479</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>0.99779009400869934</v>
+        <v>0.99898274168654411</v>
       </c>
       <c r="R26" s="5">
         <v>14719</v>
@@ -4700,14 +4700,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9828</v>
+        <v>9847</v>
       </c>
       <c r="U26" s="5">
-        <v>14583</v>
+        <v>14602</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>0.99076024186425704</v>
+        <v>0.99205109042733886</v>
       </c>
       <c r="W26" s="5">
         <v>15123</v>
@@ -4717,14 +4717,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9834</v>
+        <v>9857</v>
       </c>
       <c r="Z26" s="5">
-        <v>14802</v>
+        <v>14825</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.97877405276730811</v>
+        <v>0.98029491503008659</v>
       </c>
       <c r="AB26" s="5">
         <v>29054</v>
@@ -4734,14 +4734,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>20699</v>
+        <v>20751</v>
       </c>
       <c r="AE26" s="5">
-        <v>28742</v>
+        <v>28794</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.9892613753700007</v>
+        <v>0.99105114614166723</v>
       </c>
       <c r="AG26" s="5">
         <v>14835</v>
@@ -4751,14 +4751,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9651</v>
+        <v>9683</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14612</v>
+        <v>14644</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>0.98496798112571626</v>
+        <v>0.98712504213009777</v>
       </c>
       <c r="AL26" s="5">
         <v>15316</v>
@@ -4768,14 +4768,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="14"/>
-        <v>9408</v>
+        <v>9446</v>
       </c>
       <c r="AO26" s="5">
-        <v>14884</v>
+        <v>14922</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.97179420214155132</v>
+        <v>0.97427526769391481</v>
       </c>
       <c r="AQ26" s="5">
         <v>29312</v>
@@ -4785,14 +4785,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="16"/>
-        <v>20908</v>
+        <v>21039</v>
       </c>
       <c r="AT26" s="5">
-        <v>28964</v>
+        <v>29095</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.98812772925764192</v>
+        <v>0.99259688864628826</v>
       </c>
       <c r="AV26" s="5">
         <v>15164</v>
@@ -4802,14 +4802,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="18"/>
-        <v>2744</v>
+        <v>2829</v>
       </c>
       <c r="AY26" s="5">
-        <v>14740</v>
+        <v>14825</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.97203903983117912</v>
+        <v>0.97764442099709836</v>
       </c>
       <c r="BA26" s="5">
         <v>15499</v>
@@ -4819,14 +4819,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="20"/>
-        <v>10052</v>
+        <v>10163</v>
       </c>
       <c r="BD26" s="5">
-        <v>14890</v>
+        <v>15001</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.96070714239628363</v>
+        <v>0.96786889476740434</v>
       </c>
       <c r="BF26" s="5">
         <v>29635</v>
@@ -4836,14 +4836,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="22"/>
-        <v>20247</v>
+        <v>20687</v>
       </c>
       <c r="BI26" s="5">
-        <v>28405</v>
+        <v>28845</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.95849502277712162</v>
+        <v>0.97334233170237894</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>80258</v>
+        <v>80340</v>
       </c>
       <c r="F27" s="5">
-        <v>129615</v>
+        <v>129697</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.98846165578671219</v>
+        <v>0.98908699896284547</v>
       </c>
       <c r="H27" s="5">
         <v>134384</v>
@@ -4878,14 +4878,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>79493</v>
+        <v>79596</v>
       </c>
       <c r="K27" s="5">
-        <v>130440</v>
+        <v>130543</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.9706512680080962</v>
+        <v>0.97141772830098816</v>
       </c>
       <c r="M27" s="5">
         <v>190911</v>
@@ -4895,14 +4895,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>121747</v>
+        <v>121927</v>
       </c>
       <c r="P27" s="5">
-        <v>191168</v>
+        <v>191348</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>1.0013461770144203</v>
+        <v>1.0022890247288003</v>
       </c>
       <c r="R27" s="5">
         <v>131264</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>76336</v>
+        <v>76453</v>
       </c>
       <c r="U27" s="5">
-        <v>130289</v>
+        <v>130406</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99257222086786934</v>
+        <v>0.99346355436372502</v>
       </c>
       <c r="W27" s="5">
         <v>134144</v>
@@ -4929,14 +4929,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>76205</v>
+        <v>76354</v>
       </c>
       <c r="Z27" s="5">
-        <v>131675</v>
+        <v>131824</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.98159440601145043</v>
+        <v>0.98270515267175573</v>
       </c>
       <c r="AB27" s="5">
         <v>194609</v>
@@ -4946,14 +4946,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>125292</v>
+        <v>125607</v>
       </c>
       <c r="AE27" s="5">
-        <v>193256</v>
+        <v>193571</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99304759800420328</v>
+        <v>0.99466622818060835</v>
       </c>
       <c r="AG27" s="5">
         <v>134089</v>
@@ -4963,14 +4963,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>78964</v>
+        <v>79198</v>
       </c>
       <c r="AJ27" s="5">
-        <v>131979</v>
+        <v>132213</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.98426418274429672</v>
+        <v>0.98600929233568746</v>
       </c>
       <c r="AL27" s="5">
         <v>137688</v>
@@ -4980,14 +4980,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="14"/>
-        <v>79740</v>
+        <v>80109</v>
       </c>
       <c r="AO27" s="5">
-        <v>136129</v>
+        <v>136498</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="15"/>
-        <v>0.98867729940154547</v>
+        <v>0.99135727151240483</v>
       </c>
       <c r="AQ27" s="5">
         <v>200322</v>
@@ -4997,14 +4997,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="16"/>
-        <v>127030</v>
+        <v>127904</v>
       </c>
       <c r="AT27" s="5">
-        <v>198943</v>
+        <v>199817</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="17"/>
-        <v>0.99311608310619903</v>
+        <v>0.99747905871546805</v>
       </c>
       <c r="AV27" s="5">
         <v>139481</v>
@@ -5014,14 +5014,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="18"/>
-        <v>29730</v>
+        <v>30596</v>
       </c>
       <c r="AY27" s="5">
-        <v>136972</v>
+        <v>137838</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="19"/>
-        <v>0.98201188692366703</v>
+        <v>0.98822061786193105</v>
       </c>
       <c r="BA27" s="5">
         <v>143305</v>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="20"/>
-        <v>79563</v>
+        <v>80754</v>
       </c>
       <c r="BD27" s="5">
-        <v>138544</v>
+        <v>139735</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="21"/>
-        <v>0.96677715362339067</v>
+        <v>0.97508809881022995</v>
       </c>
       <c r="BF27" s="5">
         <v>208143</v>
@@ -5048,14 +5048,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>124845</v>
+        <v>128661</v>
       </c>
       <c r="BI27" s="5">
-        <v>196869</v>
+        <v>200685</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="23"/>
-        <v>0.9458353151439155</v>
+        <v>0.96416886467476681</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="E28" s="3">
         <f t="shared" si="0"/>
-        <v>189312</v>
+        <v>189412</v>
       </c>
       <c r="F28" s="5">
-        <v>434677</v>
+        <v>434777</v>
       </c>
       <c r="G28" s="4">
         <f t="shared" si="1"/>
-        <v>0.99351790689648078</v>
+        <v>0.99374647153341733</v>
       </c>
       <c r="H28" s="5">
         <v>447363</v>
@@ -5090,14 +5090,14 @@
       </c>
       <c r="J28" s="3">
         <f t="shared" si="2"/>
-        <v>191646</v>
+        <v>191772</v>
       </c>
       <c r="K28" s="5">
-        <v>442338</v>
+        <v>442464</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="3"/>
-        <v>0.98876751094748561</v>
+        <v>0.98904916141925014</v>
       </c>
       <c r="M28" s="5">
         <v>722935</v>
@@ -5107,14 +5107,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>334256</v>
+        <v>334537</v>
       </c>
       <c r="P28" s="5">
-        <v>718571</v>
+        <v>718852</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99396349602661371</v>
+        <v>0.99435218933929048</v>
       </c>
       <c r="R28" s="5">
         <v>448339</v>
@@ -5124,14 +5124,14 @@
       </c>
       <c r="T28" s="3">
         <f t="shared" si="6"/>
-        <v>185857</v>
+        <v>186036</v>
       </c>
       <c r="U28" s="5">
-        <v>445375</v>
+        <v>445554</v>
       </c>
       <c r="V28" s="4">
         <f t="shared" si="7"/>
-        <v>0.99338893114362126</v>
+        <v>0.99378818260289647</v>
       </c>
       <c r="W28" s="5">
         <v>458076</v>
@@ -5141,14 +5141,14 @@
       </c>
       <c r="Y28" s="3">
         <f t="shared" si="8"/>
-        <v>187443</v>
+        <v>187658</v>
       </c>
       <c r="Z28" s="5">
-        <v>450672</v>
+        <v>450887</v>
       </c>
       <c r="AA28" s="4">
         <f t="shared" si="9"/>
-        <v>0.98383674324784531</v>
+        <v>0.9843060976781145</v>
       </c>
       <c r="AB28" s="5">
         <v>737235</v>
@@ -5158,14 +5158,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>353633</v>
+        <v>354168</v>
       </c>
       <c r="AE28" s="5">
-        <v>730545</v>
+        <v>731080</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.9909255529105373</v>
+        <v>0.99165123739377536</v>
       </c>
       <c r="AG28" s="5">
         <v>456666</v>
@@ -5175,14 +5175,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>192885</v>
+        <v>193288</v>
       </c>
       <c r="AJ28" s="5">
-        <v>451266</v>
+        <v>451669</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.98817516521921933</v>
+        <v>0.9890576482593405</v>
       </c>
       <c r="AL28" s="5">
         <v>468801</v>
@@ -5192,14 +5192,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="14"/>
-        <v>193497</v>
+        <v>194147</v>
       </c>
       <c r="AO28" s="5">
-        <v>464240</v>
+        <v>464890</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" si="15"/>
-        <v>0.99027092519000603</v>
+        <v>0.99165744100375208</v>
       </c>
       <c r="AQ28" s="5">
         <v>756132</v>
@@ -5209,14 +5209,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="16"/>
-        <v>352464</v>
+        <v>354111</v>
       </c>
       <c r="AT28" s="5">
-        <v>751477</v>
+        <v>753124</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="17"/>
-        <v>0.99384366750778963</v>
+        <v>0.99602185861727843</v>
       </c>
       <c r="AV28" s="5">
         <v>474991</v>
@@ -5226,14 +5226,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="18"/>
-        <v>64336</v>
+        <v>65999</v>
       </c>
       <c r="AY28" s="5">
-        <v>469371</v>
+        <v>471034</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" si="19"/>
-        <v>0.98816819687109858</v>
+        <v>0.99166931583966855</v>
       </c>
       <c r="BA28" s="5">
         <v>487540</v>
@@ -5243,14 +5243,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="20"/>
-        <v>195702</v>
+        <v>198092</v>
       </c>
       <c r="BD28" s="5">
-        <v>476276</v>
+        <v>478666</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" si="21"/>
-        <v>0.97689625466628383</v>
+        <v>0.9817984165401813</v>
       </c>
       <c r="BF28" s="5">
         <v>779284</v>
@@ -5260,14 +5260,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>347227</v>
+        <v>355338</v>
       </c>
       <c r="BI28" s="5">
-        <v>754765</v>
+        <v>762876</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.96853650273841119</v>
+        <v>0.97894477494725929</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5285,14 +5285,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>78351</v>
+        <v>78379</v>
       </c>
       <c r="F29" s="5">
-        <v>142684</v>
+        <v>142712</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.9925705381490344</v>
+        <v>0.99276531804774892</v>
       </c>
       <c r="H29" s="5">
         <v>146310</v>
@@ -5302,14 +5302,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>77811</v>
+        <v>77843</v>
       </c>
       <c r="K29" s="5">
-        <v>144184</v>
+        <v>144216</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98546920921331416</v>
+        <v>0.98568792290342422</v>
       </c>
       <c r="M29" s="5">
         <v>194093</v>
@@ -5319,14 +5319,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>106402</v>
+        <v>106460</v>
       </c>
       <c r="P29" s="5">
-        <v>191829</v>
+        <v>191887</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98833548865749921</v>
+        <v>0.98863431447811101</v>
       </c>
       <c r="R29" s="5">
         <v>146918</v>
@@ -5336,14 +5336,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>77399</v>
+        <v>77458</v>
       </c>
       <c r="U29" s="5">
-        <v>145143</v>
+        <v>145202</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.98791843068922802</v>
+        <v>0.98832001524660018</v>
       </c>
       <c r="W29" s="5">
         <v>149105</v>
@@ -5353,14 +5353,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>75521</v>
+        <v>75598</v>
       </c>
       <c r="Z29" s="5">
-        <v>146495</v>
+        <v>146572</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98249555682237355</v>
+        <v>0.98301197142952956</v>
       </c>
       <c r="AB29" s="5">
         <v>197403</v>
@@ -5370,14 +5370,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>109869</v>
+        <v>110014</v>
       </c>
       <c r="AE29" s="5">
-        <v>194735</v>
+        <v>194880</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.98648450124871456</v>
+        <v>0.98721903922432785</v>
       </c>
       <c r="AG29" s="5">
         <v>149309</v>
@@ -5387,14 +5387,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>78449</v>
+        <v>78581</v>
       </c>
       <c r="AJ29" s="5">
-        <v>147233</v>
+        <v>147365</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.98609594867020745</v>
+        <v>0.98698002129811335</v>
       </c>
       <c r="AL29" s="5">
         <v>152026</v>
@@ -5404,14 +5404,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="14"/>
-        <v>79415</v>
+        <v>79643</v>
       </c>
       <c r="AO29" s="5">
-        <v>151894</v>
+        <v>152122</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="15"/>
-        <v>0.99913172746766998</v>
+        <v>1.0006314709326036</v>
       </c>
       <c r="AQ29" s="5">
         <v>203571</v>
@@ -5421,14 +5421,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="16"/>
-        <v>113026</v>
+        <v>113504</v>
       </c>
       <c r="AT29" s="5">
-        <v>202663</v>
+        <v>203141</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="17"/>
-        <v>0.99553963973257487</v>
+        <v>0.99788771485132954</v>
       </c>
       <c r="AV29" s="5">
         <v>155780</v>
@@ -5438,14 +5438,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="18"/>
-        <v>25325</v>
+        <v>25898</v>
       </c>
       <c r="AY29" s="5">
-        <v>154674</v>
+        <v>155247</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="19"/>
-        <v>0.99290024393375276</v>
+        <v>0.9965785081525228</v>
       </c>
       <c r="BA29" s="5">
         <v>159604</v>
@@ -5455,14 +5455,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="20"/>
-        <v>81300</v>
+        <v>82166</v>
       </c>
       <c r="BD29" s="5">
-        <v>156859</v>
+        <v>157725</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="21"/>
-        <v>0.98280118292774621</v>
+        <v>0.98822711210245362</v>
       </c>
       <c r="BF29" s="5">
         <v>211893</v>
@@ -5472,14 +5472,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>110974</v>
+        <v>113280</v>
       </c>
       <c r="BI29" s="5">
-        <v>205181</v>
+        <v>207487</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.96832363504221475</v>
+        <v>0.97920648629260998</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="0"/>
-        <v>109307</v>
+        <v>109351</v>
       </c>
       <c r="F30" s="5">
-        <v>185314</v>
+        <v>185358</v>
       </c>
       <c r="G30" s="4">
         <f t="shared" si="1"/>
-        <v>0.99485698333619654</v>
+        <v>0.99509319704518129</v>
       </c>
       <c r="H30" s="5">
         <v>190966</v>
@@ -5514,14 +5514,14 @@
       </c>
       <c r="J30" s="3">
         <f t="shared" si="2"/>
-        <v>109576</v>
+        <v>109623</v>
       </c>
       <c r="K30" s="5">
-        <v>188295</v>
+        <v>188342</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="3"/>
-        <v>0.98601321701245248</v>
+        <v>0.98625933412230449</v>
       </c>
       <c r="M30" s="5">
         <v>320227</v>
@@ -5531,14 +5531,14 @@
       </c>
       <c r="O30" s="3">
         <f t="shared" si="4"/>
-        <v>196622</v>
+        <v>196732</v>
       </c>
       <c r="P30" s="5">
-        <v>318356</v>
+        <v>318466</v>
       </c>
       <c r="Q30" s="4">
         <f t="shared" si="5"/>
-        <v>0.99415726968681595</v>
+        <v>0.99450077601201647</v>
       </c>
       <c r="R30" s="5">
         <v>189502</v>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="T30" s="3">
         <f t="shared" si="6"/>
-        <v>105876</v>
+        <v>105945</v>
       </c>
       <c r="U30" s="5">
-        <v>188083</v>
+        <v>188152</v>
       </c>
       <c r="V30" s="4">
         <f t="shared" si="7"/>
-        <v>0.99251195238044976</v>
+        <v>0.99287606463256328</v>
       </c>
       <c r="W30" s="5">
         <v>194334</v>
@@ -5565,14 +5565,14 @@
       </c>
       <c r="Y30" s="3">
         <f t="shared" si="8"/>
-        <v>104513</v>
+        <v>104601</v>
       </c>
       <c r="Z30" s="5">
-        <v>190469</v>
+        <v>190557</v>
       </c>
       <c r="AA30" s="4">
         <f t="shared" si="9"/>
-        <v>0.98011156050922643</v>
+        <v>0.98056438914446264</v>
       </c>
       <c r="AB30" s="5">
         <v>325942</v>
@@ -5582,14 +5582,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>203033</v>
+        <v>203236</v>
       </c>
       <c r="AE30" s="5">
-        <v>323012</v>
+        <v>323215</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.9910106706101085</v>
+        <v>0.99163348080333313</v>
       </c>
       <c r="AG30" s="5">
         <v>192789</v>
@@ -5599,14 +5599,14 @@
       </c>
       <c r="AI30" s="3">
         <f t="shared" si="12"/>
-        <v>108950</v>
+        <v>109091</v>
       </c>
       <c r="AJ30" s="5">
-        <v>190984</v>
+        <v>191125</v>
       </c>
       <c r="AK30" s="4">
         <f t="shared" si="13"/>
-        <v>0.9906374326336046</v>
+        <v>0.99136880216194911</v>
       </c>
       <c r="AL30" s="5">
         <v>197994</v>
@@ -5616,14 +5616,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="14"/>
-        <v>108466</v>
+        <v>108739</v>
       </c>
       <c r="AO30" s="5">
-        <v>195757</v>
+        <v>196030</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="15"/>
-        <v>0.98870167782862106</v>
+        <v>0.99008050749012599</v>
       </c>
       <c r="AQ30" s="5">
         <v>333633</v>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="16"/>
-        <v>204921</v>
+        <v>205682</v>
       </c>
       <c r="AT30" s="5">
-        <v>331212</v>
+        <v>331973</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="17"/>
-        <v>0.99274352357230844</v>
+        <v>0.99502447299877406</v>
       </c>
       <c r="AV30" s="5">
         <v>198460</v>
@@ -5650,14 +5650,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="18"/>
-        <v>36154</v>
+        <v>36851</v>
       </c>
       <c r="AY30" s="5">
-        <v>196449</v>
+        <v>197146</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="19"/>
-        <v>0.98986697571298998</v>
+        <v>0.99337901844200338</v>
       </c>
       <c r="BA30" s="5">
         <v>203942</v>
@@ -5667,14 +5667,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="20"/>
-        <v>108084</v>
+        <v>109134</v>
       </c>
       <c r="BD30" s="5">
-        <v>199093</v>
+        <v>200143</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="21"/>
-        <v>0.97622363220915753</v>
+        <v>0.98137215482833351</v>
       </c>
       <c r="BF30" s="5">
         <v>342999</v>
@@ -5684,14 +5684,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>199178</v>
+        <v>203808</v>
       </c>
       <c r="BI30" s="5">
-        <v>329984</v>
+        <v>334614</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.96205528296000864</v>
+        <v>0.97555386458852644</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5709,14 +5709,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>37015</v>
+        <v>37031</v>
       </c>
       <c r="F31" s="5">
-        <v>83244</v>
+        <v>83260</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>1.0043555373236972</v>
+        <v>1.0045485805291796</v>
       </c>
       <c r="H31" s="5">
         <v>85478</v>
@@ -5726,14 +5726,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35481</v>
+        <v>35501</v>
       </c>
       <c r="K31" s="5">
-        <v>84747</v>
+        <v>84767</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.99144809190668948</v>
+        <v>0.99168207024029575</v>
       </c>
       <c r="M31" s="5">
         <v>149930</v>
@@ -5743,14 +5743,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>75381</v>
+        <v>75443</v>
       </c>
       <c r="P31" s="5">
-        <v>150992</v>
+        <v>151054</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0070833055425865</v>
+        <v>1.0074968318548656</v>
       </c>
       <c r="R31" s="5">
         <v>83981</v>
@@ -5760,14 +5760,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34250</v>
+        <v>34281</v>
       </c>
       <c r="U31" s="5">
-        <v>84057</v>
+        <v>84088</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>1.0009049665995879</v>
+        <v>1.0012740977125778</v>
       </c>
       <c r="W31" s="5">
         <v>85994</v>
@@ -5777,14 +5777,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>33851</v>
+        <v>33887</v>
       </c>
       <c r="Z31" s="5">
-        <v>85426</v>
+        <v>85462</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.99339488801544296</v>
+        <v>0.99381352187361904</v>
       </c>
       <c r="AB31" s="5">
         <v>153633</v>
@@ -5794,14 +5794,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>77893</v>
+        <v>78006</v>
       </c>
       <c r="AE31" s="5">
-        <v>153621</v>
+        <v>153734</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>0.99992189178106261</v>
+        <v>1.0006574108427226</v>
       </c>
       <c r="AG31" s="5">
         <v>85109</v>
@@ -5811,14 +5811,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>35610</v>
+        <v>35671</v>
       </c>
       <c r="AJ31" s="5">
-        <v>85427</v>
+        <v>85488</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>1.003736385106158</v>
+        <v>1.0044531130667731</v>
       </c>
       <c r="AL31" s="5">
         <v>88549</v>
@@ -5828,14 +5828,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="14"/>
-        <v>34650</v>
+        <v>34734</v>
       </c>
       <c r="AO31" s="5">
-        <v>87947</v>
+        <v>88031</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="15"/>
-        <v>0.99320150425188314</v>
+        <v>0.99415013156557386</v>
       </c>
       <c r="AQ31" s="5">
         <v>156407</v>
@@ -5845,14 +5845,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="16"/>
-        <v>78069</v>
+        <v>78383</v>
       </c>
       <c r="AT31" s="5">
-        <v>157278</v>
+        <v>157592</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="17"/>
-        <v>1.0055688044652733</v>
+        <v>1.0075763872460952</v>
       </c>
       <c r="AV31" s="5">
         <v>87916</v>
@@ -5862,14 +5862,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="18"/>
-        <v>16532</v>
+        <v>16711</v>
       </c>
       <c r="AY31" s="5">
-        <v>87958</v>
+        <v>88137</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="19"/>
-        <v>1.0004777287410711</v>
+        <v>1.0025137631375405</v>
       </c>
       <c r="BA31" s="5">
         <v>90084</v>
@@ -5879,14 +5879,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="20"/>
-        <v>35073</v>
+        <v>35343</v>
       </c>
       <c r="BD31" s="5">
-        <v>89551</v>
+        <v>89821</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="21"/>
-        <v>0.99408330003108214</v>
+        <v>0.99708050264197856</v>
       </c>
       <c r="BF31" s="5">
         <v>159779</v>
@@ -5896,14 +5896,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>76366</v>
+        <v>78766</v>
       </c>
       <c r="BI31" s="5">
-        <v>156139</v>
+        <v>158539</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>0.97721853309884277</v>
+        <v>0.99223928050619914</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>107508</v>
+        <v>107532</v>
       </c>
       <c r="F32" s="5">
-        <v>230802</v>
+        <v>230826</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99477617729964574</v>
+        <v>0.99487961933331615</v>
       </c>
       <c r="H32" s="5">
         <v>238678</v>
@@ -5938,14 +5938,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>107571</v>
+        <v>107608</v>
       </c>
       <c r="K32" s="5">
-        <v>235307</v>
+        <v>235344</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98587636899923747</v>
+        <v>0.98603138957088632</v>
       </c>
       <c r="M32" s="5">
         <v>498323</v>
@@ -5955,14 +5955,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>270321</v>
+        <v>270422</v>
       </c>
       <c r="P32" s="5">
-        <v>495686</v>
+        <v>495787</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99470825147544861</v>
+        <v>0.99491093126345764</v>
       </c>
       <c r="R32" s="5">
         <v>234167</v>
@@ -5972,14 +5972,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>102936</v>
+        <v>102996</v>
       </c>
       <c r="U32" s="5">
-        <v>232875</v>
+        <v>232935</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99448257013157282</v>
+        <v>0.9947387975248434</v>
       </c>
       <c r="W32" s="5">
         <v>242821</v>
@@ -5989,14 +5989,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>103517</v>
+        <v>103597</v>
       </c>
       <c r="Z32" s="5">
-        <v>237260</v>
+        <v>237340</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.97709835640245279</v>
+        <v>0.97742781719867722</v>
       </c>
       <c r="AB32" s="5">
         <v>507064</v>
@@ -6006,14 +6006,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>280400</v>
+        <v>280636</v>
       </c>
       <c r="AE32" s="5">
-        <v>504621</v>
+        <v>504857</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99518206774687223</v>
+        <v>0.99564749222977766</v>
       </c>
       <c r="AG32" s="5">
         <v>238186</v>
@@ -6023,14 +6023,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>105736</v>
+        <v>105864</v>
       </c>
       <c r="AJ32" s="5">
-        <v>236572</v>
+        <v>236700</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.99322378309388459</v>
+        <v>0.99376117823885535</v>
       </c>
       <c r="AL32" s="5">
         <v>247675</v>
@@ -6040,14 +6040,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="14"/>
-        <v>105922</v>
+        <v>106108</v>
       </c>
       <c r="AO32" s="5">
-        <v>246037</v>
+        <v>246223</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="15"/>
-        <v>0.9933864943979005</v>
+        <v>0.99413747855051982</v>
       </c>
       <c r="AQ32" s="5">
         <v>518099</v>
@@ -6057,14 +6057,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="16"/>
-        <v>278471</v>
+        <v>279289</v>
       </c>
       <c r="AT32" s="5">
-        <v>518177</v>
+        <v>518995</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="17"/>
-        <v>1.0001505503774375</v>
+        <v>1.0017293992074874</v>
       </c>
       <c r="AV32" s="5">
         <v>246693</v>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="18"/>
-        <v>41769</v>
+        <v>42299</v>
       </c>
       <c r="AY32" s="5">
-        <v>246605</v>
+        <v>247135</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="19"/>
-        <v>0.99964328132537206</v>
+        <v>1.0017917006157451</v>
       </c>
       <c r="BA32" s="5">
         <v>255610</v>
@@ -6091,14 +6091,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="20"/>
-        <v>108485</v>
+        <v>109338</v>
       </c>
       <c r="BD32" s="5">
-        <v>253224</v>
+        <v>254077</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="21"/>
-        <v>0.99066546692226443</v>
+        <v>0.99400258205860492</v>
       </c>
       <c r="BF32" s="5">
         <v>535637</v>
@@ -6108,14 +6108,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>268346</v>
+        <v>274679</v>
       </c>
       <c r="BI32" s="5">
-        <v>522199</v>
+        <v>528532</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.97491211398764466</v>
+        <v>0.98673541969654821</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -6133,14 +6133,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112669</v>
+        <v>112688</v>
       </c>
       <c r="F33" s="5">
-        <v>717037</v>
+        <v>717056</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>1.0017379326145968</v>
+        <v>1.0017644766014755</v>
       </c>
       <c r="H33" s="5">
         <v>726544</v>
@@ -6150,14 +6150,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>106278</v>
+        <v>106306</v>
       </c>
       <c r="K33" s="5">
-        <v>729397</v>
+        <v>729425</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>1.0039268096632825</v>
+        <v>1.0039653482789754</v>
       </c>
       <c r="M33" s="5">
         <v>1152516</v>
@@ -6167,14 +6167,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>203597</v>
+        <v>203658</v>
       </c>
       <c r="P33" s="5">
-        <v>1155925</v>
+        <v>1155986</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0029578765067035</v>
+        <v>1.0030108041884018</v>
       </c>
       <c r="R33" s="5">
         <v>733468</v>
@@ -6184,14 +6184,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>105014</v>
+        <v>105055</v>
       </c>
       <c r="U33" s="5">
-        <v>736301</v>
+        <v>736342</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>1.0038624725277723</v>
+        <v>1.0039183713536242</v>
       </c>
       <c r="W33" s="5">
         <v>745690</v>
@@ -6201,14 +6201,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>105140</v>
+        <v>105201</v>
       </c>
       <c r="Z33" s="5">
-        <v>746097</v>
+        <v>746158</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>1.0005458032158134</v>
+        <v>1.0006276066461934</v>
       </c>
       <c r="AB33" s="5">
         <v>1180887</v>
@@ -6218,14 +6218,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>209295</v>
+        <v>209436</v>
       </c>
       <c r="AE33" s="5">
-        <v>1182367</v>
+        <v>1182508</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0012532951925122</v>
+        <v>1.0013726969642311</v>
       </c>
       <c r="AG33" s="5">
         <v>749948</v>
@@ -6235,14 +6235,14 @@
       </c>
       <c r="AI33" s="3">
         <f t="shared" si="12"/>
-        <v>110808</v>
+        <v>110917</v>
       </c>
       <c r="AJ33" s="5">
-        <v>750663</v>
+        <v>750772</v>
       </c>
       <c r="AK33" s="4">
         <f t="shared" si="13"/>
-        <v>1.0009533994356943</v>
+        <v>1.0010987428461706</v>
       </c>
       <c r="AL33" s="5">
         <v>765123</v>
@@ -6252,14 +6252,14 @@
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="14"/>
-        <v>110619</v>
+        <v>110809</v>
       </c>
       <c r="AO33" s="5">
-        <v>773482</v>
+        <v>773672</v>
       </c>
       <c r="AP33" s="4">
         <f t="shared" si="15"/>
-        <v>1.0109250408104318</v>
+        <v>1.0111733668965643</v>
       </c>
       <c r="AQ33" s="5">
         <v>1217820</v>
@@ -6269,14 +6269,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="16"/>
-        <v>215825</v>
+        <v>216403</v>
       </c>
       <c r="AT33" s="5">
-        <v>1224855</v>
+        <v>1225433</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="17"/>
-        <v>1.0057767157708035</v>
+        <v>1.0062513343515462</v>
       </c>
       <c r="AV33" s="5">
         <v>779865</v>
@@ -6286,14 +6286,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="18"/>
-        <v>71420</v>
+        <v>72029</v>
       </c>
       <c r="AY33" s="5">
-        <v>783949</v>
+        <v>784558</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="19"/>
-        <v>1.0052368038057868</v>
+        <v>1.0060177081930848</v>
       </c>
       <c r="BA33" s="5">
         <v>794982</v>
@@ -6303,14 +6303,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="20"/>
-        <v>106634</v>
+        <v>107704</v>
       </c>
       <c r="BD33" s="5">
-        <v>798470</v>
+        <v>799540</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="21"/>
-        <v>1.0043875207237396</v>
+        <v>1.0057334631475934</v>
       </c>
       <c r="BF33" s="5">
         <v>1258934</v>
@@ -6320,14 +6320,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>224156</v>
+        <v>229367</v>
       </c>
       <c r="BI33" s="5">
-        <v>1253682</v>
+        <v>1258893</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>0.99582821657052711</v>
+        <v>0.99996743276454525</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="O35" s="3">
         <f t="shared" ref="O35:O47" si="28">P35-N35</f>
-        <v>2840</v>
+        <v>2841</v>
       </c>
       <c r="P35" s="5">
-        <v>15081</v>
+        <v>15082</v>
       </c>
       <c r="Q35" s="4">
         <f t="shared" ref="Q35:Q48" si="29">P35/M35</f>
-        <v>0.99894018679207786</v>
+        <v>0.99900642511757298</v>
       </c>
       <c r="R35" s="5">
         <v>12455</v>
@@ -6584,14 +6584,14 @@
       </c>
       <c r="T35" s="3">
         <f t="shared" ref="T35:T47" si="30">U35-S35</f>
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="U35" s="5">
-        <v>12411</v>
+        <v>12412</v>
       </c>
       <c r="V35" s="4">
         <f t="shared" ref="V35:V48" si="31">U35/R35</f>
-        <v>0.99646728221597747</v>
+        <v>0.99654757125652349</v>
       </c>
       <c r="W35" s="5">
         <v>12547</v>
@@ -6601,14 +6601,14 @@
       </c>
       <c r="Y35" s="3">
         <f t="shared" ref="Y35:Y47" si="32">Z35-X35</f>
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="Z35" s="5">
-        <v>12441</v>
+        <v>12442</v>
       </c>
       <c r="AA35" s="4">
         <f t="shared" ref="AA35:AA48" si="33">Z35/W35</f>
-        <v>0.99155176536223799</v>
+        <v>0.99163146568900928</v>
       </c>
       <c r="AB35" s="5">
         <v>15257</v>
@@ -6618,14 +6618,14 @@
       </c>
       <c r="AD35" s="3">
         <f t="shared" ref="AD35:AD47" si="34">AE35-AC35</f>
-        <v>2832</v>
+        <v>2837</v>
       </c>
       <c r="AE35" s="5">
-        <v>15199</v>
+        <v>15204</v>
       </c>
       <c r="AF35" s="4">
         <f t="shared" ref="AF35:AF48" si="35">AE35/AB35</f>
-        <v>0.99619846627777409</v>
+        <v>0.99652618470210397</v>
       </c>
       <c r="AG35" s="5">
         <v>12574</v>
@@ -6635,14 +6635,14 @@
       </c>
       <c r="AI35" s="3">
         <f t="shared" ref="AI35:AI47" si="36">AJ35-AH35</f>
-        <v>2212</v>
+        <v>2218</v>
       </c>
       <c r="AJ35" s="5">
-        <v>12525</v>
+        <v>12531</v>
       </c>
       <c r="AK35" s="4">
         <f t="shared" ref="AK35:AK48" si="37">AJ35/AG35</f>
-        <v>0.99610306982662633</v>
+        <v>0.99658024494989661</v>
       </c>
       <c r="AL35" s="5">
         <v>12702</v>
@@ -6652,14 +6652,14 @@
       </c>
       <c r="AN35" s="3">
         <f t="shared" ref="AN35:AN47" si="38">AO35-AM35</f>
-        <v>2074</v>
+        <v>2085</v>
       </c>
       <c r="AO35" s="5">
-        <v>12614</v>
+        <v>12625</v>
       </c>
       <c r="AP35" s="4">
         <f t="shared" ref="AP35:AP48" si="39">AO35/AL35</f>
-        <v>0.99307195717209884</v>
+        <v>0.99393796252558653</v>
       </c>
       <c r="AQ35" s="5">
         <v>15458</v>
@@ -6669,14 +6669,14 @@
       </c>
       <c r="AS35" s="3">
         <f t="shared" ref="AS35:AS47" si="40">AT35-AR35</f>
-        <v>2821</v>
+        <v>2848</v>
       </c>
       <c r="AT35" s="5">
-        <v>15393</v>
+        <v>15420</v>
       </c>
       <c r="AU35" s="4">
         <f t="shared" ref="AU35:AU48" si="41">AT35/AQ35</f>
-        <v>0.99579505757536546</v>
+        <v>0.99754172596713675</v>
       </c>
       <c r="AV35" s="5">
         <v>12806</v>
@@ -6686,14 +6686,14 @@
       </c>
       <c r="AX35" s="3">
         <f t="shared" ref="AX35:AX47" si="42">AY35-AW35</f>
-        <v>1979</v>
+        <v>2018</v>
       </c>
       <c r="AY35" s="5">
-        <v>12667</v>
+        <v>12706</v>
       </c>
       <c r="AZ35" s="4">
         <f t="shared" ref="AZ35:AZ48" si="43">AY35/AV35</f>
-        <v>0.98914571294705611</v>
+        <v>0.99219116039356547</v>
       </c>
       <c r="BA35" s="5">
         <v>12915</v>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="BC35" s="3">
         <f t="shared" ref="BC35:BC47" si="44">BD35-BB35</f>
-        <v>1819</v>
+        <v>1887</v>
       </c>
       <c r="BD35" s="5">
-        <v>12684</v>
+        <v>12752</v>
       </c>
       <c r="BE35" s="4">
         <f t="shared" ref="BE35:BE48" si="45">BD35/BA35</f>
-        <v>0.98211382113821133</v>
+        <v>0.98737901664730932</v>
       </c>
       <c r="BF35" s="5">
         <v>15661</v>
@@ -6720,14 +6720,14 @@
       </c>
       <c r="BH35" s="3">
         <f t="shared" ref="BH35:BH47" si="46">BI35-BG35</f>
-        <v>2552</v>
+        <v>2679</v>
       </c>
       <c r="BI35" s="5">
-        <v>15356</v>
+        <v>15483</v>
       </c>
       <c r="BJ35" s="4">
         <f t="shared" ref="BJ35:BJ48" si="47">BI35/BF35</f>
-        <v>0.98052487069791205</v>
+        <v>0.98863418683353554</v>
       </c>
     </row>
     <row r="36" spans="1:62" x14ac:dyDescent="0.3">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="24"/>
-        <v>278556</v>
+        <v>278663</v>
       </c>
       <c r="F36" s="5">
-        <v>954539</v>
+        <v>954646</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="25"/>
-        <v>1.001814632508055</v>
+        <v>1.0019269319171713</v>
       </c>
       <c r="H36" s="5">
         <v>975466</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="26"/>
-        <v>271532</v>
+        <v>271667</v>
       </c>
       <c r="K36" s="5">
-        <v>970910</v>
+        <v>971045</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="27"/>
-        <v>0.99532941178882706</v>
+        <v>0.99546780718138816</v>
       </c>
       <c r="M36" s="5">
         <v>1668278</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="28"/>
-        <v>535178</v>
+        <v>535495</v>
       </c>
       <c r="P36" s="5">
-        <v>1671091</v>
+        <v>1671408</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="29"/>
-        <v>1.0016861698110266</v>
+        <v>1.0018761861032754</v>
       </c>
       <c r="R36" s="5">
         <v>976879</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="30"/>
-        <v>261606</v>
+        <v>261803</v>
       </c>
       <c r="U36" s="5">
-        <v>976062</v>
+        <v>976259</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="31"/>
-        <v>0.99916366305345905</v>
+        <v>0.99936532569540337</v>
       </c>
       <c r="W36" s="5">
         <v>1000117</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="32"/>
-        <v>264149</v>
+        <v>264402</v>
       </c>
       <c r="Z36" s="5">
-        <v>988542</v>
+        <v>988795</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98842635411656832</v>
+        <v>0.98867932451903129</v>
       </c>
       <c r="AB36" s="5">
         <v>1701420</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="34"/>
-        <v>553855</v>
+        <v>554494</v>
       </c>
       <c r="AE36" s="5">
-        <v>1699839</v>
+        <v>1700478</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="35"/>
-        <v>0.9990707761751948</v>
+        <v>0.99944634481785799</v>
       </c>
       <c r="AG36" s="5">
         <v>996655</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="36"/>
-        <v>273315</v>
+        <v>273757</v>
       </c>
       <c r="AJ36" s="5">
-        <v>995552</v>
+        <v>995994</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="37"/>
-        <v>0.9988932980820846</v>
+        <v>0.999336781534232</v>
       </c>
       <c r="AL36" s="5">
         <v>1027093</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="38"/>
-        <v>272947</v>
+        <v>273743</v>
       </c>
       <c r="AO36" s="5">
-        <v>1031433</v>
+        <v>1032229</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="39"/>
-        <v>1.004225518039749</v>
+        <v>1.0050005208875925</v>
       </c>
       <c r="AQ36" s="5">
         <v>1750886</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="40"/>
-        <v>558236</v>
+        <v>560444</v>
       </c>
       <c r="AT36" s="5">
-        <v>1763707</v>
+        <v>1765915</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="41"/>
-        <v>1.0073225783974513</v>
+        <v>1.0085836542184927</v>
       </c>
       <c r="AV36" s="5">
         <v>1041088</v>
@@ -6898,14 +6898,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="42"/>
-        <v>164112</v>
+        <v>166276</v>
       </c>
       <c r="AY36" s="5">
-        <v>1046112</v>
+        <v>1048276</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="43"/>
-        <v>1.0048257207844102</v>
+        <v>1.0069043154853383</v>
       </c>
       <c r="BA36" s="5">
         <v>1070068</v>
@@ -6915,14 +6915,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="44"/>
-        <v>265917</v>
+        <v>269228</v>
       </c>
       <c r="BD36" s="5">
-        <v>1065887</v>
+        <v>1069198</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="45"/>
-        <v>0.99609277167432353</v>
+        <v>0.99918696755720193</v>
       </c>
       <c r="BF36" s="5">
         <v>1814069</v>
@@ -6932,14 +6932,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="46"/>
-        <v>528042</v>
+        <v>547882</v>
       </c>
       <c r="BI36" s="5">
-        <v>1779404</v>
+        <v>1799244</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="47"/>
-        <v>0.98089102454206534</v>
+        <v>0.99182776399354156</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6957,14 +6957,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="24"/>
-        <v>309064</v>
+        <v>309205</v>
       </c>
       <c r="F37" s="5">
-        <v>734544</v>
+        <v>734685</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="25"/>
-        <v>0.99066176827590668</v>
+        <v>0.99085193157358109</v>
       </c>
       <c r="H37" s="5">
         <v>747767</v>
@@ -6974,14 +6974,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="26"/>
-        <v>304659</v>
+        <v>304825</v>
       </c>
       <c r="K37" s="5">
-        <v>739654</v>
+        <v>739820</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="27"/>
-        <v>0.98915036368280496</v>
+        <v>0.98937235796712075</v>
       </c>
       <c r="M37" s="5">
         <v>922163</v>
@@ -6991,14 +6991,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="28"/>
-        <v>374596</v>
+        <v>374867</v>
       </c>
       <c r="P37" s="5">
-        <v>915556</v>
+        <v>915827</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="29"/>
-        <v>0.99283532303941924</v>
+        <v>0.99312919733279259</v>
       </c>
       <c r="R37" s="5">
         <v>751356</v>
@@ -7008,14 +7008,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="30"/>
-        <v>292487</v>
+        <v>292773</v>
       </c>
       <c r="U37" s="5">
-        <v>744507</v>
+        <v>744793</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="31"/>
-        <v>0.99088448085860759</v>
+        <v>0.9912651259855515</v>
       </c>
       <c r="W37" s="5">
         <v>760191</v>
@@ -7025,14 +7025,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="32"/>
-        <v>284638</v>
+        <v>284996</v>
       </c>
       <c r="Z37" s="5">
-        <v>750322</v>
+        <v>750680</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98701773633205336</v>
+        <v>0.98748867061041234</v>
       </c>
       <c r="AB37" s="5">
         <v>938023</v>
@@ -7042,14 +7042,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="34"/>
-        <v>392102</v>
+        <v>392727</v>
       </c>
       <c r="AE37" s="5">
-        <v>929601</v>
+        <v>930226</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="35"/>
-        <v>0.99102154211570503</v>
+        <v>0.99168783707862174</v>
       </c>
       <c r="AG37" s="5">
         <v>763648</v>
@@ -7059,14 +7059,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="36"/>
-        <v>299282</v>
+        <v>299915</v>
       </c>
       <c r="AJ37" s="5">
-        <v>755706</v>
+        <v>756339</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="37"/>
-        <v>0.9895999203821656</v>
+        <v>0.99042883632249412</v>
       </c>
       <c r="AL37" s="5">
         <v>773685</v>
@@ -7076,14 +7076,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="38"/>
-        <v>289120</v>
+        <v>290160</v>
       </c>
       <c r="AO37" s="5">
-        <v>768580</v>
+        <v>769620</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="39"/>
-        <v>0.99340170741322376</v>
+        <v>0.99474592372864923</v>
       </c>
       <c r="AQ37" s="5">
         <v>957323</v>
@@ -7093,14 +7093,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="40"/>
-        <v>388229</v>
+        <v>390468</v>
       </c>
       <c r="AT37" s="5">
-        <v>950492</v>
+        <v>952731</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99286447729763094</v>
+        <v>0.99520329084332038</v>
       </c>
       <c r="AV37" s="5">
         <v>783693</v>
@@ -7110,14 +7110,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="42"/>
-        <v>124177</v>
+        <v>126962</v>
       </c>
       <c r="AY37" s="5">
-        <v>774969</v>
+        <v>777754</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="43"/>
-        <v>0.98886808992807129</v>
+        <v>0.99242177740518289</v>
       </c>
       <c r="BA37" s="5">
         <v>794943</v>
@@ -7127,14 +7127,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="44"/>
-        <v>277405</v>
+        <v>281589</v>
       </c>
       <c r="BD37" s="5">
-        <v>779234</v>
+        <v>783418</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="45"/>
-        <v>0.9802388347340627</v>
+        <v>0.98550210518238412</v>
       </c>
       <c r="BF37" s="5">
         <v>980352</v>
@@ -7144,14 +7144,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="46"/>
-        <v>373146</v>
+        <v>383925</v>
       </c>
       <c r="BI37" s="5">
-        <v>948263</v>
+        <v>959042</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="47"/>
-        <v>0.96726787929233582</v>
+        <v>0.97826290964877927</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7169,14 +7169,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="24"/>
-        <v>10011</v>
+        <v>10019</v>
       </c>
       <c r="F38" s="5">
-        <v>26182</v>
+        <v>26190</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="25"/>
-        <v>1.0046044048806693</v>
+        <v>1.0049113652060471</v>
       </c>
       <c r="H38" s="5">
         <v>26657</v>
@@ -7186,14 +7186,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="26"/>
-        <v>9680</v>
+        <v>9691</v>
       </c>
       <c r="K38" s="5">
-        <v>26477</v>
+        <v>26488</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="27"/>
-        <v>0.99324755223768613</v>
+        <v>0.99366020182316095</v>
       </c>
       <c r="M38" s="5">
         <v>40003</v>
@@ -7203,14 +7203,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="28"/>
-        <v>14600</v>
+        <v>14620</v>
       </c>
       <c r="P38" s="5">
-        <v>40076</v>
+        <v>40096</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="29"/>
-        <v>1.0018248631352649</v>
+        <v>1.0023248256380772</v>
       </c>
       <c r="R38" s="5">
         <v>26603</v>
@@ -7220,14 +7220,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="30"/>
-        <v>9141</v>
+        <v>9159</v>
       </c>
       <c r="U38" s="5">
-        <v>26609</v>
+        <v>26627</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="31"/>
-        <v>1.0002255384731045</v>
+        <v>1.0009021538924181</v>
       </c>
       <c r="W38" s="5">
         <v>27177</v>
@@ -7237,14 +7237,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="32"/>
-        <v>9050</v>
+        <v>9070</v>
       </c>
       <c r="Z38" s="5">
-        <v>26843</v>
+        <v>26863</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="33"/>
-        <v>0.98771019612172062</v>
+        <v>0.98844611252161751</v>
       </c>
       <c r="AB38" s="5">
         <v>40627</v>
@@ -7254,14 +7254,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="34"/>
-        <v>15141</v>
+        <v>15179</v>
       </c>
       <c r="AE38" s="5">
-        <v>40654</v>
+        <v>40692</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0006645826666996</v>
+        <v>1.0015999212346469</v>
       </c>
       <c r="AG38" s="5">
         <v>26952</v>
@@ -7271,14 +7271,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="36"/>
-        <v>9434</v>
+        <v>9469</v>
       </c>
       <c r="AJ38" s="5">
-        <v>26980</v>
+        <v>27015</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0010388839418225</v>
+        <v>1.0023374888691006</v>
       </c>
       <c r="AL38" s="5">
         <v>27600</v>
@@ -7288,14 +7288,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="38"/>
-        <v>9001</v>
+        <v>9055</v>
       </c>
       <c r="AO38" s="5">
-        <v>27489</v>
+        <v>27543</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="39"/>
-        <v>0.9959782608695652</v>
+        <v>0.99793478260869561</v>
       </c>
       <c r="AQ38" s="5">
         <v>41434</v>
@@ -7305,14 +7305,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="40"/>
-        <v>15108</v>
+        <v>15244</v>
       </c>
       <c r="AT38" s="5">
-        <v>41532</v>
+        <v>41668</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0023652073176619</v>
+        <v>1.0056475358401313</v>
       </c>
       <c r="AV38" s="5">
         <v>27593</v>
@@ -7322,14 +7322,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="42"/>
-        <v>5150</v>
+        <v>5307</v>
       </c>
       <c r="AY38" s="5">
-        <v>27506</v>
+        <v>27663</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="43"/>
-        <v>0.9968470264197441</v>
+        <v>1.0025368752944588</v>
       </c>
       <c r="BA38" s="5">
         <v>28279</v>
@@ -7339,14 +7339,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="44"/>
-        <v>8317</v>
+        <v>8557</v>
       </c>
       <c r="BD38" s="5">
-        <v>27619</v>
+        <v>27859</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="45"/>
-        <v>0.97666112663106897</v>
+        <v>0.9851479896743166</v>
       </c>
       <c r="BF38" s="5">
         <v>42642</v>
@@ -7356,14 +7356,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="46"/>
-        <v>13852</v>
+        <v>14569</v>
       </c>
       <c r="BI38" s="5">
-        <v>40851</v>
+        <v>41568</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="47"/>
-        <v>0.95799915576192485</v>
+        <v>0.97481356409174058</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7483,14 +7483,14 @@
       </c>
       <c r="AI39" s="3">
         <f t="shared" si="36"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AJ39" s="5">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AK39" s="4">
         <f t="shared" si="37"/>
-        <v>0.94756554307116103</v>
+        <v>0.95131086142322097</v>
       </c>
       <c r="AL39" s="5">
         <v>276</v>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="AS39" s="3">
         <f t="shared" si="40"/>
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AT39" s="5">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AU39" s="4">
         <f t="shared" si="41"/>
-        <v>0.94970414201183428</v>
+        <v>0.95562130177514792</v>
       </c>
       <c r="AV39" s="5">
         <v>279</v>
@@ -7534,14 +7534,14 @@
       </c>
       <c r="AX39" s="3">
         <f t="shared" si="42"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AY39" s="5">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AZ39" s="4">
         <f t="shared" si="43"/>
-        <v>0.95340501792114696</v>
+        <v>0.96057347670250892</v>
       </c>
       <c r="BA39" s="5">
         <v>291</v>
@@ -7551,14 +7551,14 @@
       </c>
       <c r="BC39" s="3">
         <f t="shared" si="44"/>
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BD39" s="5">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="BE39" s="4">
         <f t="shared" si="45"/>
-        <v>0.92096219931271472</v>
+        <v>0.92783505154639179</v>
       </c>
       <c r="BF39" s="5">
         <v>344</v>
@@ -7568,14 +7568,14 @@
       </c>
       <c r="BH39" s="3">
         <f t="shared" si="46"/>
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="BI39" s="5">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="BJ39" s="4">
         <f t="shared" si="47"/>
-        <v>0.96220930232558144</v>
+        <v>0.97093023255813948</v>
       </c>
     </row>
     <row r="40" spans="1:62" x14ac:dyDescent="0.3">
@@ -7593,14 +7593,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="24"/>
-        <v>124893</v>
+        <v>124961</v>
       </c>
       <c r="F40" s="5">
-        <v>301553</v>
+        <v>301621</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="25"/>
-        <v>0.99229665607086681</v>
+        <v>0.9925204183037506</v>
       </c>
       <c r="H40" s="5">
         <v>306465</v>
@@ -7610,14 +7610,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="26"/>
-        <v>127345</v>
+        <v>127436</v>
       </c>
       <c r="K40" s="5">
-        <v>302918</v>
+        <v>303009</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="27"/>
-        <v>0.9884260845447278</v>
+        <v>0.98872301894180414</v>
       </c>
       <c r="M40" s="5">
         <v>361770</v>
@@ -7627,14 +7627,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="28"/>
-        <v>149660</v>
+        <v>149793</v>
       </c>
       <c r="P40" s="5">
-        <v>359173</v>
+        <v>359306</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="29"/>
-        <v>0.99282140586560519</v>
+        <v>0.99318904276197584</v>
       </c>
       <c r="R40" s="5">
         <v>306479</v>
@@ -7644,14 +7644,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="30"/>
-        <v>117912</v>
+        <v>118060</v>
       </c>
       <c r="U40" s="5">
-        <v>304625</v>
+        <v>304773</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="31"/>
-        <v>0.99395064588438364</v>
+        <v>0.99443355009641765</v>
       </c>
       <c r="W40" s="5">
         <v>309858</v>
@@ -7661,14 +7661,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="32"/>
-        <v>124181</v>
+        <v>124370</v>
       </c>
       <c r="Z40" s="5">
-        <v>306170</v>
+        <v>306359</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="33"/>
-        <v>0.98809777381897512</v>
+        <v>0.98870773063790507</v>
       </c>
       <c r="AB40" s="5">
         <v>365821</v>
@@ -7678,14 +7678,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="34"/>
-        <v>150344</v>
+        <v>150652</v>
       </c>
       <c r="AE40" s="5">
-        <v>363032</v>
+        <v>363340</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="35"/>
-        <v>0.99237605276897722</v>
+        <v>0.99321799459298399</v>
       </c>
       <c r="AG40" s="5">
         <v>311342</v>
@@ -7695,14 +7695,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="36"/>
-        <v>123278</v>
+        <v>123670</v>
       </c>
       <c r="AJ40" s="5">
-        <v>308636</v>
+        <v>309028</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="37"/>
-        <v>0.99130859312267539</v>
+        <v>0.9925676587161385</v>
       </c>
       <c r="AL40" s="5">
         <v>314792</v>
@@ -7712,14 +7712,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="38"/>
-        <v>124363</v>
+        <v>124983</v>
       </c>
       <c r="AO40" s="5">
-        <v>312241</v>
+        <v>312861</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99189623624488554</v>
+        <v>0.99386579074436454</v>
       </c>
       <c r="AQ40" s="5">
         <v>372144</v>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="40"/>
-        <v>156557</v>
+        <v>157772</v>
       </c>
       <c r="AT40" s="5">
-        <v>369258</v>
+        <v>370473</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99224493744357023</v>
+        <v>0.99550980265703604</v>
       </c>
       <c r="AV40" s="5">
         <v>317868</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="42"/>
-        <v>63727</v>
+        <v>65545</v>
       </c>
       <c r="AY40" s="5">
-        <v>313543</v>
+        <v>315361</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="43"/>
-        <v>0.98639372318069141</v>
+        <v>0.99211307838473828</v>
       </c>
       <c r="BA40" s="5">
         <v>321637</v>
@@ -7763,14 +7763,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="44"/>
-        <v>111637</v>
+        <v>114051</v>
       </c>
       <c r="BD40" s="5">
-        <v>314404</v>
+        <v>316818</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="45"/>
-        <v>0.97751191560672435</v>
+        <v>0.98501727102292336</v>
       </c>
       <c r="BF40" s="5">
         <v>380248</v>
@@ -7780,14 +7780,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="46"/>
-        <v>150060</v>
+        <v>154732</v>
       </c>
       <c r="BI40" s="5">
-        <v>367001</v>
+        <v>371673</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="47"/>
-        <v>0.96516220992615342</v>
+        <v>0.97744892806799777</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7805,14 +7805,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="24"/>
-        <v>370841</v>
+        <v>370965</v>
       </c>
       <c r="F41" s="5">
-        <v>976043</v>
+        <v>976167</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="25"/>
-        <v>0.99857790764175136</v>
+        <v>0.99870477055716356</v>
       </c>
       <c r="H41" s="5">
         <v>983280</v>
@@ -7822,14 +7822,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="26"/>
-        <v>379780</v>
+        <v>379923</v>
       </c>
       <c r="K41" s="5">
-        <v>980560</v>
+        <v>980703</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="27"/>
-        <v>0.99723374827109268</v>
+        <v>0.99737917988772273</v>
       </c>
       <c r="M41" s="5">
         <v>1084276</v>
@@ -7839,14 +7839,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="28"/>
-        <v>390389</v>
+        <v>390598</v>
       </c>
       <c r="P41" s="5">
-        <v>1083068</v>
+        <v>1083277</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="29"/>
-        <v>0.99888589252183024</v>
+        <v>0.999078647871944</v>
       </c>
       <c r="R41" s="5">
         <v>988018</v>
@@ -7856,14 +7856,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="30"/>
-        <v>349114</v>
+        <v>349326</v>
       </c>
       <c r="U41" s="5">
-        <v>988318</v>
+        <v>988530</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="31"/>
-        <v>1.0003036381928265</v>
+        <v>1.0005182091824238</v>
       </c>
       <c r="W41" s="5">
         <v>994033</v>
@@ -7873,14 +7873,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="32"/>
-        <v>343520</v>
+        <v>343767</v>
       </c>
       <c r="Z41" s="5">
-        <v>993452</v>
+        <v>993699</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="33"/>
-        <v>0.99941551236226567</v>
+        <v>0.99966399505851411</v>
       </c>
       <c r="AB41" s="5">
         <v>1097882</v>
@@ -7890,14 +7890,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="34"/>
-        <v>394702</v>
+        <v>395059</v>
       </c>
       <c r="AE41" s="5">
-        <v>1097499</v>
+        <v>1097856</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="35"/>
-        <v>0.9996511464802228</v>
+        <v>0.99997631803782194</v>
       </c>
       <c r="AG41" s="5">
         <v>1002140</v>
@@ -7907,14 +7907,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="36"/>
-        <v>354282</v>
+        <v>354708</v>
       </c>
       <c r="AJ41" s="5">
-        <v>1001657</v>
+        <v>1002083</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99951803141277662</v>
+        <v>0.99994312171952027</v>
       </c>
       <c r="AL41" s="5">
         <v>1011306</v>
@@ -7924,14 +7924,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="38"/>
-        <v>343062</v>
+        <v>343728</v>
       </c>
       <c r="AO41" s="5">
-        <v>1014537</v>
+        <v>1015203</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="39"/>
-        <v>1.003194878701402</v>
+        <v>1.0038534330855349</v>
       </c>
       <c r="AQ41" s="5">
         <v>1119532</v>
@@ -7941,14 +7941,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="40"/>
-        <v>396389</v>
+        <v>397551</v>
       </c>
       <c r="AT41" s="5">
-        <v>1123232</v>
+        <v>1124394</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="41"/>
-        <v>1.0033049524265496</v>
+        <v>1.0043428861345634</v>
       </c>
       <c r="AV41" s="5">
         <v>1028062</v>
@@ -7958,14 +7958,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="42"/>
-        <v>148542</v>
+        <v>150122</v>
       </c>
       <c r="AY41" s="5">
-        <v>1028250</v>
+        <v>1029830</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="43"/>
-        <v>1.0001828683484071</v>
+        <v>1.0017197406382106</v>
       </c>
       <c r="BA41" s="5">
         <v>1037044</v>
@@ -7975,14 +7975,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="44"/>
-        <v>329795</v>
+        <v>332260</v>
       </c>
       <c r="BD41" s="5">
-        <v>1034612</v>
+        <v>1037077</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="45"/>
-        <v>0.99765487288871058</v>
+        <v>1.0000318212149146</v>
       </c>
       <c r="BF41" s="5">
         <v>1143357</v>
@@ -7992,14 +7992,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="46"/>
-        <v>390345</v>
+        <v>396631</v>
       </c>
       <c r="BI41" s="5">
-        <v>1134179</v>
+        <v>1140465</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99197276091369535</v>
+        <v>0.99747060629357231</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8017,14 +8017,14 @@
       </c>
       <c r="E42" s="3">
         <f t="shared" si="24"/>
-        <v>9254</v>
+        <v>9255</v>
       </c>
       <c r="F42" s="5">
-        <v>19587</v>
+        <v>19588</v>
       </c>
       <c r="G42" s="4">
         <f t="shared" si="25"/>
-        <v>0.99547672291116085</v>
+        <v>0.99552754624923767</v>
       </c>
       <c r="H42" s="5">
         <v>19882</v>
@@ -8034,14 +8034,14 @@
       </c>
       <c r="J42" s="3">
         <f t="shared" si="26"/>
-        <v>9524</v>
+        <v>9525</v>
       </c>
       <c r="K42" s="5">
-        <v>19681</v>
+        <v>19682</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="27"/>
-        <v>0.98989035308319084</v>
+        <v>0.98994064983402075</v>
       </c>
       <c r="M42" s="5">
         <v>21930</v>
@@ -8051,14 +8051,14 @@
       </c>
       <c r="O42" s="3">
         <f t="shared" si="28"/>
-        <v>9987</v>
+        <v>9992</v>
       </c>
       <c r="P42" s="5">
-        <v>21778</v>
+        <v>21783</v>
       </c>
       <c r="Q42" s="4">
         <f t="shared" si="29"/>
-        <v>0.99306885544915635</v>
+        <v>0.99329685362517095</v>
       </c>
       <c r="R42" s="5">
         <v>20021</v>
@@ -8068,14 +8068,14 @@
       </c>
       <c r="T42" s="3">
         <f t="shared" si="30"/>
-        <v>8928</v>
+        <v>8933</v>
       </c>
       <c r="U42" s="5">
-        <v>19812</v>
+        <v>19817</v>
       </c>
       <c r="V42" s="4">
         <f t="shared" si="31"/>
-        <v>0.98956096099095947</v>
+        <v>0.98981069876629535</v>
       </c>
       <c r="W42" s="5">
         <v>20153</v>
@@ -8085,14 +8085,14 @@
       </c>
       <c r="Y42" s="3">
         <f t="shared" si="32"/>
-        <v>8700</v>
+        <v>8709</v>
       </c>
       <c r="Z42" s="5">
-        <v>19907</v>
+        <v>19916</v>
       </c>
       <c r="AA42" s="4">
         <f t="shared" si="33"/>
-        <v>0.98779338063811839</v>
+        <v>0.98823996427330918</v>
       </c>
       <c r="AB42" s="5">
         <v>22238</v>
@@ -8102,14 +8102,14 @@
       </c>
       <c r="AD42" s="3">
         <f t="shared" si="34"/>
-        <v>10012</v>
+        <v>10024</v>
       </c>
       <c r="AE42" s="5">
-        <v>22067</v>
+        <v>22079</v>
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="35"/>
-        <v>0.99231045957370267</v>
+        <v>0.99285007644572354</v>
       </c>
       <c r="AG42" s="5">
         <v>20276</v>
@@ -8119,14 +8119,14 @@
       </c>
       <c r="AI42" s="3">
         <f t="shared" si="36"/>
-        <v>9048</v>
+        <v>9062</v>
       </c>
       <c r="AJ42" s="5">
-        <v>20147</v>
+        <v>20161</v>
       </c>
       <c r="AK42" s="4">
         <f t="shared" si="37"/>
-        <v>0.99363779838232391</v>
+        <v>0.9943282698757151</v>
       </c>
       <c r="AL42" s="5">
         <v>20453</v>
@@ -8136,14 +8136,14 @@
       </c>
       <c r="AN42" s="3">
         <f t="shared" si="38"/>
-        <v>8745</v>
+        <v>8762</v>
       </c>
       <c r="AO42" s="5">
-        <v>20333</v>
+        <v>20350</v>
       </c>
       <c r="AP42" s="4">
         <f t="shared" si="39"/>
-        <v>0.99413289004058081</v>
+        <v>0.99496406395149861</v>
       </c>
       <c r="AQ42" s="5">
         <v>22621</v>
@@ -8153,14 +8153,14 @@
       </c>
       <c r="AS42" s="3">
         <f t="shared" si="40"/>
-        <v>10247</v>
+        <v>10290</v>
       </c>
       <c r="AT42" s="5">
-        <v>22548</v>
+        <v>22591</v>
       </c>
       <c r="AU42" s="4">
         <f t="shared" si="41"/>
-        <v>0.99677291012775737</v>
+        <v>0.99867379868264006</v>
       </c>
       <c r="AV42" s="5">
         <v>20714</v>
@@ -8170,14 +8170,14 @@
       </c>
       <c r="AX42" s="3">
         <f t="shared" si="42"/>
-        <v>3857</v>
+        <v>3931</v>
       </c>
       <c r="AY42" s="5">
-        <v>20553</v>
+        <v>20627</v>
       </c>
       <c r="AZ42" s="4">
         <f t="shared" si="43"/>
-        <v>0.99222747899971031</v>
+        <v>0.99579994206816647</v>
       </c>
       <c r="BA42" s="5">
         <v>20927</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="BC42" s="3">
         <f t="shared" si="44"/>
-        <v>8449</v>
+        <v>8576</v>
       </c>
       <c r="BD42" s="5">
-        <v>20611</v>
+        <v>20738</v>
       </c>
       <c r="BE42" s="4">
         <f t="shared" si="45"/>
-        <v>0.98489989009413681</v>
+        <v>0.99096860515124008</v>
       </c>
       <c r="BF42" s="5">
         <v>23165</v>
@@ -8204,14 +8204,14 @@
       </c>
       <c r="BH42" s="3">
         <f t="shared" si="46"/>
-        <v>10041</v>
+        <v>10296</v>
       </c>
       <c r="BI42" s="5">
-        <v>22558</v>
+        <v>22813</v>
       </c>
       <c r="BJ42" s="4">
         <f t="shared" si="47"/>
-        <v>0.97379667601985753</v>
+        <v>0.98480466220591412</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="24"/>
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="F43" s="5">
-        <v>3886</v>
+        <v>3887</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="25"/>
-        <v>0.99284619315278488</v>
+        <v>0.99310168625447115</v>
       </c>
       <c r="H43" s="5">
         <v>3941</v>
@@ -8246,14 +8246,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="26"/>
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="K43" s="5">
-        <v>3926</v>
+        <v>3927</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="27"/>
-        <v>0.99619385942654148</v>
+        <v>0.99644760213143868</v>
       </c>
       <c r="M43" s="5">
         <v>4896</v>
@@ -8263,14 +8263,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="28"/>
-        <v>2717</v>
+        <v>2719</v>
       </c>
       <c r="P43" s="5">
-        <v>4861</v>
+        <v>4863</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="29"/>
-        <v>0.99285130718954251</v>
+        <v>0.99325980392156865</v>
       </c>
       <c r="R43" s="5">
         <v>3969</v>
@@ -8297,14 +8297,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="32"/>
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="Z43" s="5">
-        <v>3971</v>
+        <v>3973</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="33"/>
-        <v>0.99052132701421802</v>
+        <v>0.99102020453978545</v>
       </c>
       <c r="AB43" s="5">
         <v>4962</v>
@@ -8314,14 +8314,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="34"/>
-        <v>2683</v>
+        <v>2688</v>
       </c>
       <c r="AE43" s="5">
-        <v>4937</v>
+        <v>4942</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99496170898831116</v>
+        <v>0.99596936719064888</v>
       </c>
       <c r="AG43" s="5">
         <v>4018</v>
@@ -8331,14 +8331,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="36"/>
-        <v>2243</v>
+        <v>2247</v>
       </c>
       <c r="AJ43" s="5">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="37"/>
-        <v>0.99701343952215027</v>
+        <v>0.99800895968143355</v>
       </c>
       <c r="AL43" s="5">
         <v>4086</v>
@@ -8348,14 +8348,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="38"/>
-        <v>2143</v>
+        <v>2152</v>
       </c>
       <c r="AO43" s="5">
-        <v>4058</v>
+        <v>4067</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="39"/>
-        <v>0.9931473323543808</v>
+        <v>0.99534997552618698</v>
       </c>
       <c r="AQ43" s="5">
         <v>5072</v>
@@ -8365,14 +8365,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="40"/>
-        <v>2908</v>
+        <v>2930</v>
       </c>
       <c r="AT43" s="5">
-        <v>5046</v>
+        <v>5068</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="41"/>
-        <v>0.99487381703470035</v>
+        <v>0.99921135646687698</v>
       </c>
       <c r="AV43" s="5">
         <v>4151</v>
@@ -8382,14 +8382,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="42"/>
-        <v>1221</v>
+        <v>1255</v>
       </c>
       <c r="AY43" s="5">
-        <v>4062</v>
+        <v>4096</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="43"/>
-        <v>0.97855938328113712</v>
+        <v>0.98675018067935438</v>
       </c>
       <c r="BA43" s="5">
         <v>4249</v>
@@ -8399,14 +8399,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="44"/>
-        <v>2127</v>
+        <v>2175</v>
       </c>
       <c r="BD43" s="5">
-        <v>4095</v>
+        <v>4143</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="45"/>
-        <v>0.96375617792421742</v>
+        <v>0.97505295363614963</v>
       </c>
       <c r="BF43" s="5">
         <v>5295</v>
@@ -8416,14 +8416,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="46"/>
-        <v>2686</v>
+        <v>2837</v>
       </c>
       <c r="BI43" s="5">
-        <v>4899</v>
+        <v>5050</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="47"/>
-        <v>0.92521246458923512</v>
+        <v>0.95372993389990557</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8441,14 +8441,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="24"/>
-        <v>185961</v>
+        <v>186022</v>
       </c>
       <c r="F44" s="5">
-        <v>379978</v>
+        <v>380039</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="25"/>
-        <v>0.99071799925952575</v>
+        <v>0.99087704477783167</v>
       </c>
       <c r="H44" s="5">
         <v>388149</v>
@@ -8458,14 +8458,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="26"/>
-        <v>184437</v>
+        <v>184516</v>
       </c>
       <c r="K44" s="5">
-        <v>383241</v>
+        <v>383320</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="27"/>
-        <v>0.98735537126206685</v>
+        <v>0.98755890134973945</v>
       </c>
       <c r="M44" s="5">
         <v>456953</v>
@@ -8475,14 +8475,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="28"/>
-        <v>212005</v>
+        <v>212126</v>
       </c>
       <c r="P44" s="5">
-        <v>453811</v>
+        <v>453932</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="29"/>
-        <v>0.99312401931927352</v>
+        <v>0.99338881679297431</v>
       </c>
       <c r="R44" s="5">
         <v>388846</v>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="30"/>
-        <v>181286</v>
+        <v>181409</v>
       </c>
       <c r="U44" s="5">
-        <v>385380</v>
+        <v>385503</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="31"/>
-        <v>0.99108644553370739</v>
+        <v>0.99140276613363643</v>
       </c>
       <c r="W44" s="5">
         <v>393146</v>
@@ -8509,14 +8509,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="32"/>
-        <v>178405</v>
+        <v>178550</v>
       </c>
       <c r="Z44" s="5">
-        <v>387993</v>
+        <v>388138</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="33"/>
-        <v>0.986892910013074</v>
+        <v>0.98726172973907911</v>
       </c>
       <c r="AB44" s="5">
         <v>465292</v>
@@ -8526,14 +8526,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="34"/>
-        <v>222698</v>
+        <v>222915</v>
       </c>
       <c r="AE44" s="5">
-        <v>460722</v>
+        <v>460939</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="35"/>
-        <v>0.99017821067200806</v>
+        <v>0.99064458447598502</v>
       </c>
       <c r="AG44" s="5">
         <v>393778</v>
@@ -8543,14 +8543,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="36"/>
-        <v>180954</v>
+        <v>181184</v>
       </c>
       <c r="AJ44" s="5">
-        <v>391561</v>
+        <v>391791</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="37"/>
-        <v>0.99436992417047165</v>
+        <v>0.99495400961963343</v>
       </c>
       <c r="AL44" s="5">
         <v>398873</v>
@@ -8560,14 +8560,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="38"/>
-        <v>179471</v>
+        <v>179888</v>
       </c>
       <c r="AO44" s="5">
-        <v>400975</v>
+        <v>401392</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="39"/>
-        <v>1.0052698477961657</v>
+        <v>1.0063152933389825</v>
       </c>
       <c r="AQ44" s="5">
         <v>476819</v>
@@ -8577,14 +8577,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="40"/>
-        <v>222200</v>
+        <v>223044</v>
       </c>
       <c r="AT44" s="5">
-        <v>477839</v>
+        <v>478683</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="41"/>
-        <v>1.0021391765009364</v>
+        <v>1.0039092401938681</v>
       </c>
       <c r="AV44" s="5">
         <v>408878</v>
@@ -8594,14 +8594,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="42"/>
-        <v>73046</v>
+        <v>74221</v>
       </c>
       <c r="AY44" s="5">
-        <v>408424</v>
+        <v>409599</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="43"/>
-        <v>0.99888964434378957</v>
+        <v>1.0017633621764928</v>
       </c>
       <c r="BA44" s="5">
         <v>416024</v>
@@ -8611,14 +8611,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="44"/>
-        <v>177571</v>
+        <v>179560</v>
       </c>
       <c r="BD44" s="5">
-        <v>412637</v>
+        <v>414626</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="45"/>
-        <v>0.99185864277060942</v>
+        <v>0.99663961694517622</v>
       </c>
       <c r="BF44" s="5">
         <v>493955</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="46"/>
-        <v>222811</v>
+        <v>228226</v>
       </c>
       <c r="BI44" s="5">
-        <v>482776</v>
+        <v>488191</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="47"/>
-        <v>0.97736838375965418</v>
+        <v>0.98833092083286944</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8653,14 +8653,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="24"/>
-        <v>138416</v>
+        <v>138448</v>
       </c>
       <c r="F45" s="5">
-        <v>276910</v>
+        <v>276942</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="25"/>
-        <v>0.99788825784876178</v>
+        <v>0.99800357482630375</v>
       </c>
       <c r="H45" s="5">
         <v>280269</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="26"/>
-        <v>138726</v>
+        <v>138768</v>
       </c>
       <c r="K45" s="5">
-        <v>278853</v>
+        <v>278895</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="27"/>
-        <v>0.99494771094912393</v>
+        <v>0.99509756698029395</v>
       </c>
       <c r="M45" s="5">
         <v>334005</v>
@@ -8687,14 +8687,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="28"/>
-        <v>162422</v>
+        <v>162491</v>
       </c>
       <c r="P45" s="5">
-        <v>332158</v>
+        <v>332227</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="29"/>
-        <v>0.99447014266253497</v>
+        <v>0.99467672639631144</v>
       </c>
       <c r="R45" s="5">
         <v>281510</v>
@@ -8704,14 +8704,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="30"/>
-        <v>134264</v>
+        <v>134330</v>
       </c>
       <c r="U45" s="5">
-        <v>279845</v>
+        <v>279911</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="31"/>
-        <v>0.99408546765656636</v>
+        <v>0.9943199175872971</v>
       </c>
       <c r="W45" s="5">
         <v>284325</v>
@@ -8721,14 +8721,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="32"/>
-        <v>133068</v>
+        <v>133155</v>
       </c>
       <c r="Z45" s="5">
-        <v>280967</v>
+        <v>281054</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="33"/>
-        <v>0.98818957179284272</v>
+        <v>0.98849555965884106</v>
       </c>
       <c r="AB45" s="5">
         <v>338696</v>
@@ -8738,14 +8738,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="34"/>
-        <v>171745</v>
+        <v>171892</v>
       </c>
       <c r="AE45" s="5">
-        <v>335015</v>
+        <v>335162</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98913184684791078</v>
+        <v>0.98956586437395189</v>
       </c>
       <c r="AG45" s="5">
         <v>285325</v>
@@ -8755,14 +8755,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="36"/>
-        <v>139441</v>
+        <v>139592</v>
       </c>
       <c r="AJ45" s="5">
-        <v>282640</v>
+        <v>282791</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="37"/>
-        <v>0.99058967843687018</v>
+        <v>0.99111889950056953</v>
       </c>
       <c r="AL45" s="5">
         <v>289428</v>
@@ -8772,14 +8772,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="38"/>
-        <v>135444</v>
+        <v>135710</v>
       </c>
       <c r="AO45" s="5">
-        <v>289278</v>
+        <v>289544</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="39"/>
-        <v>0.99948173639039761</v>
+        <v>1.0004007905247592</v>
       </c>
       <c r="AQ45" s="5">
         <v>348161</v>
@@ -8789,14 +8789,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="40"/>
-        <v>170831</v>
+        <v>171505</v>
       </c>
       <c r="AT45" s="5">
-        <v>346685</v>
+        <v>347359</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="41"/>
-        <v>0.99576058202957829</v>
+        <v>0.99769646801336165</v>
       </c>
       <c r="AV45" s="5">
         <v>296165</v>
@@ -8806,14 +8806,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="42"/>
-        <v>51815</v>
+        <v>52732</v>
       </c>
       <c r="AY45" s="5">
-        <v>293848</v>
+        <v>294765</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="43"/>
-        <v>0.9921766582817011</v>
+        <v>0.99527290530616375</v>
       </c>
       <c r="BA45" s="5">
         <v>300603</v>
@@ -8823,14 +8823,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="44"/>
-        <v>133855</v>
+        <v>135352</v>
       </c>
       <c r="BD45" s="5">
-        <v>296656</v>
+        <v>298153</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98686972518571003</v>
+        <v>0.99184971540536859</v>
       </c>
       <c r="BF45" s="5">
         <v>359430</v>
@@ -8840,14 +8840,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="46"/>
-        <v>173496</v>
+        <v>177671</v>
       </c>
       <c r="BI45" s="5">
-        <v>349771</v>
+        <v>353946</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="47"/>
-        <v>0.97312689536210106</v>
+        <v>0.9847425089725399</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8865,14 +8865,14 @@
       </c>
       <c r="E46" s="3">
         <f t="shared" si="24"/>
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="F46" s="5">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="G46" s="4">
         <f t="shared" si="25"/>
-        <v>1.0279835390946501</v>
+        <v>1.0288065843621399</v>
       </c>
       <c r="H46" s="5">
         <v>2594</v>
@@ -8882,14 +8882,14 @@
       </c>
       <c r="J46" s="3">
         <f t="shared" si="26"/>
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="K46" s="5">
-        <v>2645</v>
+        <v>2648</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="27"/>
-        <v>1.0196607555898227</v>
+        <v>1.0208172706245182</v>
       </c>
       <c r="M46" s="5">
         <v>8454</v>
@@ -8899,14 +8899,14 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="28"/>
-        <v>5764</v>
+        <v>5767</v>
       </c>
       <c r="P46" s="5">
-        <v>8619</v>
+        <v>8622</v>
       </c>
       <c r="Q46" s="4">
         <f t="shared" si="29"/>
-        <v>1.0195173882185948</v>
+        <v>1.0198722498225692</v>
       </c>
       <c r="R46" s="5">
         <v>2484</v>
@@ -8916,14 +8916,14 @@
       </c>
       <c r="T46" s="3">
         <f t="shared" si="30"/>
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="U46" s="5">
-        <v>2590</v>
+        <v>2595</v>
       </c>
       <c r="V46" s="4">
         <f t="shared" si="31"/>
-        <v>1.0426731078904992</v>
+        <v>1.0446859903381642</v>
       </c>
       <c r="W46" s="5">
         <v>2748</v>
@@ -8933,14 +8933,14 @@
       </c>
       <c r="Y46" s="3">
         <f t="shared" si="32"/>
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="Z46" s="5">
-        <v>2696</v>
+        <v>2703</v>
       </c>
       <c r="AA46" s="4">
         <f t="shared" si="33"/>
-        <v>0.98107714701601167</v>
+        <v>0.98362445414847166</v>
       </c>
       <c r="AB46" s="5">
         <v>8770</v>
@@ -8950,14 +8950,14 @@
       </c>
       <c r="AD46" s="3">
         <f t="shared" si="34"/>
-        <v>5862</v>
+        <v>5872</v>
       </c>
       <c r="AE46" s="5">
-        <v>8848</v>
+        <v>8858</v>
       </c>
       <c r="AF46" s="4">
         <f t="shared" si="35"/>
-        <v>1.0088939566704676</v>
+        <v>1.0100342075256556</v>
       </c>
       <c r="AG46" s="5">
         <v>2523</v>
@@ -8967,14 +8967,14 @@
       </c>
       <c r="AI46" s="3">
         <f t="shared" si="36"/>
-        <v>1496</v>
+        <v>1501</v>
       </c>
       <c r="AJ46" s="5">
-        <v>2552</v>
+        <v>2557</v>
       </c>
       <c r="AK46" s="4">
         <f t="shared" si="37"/>
-        <v>1.0114942528735633</v>
+        <v>1.0134760206103846</v>
       </c>
       <c r="AL46" s="5">
         <v>2722</v>
@@ -8984,14 +8984,14 @@
       </c>
       <c r="AN46" s="3">
         <f t="shared" si="38"/>
-        <v>1496</v>
+        <v>1505</v>
       </c>
       <c r="AO46" s="5">
-        <v>2660</v>
+        <v>2669</v>
       </c>
       <c r="AP46" s="4">
         <f t="shared" si="39"/>
-        <v>0.97722263041880975</v>
+        <v>0.98052902277736953</v>
       </c>
       <c r="AQ46" s="5">
         <v>8967</v>
@@ -9001,14 +9001,14 @@
       </c>
       <c r="AS46" s="3">
         <f t="shared" si="40"/>
-        <v>5735</v>
+        <v>5775</v>
       </c>
       <c r="AT46" s="5">
-        <v>8955</v>
+        <v>8995</v>
       </c>
       <c r="AU46" s="4">
         <f t="shared" si="41"/>
-        <v>0.99866175978588156</v>
+        <v>1.0031225604996097</v>
       </c>
       <c r="AV46" s="5">
         <v>2626</v>
@@ -9018,14 +9018,14 @@
       </c>
       <c r="AX46" s="3">
         <f t="shared" si="42"/>
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="AY46" s="5">
-        <v>2618</v>
+        <v>2629</v>
       </c>
       <c r="AZ46" s="4">
         <f t="shared" si="43"/>
-        <v>0.99695354150799698</v>
+        <v>1.0011424219345011</v>
       </c>
       <c r="BA46" s="5">
         <v>2791</v>
@@ -9035,14 +9035,14 @@
       </c>
       <c r="BC46" s="3">
         <f t="shared" si="44"/>
-        <v>1444</v>
+        <v>1460</v>
       </c>
       <c r="BD46" s="5">
-        <v>2663</v>
+        <v>2679</v>
       </c>
       <c r="BE46" s="4">
         <f t="shared" si="45"/>
-        <v>0.95413830168398428</v>
+        <v>0.95987101397348618</v>
       </c>
       <c r="BF46" s="5">
         <v>9093</v>
@@ -9052,14 +9052,14 @@
       </c>
       <c r="BH46" s="3">
         <f t="shared" si="46"/>
-        <v>5716</v>
+        <v>5907</v>
       </c>
       <c r="BI46" s="5">
-        <v>8786</v>
+        <v>8977</v>
       </c>
       <c r="BJ46" s="4">
         <f t="shared" si="47"/>
-        <v>0.96623776531397776</v>
+        <v>0.98724293412515118</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9247,14 +9247,14 @@
       </c>
       <c r="BC47" s="3">
         <f t="shared" si="44"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD47" s="5">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BE47" s="4">
         <f t="shared" si="45"/>
-        <v>0.89473684210526316</v>
+        <v>0.90789473684210531</v>
       </c>
       <c r="BF47" s="5">
         <v>72</v>
@@ -9264,14 +9264,14 @@
       </c>
       <c r="BH47" s="3">
         <f t="shared" si="46"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BI47" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="BJ47" s="4">
         <f t="shared" si="47"/>
-        <v>0.97222222222222221</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
@@ -9289,15 +9289,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3387264</v>
+        <v>3388733</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>8581620</v>
+        <v>8583089</v>
       </c>
       <c r="G48" s="6">
         <f t="shared" si="25"/>
-        <v>0.9951915115288219</v>
+        <v>0.99536186821327499</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9309,15 +9309,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3393649</v>
+        <v>3395443</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>8698422</v>
+        <v>8700216</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" si="27"/>
-        <v>0.99148569625010219</v>
+        <v>0.99169018452844426</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9329,15 +9329,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>5477288</v>
+        <v>5480981</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>13318904</v>
+        <v>13322597</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" si="29"/>
-        <v>0.99726052752384764</v>
+        <v>0.99753704300351065</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9349,15 +9349,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3276961</v>
+        <v>3279680</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>8727892</v>
+        <v>8730611</v>
       </c>
       <c r="V48" s="6">
         <f t="shared" si="31"/>
-        <v>0.99512578440666033</v>
+        <v>0.99543579592007059</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9369,15 +9369,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3253171</v>
+        <v>3256575</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>8824821</v>
+        <v>8828225</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" si="33"/>
-        <v>0.98793718226540106</v>
+        <v>0.98831825947574115</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9389,15 +9389,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5693892</v>
+        <v>5701313</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>13535665</v>
+        <v>13543086</v>
       </c>
       <c r="AF48" s="6">
         <f t="shared" si="35"/>
-        <v>0.99469826518741811</v>
+        <v>0.99524361377767623</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9409,15 +9409,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>3367901</v>
+        <v>3373852</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>8863388</v>
+        <v>8869339</v>
       </c>
       <c r="AK48" s="6">
         <f t="shared" si="37"/>
-        <v>0.99397607115494002</v>
+        <v>0.99464344029182572</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9429,15 +9429,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3358741</v>
+        <v>3368463</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>9124206</v>
+        <v>9133928</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" si="39"/>
-        <v>0.99965444553518212</v>
+        <v>1.0007195947130385</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9449,15 +9449,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>5734939</v>
+        <v>5759491</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>13974329</v>
+        <v>13998881</v>
       </c>
       <c r="AU48" s="6">
         <f t="shared" si="41"/>
-        <v>0.99979995886135387</v>
+        <v>1.0015565432805387</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9469,15 +9469,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>1421370</v>
+        <v>1446488</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>9220432</v>
+        <v>9245550</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" si="43"/>
-        <v>0.99674290059349913</v>
+        <v>0.99945819508047185</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9489,15 +9489,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3330332</v>
+        <v>3367981</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>9359776</v>
+        <v>9397425</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" si="45"/>
-        <v>0.98828714441005183</v>
+        <v>0.99226245564612137</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9509,15 +9509,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5654346</v>
+        <v>5795272</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>14104108</v>
+        <v>14245034</v>
       </c>
       <c r="BJ48" s="6">
         <f t="shared" si="47"/>
-        <v>0.97737549662720025</v>
+        <v>0.98714127686921804</v>
       </c>
     </row>
   </sheetData>
